--- a/docs/ozon/Озон_рабочая_книга.xlsx
+++ b/docs/ozon/Озон_рабочая_книга.xlsx
@@ -21,6 +21,7 @@
     <sheet name="Тренажер для кисти" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="Фитнес и йога" sheetId="13" state="visible" r:id="rId13"/>
     <sheet name="Шпатель-скребок кондитерский" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Что уточнить" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -30,7 +31,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -65,8 +66,12 @@
     <font>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -93,6 +98,16 @@
         <fgColor rgb="00EDEDED"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -111,7 +126,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -130,6 +145,9 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -761,7 +779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -888,6 +906,207 @@
       <c r="K2" s="6" t="inlineStr">
         <is>
           <t>Выберите из списка.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ACRB1MS106WH</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>9506919000 - Прочий инвентарь и оборудование для занятий общей физкультурой, гимнастикой или атлетикой</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ACRB1MS106PN</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>9506919000 - Прочий инвентарь и оборудование для занятий общей физкультурой, гимнастикой или атлетикой</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ACRB1MS106BL</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>9506919000 - Прочий инвентарь и оборудование для занятий общей физкультурой, гимнастикой или атлетикой</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ACRB1MS106RJ</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>9506919000 - Прочий инвентарь и оборудование для занятий общей физкультурой, гимнастикой или атлетикой</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ACRB1MS106BС</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>9506919000 - Прочий инвентарь и оборудование для занятий общей физкультурой, гимнастикой или атлетикой</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ACRB1MS107WH</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>9506919000 - Прочий инвентарь и оборудование для занятий общей физкультурой, гимнастикой или атлетикой</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ACRB1MS107PN</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>9506919000 - Прочий инвентарь и оборудование для занятий общей физкультурой, гимнастикой или атлетикой</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ACRB1MS107BL</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>9506919000 - Прочий инвентарь и оборудование для занятий общей физкультурой, гимнастикой или атлетикой</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ACRB1MS107RJ</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>9506919000 - Прочий инвентарь и оборудование для занятий общей физкультурой, гимнастикой или атлетикой</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ACRB1MS107BС</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>9506919000 - Прочий инвентарь и оборудование для занятий общей физкультурой, гимнастикой или атлетикой</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ACRB1MS109PN</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>9506919000 - Прочий инвентарь и оборудование для занятий общей физкультурой, гимнастикой или атлетикой</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ACRB1MS109BL</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>9506919000 - Прочий инвентарь и оборудование для занятий общей физкультурой, гимнастикой или атлетикой</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ACRB1MS109RJ</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>9506919000 - Прочий инвентарь и оборудование для занятий общей физкультурой, гимнастикой или атлетикой</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ACRB1MS109BС</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>9506919000 - Прочий инвентарь и оборудование для занятий общей физкультурой, гимнастикой или атлетикой</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>ACRB1MS109LI</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>9506919000 - Прочий инвентарь и оборудование для занятий общей физкультурой, гимнастикой или атлетикой</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ACRB1MS103BL</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>ACRB1MS103LI</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ACRB1MS103RJ</t>
         </is>
       </c>
     </row>
@@ -919,7 +1138,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:R11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1123,6 +1342,114 @@
       <c r="R2" s="6" t="inlineStr">
         <is>
           <t>Перечислите, что входит в комплект вместе с товаром: инструкция, чехол, комплект проводов и т.п.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ACRA7TB201BC</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>3926909709 - Изделия прочие из пластмасс и изделия из прочих материалов товарных позиций 3901 - 3914, прочие, прочие, прочие, прочие</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ACRA7TB201CL</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>3926909709 - Изделия прочие из пластмасс и изделия из прочих материалов товарных позиций 3901 - 3914, прочие, прочие, прочие, прочие</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ACRA7TB201WH</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>3926909709 - Изделия прочие из пластмасс и изделия из прочих материалов товарных позиций 3901 - 3914, прочие, прочие, прочие, прочие</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ACRA7TB201LI</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>3926909709 - Изделия прочие из пластмасс и изделия из прочих материалов товарных позиций 3901 - 3914, прочие, прочие, прочие, прочие</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ACRA7TB101BC</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>3926909709 - Изделия прочие из пластмасс и изделия из прочих материалов товарных позиций 3901 - 3914, прочие, прочие, прочие, прочие</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ACRA7TB101CL</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>3926909709 - Изделия прочие из пластмасс и изделия из прочих материалов товарных позиций 3901 - 3914, прочие, прочие, прочие, прочие</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ACRA7TB301GR</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>3926909709 - Изделия прочие из пластмасс и изделия из прочих материалов товарных позиций 3901 - 3914, прочие, прочие, прочие, прочие</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ACRA7TB301CL</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>3926909709 - Изделия прочие из пластмасс и изделия из прочих материалов товарных позиций 3901 - 3914, прочие, прочие, прочие, прочие</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ACRA7TB301WH</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>3926909709 - Изделия прочие из пластмасс и изделия из прочих материалов товарных позиций 3901 - 3914, прочие, прочие, прочие, прочие</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1631,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1453,6 +1780,70 @@
       <c r="M2" s="6" t="inlineStr">
         <is>
           <t>Период, в течение которого производитель отвечает за качество товара.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ACRB3FR101CL</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>9506919000 - Прочий инвентарь и оборудование для занятий общей физкультурой, гимнастикой или атлетикой</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ACRB5FR200CL</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>9506919000 - Прочий инвентарь и оборудование для занятий общей физкультурой, гимнастикой или атлетикой</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ACRB4FR300CL</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>9506919000 - Прочий инвентарь и оборудование для занятий общей физкультурой, гимнастикой или атлетикой</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ACRB5FR400CL</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ACRB1SK101BC</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ACRB1SK101RD</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ACRB1SK101BL</t>
         </is>
       </c>
     </row>
@@ -1487,7 +1878,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:O3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1658,6 +2049,13 @@
       <c r="O2" s="6" t="inlineStr">
         <is>
           <t>Перечислите, что входит в комплект вместе с товаром: инструкция, чехол, комплект проводов и т.п.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>AKTA2KN101YL</t>
         </is>
       </c>
     </row>
@@ -1686,13 +2084,275 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="55" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>Артикул</t>
+        </is>
+      </c>
+      <c r="B1" s="10" t="inlineStr">
+        <is>
+          <t>Название</t>
+        </is>
+      </c>
+      <c r="C1" s="10" t="inlineStr">
+        <is>
+          <t>Предмет на WB</t>
+        </is>
+      </c>
+      <c r="D1" s="10" t="inlineStr">
+        <is>
+          <t>Почему без категории</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ACRF1KP101BC</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Капа черный/красный - черная коробка</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Капы</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>шаблон не скачан</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ACRF1KP102BC</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Капа черный/белый-черная коробка</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Капы</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>шаблон не скачан</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ACRF1KP103BC</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Капа белый/черный</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Капы</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>шаблон не скачан</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ACRF1KP101RD</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Капа белый/красный</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Капы</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>шаблон не скачан</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ACRF1KP102RD</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Капа красный/белый</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Капы</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>шаблон не скачан</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ACRF1KP101BL</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Капа синий/белый</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Капы</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>шаблон не скачан</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ACRF1KP101GN</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Капа зеленый/белый</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Капы</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>шаблон не скачан</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ACRF1KP102GN</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Капа зеленый/черный</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Капы</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>шаблон не скачан</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ACRA7TB101WH</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Таблетница круглая 7*2 бел Д</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>нет в базе</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>предмет WB не сопоставлен</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>AKTA1PR101GR</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Чеснокодавка</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Прессы для чеснока</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>шаблон не скачан</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC2"/>
+  <dimension ref="A1:AC76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2017,6 +2677,3029 @@
       <c r="AC2" s="6" t="inlineStr">
         <is>
           <t>Сколько заводских упаковок продаёте под этим SKU.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ACRF1BN101PN</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Маска-бандаж</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Бандаж для лица розовый</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>2038161736993</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>120</v>
+      </c>
+      <c r="M3" t="n">
+        <v>20</v>
+      </c>
+      <c r="N3" t="n">
+        <v>140</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>АРОЛС</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ACRF1BN101BC</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Маска-бандаж</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Бандаж для лица черный</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2453533282</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>2038162681926</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>40</v>
+      </c>
+      <c r="L4" t="n">
+        <v>120</v>
+      </c>
+      <c r="M4" t="n">
+        <v>20</v>
+      </c>
+      <c r="N4" t="n">
+        <v>140</v>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>АРОЛС</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ACRF1BN201GR</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Маска-бандаж</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Бандаж для лица серый</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2419349210</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>2038172050200</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>90</v>
+      </c>
+      <c r="L5" t="n">
+        <v>140</v>
+      </c>
+      <c r="M5" t="n">
+        <v>30</v>
+      </c>
+      <c r="N5" t="n">
+        <v>190</v>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>АРОЛС</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>AHMA7BW101BG</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Мешок для стирки</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Мешки 7 шт.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2419349460</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>2038337652454</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>315</v>
+      </c>
+      <c r="L6" t="n">
+        <v>210</v>
+      </c>
+      <c r="M6" t="n">
+        <v>60</v>
+      </c>
+      <c r="N6" t="n">
+        <v>300</v>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>АРОЛС</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>AHMA1BW101BG</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Мешок для стирки</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Мешок для бюстгалтеров</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2138709303</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>2038597850744</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>60</v>
+      </c>
+      <c r="L7" t="n">
+        <v>170</v>
+      </c>
+      <c r="M7" t="n">
+        <v>30</v>
+      </c>
+      <c r="N7" t="n">
+        <v>180</v>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>АРОЛС</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>AHMA3BW101BG</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Мешок для стирки</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Мешки 3 шт.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2419349262</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>2038627692689</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>200</v>
+      </c>
+      <c r="M8" t="n">
+        <v>50</v>
+      </c>
+      <c r="N8" t="n">
+        <v>250</v>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>АРОЛС</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>AHMA3BW102BG</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Мешок для стирки</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Мешки/деликат 3 шт.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2576041357</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>2038627713902</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>60</v>
+      </c>
+      <c r="L9" t="n">
+        <v>170</v>
+      </c>
+      <c r="M9" t="n">
+        <v>40</v>
+      </c>
+      <c r="N9" t="n">
+        <v>250</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>АРОЛС</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>AHMA3BW201WH</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Мешок для стирки</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Мешки/шнурок мелк 3 шт.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2419349585</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>2038606201642</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>30</v>
+      </c>
+      <c r="L10" t="n">
+        <v>150</v>
+      </c>
+      <c r="M10" t="n">
+        <v>30</v>
+      </c>
+      <c r="N10" t="n">
+        <v>210</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>АРОЛС</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>AHMA3BW202WH</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Мешок для стирки</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Мешки/шнурок крупн 3 шт.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2419349501</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>2038606256161</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>30</v>
+      </c>
+      <c r="L11" t="n">
+        <v>150</v>
+      </c>
+      <c r="M11" t="n">
+        <v>30</v>
+      </c>
+      <c r="N11" t="n">
+        <v>210</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>АРОЛС</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>AHMA2BW201WH</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Мешок для стирки</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Мешки 2 шт. серый</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2419349453</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>2039404446068</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>30</v>
+      </c>
+      <c r="L12" t="n">
+        <v>160</v>
+      </c>
+      <c r="M12" t="n">
+        <v>30</v>
+      </c>
+      <c r="N12" t="n">
+        <v>200</v>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>АРОЛС</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>AHMA2BW202WH</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Мешок для стирки</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Мешки 2 шт. розовый</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>2040278862540</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>160</v>
+      </c>
+      <c r="M13" t="n">
+        <v>30</v>
+      </c>
+      <c r="N13" t="n">
+        <v>200</v>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>АРОЛС</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>AHMA1BW112WH</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Мешок для стирки</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Мешок 60*80 крупн</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2419349360</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>2040335626849</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>100</v>
+      </c>
+      <c r="L14" t="n">
+        <v>220</v>
+      </c>
+      <c r="M14" t="n">
+        <v>10</v>
+      </c>
+      <c r="N14" t="n">
+        <v>280</v>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>АРОЛС</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>AHMA1BW111WH</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Мешок для стирки</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Мешок 60*80 мелк</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2419349422</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>2040335648124</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>100</v>
+      </c>
+      <c r="L15" t="n">
+        <v>220</v>
+      </c>
+      <c r="M15" t="n">
+        <v>10</v>
+      </c>
+      <c r="N15" t="n">
+        <v>280</v>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>АРОЛС</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>AHMA1BW302WH</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Мешок для стирки</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Мешок для обуви XL - 35 см</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>2040478696884</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>220</v>
+      </c>
+      <c r="M16" t="n">
+        <v>40</v>
+      </c>
+      <c r="N16" t="n">
+        <v>220</v>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>АРОЛС</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>ACRH1MS101RJ</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Аксессуар для массажа</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Массажер для пальцев</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1597441701</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>2038430289250</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>40</v>
+      </c>
+      <c r="L17" t="n">
+        <v>40</v>
+      </c>
+      <c r="M17" t="n">
+        <v>40</v>
+      </c>
+      <c r="N17" t="n">
+        <v>150</v>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>АРОЛС</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ACRB1MS101RJ</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Аксессуар для массажа</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Массажер для тела оранжевый</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2415742732</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>2039813223373</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>160</v>
+      </c>
+      <c r="L18" t="n">
+        <v>60</v>
+      </c>
+      <c r="M18" t="n">
+        <v>30</v>
+      </c>
+      <c r="N18" t="n">
+        <v>550</v>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>АРОЛС</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>ACRB1MS101PN</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Аксессуар для массажа</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Массажер для тела розовый</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2415742511</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>2041591042329</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>160</v>
+      </c>
+      <c r="L19" t="n">
+        <v>60</v>
+      </c>
+      <c r="M19" t="n">
+        <v>30</v>
+      </c>
+      <c r="N19" t="n">
+        <v>550</v>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>АРОЛС</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ACRB1MS101BL</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Аксессуар для массажа</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Массажер для тела голубой</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2415742636</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>2041591055954</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>160</v>
+      </c>
+      <c r="L20" t="n">
+        <v>60</v>
+      </c>
+      <c r="M20" t="n">
+        <v>30</v>
+      </c>
+      <c r="N20" t="n">
+        <v>550</v>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>АРОЛС</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ACRB1MS106WH</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Спортивный массажный мяч</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Мяч с шипами белый 6 см</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1980924906</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>2040278804496</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>40</v>
+      </c>
+      <c r="L21" t="n">
+        <v>70</v>
+      </c>
+      <c r="M21" t="n">
+        <v>70</v>
+      </c>
+      <c r="N21" t="n">
+        <v>70</v>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>АРОЛС</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ACRB1MS106PN</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Спортивный массажный мяч</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Мяч с шипами розовый 6 см</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1980925084</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>2040278810534</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>40</v>
+      </c>
+      <c r="L22" t="n">
+        <v>70</v>
+      </c>
+      <c r="M22" t="n">
+        <v>70</v>
+      </c>
+      <c r="N22" t="n">
+        <v>70</v>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>АРОЛС</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>ACRB1MS106BL</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Спортивный массажный мяч</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Мяч с шипами голубой 6 см</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1980924909</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>2040278804649</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>40</v>
+      </c>
+      <c r="L23" t="n">
+        <v>70</v>
+      </c>
+      <c r="M23" t="n">
+        <v>70</v>
+      </c>
+      <c r="N23" t="n">
+        <v>70</v>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>АРОЛС</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>ACRB1MS106RJ</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Спортивный массажный мяч</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Мяч с шипами оранжевый 6 см</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1980924947</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>2039818580389</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>40</v>
+      </c>
+      <c r="L24" t="n">
+        <v>70</v>
+      </c>
+      <c r="M24" t="n">
+        <v>70</v>
+      </c>
+      <c r="N24" t="n">
+        <v>70</v>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>АРОЛС</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ACRB1MS106BС</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Спортивный массажный мяч</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Мяч с шипами черный 6 см</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1980924996</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>2043369663040</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>40</v>
+      </c>
+      <c r="L25" t="n">
+        <v>70</v>
+      </c>
+      <c r="M25" t="n">
+        <v>70</v>
+      </c>
+      <c r="N25" t="n">
+        <v>70</v>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>АРОЛС</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ACRB1MS107WH</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Спортивный массажный мяч</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Мяч с шипами белый 7 см</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2415742768</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>2044025326637</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>60</v>
+      </c>
+      <c r="L26" t="n">
+        <v>80</v>
+      </c>
+      <c r="M26" t="n">
+        <v>80</v>
+      </c>
+      <c r="N26" t="n">
+        <v>80</v>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>АРОЛС</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ACRB1MS107PN</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Спортивный массажный мяч</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Мяч с шипами розовый 7 см</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2415742912</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>2044025316447</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>60</v>
+      </c>
+      <c r="L27" t="n">
+        <v>80</v>
+      </c>
+      <c r="M27" t="n">
+        <v>80</v>
+      </c>
+      <c r="N27" t="n">
+        <v>80</v>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>АРОЛС</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>ACRB1MS107BL</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Спортивный массажный мяч</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Мяч с шипами голубой 7 см</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2415742611</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>2044025338661</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>60</v>
+      </c>
+      <c r="L28" t="n">
+        <v>80</v>
+      </c>
+      <c r="M28" t="n">
+        <v>80</v>
+      </c>
+      <c r="N28" t="n">
+        <v>80</v>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>АРОЛС</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>ACRB1MS107RJ</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Спортивный массажный мяч</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Мяч с шипами оранжевый 7 см</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2415742942</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>2044025288003</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>60</v>
+      </c>
+      <c r="L29" t="n">
+        <v>80</v>
+      </c>
+      <c r="M29" t="n">
+        <v>80</v>
+      </c>
+      <c r="N29" t="n">
+        <v>80</v>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>АРОЛС</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>ACRB1MS107BС</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Спортивный массажный мяч</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Мяч с шипами черный 7 см</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2415742795</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>2044025344532</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>60</v>
+      </c>
+      <c r="L30" t="n">
+        <v>80</v>
+      </c>
+      <c r="M30" t="n">
+        <v>80</v>
+      </c>
+      <c r="N30" t="n">
+        <v>80</v>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>АРОЛС</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>ACRB1MS109PN</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Спортивный массажный мяч</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Мяч с шипами розовый 9 см</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2415742470</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>2044025321588</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>100</v>
+      </c>
+      <c r="L31" t="n">
+        <v>90</v>
+      </c>
+      <c r="M31" t="n">
+        <v>90</v>
+      </c>
+      <c r="N31" t="n">
+        <v>90</v>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>АРОЛС</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>ACRB1MS109BL</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Спортивный массажный мяч</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Мяч с шипами голубой 9 см</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2415742615</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>2044025342057</t>
+        </is>
+      </c>
+      <c r="K32" t="n">
+        <v>100</v>
+      </c>
+      <c r="L32" t="n">
+        <v>90</v>
+      </c>
+      <c r="M32" t="n">
+        <v>90</v>
+      </c>
+      <c r="N32" t="n">
+        <v>90</v>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>АРОЛС</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>ACRB1MS109RJ</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Спортивный массажный мяч</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Мяч с шипами оранжевый 9 см</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2415742943</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>2044025291485</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
+        <v>100</v>
+      </c>
+      <c r="L33" t="n">
+        <v>90</v>
+      </c>
+      <c r="M33" t="n">
+        <v>90</v>
+      </c>
+      <c r="N33" t="n">
+        <v>90</v>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>АРОЛС</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>ACRB1MS109BС</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Спортивный массажный мяч</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Мяч с шипами черный 9 см</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2415742693</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>2044025347953</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
+        <v>100</v>
+      </c>
+      <c r="L34" t="n">
+        <v>90</v>
+      </c>
+      <c r="M34" t="n">
+        <v>90</v>
+      </c>
+      <c r="N34" t="n">
+        <v>90</v>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>АРОЛС</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>ACRB1MS109LI</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Спортивный массажный мяч</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Мяч с шипами фиолетовый 9 см</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2415742565</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>2044025354937</t>
+        </is>
+      </c>
+      <c r="K35" t="n">
+        <v>100</v>
+      </c>
+      <c r="L35" t="n">
+        <v>90</v>
+      </c>
+      <c r="M35" t="n">
+        <v>90</v>
+      </c>
+      <c r="N35" t="n">
+        <v>90</v>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>АРОЛС</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>ACRB1MS103BL</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Спортивный массажный мяч</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Мяч гладкий голубой</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>2415743200</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>2042986356632</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
+        <v>80</v>
+      </c>
+      <c r="M36" t="n">
+        <v>60</v>
+      </c>
+      <c r="N36" t="n">
+        <v>80</v>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>АРОЛС</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>ACRB1MS103LI</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Спортивный массажный мяч</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Мяч гладкий сиреневый</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2415742578</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>2042986372359</t>
+        </is>
+      </c>
+      <c r="L37" t="n">
+        <v>80</v>
+      </c>
+      <c r="M37" t="n">
+        <v>60</v>
+      </c>
+      <c r="N37" t="n">
+        <v>80</v>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>АРОЛС</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>ACRB1MS103RJ</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Спортивный массажный мяч</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Мяч гладкий оранжевый</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2415742537</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>2042986377583</t>
+        </is>
+      </c>
+      <c r="L38" t="n">
+        <v>80</v>
+      </c>
+      <c r="M38" t="n">
+        <v>60</v>
+      </c>
+      <c r="N38" t="n">
+        <v>80</v>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>АРОЛС</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>ACRB3FR101CL</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Фитнес и йога</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Набор эластичных лент 3 шт. в мешке</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2009273449</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>2048933027488</t>
+        </is>
+      </c>
+      <c r="K39" t="n">
+        <v>365</v>
+      </c>
+      <c r="L39" t="n">
+        <v>110</v>
+      </c>
+      <c r="M39" t="n">
+        <v>60</v>
+      </c>
+      <c r="N39" t="n">
+        <v>300</v>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>АРОЛС</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>ACRB5FR200CL</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Фитнес и йога</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Набор эластичных лент 5 шт. в мешке</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2009273377</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>2046392546618</t>
+        </is>
+      </c>
+      <c r="K40" t="n">
+        <v>240</v>
+      </c>
+      <c r="L40" t="n">
+        <v>100</v>
+      </c>
+      <c r="M40" t="n">
+        <v>50</v>
+      </c>
+      <c r="N40" t="n">
+        <v>190</v>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>АРОЛС</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>ACRB4FR300CL</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Фитнес и йога</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Набор эластичных лент 4 шт.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2009273409</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>2046392546632</t>
+        </is>
+      </c>
+      <c r="L41" t="n">
+        <v>100</v>
+      </c>
+      <c r="M41" t="n">
+        <v>50</v>
+      </c>
+      <c r="N41" t="n">
+        <v>170</v>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>АРОЛС</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>ACRB5FR400CL</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Фитнес и йога</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Набор эластичных лент 5 шт.</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>2046392546656</t>
+        </is>
+      </c>
+      <c r="L42" t="n">
+        <v>80</v>
+      </c>
+      <c r="M42" t="n">
+        <v>40</v>
+      </c>
+      <c r="N42" t="n">
+        <v>200</v>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>АРОЛС</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>ACRB1SK101BC</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Фитнес и йога</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Скакалка черная</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2415742680</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>2041473034138</t>
+        </is>
+      </c>
+      <c r="L43" t="n">
+        <v>100</v>
+      </c>
+      <c r="M43" t="n">
+        <v>20</v>
+      </c>
+      <c r="N43" t="n">
+        <v>200</v>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>АРОЛС</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>ACRB1SK101RD</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Фитнес и йога</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Скакалка красная</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2415742649</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>2041473034145</t>
+        </is>
+      </c>
+      <c r="L44" t="n">
+        <v>100</v>
+      </c>
+      <c r="M44" t="n">
+        <v>20</v>
+      </c>
+      <c r="N44" t="n">
+        <v>200</v>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>АРОЛС</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>ACRB1SK101BL</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Фитнес и йога</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Скакалка синяя</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2415743140</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>2041473034169</t>
+        </is>
+      </c>
+      <c r="L45" t="n">
+        <v>100</v>
+      </c>
+      <c r="M45" t="n">
+        <v>20</v>
+      </c>
+      <c r="N45" t="n">
+        <v>200</v>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>АРОЛС</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>ACRF1KP101BC</t>
+        </is>
+      </c>
+      <c r="B46" s="8" t="inlineStr"/>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Капа черный/красный - черная коробка</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>2046391283330</t>
+        </is>
+      </c>
+      <c r="L46" t="n">
+        <v>70</v>
+      </c>
+      <c r="M46" t="n">
+        <v>70</v>
+      </c>
+      <c r="N46" t="n">
+        <v>70</v>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>AROLS</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>ACRF1KP102BC</t>
+        </is>
+      </c>
+      <c r="B47" s="8" t="inlineStr"/>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Капа черный/белый-черная коробка</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>2046391283385</t>
+        </is>
+      </c>
+      <c r="L47" t="n">
+        <v>70</v>
+      </c>
+      <c r="M47" t="n">
+        <v>70</v>
+      </c>
+      <c r="N47" t="n">
+        <v>70</v>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>AROLS</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>ACRF1KP103BC</t>
+        </is>
+      </c>
+      <c r="B48" s="8" t="inlineStr"/>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Капа белый/черный</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>2046391283415</t>
+        </is>
+      </c>
+      <c r="L48" t="n">
+        <v>70</v>
+      </c>
+      <c r="M48" t="n">
+        <v>70</v>
+      </c>
+      <c r="N48" t="n">
+        <v>70</v>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>AROLS</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>ACRF1KP101RD</t>
+        </is>
+      </c>
+      <c r="B49" s="8" t="inlineStr"/>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Капа белый/красный</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>2046391283446</t>
+        </is>
+      </c>
+      <c r="L49" t="n">
+        <v>70</v>
+      </c>
+      <c r="M49" t="n">
+        <v>70</v>
+      </c>
+      <c r="N49" t="n">
+        <v>70</v>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>AROLS</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>ACRF1KP102RD</t>
+        </is>
+      </c>
+      <c r="B50" s="8" t="inlineStr"/>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Капа красный/белый</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>2046391283507</t>
+        </is>
+      </c>
+      <c r="L50" t="n">
+        <v>70</v>
+      </c>
+      <c r="M50" t="n">
+        <v>70</v>
+      </c>
+      <c r="N50" t="n">
+        <v>70</v>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>AROLS</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>ACRF1KP101BL</t>
+        </is>
+      </c>
+      <c r="B51" s="8" t="inlineStr"/>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Капа синий/белый</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>2046391283545</t>
+        </is>
+      </c>
+      <c r="L51" t="n">
+        <v>70</v>
+      </c>
+      <c r="M51" t="n">
+        <v>70</v>
+      </c>
+      <c r="N51" t="n">
+        <v>70</v>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>AROLS</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>ACRF1KP101GN</t>
+        </is>
+      </c>
+      <c r="B52" s="8" t="inlineStr"/>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Капа зеленый/белый</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>2046391283569</t>
+        </is>
+      </c>
+      <c r="L52" t="n">
+        <v>70</v>
+      </c>
+      <c r="M52" t="n">
+        <v>70</v>
+      </c>
+      <c r="N52" t="n">
+        <v>70</v>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>AROLS</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>ACRF1KP102GN</t>
+        </is>
+      </c>
+      <c r="B53" s="8" t="inlineStr"/>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Капа зеленый/черный</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>2046391283613</t>
+        </is>
+      </c>
+      <c r="L53" t="n">
+        <v>70</v>
+      </c>
+      <c r="M53" t="n">
+        <v>70</v>
+      </c>
+      <c r="N53" t="n">
+        <v>70</v>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>AROLS</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>ACRA7TB201BC</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Таблетница</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Таблетница прям 7*2 черн</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1980946313</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>2038891723249</t>
+        </is>
+      </c>
+      <c r="K54" t="n">
+        <v>160</v>
+      </c>
+      <c r="L54" t="n">
+        <v>120</v>
+      </c>
+      <c r="M54" t="n">
+        <v>50</v>
+      </c>
+      <c r="N54" t="n">
+        <v>160</v>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>АРОЛС</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>ACRA7TB201CL</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Таблетница</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Таблетница прям 7*2 черн/цветн</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>2168964833</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>2044025155923</t>
+        </is>
+      </c>
+      <c r="K55" t="n">
+        <v>160</v>
+      </c>
+      <c r="L55" t="n">
+        <v>120</v>
+      </c>
+      <c r="M55" t="n">
+        <v>50</v>
+      </c>
+      <c r="N55" t="n">
+        <v>160</v>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>АРОЛС</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>ACRA7TB201WH</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Таблетница</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Таблетница прям 7*2 бел/цветн</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>2409846808</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>2044516485386</t>
+        </is>
+      </c>
+      <c r="K56" t="n">
+        <v>160</v>
+      </c>
+      <c r="L56" t="n">
+        <v>120</v>
+      </c>
+      <c r="M56" t="n">
+        <v>50</v>
+      </c>
+      <c r="N56" t="n">
+        <v>160</v>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>АРОЛС</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>ACRA7TB201LI</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Таблетница</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Таблетница прям 7*2 сирен/цветн</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>2409845343</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>2044516498812</t>
+        </is>
+      </c>
+      <c r="K57" t="n">
+        <v>160</v>
+      </c>
+      <c r="L57" t="n">
+        <v>120</v>
+      </c>
+      <c r="M57" t="n">
+        <v>50</v>
+      </c>
+      <c r="N57" t="n">
+        <v>160</v>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>АРОЛС</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>ACRA7TB101BC</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Таблетница</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Таблетница круглая 7*2 черн Д</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>2087001323</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>2038890789598</t>
+        </is>
+      </c>
+      <c r="L58" t="n">
+        <v>120</v>
+      </c>
+      <c r="M58" t="n">
+        <v>70</v>
+      </c>
+      <c r="N58" t="n">
+        <v>170</v>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>АРОЛС</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>ACRA7TB101CL</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Таблетница</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Таблетница круглая 7*2 черн/цвет Д</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>2087000633</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>2042160422832</t>
+        </is>
+      </c>
+      <c r="L59" t="n">
+        <v>120</v>
+      </c>
+      <c r="M59" t="n">
+        <v>70</v>
+      </c>
+      <c r="N59" t="n">
+        <v>170</v>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>АРОЛС</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>ACRA7TB101WH</t>
+        </is>
+      </c>
+      <c r="B60" s="8" t="inlineStr"/>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Таблетница круглая 7*2 бел Д</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>2054786826888</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>ACRA7TB301GR</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Таблетница</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Таблетница круглая 7*2 сер</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>2082252055</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>2041680530447</t>
+        </is>
+      </c>
+      <c r="K61" t="n">
+        <v>150</v>
+      </c>
+      <c r="L61" t="n">
+        <v>120</v>
+      </c>
+      <c r="M61" t="n">
+        <v>70</v>
+      </c>
+      <c r="N61" t="n">
+        <v>170</v>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>АРОЛС</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>ACRA7TB301CL</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Таблетница</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Таблетница круглая 7*2 сер /цвет</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>2082255799</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>2043048226719</t>
+        </is>
+      </c>
+      <c r="K62" t="n">
+        <v>150</v>
+      </c>
+      <c r="L62" t="n">
+        <v>120</v>
+      </c>
+      <c r="M62" t="n">
+        <v>70</v>
+      </c>
+      <c r="N62" t="n">
+        <v>170</v>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>АРОЛС</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>ACRA7TB301WH</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Таблетница</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Таблетница круглая 7*2 бел</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>2138705583</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>2041532808502</t>
+        </is>
+      </c>
+      <c r="K63" t="n">
+        <v>150</v>
+      </c>
+      <c r="L63" t="n">
+        <v>120</v>
+      </c>
+      <c r="M63" t="n">
+        <v>70</v>
+      </c>
+      <c r="N63" t="n">
+        <v>170</v>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>АРОЛС</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>AAND1BL101RD</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Игрушка для животных</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Мяч регби красный</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>2415742463</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>2040903539366</t>
+        </is>
+      </c>
+      <c r="L64" t="n">
+        <v>80</v>
+      </c>
+      <c r="M64" t="n">
+        <v>60</v>
+      </c>
+      <c r="N64" t="n">
+        <v>110</v>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>АРОЛС</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>AAND1BL101BL</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Игрушка для животных</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Мяч регби синий</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>2415743157</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>2040903547941</t>
+        </is>
+      </c>
+      <c r="L65" t="n">
+        <v>80</v>
+      </c>
+      <c r="M65" t="n">
+        <v>60</v>
+      </c>
+      <c r="N65" t="n">
+        <v>110</v>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>АРОЛС</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>AAND1BL102RD</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Игрушка для животных</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Мяч шина красный</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1980956952</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>2040902555480</t>
+        </is>
+      </c>
+      <c r="L66" t="n">
+        <v>90</v>
+      </c>
+      <c r="M66" t="n">
+        <v>70</v>
+      </c>
+      <c r="N66" t="n">
+        <v>120</v>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>АРОЛС</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>AAND1BL102BL</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Игрушка для животных</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Мяч шина синий</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1980958902</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>2040900511679</t>
+        </is>
+      </c>
+      <c r="L67" t="n">
+        <v>90</v>
+      </c>
+      <c r="M67" t="n">
+        <v>70</v>
+      </c>
+      <c r="N67" t="n">
+        <v>120</v>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>АРОЛС</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>AAND1RP301BG</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Игрушка для животных</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Канат бол бежевый 55см/520гр</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>2041534216404</t>
+        </is>
+      </c>
+      <c r="L68" t="n">
+        <v>190</v>
+      </c>
+      <c r="M68" t="n">
+        <v>80</v>
+      </c>
+      <c r="N68" t="n">
+        <v>190</v>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>АРОЛС</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>AAND1RP301YL</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Игрушка для животных</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Канат мал желтый 55см/330гр</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>2041534288661</t>
+        </is>
+      </c>
+      <c r="L69" t="n">
+        <v>150</v>
+      </c>
+      <c r="M69" t="n">
+        <v>60</v>
+      </c>
+      <c r="N69" t="n">
+        <v>210</v>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>АРОЛС</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>AKTA4ST101CL</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Пробка</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Набор пробок 4 шт. в коробке нежн</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>2415742645</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>2041533648312</t>
+        </is>
+      </c>
+      <c r="K70" t="n">
+        <v>50</v>
+      </c>
+      <c r="L70" t="n">
+        <v>70</v>
+      </c>
+      <c r="M70" t="n">
+        <v>60</v>
+      </c>
+      <c r="N70" t="n">
+        <v>70</v>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>АРОЛС</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>AKTA4ST103CL</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Пробка</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Набор пробок 4 шт. в коробке ярк</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>2415742703</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>2043369755509</t>
+        </is>
+      </c>
+      <c r="K71" t="n">
+        <v>50</v>
+      </c>
+      <c r="L71" t="n">
+        <v>70</v>
+      </c>
+      <c r="M71" t="n">
+        <v>60</v>
+      </c>
+      <c r="N71" t="n">
+        <v>70</v>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>АРОЛС</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>AKTA4ST102CL</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Пробка</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Набор пробок 4 шт.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>2415742927</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>2042678197468</t>
+        </is>
+      </c>
+      <c r="L72" t="n">
+        <v>120</v>
+      </c>
+      <c r="M72" t="n">
+        <v>30</v>
+      </c>
+      <c r="N72" t="n">
+        <v>160</v>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>АРОЛС</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>AKTA2KN101YL</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Шпатель-скребок кондитерский</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Шпатель желтый</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>2086999506</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>2041533399818</t>
+        </is>
+      </c>
+      <c r="K73" t="n">
+        <v>200</v>
+      </c>
+      <c r="L73" t="n">
+        <v>120</v>
+      </c>
+      <c r="M73" t="n">
+        <v>30</v>
+      </c>
+      <c r="N73" t="n">
+        <v>160</v>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>АРОЛС</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>AKTA2KN102YL</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Кухонный нож</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Нож для пиццы желтый</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>2092093001</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>2041533038113</t>
+        </is>
+      </c>
+      <c r="L74" t="n">
+        <v>130</v>
+      </c>
+      <c r="M74" t="n">
+        <v>30</v>
+      </c>
+      <c r="N74" t="n">
+        <v>160</v>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>АРОЛС</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>AKTA2KN102GN</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Кухонный нож</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Нож для пиццы зеленый</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>2087000111</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>2042777181566</t>
+        </is>
+      </c>
+      <c r="L75" t="n">
+        <v>130</v>
+      </c>
+      <c r="M75" t="n">
+        <v>30</v>
+      </c>
+      <c r="N75" t="n">
+        <v>160</v>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>АРОЛС</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>AKTA1PR101GR</t>
+        </is>
+      </c>
+      <c r="B76" s="8" t="inlineStr"/>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Чеснокодавка</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>2042987041841</t>
+        </is>
+      </c>
+      <c r="L76" t="n">
+        <v>60</v>
+      </c>
+      <c r="M76" t="n">
+        <v>30</v>
+      </c>
+      <c r="N76" t="n">
+        <v>210</v>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>АРОЛС</t>
         </is>
       </c>
     </row>
@@ -34110,7 +37793,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:R6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -34316,6 +37999,42 @@
           <t>Срок годности, установленный производителем.</t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ACRH1MS101RJ</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>9019109009 - Прочая аппаратура для механотерапии, аппараты массажные, аппаратура для  психологических тестов для определения способностей</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ACRB1MS101RJ</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ACRB1MS101PN</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ACRB1MS101BL</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="7">
@@ -34351,7 +38070,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S2"/>
+  <dimension ref="A1:S8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -34566,6 +38285,78 @@
       <c r="S2" s="6" t="inlineStr">
         <is>
           <t>Признак для товаров, которые содержат эротику, сцены секса, изображения с нецензурными выражениями, даже если они написаны частично или со спец.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>AAND1BL101RD</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>4016999708 - Изделия из вулканизованной резины, кроме твердой резины, прочие: прочие, прочие</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>AAND1BL101BL</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>4016999708 - Изделия из вулканизованной резины, кроме твердой резины, прочие: прочие, прочие</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>AAND1BL102RD</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>4016999708 - Изделия из вулканизованной резины, кроме твердой резины, прочие: прочие, прочие</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>AAND1BL102BL</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>4016999708 - Изделия из вулканизованной резины, кроме твердой резины, прочие: прочие, прочие</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>AAND1RP301BG</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>5609000000 - Изделия из нитей или пряжи, плоских или аналогичных нитей товарной позиции 5404 или 5405, бечевка, веревки, канаты или тросы, в другом месте не поименованные</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>AAND1RP301YL</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>5609000000 - Изделия из нитей или пряжи, плоских или аналогичных нитей товарной позиции 5404 или 5405, бечевка, веревки, канаты или тросы, в другом месте не поименованные</t>
         </is>
       </c>
     </row>
@@ -34609,7 +38400,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:P4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -34791,6 +38582,30 @@
       <c r="P2" s="6" t="inlineStr">
         <is>
           <t>Перечислите, что входит в комплект вместе с товаром: инструкция, чехол, комплект проводов и т.п.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>AKTA2KN102YL</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>8211930000 - Прочие ножи с нефиксированными лезвиями</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>AKTA2KN102GN</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>8211930000 - Прочие ножи с нефиксированными лезвиями</t>
         </is>
       </c>
     </row>
@@ -34834,7 +38649,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:P5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -35016,6 +38831,27 @@
       <c r="P2" s="6" t="inlineStr">
         <is>
           <t>Срок годности, установленный производителем.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ACRF1BN101PN</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ACRF1BN101BC</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ACRF1BN201GR</t>
         </is>
       </c>
     </row>
@@ -35053,7 +38889,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -35191,6 +39027,128 @@
       <c r="L2" s="6" t="inlineStr">
         <is>
           <t>Перечислите, что входит в комплект вместе с товаром: инструкция, чехол, комплект проводов и т.п.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>AHMA7BW101BG</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>6307909800 - Прочие готовые изделия, включая выкройки одежды</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>AHMA1BW101BG</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>6307909800 - Прочие готовые изделия, включая выкройки одежды</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>AHMA3BW101BG</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>6307909800 - Прочие готовые изделия, включая выкройки одежды</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>AHMA3BW102BG</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>6307909800 - Прочие готовые изделия, включая выкройки одежды</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>AHMA3BW201WH</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>6307909800 - Прочие готовые изделия, включая выкройки одежды</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>AHMA3BW202WH</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>AHMA2BW201WH</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>6307909800 - Прочие готовые изделия, включая выкройки одежды</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>AHMA2BW202WH</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>AHMA1BW112WH</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>6307909800 - Прочие готовые изделия, включая выкройки одежды</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>AHMA1BW111WH</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>6307909800 - Прочие готовые изделия, включая выкройки одежды</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>AHMA1BW302WH</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>6307909800 - Прочие готовые изделия, включая выкройки одежды</t>
         </is>
       </c>
     </row>
@@ -35219,7 +39177,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:O5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -35390,6 +39348,37 @@
       <c r="O2" s="6" t="inlineStr">
         <is>
           <t>Перечислите, что входит в комплект вместе с товаром: инструкция, чехол, комплект проводов и т.п.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>AKTA4ST101CL</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>3923509000 - Прочие пробки, крышки, колпаки и другие укупорочные средства, из пластмасс</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>AKTA4ST103CL</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>3923509000 - Прочие пробки, крышки, колпаки и другие укупорочные средства, из пластмасс</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>AKTA4ST102CL</t>
         </is>
       </c>
     </row>

--- a/docs/ozon/Озон_рабочая_книга.xlsx
+++ b/docs/ozon/Озон_рабочая_книга.xlsx
@@ -21,7 +21,7 @@
     <sheet name="Тренажер для кисти" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="Фитнес и йога" sheetId="13" state="visible" r:id="rId13"/>
     <sheet name="Шпатель-скребок кондитерский" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Что уточнить" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Без категории" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -147,7 +147,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2090,13 +2090,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="55" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2120,6 +2121,11 @@
           <t>Почему без категории</t>
         </is>
       </c>
+      <c r="E1" s="10" t="inlineStr">
+        <is>
+          <t>Решение владелицы</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2142,6 +2148,11 @@
           <t>шаблон не скачан</t>
         </is>
       </c>
+      <c r="E2" s="9" t="inlineStr">
+        <is>
+          <t>Пока не продаются. Шаблон не нужен</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2164,6 +2175,11 @@
           <t>шаблон не скачан</t>
         </is>
       </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>Пока не продаются. Шаблон не нужен</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2186,6 +2202,11 @@
           <t>шаблон не скачан</t>
         </is>
       </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>Пока не продаются. Шаблон не нужен</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2208,6 +2229,11 @@
           <t>шаблон не скачан</t>
         </is>
       </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>Пока не продаются. Шаблон не нужен</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2230,6 +2256,11 @@
           <t>шаблон не скачан</t>
         </is>
       </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>Пока не продаются. Шаблон не нужен</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2252,6 +2283,11 @@
           <t>шаблон не скачан</t>
         </is>
       </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>Пока не продаются. Шаблон не нужен</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2274,6 +2310,11 @@
           <t>шаблон не скачан</t>
         </is>
       </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>Пока не продаются. Шаблон не нужен</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2296,6 +2337,11 @@
           <t>шаблон не скачан</t>
         </is>
       </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>Пока не продаются. Шаблон не нужен</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2318,6 +2364,11 @@
           <t>предмет WB не сопоставлен</t>
         </is>
       </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>Артикул будет добавлен позже</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2338,6 +2389,11 @@
       <c r="D11" t="inlineStr">
         <is>
           <t>шаблон не скачан</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>Сняты с продажи</t>
         </is>
       </c>
     </row>

--- a/docs/ozon/Озон_рабочая_книга.xlsx
+++ b/docs/ozon/Озон_рабочая_книга.xlsx
@@ -71,7 +71,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -96,6 +96,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00EDEDED"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00595959"/>
       </patternFill>
     </fill>
     <fill>
@@ -126,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -139,14 +144,17 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -853,57 +861,57 @@
       </c>
     </row>
     <row r="2" ht="46" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>Тот же артикул, что на листе «Товары».</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>Выберите одно значение из списка.</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>Текстовое описание цвета - заполните, если товар имеет маркетинговое название цвета от поставщика, номер тона или оттенка, например: "№17 Нежная голубая лазурь"</t>
         </is>
       </c>
-      <c r="D2" s="6" t="inlineStr">
+      <c r="D2" s="7" t="inlineStr">
         <is>
           <t>Серия моделей, приуроченная к конкретному сезону продажи.</t>
         </is>
       </c>
-      <c r="E2" s="6" t="inlineStr">
+      <c r="E2" s="7" t="inlineStr">
         <is>
           <t>Выберите из списка наиболее подходящий тип товара.</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" s="7" t="inlineStr">
         <is>
           <t>Период, в течение которого производитель отвечает за качество товара.</t>
         </is>
       </c>
-      <c r="G2" s="6" t="inlineStr">
+      <c r="G2" s="7" t="inlineStr">
         <is>
           <t>Можно указать только целое число или десятичную дробь.</t>
         </is>
       </c>
-      <c r="H2" s="6" t="inlineStr">
+      <c r="H2" s="7" t="inlineStr">
         <is>
           <t>Выберите из списка или укажите вручную.</t>
         </is>
       </c>
-      <c r="I2" s="6" t="inlineStr">
+      <c r="I2" s="7" t="inlineStr">
         <is>
           <t>Количество единиц товара, которое будет продано клиенту за указанную цену.</t>
         </is>
       </c>
-      <c r="J2" s="6" t="inlineStr">
+      <c r="J2" s="7" t="inlineStr">
         <is>
           <t>Указывается значение без единицы измерения.</t>
         </is>
       </c>
-      <c r="K2" s="6" t="inlineStr">
+      <c r="K2" s="7" t="inlineStr">
         <is>
           <t>Выберите из списка.</t>
         </is>
@@ -915,7 +923,7 @@
           <t>ACRB1MS106WH</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>9506919000 - Прочий инвентарь и оборудование для занятий общей физкультурой, гимнастикой или атлетикой</t>
         </is>
@@ -927,7 +935,7 @@
           <t>ACRB1MS106PN</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>9506919000 - Прочий инвентарь и оборудование для занятий общей физкультурой, гимнастикой или атлетикой</t>
         </is>
@@ -939,7 +947,7 @@
           <t>ACRB1MS106BL</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>9506919000 - Прочий инвентарь и оборудование для занятий общей физкультурой, гимнастикой или атлетикой</t>
         </is>
@@ -951,7 +959,7 @@
           <t>ACRB1MS106RJ</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>9506919000 - Прочий инвентарь и оборудование для занятий общей физкультурой, гимнастикой или атлетикой</t>
         </is>
@@ -963,7 +971,7 @@
           <t>ACRB1MS106BС</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>9506919000 - Прочий инвентарь и оборудование для занятий общей физкультурой, гимнастикой или атлетикой</t>
         </is>
@@ -975,7 +983,7 @@
           <t>ACRB1MS107WH</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>9506919000 - Прочий инвентарь и оборудование для занятий общей физкультурой, гимнастикой или атлетикой</t>
         </is>
@@ -987,7 +995,7 @@
           <t>ACRB1MS107PN</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>9506919000 - Прочий инвентарь и оборудование для занятий общей физкультурой, гимнастикой или атлетикой</t>
         </is>
@@ -999,7 +1007,7 @@
           <t>ACRB1MS107BL</t>
         </is>
       </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>9506919000 - Прочий инвентарь и оборудование для занятий общей физкультурой, гимнастикой или атлетикой</t>
         </is>
@@ -1011,7 +1019,7 @@
           <t>ACRB1MS107RJ</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>9506919000 - Прочий инвентарь и оборудование для занятий общей физкультурой, гимнастикой или атлетикой</t>
         </is>
@@ -1023,7 +1031,7 @@
           <t>ACRB1MS107BС</t>
         </is>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>9506919000 - Прочий инвентарь и оборудование для занятий общей физкультурой, гимнастикой или атлетикой</t>
         </is>
@@ -1035,7 +1043,7 @@
           <t>ACRB1MS109PN</t>
         </is>
       </c>
-      <c r="B13" s="9" t="inlineStr">
+      <c r="B13" s="10" t="inlineStr">
         <is>
           <t>9506919000 - Прочий инвентарь и оборудование для занятий общей физкультурой, гимнастикой или атлетикой</t>
         </is>
@@ -1047,7 +1055,7 @@
           <t>ACRB1MS109BL</t>
         </is>
       </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B14" s="10" t="inlineStr">
         <is>
           <t>9506919000 - Прочий инвентарь и оборудование для занятий общей физкультурой, гимнастикой или атлетикой</t>
         </is>
@@ -1059,7 +1067,7 @@
           <t>ACRB1MS109RJ</t>
         </is>
       </c>
-      <c r="B15" s="9" t="inlineStr">
+      <c r="B15" s="10" t="inlineStr">
         <is>
           <t>9506919000 - Прочий инвентарь и оборудование для занятий общей физкультурой, гимнастикой или атлетикой</t>
         </is>
@@ -1071,7 +1079,7 @@
           <t>ACRB1MS109BС</t>
         </is>
       </c>
-      <c r="B16" s="9" t="inlineStr">
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>9506919000 - Прочий инвентарь и оборудование для занятий общей физкультурой, гимнастикой или атлетикой</t>
         </is>
@@ -1083,7 +1091,7 @@
           <t>ACRB1MS109LI</t>
         </is>
       </c>
-      <c r="B17" s="9" t="inlineStr">
+      <c r="B17" s="10" t="inlineStr">
         <is>
           <t>9506919000 - Прочий инвентарь и оборудование для занятий общей физкультурой, гимнастикой или атлетикой</t>
         </is>
@@ -1254,92 +1262,92 @@
       </c>
     </row>
     <row r="2" ht="46" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>Тот же артикул, что на листе «Товары».</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>Выберите одно значение из списка.</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>Можно указать только целое число.</t>
         </is>
       </c>
-      <c r="D2" s="6" t="inlineStr">
+      <c r="D2" s="7" t="inlineStr">
         <is>
           <t>Выберите из списка наиболее подходящий тип товара.</t>
         </is>
       </c>
-      <c r="E2" s="6" t="inlineStr">
+      <c r="E2" s="7" t="inlineStr">
         <is>
           <t>Можно указать только целое число.</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" s="7" t="inlineStr">
         <is>
           <t>Выберите из списка или укажите вручную.</t>
         </is>
       </c>
-      <c r="G2" s="6" t="inlineStr">
+      <c r="G2" s="7" t="inlineStr">
         <is>
           <t>Срок годности, установленный производителем.</t>
         </is>
       </c>
-      <c r="H2" s="6" t="inlineStr">
+      <c r="H2" s="7" t="inlineStr">
         <is>
           <t>Количество единиц товара, которое будет продано клиенту за указанную цену.</t>
         </is>
       </c>
-      <c r="I2" s="6" t="inlineStr">
+      <c r="I2" s="7" t="inlineStr">
         <is>
           <t>В порядке убывания перечислите материалы, из которых изготовлен товар.</t>
         </is>
       </c>
-      <c r="J2" s="6" t="inlineStr">
+      <c r="J2" s="7" t="inlineStr">
         <is>
           <t>Размеры сторон товара в упаковке в сантиметрах.</t>
         </is>
       </c>
-      <c r="K2" s="6" t="inlineStr">
+      <c r="K2" s="7" t="inlineStr">
         <is>
           <t>Можно указать только целое число или десятичную дробь.</t>
         </is>
       </c>
-      <c r="L2" s="6" t="inlineStr">
+      <c r="L2" s="7" t="inlineStr">
         <is>
           <t>Можно указать только целое число или десятичную дробь.</t>
         </is>
       </c>
-      <c r="M2" s="6" t="inlineStr">
+      <c r="M2" s="7" t="inlineStr">
         <is>
           <t>Можно указать только целое число или десятичную дробь.</t>
         </is>
       </c>
-      <c r="N2" s="6" t="inlineStr">
+      <c r="N2" s="7" t="inlineStr">
         <is>
           <t>Размеры сторон товара без упаковки в миллиметрах.</t>
         </is>
       </c>
-      <c r="O2" s="6" t="inlineStr">
+      <c r="O2" s="7" t="inlineStr">
         <is>
           <t>Вес товара без упаковки (нетто) в граммах в расчете на 1 SKU.</t>
         </is>
       </c>
-      <c r="P2" s="6" t="inlineStr">
+      <c r="P2" s="7" t="inlineStr">
         <is>
           <t>Выберите из списка или укажите вручную.</t>
         </is>
       </c>
-      <c r="Q2" s="6" t="inlineStr">
+      <c r="Q2" s="7" t="inlineStr">
         <is>
           <t>Признак для товаров, которые содержат эротику, сцены секса, изображения с нецензурными выражениями, даже если они написаны частично или со спец.</t>
         </is>
       </c>
-      <c r="R2" s="6" t="inlineStr">
+      <c r="R2" s="7" t="inlineStr">
         <is>
           <t>Перечислите, что входит в комплект вместе с товаром: инструкция, чехол, комплект проводов и т.п.</t>
         </is>
@@ -1351,7 +1359,7 @@
           <t>ACRA7TB201BC</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>3926909709 - Изделия прочие из пластмасс и изделия из прочих материалов товарных позиций 3901 - 3914, прочие, прочие, прочие, прочие</t>
         </is>
@@ -1363,7 +1371,7 @@
           <t>ACRA7TB201CL</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>3926909709 - Изделия прочие из пластмасс и изделия из прочих материалов товарных позиций 3901 - 3914, прочие, прочие, прочие, прочие</t>
         </is>
@@ -1375,7 +1383,7 @@
           <t>ACRA7TB201WH</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>3926909709 - Изделия прочие из пластмасс и изделия из прочих материалов товарных позиций 3901 - 3914, прочие, прочие, прочие, прочие</t>
         </is>
@@ -1387,7 +1395,7 @@
           <t>ACRA7TB201LI</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>3926909709 - Изделия прочие из пластмасс и изделия из прочих материалов товарных позиций 3901 - 3914, прочие, прочие, прочие, прочие</t>
         </is>
@@ -1399,7 +1407,7 @@
           <t>ACRA7TB101BC</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>3926909709 - Изделия прочие из пластмасс и изделия из прочих материалов товарных позиций 3901 - 3914, прочие, прочие, прочие, прочие</t>
         </is>
@@ -1411,7 +1419,7 @@
           <t>ACRA7TB101CL</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>3926909709 - Изделия прочие из пластмасс и изделия из прочих материалов товарных позиций 3901 - 3914, прочие, прочие, прочие, прочие</t>
         </is>
@@ -1423,7 +1431,7 @@
           <t>ACRA7TB301GR</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>3926909709 - Изделия прочие из пластмасс и изделия из прочих материалов товарных позиций 3901 - 3914, прочие, прочие, прочие, прочие</t>
         </is>
@@ -1435,7 +1443,7 @@
           <t>ACRA7TB301CL</t>
         </is>
       </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>3926909709 - Изделия прочие из пластмасс и изделия из прочих материалов товарных позиций 3901 - 3914, прочие, прочие, прочие, прочие</t>
         </is>
@@ -1447,7 +1455,7 @@
           <t>ACRA7TB301WH</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>3926909709 - Изделия прочие из пластмасс и изделия из прочих материалов товарных позиций 3901 - 3914, прочие, прочие, прочие, прочие</t>
         </is>
@@ -1549,52 +1557,52 @@
       </c>
     </row>
     <row r="2" ht="46" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>Тот же артикул, что на листе «Товары».</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>Выберите одно значение из списка.</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>Можно указать только целое число или десятичную дробь.</t>
         </is>
       </c>
-      <c r="D2" s="6" t="inlineStr">
+      <c r="D2" s="7" t="inlineStr">
         <is>
           <t>Выберите из списка наиболее подходящий тип товара.</t>
         </is>
       </c>
-      <c r="E2" s="6" t="inlineStr">
+      <c r="E2" s="7" t="inlineStr">
         <is>
           <t>Вес товара без упаковки (нетто) в граммах в расчете на 1 SKU.</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" s="7" t="inlineStr">
         <is>
           <t>Выберите из списка.</t>
         </is>
       </c>
-      <c r="G2" s="6" t="inlineStr">
+      <c r="G2" s="7" t="inlineStr">
         <is>
           <t>Выберите из списка или укажите вручную.</t>
         </is>
       </c>
-      <c r="H2" s="6" t="inlineStr">
+      <c r="H2" s="7" t="inlineStr">
         <is>
           <t>Выберите из списка или укажите вручную.</t>
         </is>
       </c>
-      <c r="I2" s="6" t="inlineStr">
+      <c r="I2" s="7" t="inlineStr">
         <is>
           <t>Выберите из списка или укажите вручную.</t>
         </is>
       </c>
-      <c r="J2" s="6" t="inlineStr">
+      <c r="J2" s="7" t="inlineStr">
         <is>
           <t>Период, в течение которого производитель отвечает за качество товара.</t>
         </is>
@@ -1717,67 +1725,67 @@
       </c>
     </row>
     <row r="2" ht="46" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>Тот же артикул, что на листе «Товары».</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>Выберите одно значение из списка.</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>Можно указать только целое число или десятичную дробь.</t>
         </is>
       </c>
-      <c r="D2" s="6" t="inlineStr">
+      <c r="D2" s="7" t="inlineStr">
         <is>
           <t>Выберите из списка наиболее подходящий тип товара.</t>
         </is>
       </c>
-      <c r="E2" s="6" t="inlineStr">
+      <c r="E2" s="7" t="inlineStr">
         <is>
           <t>Вес товара без упаковки (нетто) в граммах в расчете на 1 SKU.</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" s="7" t="inlineStr">
         <is>
           <t>Можно указать только целое число или десятичную дробь.</t>
         </is>
       </c>
-      <c r="G2" s="6" t="inlineStr">
+      <c r="G2" s="7" t="inlineStr">
         <is>
           <t>Можно указать только целое число.</t>
         </is>
       </c>
-      <c r="H2" s="6" t="inlineStr">
+      <c r="H2" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Миниатюрное изображение, которое заменяет стандартный кружок цвета, например: крупный фрагмент товара, по которому понятен цвет, мазок краски или косметический </t>
         </is>
       </c>
-      <c r="I2" s="6" t="inlineStr">
+      <c r="I2" s="7" t="inlineStr">
         <is>
           <t>Выберите из списка или укажите вручную.</t>
         </is>
       </c>
-      <c r="J2" s="6" t="inlineStr">
+      <c r="J2" s="7" t="inlineStr">
         <is>
           <t>Выберите из списка или укажите вручную.</t>
         </is>
       </c>
-      <c r="K2" s="6" t="inlineStr">
+      <c r="K2" s="7" t="inlineStr">
         <is>
           <t>Выберите из списка или укажите вручную.</t>
         </is>
       </c>
-      <c r="L2" s="6" t="inlineStr">
+      <c r="L2" s="7" t="inlineStr">
         <is>
           <t>Перечислите, что входит в комплект вместе с товаром: инструкция, чехол, комплект проводов и т.п.</t>
         </is>
       </c>
-      <c r="M2" s="6" t="inlineStr">
+      <c r="M2" s="7" t="inlineStr">
         <is>
           <t>Период, в течение которого производитель отвечает за качество товара.</t>
         </is>
@@ -1789,7 +1797,7 @@
           <t>ACRB3FR101CL</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>9506919000 - Прочий инвентарь и оборудование для занятий общей физкультурой, гимнастикой или атлетикой</t>
         </is>
@@ -1801,7 +1809,7 @@
           <t>ACRB5FR200CL</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>9506919000 - Прочий инвентарь и оборудование для занятий общей физкультурой, гимнастикой или атлетикой</t>
         </is>
@@ -1813,7 +1821,7 @@
           <t>ACRB4FR300CL</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>9506919000 - Прочий инвентарь и оборудование для занятий общей физкультурой, гимнастикой или атлетикой</t>
         </is>
@@ -1976,77 +1984,77 @@
       </c>
     </row>
     <row r="2" ht="46" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>Тот же артикул, что на листе «Товары».</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>Выберите одно значение из списка.</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>Текстовое описание цвета - заполните, если товар имеет маркетинговое название цвета от поставщика, номер тона или оттенка, например: "№17 Нежная голубая лазурь"</t>
         </is>
       </c>
-      <c r="D2" s="6" t="inlineStr">
+      <c r="D2" s="7" t="inlineStr">
         <is>
           <t>Можно указать только целое число или десятичную дробь.</t>
         </is>
       </c>
-      <c r="E2" s="6" t="inlineStr">
+      <c r="E2" s="7" t="inlineStr">
         <is>
           <t>Можно указать только целое число.</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" s="7" t="inlineStr">
         <is>
           <t>Выберите из списка наиболее подходящий тип товара.</t>
         </is>
       </c>
-      <c r="G2" s="6" t="inlineStr">
+      <c r="G2" s="7" t="inlineStr">
         <is>
           <t>Вес товара без упаковки (нетто) в граммах в расчете на 1 SKU.</t>
         </is>
       </c>
-      <c r="H2" s="6" t="inlineStr">
+      <c r="H2" s="7" t="inlineStr">
         <is>
           <t>Выберите из списка.</t>
         </is>
       </c>
-      <c r="I2" s="6" t="inlineStr">
+      <c r="I2" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Миниатюрное изображение, которое заменяет стандартный кружок цвета, например: крупный фрагмент товара, по которому понятен цвет, мазок краски или косметический </t>
         </is>
       </c>
-      <c r="J2" s="6" t="inlineStr">
+      <c r="J2" s="7" t="inlineStr">
         <is>
           <t>Можно указать только целое число или десятичную дробь.</t>
         </is>
       </c>
-      <c r="K2" s="6" t="inlineStr">
+      <c r="K2" s="7" t="inlineStr">
         <is>
           <t>Выберите из списка или укажите вручную.</t>
         </is>
       </c>
-      <c r="L2" s="6" t="inlineStr">
+      <c r="L2" s="7" t="inlineStr">
         <is>
           <t>Выберите из списка или укажите вручную.</t>
         </is>
       </c>
-      <c r="M2" s="6" t="inlineStr">
+      <c r="M2" s="7" t="inlineStr">
         <is>
           <t>Период, в течение которого производитель отвечает за качество товара.</t>
         </is>
       </c>
-      <c r="N2" s="6" t="inlineStr">
+      <c r="N2" s="7" t="inlineStr">
         <is>
           <t>Автоматически укажем значение "Фабричное производство", если оставите это поле пустым.</t>
         </is>
       </c>
-      <c r="O2" s="6" t="inlineStr">
+      <c r="O2" s="7" t="inlineStr">
         <is>
           <t>Перечислите, что входит в комплект вместе с товаром: инструкция, чехол, комплект проводов и т.п.</t>
         </is>
@@ -2101,27 +2109,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>Артикул</t>
         </is>
       </c>
-      <c r="B1" s="10" t="inlineStr">
+      <c r="B1" s="11" t="inlineStr">
         <is>
           <t>Название</t>
         </is>
       </c>
-      <c r="C1" s="10" t="inlineStr">
+      <c r="C1" s="11" t="inlineStr">
         <is>
           <t>Предмет на WB</t>
         </is>
       </c>
-      <c r="D1" s="10" t="inlineStr">
+      <c r="D1" s="11" t="inlineStr">
         <is>
           <t>Почему без категории</t>
         </is>
       </c>
-      <c r="E1" s="10" t="inlineStr">
+      <c r="E1" s="11" t="inlineStr">
         <is>
           <t>Решение владелицы</t>
         </is>
@@ -2148,7 +2156,7 @@
           <t>шаблон не скачан</t>
         </is>
       </c>
-      <c r="E2" s="9" t="inlineStr">
+      <c r="E2" s="10" t="inlineStr">
         <is>
           <t>Пока не продаются. Шаблон не нужен</t>
         </is>
@@ -2175,7 +2183,7 @@
           <t>шаблон не скачан</t>
         </is>
       </c>
-      <c r="E3" s="9" t="inlineStr">
+      <c r="E3" s="10" t="inlineStr">
         <is>
           <t>Пока не продаются. Шаблон не нужен</t>
         </is>
@@ -2202,7 +2210,7 @@
           <t>шаблон не скачан</t>
         </is>
       </c>
-      <c r="E4" s="9" t="inlineStr">
+      <c r="E4" s="10" t="inlineStr">
         <is>
           <t>Пока не продаются. Шаблон не нужен</t>
         </is>
@@ -2229,7 +2237,7 @@
           <t>шаблон не скачан</t>
         </is>
       </c>
-      <c r="E5" s="9" t="inlineStr">
+      <c r="E5" s="10" t="inlineStr">
         <is>
           <t>Пока не продаются. Шаблон не нужен</t>
         </is>
@@ -2256,7 +2264,7 @@
           <t>шаблон не скачан</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E6" s="10" t="inlineStr">
         <is>
           <t>Пока не продаются. Шаблон не нужен</t>
         </is>
@@ -2283,7 +2291,7 @@
           <t>шаблон не скачан</t>
         </is>
       </c>
-      <c r="E7" s="9" t="inlineStr">
+      <c r="E7" s="10" t="inlineStr">
         <is>
           <t>Пока не продаются. Шаблон не нужен</t>
         </is>
@@ -2310,7 +2318,7 @@
           <t>шаблон не скачан</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="E8" s="10" t="inlineStr">
         <is>
           <t>Пока не продаются. Шаблон не нужен</t>
         </is>
@@ -2337,7 +2345,7 @@
           <t>шаблон не скачан</t>
         </is>
       </c>
-      <c r="E9" s="9" t="inlineStr">
+      <c r="E9" s="10" t="inlineStr">
         <is>
           <t>Пока не продаются. Шаблон не нужен</t>
         </is>
@@ -2364,7 +2372,7 @@
           <t>предмет WB не сопоставлен</t>
         </is>
       </c>
-      <c r="E10" s="9" t="inlineStr">
+      <c r="E10" s="10" t="inlineStr">
         <is>
           <t>Артикул будет добавлен позже</t>
         </is>
@@ -2391,7 +2399,7 @@
           <t>шаблон не скачан</t>
         </is>
       </c>
-      <c r="E11" s="9" t="inlineStr">
+      <c r="E11" s="10" t="inlineStr">
         <is>
           <t>Сняты с продажи</t>
         </is>
@@ -2408,7 +2416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC76"/>
+  <dimension ref="A1:AJ76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2440,6 +2448,13 @@
     <col width="31" customWidth="1" min="27" max="27"/>
     <col width="26" customWidth="1" min="28" max="28"/>
     <col width="33" customWidth="1" min="29" max="29"/>
+    <col width="26" customWidth="1" min="30" max="30"/>
+    <col width="26" customWidth="1" min="31" max="31"/>
+    <col width="26" customWidth="1" min="32" max="32"/>
+    <col width="26" customWidth="1" min="33" max="33"/>
+    <col width="26" customWidth="1" min="34" max="34"/>
+    <col width="26" customWidth="1" min="35" max="35"/>
+    <col width="26" customWidth="1" min="36" max="36"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -2588,151 +2603,221 @@
           <t>Количество заводских упаковок</t>
         </is>
       </c>
+      <c r="AD1" s="6" t="inlineStr">
+        <is>
+          <t>Ядро запросов</t>
+        </is>
+      </c>
+      <c r="AE1" s="6" t="inlineStr">
+        <is>
+          <t>Инфографика — задание</t>
+        </is>
+      </c>
+      <c r="AF1" s="6" t="inlineStr">
+        <is>
+          <t>Видео — задание</t>
+        </is>
+      </c>
+      <c r="AG1" s="6" t="inlineStr">
+        <is>
+          <t>Видеообложка — задание</t>
+        </is>
+      </c>
+      <c r="AH1" s="6" t="inlineStr">
+        <is>
+          <t>Rich-контент — задание</t>
+        </is>
+      </c>
+      <c r="AI1" s="6" t="inlineStr">
+        <is>
+          <t>Контент-рейтинг</t>
+        </is>
+      </c>
+      <c r="AJ1" s="6" t="inlineStr">
+        <is>
+          <t>Статус разбора</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="46" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>Ваш код товара. По нему строка связывается с листом категории.</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>Из списка. Определяет, в какой шаблон Ozon уйдёт строка.</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>Ознакомьтесь с Требованиями к названию, чтобы указать правильное название товара и пройти модерацию.</t>
         </is>
       </c>
-      <c r="D2" s="6" t="inlineStr">
+      <c r="D2" s="7" t="inlineStr">
         <is>
           <t>Цена, которую вы устанавливаете вручную</t>
         </is>
       </c>
-      <c r="E2" s="6" t="inlineStr">
+      <c r="E2" s="7" t="inlineStr">
         <is>
           <t>Цена, которую покупатель видит зачёркнутой</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" s="7" t="inlineStr">
         <is>
           <t>Укажите ставку НДС.</t>
         </is>
       </c>
-      <c r="G2" s="6" t="inlineStr">
+      <c r="G2" s="7" t="inlineStr">
         <is>
           <t>Добавим товару пометку «Рассрочка 0–0–6» и будем отображать в специальных подборках.</t>
         </is>
       </c>
-      <c r="H2" s="6" t="inlineStr">
+      <c r="H2" s="7" t="inlineStr">
         <is>
           <t>Подключим товару ускоренный сбор отзывов.</t>
         </is>
       </c>
-      <c r="I2" s="6" t="inlineStr">
+      <c r="I2" s="7" t="inlineStr">
         <is>
           <t>Заполните поле, если хотите скопировать чужой товар, размещённый на Ozon.</t>
         </is>
       </c>
-      <c r="J2" s="6" t="inlineStr">
+      <c r="J2" s="7" t="inlineStr">
         <is>
           <t>Введите штрихкод товара от производителя и наклейте его на упаковку.</t>
         </is>
       </c>
-      <c r="K2" s="6" t="inlineStr">
+      <c r="K2" s="7" t="inlineStr">
         <is>
           <t>Можем взять дополнительную плату, если ОВХ отличаются от реальных.</t>
         </is>
       </c>
-      <c r="L2" s="6" t="inlineStr">
+      <c r="L2" s="7" t="inlineStr">
         <is>
           <t>Можем взять дополнительную плату, если ОВХ отличаются от реальных.</t>
         </is>
       </c>
-      <c r="M2" s="6" t="inlineStr">
+      <c r="M2" s="7" t="inlineStr">
         <is>
           <t>Можем взять дополнительную плату, если ОВХ отличаются от реальных.</t>
         </is>
       </c>
-      <c r="N2" s="6" t="inlineStr">
+      <c r="N2" s="7" t="inlineStr">
         <is>
           <t>Можем взять дополнительную плату, если ОВХ отличаются от реальных.</t>
         </is>
       </c>
-      <c r="O2" s="6" t="inlineStr">
+      <c r="O2" s="7" t="inlineStr">
         <is>
           <t>Вы можете загрузить товары в xls-шаблоне и API без фото, а потом загрузить фото через карточку товара или раздел «Обновить изображения» Требования к изображения</t>
         </is>
       </c>
-      <c r="P2" s="6" t="inlineStr">
+      <c r="P2" s="7" t="inlineStr">
         <is>
           <t>Вы можете загрузить товары в xls-шаблоне и API без фото, а потом загрузить фото через карточку товара или раздел «Обновить изображения» Требования к изображения</t>
         </is>
       </c>
-      <c r="Q2" s="6" t="inlineStr">
+      <c r="Q2" s="7" t="inlineStr">
         <is>
           <t>Название файла с изображением товара.</t>
         </is>
       </c>
-      <c r="R2" s="6" t="inlineStr">
+      <c r="R2" s="7" t="inlineStr">
         <is>
           <t>Среди брендов есть продвигаемые — в вашем личном кабинете отмечаем их значком молнии.</t>
         </is>
       </c>
-      <c r="S2" s="6" t="inlineStr">
+      <c r="S2" s="7" t="inlineStr">
         <is>
           <t>Заполните данное поле любым одинаковым значением на товарах, которые хотите объединить.</t>
         </is>
       </c>
-      <c r="T2" s="6" t="inlineStr">
+      <c r="T2" s="7" t="inlineStr">
         <is>
           <t>Основной или доминирующий цвет товара.</t>
         </is>
       </c>
-      <c r="U2" s="6" t="inlineStr">
+      <c r="U2" s="7" t="inlineStr">
         <is>
           <t>Выберите «Да», если товар имеет код маркировки (КИЗ).</t>
         </is>
       </c>
-      <c r="V2" s="6" t="inlineStr">
+      <c r="V2" s="7" t="inlineStr">
         <is>
           <t>УЕИ – унифицированная единица измерения.</t>
         </is>
       </c>
-      <c r="W2" s="6" t="inlineStr">
+      <c r="W2" s="7" t="inlineStr">
         <is>
           <t>Заполните поле (укажите целое число), чтобы продавать товар оптом покупателям-юрлицам.</t>
         </is>
       </c>
-      <c r="X2" s="6" t="inlineStr">
+      <c r="X2" s="7" t="inlineStr">
         <is>
           <t>Хештеги работают так же, как в соцсетях: покупатели могут нажать на них в карточке или написать в поиске.</t>
         </is>
       </c>
-      <c r="Y2" s="6" t="inlineStr">
+      <c r="Y2" s="7" t="inlineStr">
         <is>
           <t>Описание товара, маркетинговый текст</t>
         </is>
       </c>
-      <c r="Z2" s="6" t="inlineStr">
+      <c r="Z2" s="7" t="inlineStr">
         <is>
           <t>Добавьте расширенное описание товара с фото и видео по шаблону в формате JSON.</t>
         </is>
       </c>
-      <c r="AA2" s="6" t="inlineStr">
+      <c r="AA2" s="7" t="inlineStr">
         <is>
           <t>Введите одинаковое значение в этом атрибуте для объединения товаров в группу "Похожие".</t>
         </is>
       </c>
-      <c r="AB2" s="6" t="inlineStr">
+      <c r="AB2" s="7" t="inlineStr">
         <is>
           <t>Страна, в которой изготовлен/собран товар и которая указана на упаковке.</t>
         </is>
       </c>
-      <c r="AC2" s="6" t="inlineStr">
+      <c r="AC2" s="7" t="inlineStr">
         <is>
           <t>Сколько заводских упаковок продаёте под этим SKU.</t>
+        </is>
+      </c>
+      <c r="AD2" s="7" t="inlineStr">
+        <is>
+          <t>РАБОЧАЯ КОЛОНКА, в Ozon не уходит. Запросы из отчёта «Поисковые запросы», подо что пишется текст.</t>
+        </is>
+      </c>
+      <c r="AE2" s="7" t="inlineStr">
+        <is>
+          <t>РАБОЧАЯ КОЛОНКА. Что переделать на слайдах. Не разбираем сейчас.</t>
+        </is>
+      </c>
+      <c r="AF2" s="7" t="inlineStr">
+        <is>
+          <t>РАБОЧАЯ КОЛОНКА. Ozon с конца 2025 считает медиа по видео, а не по фото 360. Не разбираем сейчас.</t>
+        </is>
+      </c>
+      <c r="AG2" s="7" t="inlineStr">
+        <is>
+          <t>РАБОЧАЯ КОЛОНКА. Отдельный элемент, влияет на блок «Медиа» контент-рейтинга. Не разбираем сейчас.</t>
+        </is>
+      </c>
+      <c r="AH2" s="7" t="inlineStr">
+        <is>
+          <t>РАБОЧАЯ КОЛОНКА. Что показать в rich. Не разбираем сейчас.</t>
+        </is>
+      </c>
+      <c r="AI2" s="7" t="inlineStr">
+        <is>
+          <t>РАБОЧАЯ КОЛОНКА. Из кабинета: «Товары и цены». Ozon рекомендует держать выше 85.</t>
+        </is>
+      </c>
+      <c r="AJ2" s="7" t="inlineStr">
+        <is>
+          <t>РАБОЧАЯ КОЛОНКА. Где мы по этой карточке.</t>
         </is>
       </c>
     </row>
@@ -4578,7 +4663,7 @@
           <t>ACRF1KP101BC</t>
         </is>
       </c>
-      <c r="B46" s="8" t="inlineStr"/>
+      <c r="B46" s="9" t="inlineStr"/>
       <c r="C46" t="inlineStr">
         <is>
           <t>Капа черный/красный - черная коробка</t>
@@ -4610,7 +4695,7 @@
           <t>ACRF1KP102BC</t>
         </is>
       </c>
-      <c r="B47" s="8" t="inlineStr"/>
+      <c r="B47" s="9" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
           <t>Капа черный/белый-черная коробка</t>
@@ -4642,7 +4727,7 @@
           <t>ACRF1KP103BC</t>
         </is>
       </c>
-      <c r="B48" s="8" t="inlineStr"/>
+      <c r="B48" s="9" t="inlineStr"/>
       <c r="C48" t="inlineStr">
         <is>
           <t>Капа белый/черный</t>
@@ -4674,7 +4759,7 @@
           <t>ACRF1KP101RD</t>
         </is>
       </c>
-      <c r="B49" s="8" t="inlineStr"/>
+      <c r="B49" s="9" t="inlineStr"/>
       <c r="C49" t="inlineStr">
         <is>
           <t>Капа белый/красный</t>
@@ -4706,7 +4791,7 @@
           <t>ACRF1KP102RD</t>
         </is>
       </c>
-      <c r="B50" s="8" t="inlineStr"/>
+      <c r="B50" s="9" t="inlineStr"/>
       <c r="C50" t="inlineStr">
         <is>
           <t>Капа красный/белый</t>
@@ -4738,7 +4823,7 @@
           <t>ACRF1KP101BL</t>
         </is>
       </c>
-      <c r="B51" s="8" t="inlineStr"/>
+      <c r="B51" s="9" t="inlineStr"/>
       <c r="C51" t="inlineStr">
         <is>
           <t>Капа синий/белый</t>
@@ -4770,7 +4855,7 @@
           <t>ACRF1KP101GN</t>
         </is>
       </c>
-      <c r="B52" s="8" t="inlineStr"/>
+      <c r="B52" s="9" t="inlineStr"/>
       <c r="C52" t="inlineStr">
         <is>
           <t>Капа зеленый/белый</t>
@@ -4802,7 +4887,7 @@
           <t>ACRF1KP102GN</t>
         </is>
       </c>
-      <c r="B53" s="8" t="inlineStr"/>
+      <c r="B53" s="9" t="inlineStr"/>
       <c r="C53" t="inlineStr">
         <is>
           <t>Капа зеленый/черный</t>
@@ -5092,7 +5177,7 @@
           <t>ACRA7TB101WH</t>
         </is>
       </c>
-      <c r="B60" s="8" t="inlineStr"/>
+      <c r="B60" s="9" t="inlineStr"/>
       <c r="C60" t="inlineStr">
         <is>
           <t>Таблетница круглая 7*2 бел Д</t>
@@ -5733,7 +5818,7 @@
           <t>AKTA1PR101GR</t>
         </is>
       </c>
-      <c r="B76" s="8" t="inlineStr"/>
+      <c r="B76" s="9" t="inlineStr"/>
       <c r="C76" t="inlineStr">
         <is>
           <t>Чеснокодавка</t>
@@ -5841,272 +5926,272 @@
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>Общий — Вид выпуска товара</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" s="8" t="inlineStr">
         <is>
           <t>Общий — Вид игрушки для животных</t>
         </is>
       </c>
-      <c r="C1" s="7" t="inlineStr">
+      <c r="C1" s="8" t="inlineStr">
         <is>
           <t>Общий — Вид массажа</t>
         </is>
       </c>
-      <c r="D1" s="7" t="inlineStr">
+      <c r="D1" s="8" t="inlineStr">
         <is>
           <t>Общий — Вид эспандера</t>
         </is>
       </c>
-      <c r="E1" s="7" t="inlineStr">
+      <c r="E1" s="8" t="inlineStr">
         <is>
           <t>Общий — Возрастной диапазон</t>
         </is>
       </c>
-      <c r="F1" s="7" t="inlineStr">
+      <c r="F1" s="8" t="inlineStr">
         <is>
           <t>Общий — Гарантия</t>
         </is>
       </c>
-      <c r="G1" s="7" t="inlineStr">
+      <c r="G1" s="8" t="inlineStr">
         <is>
           <t>Общий — Зоны массажа</t>
         </is>
       </c>
-      <c r="H1" s="7" t="inlineStr">
+      <c r="H1" s="8" t="inlineStr">
         <is>
           <t>Общий — Класс опасности пиротехнического изделия</t>
         </is>
       </c>
-      <c r="I1" s="7" t="inlineStr">
+      <c r="I1" s="8" t="inlineStr">
         <is>
           <t>Общий — Коллекция</t>
         </is>
       </c>
-      <c r="J1" s="7" t="inlineStr">
+      <c r="J1" s="8" t="inlineStr">
         <is>
           <t>Общий — Материал лезвия</t>
         </is>
       </c>
-      <c r="K1" s="7" t="inlineStr">
+      <c r="K1" s="8" t="inlineStr">
         <is>
           <t>Общий — Материал лопатки</t>
         </is>
       </c>
-      <c r="L1" s="7" t="inlineStr">
+      <c r="L1" s="8" t="inlineStr">
         <is>
           <t>Общий — Материал рукояти</t>
         </is>
       </c>
-      <c r="M1" s="7" t="inlineStr">
+      <c r="M1" s="8" t="inlineStr">
         <is>
           <t>Общий — Место для игр</t>
         </is>
       </c>
-      <c r="N1" s="7" t="inlineStr">
+      <c r="N1" s="8" t="inlineStr">
         <is>
           <t>Общий — Можно мыть в посудомоечной машине</t>
         </is>
       </c>
-      <c r="O1" s="7" t="inlineStr">
+      <c r="O1" s="8" t="inlineStr">
         <is>
           <t>Общий — Назначение</t>
         </is>
       </c>
-      <c r="P1" s="7" t="inlineStr">
+      <c r="P1" s="8" t="inlineStr">
         <is>
           <t>Общий — Назначение игрушки</t>
         </is>
       </c>
-      <c r="Q1" s="7" t="inlineStr">
+      <c r="Q1" s="8" t="inlineStr">
         <is>
           <t>Общий — Назначение питьевого стекла</t>
         </is>
       </c>
-      <c r="R1" s="7" t="inlineStr">
+      <c r="R1" s="8" t="inlineStr">
         <is>
           <t>Общий — Особенности игрушки</t>
         </is>
       </c>
-      <c r="S1" s="7" t="inlineStr">
+      <c r="S1" s="8" t="inlineStr">
         <is>
           <t>Общий — Особенности пробки</t>
         </is>
       </c>
-      <c r="T1" s="7" t="inlineStr">
+      <c r="T1" s="8" t="inlineStr">
         <is>
           <t>Общий — Особенности состава</t>
         </is>
       </c>
-      <c r="U1" s="7" t="inlineStr">
+      <c r="U1" s="8" t="inlineStr">
         <is>
           <t>Общий — Особенности тренажеров</t>
         </is>
       </c>
-      <c r="V1" s="7" t="inlineStr">
+      <c r="V1" s="8" t="inlineStr">
         <is>
           <t>Общий — Особенности фитнес-инвентаря</t>
         </is>
       </c>
-      <c r="W1" s="7" t="inlineStr">
+      <c r="W1" s="8" t="inlineStr">
         <is>
           <t>Общий — Пол</t>
         </is>
       </c>
-      <c r="X1" s="7" t="inlineStr">
+      <c r="X1" s="8" t="inlineStr">
         <is>
           <t>Общий — Предназначено для</t>
         </is>
       </c>
-      <c r="Y1" s="7" t="inlineStr">
+      <c r="Y1" s="8" t="inlineStr">
         <is>
           <t>Общий — Размер</t>
         </is>
       </c>
-      <c r="Z1" s="7" t="inlineStr">
+      <c r="Z1" s="8" t="inlineStr">
         <is>
           <t>Общий — Страна-изготовитель</t>
         </is>
       </c>
-      <c r="AA1" s="7" t="inlineStr">
+      <c r="AA1" s="8" t="inlineStr">
         <is>
           <t>Общий — Тип режущей кромки</t>
         </is>
       </c>
-      <c r="AB1" s="7" t="inlineStr">
+      <c r="AB1" s="8" t="inlineStr">
         <is>
           <t>Общий — Тренируемые группы мышц</t>
         </is>
       </c>
-      <c r="AC1" s="7" t="inlineStr">
+      <c r="AC1" s="8" t="inlineStr">
         <is>
           <t>Общий — Упаковка</t>
         </is>
       </c>
-      <c r="AD1" s="7" t="inlineStr">
+      <c r="AD1" s="8" t="inlineStr">
         <is>
           <t>Общий — Цвет товара</t>
         </is>
       </c>
-      <c r="AE1" s="7" t="inlineStr">
+      <c r="AE1" s="8" t="inlineStr">
         <is>
           <t>Общий — Целевая аудитория</t>
         </is>
       </c>
-      <c r="AF1" s="7" t="inlineStr">
+      <c r="AF1" s="8" t="inlineStr">
         <is>
           <t>Аксессуар для массажа — Материал</t>
         </is>
       </c>
-      <c r="AG1" s="7" t="inlineStr">
+      <c r="AG1" s="8" t="inlineStr">
         <is>
           <t>Аксессуар для массажа — ТН ВЭД коды ЕАЭС</t>
         </is>
       </c>
-      <c r="AH1" s="7" t="inlineStr">
+      <c r="AH1" s="8" t="inlineStr">
         <is>
           <t>Аксессуар для массажа — Тип</t>
         </is>
       </c>
-      <c r="AI1" s="7" t="inlineStr">
+      <c r="AI1" s="8" t="inlineStr">
         <is>
           <t>Игрушка для животных — Материал</t>
         </is>
       </c>
-      <c r="AJ1" s="7" t="inlineStr">
+      <c r="AJ1" s="8" t="inlineStr">
         <is>
           <t>Игрушка для животных — ТН ВЭД коды ЕАЭС</t>
         </is>
       </c>
-      <c r="AK1" s="7" t="inlineStr">
+      <c r="AK1" s="8" t="inlineStr">
         <is>
           <t>Кухонный нож — ТН ВЭД коды ЕАЭС</t>
         </is>
       </c>
-      <c r="AL1" s="7" t="inlineStr">
+      <c r="AL1" s="8" t="inlineStr">
         <is>
           <t>Кухонный нож — Тип</t>
         </is>
       </c>
-      <c r="AM1" s="7" t="inlineStr">
+      <c r="AM1" s="8" t="inlineStr">
         <is>
           <t>Маска-бандаж — ТН ВЭД коды ЕАЭС</t>
         </is>
       </c>
-      <c r="AN1" s="7" t="inlineStr">
+      <c r="AN1" s="8" t="inlineStr">
         <is>
           <t>Маска-бандаж — Тип</t>
         </is>
       </c>
-      <c r="AO1" s="7" t="inlineStr">
+      <c r="AO1" s="8" t="inlineStr">
         <is>
           <t>Мешок для стирки — Материал</t>
         </is>
       </c>
-      <c r="AP1" s="7" t="inlineStr">
+      <c r="AP1" s="8" t="inlineStr">
         <is>
           <t>Мешок для стирки — ТН ВЭД коды ЕАЭС</t>
         </is>
       </c>
-      <c r="AQ1" s="7" t="inlineStr">
+      <c r="AQ1" s="8" t="inlineStr">
         <is>
           <t>Пробка — Материал</t>
         </is>
       </c>
-      <c r="AR1" s="7" t="inlineStr">
+      <c r="AR1" s="8" t="inlineStr">
         <is>
           <t>Пробка — ТН ВЭД коды ЕАЭС</t>
         </is>
       </c>
-      <c r="AS1" s="7" t="inlineStr">
+      <c r="AS1" s="8" t="inlineStr">
         <is>
           <t>Спортивный массажный мяч — Материал</t>
         </is>
       </c>
-      <c r="AT1" s="7" t="inlineStr">
+      <c r="AT1" s="8" t="inlineStr">
         <is>
           <t>Спортивный массажный мяч — ТН ВЭД коды ЕАЭС</t>
         </is>
       </c>
-      <c r="AU1" s="7" t="inlineStr">
+      <c r="AU1" s="8" t="inlineStr">
         <is>
           <t>Таблетница — Материал</t>
         </is>
       </c>
-      <c r="AV1" s="7" t="inlineStr">
+      <c r="AV1" s="8" t="inlineStr">
         <is>
           <t>Таблетница — ТН ВЭД коды ЕАЭС</t>
         </is>
       </c>
-      <c r="AW1" s="7" t="inlineStr">
+      <c r="AW1" s="8" t="inlineStr">
         <is>
           <t>Таблетница — Тип</t>
         </is>
       </c>
-      <c r="AX1" s="7" t="inlineStr">
+      <c r="AX1" s="8" t="inlineStr">
         <is>
           <t>Тренажер для кисти — ТН ВЭД коды ЕАЭС</t>
         </is>
       </c>
-      <c r="AY1" s="7" t="inlineStr">
+      <c r="AY1" s="8" t="inlineStr">
         <is>
           <t>Фитнес и йога — ТН ВЭД коды ЕАЭС</t>
         </is>
       </c>
-      <c r="AZ1" s="7" t="inlineStr">
+      <c r="AZ1" s="8" t="inlineStr">
         <is>
           <t>Фитнес и йога — Тип</t>
         </is>
       </c>
-      <c r="BA1" s="7" t="inlineStr">
+      <c r="BA1" s="8" t="inlineStr">
         <is>
           <t>Шпатель-скребок кондитерский — ТН ВЭД коды ЕАЭС</t>
         </is>
       </c>
-      <c r="BB1" s="7" t="inlineStr">
+      <c r="BB1" s="8" t="inlineStr">
         <is>
           <t>Шпатель-скребок кондитерский — Тип</t>
         </is>
@@ -37965,92 +38050,92 @@
       </c>
     </row>
     <row r="2" ht="46" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>Тот же артикул, что на листе «Товары».</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>Выберите одно значение из списка.</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>Выберите из списка наиболее подходящий тип товара.</t>
         </is>
       </c>
-      <c r="D2" s="6" t="inlineStr">
+      <c r="D2" s="7" t="inlineStr">
         <is>
           <t>Текстовое описание цвета - заполните, если товар имеет маркетинговое название цвета от поставщика, номер тона или оттенка, например: "№17 Нежная голубая лазурь"</t>
         </is>
       </c>
-      <c r="E2" s="6" t="inlineStr">
+      <c r="E2" s="7" t="inlineStr">
         <is>
           <t>Вес товара без упаковки (нетто) в граммах в расчете на 1 SKU.</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" s="7" t="inlineStr">
         <is>
           <t>Укажите наименование организации, которая является производителем товара</t>
         </is>
       </c>
-      <c r="G2" s="6" t="inlineStr">
+      <c r="G2" s="7" t="inlineStr">
         <is>
           <t>Если информация о способе применения указана на упаковке или этикетке, то в данном поле информация должна либо дублировать, либо содержать больше данных.</t>
         </is>
       </c>
-      <c r="H2" s="6" t="inlineStr">
+      <c r="H2" s="7" t="inlineStr">
         <is>
           <t>Выберите из списка или укажите вручную.</t>
         </is>
       </c>
-      <c r="I2" s="6" t="inlineStr">
+      <c r="I2" s="7" t="inlineStr">
         <is>
           <t>Укажите зону использования массажера, это необходимо для правильной навигации на сайте.</t>
         </is>
       </c>
-      <c r="J2" s="6" t="inlineStr">
+      <c r="J2" s="7" t="inlineStr">
         <is>
           <t>Можно указать только целое число или десятичную дробь.</t>
         </is>
       </c>
-      <c r="K2" s="6" t="inlineStr">
+      <c r="K2" s="7" t="inlineStr">
         <is>
           <t>В порядке убывания перечислите материалы, из которых изготовлен товар.</t>
         </is>
       </c>
-      <c r="L2" s="6" t="inlineStr">
+      <c r="L2" s="7" t="inlineStr">
         <is>
           <t>Можно указать только целое число или десятичную дробь.</t>
         </is>
       </c>
-      <c r="M2" s="6" t="inlineStr">
+      <c r="M2" s="7" t="inlineStr">
         <is>
           <t>Можно указать только целое число или десятичную дробь.</t>
         </is>
       </c>
-      <c r="N2" s="6" t="inlineStr">
+      <c r="N2" s="7" t="inlineStr">
         <is>
           <t>Выберите не больше 2 подходящих значений из списка.</t>
         </is>
       </c>
-      <c r="O2" s="6" t="inlineStr">
+      <c r="O2" s="7" t="inlineStr">
         <is>
           <t>Перечислите, что входит в комплект вместе с товаром: инструкция, чехол, комплект проводов и т.п.</t>
         </is>
       </c>
-      <c r="P2" s="6" t="inlineStr">
+      <c r="P2" s="7" t="inlineStr">
         <is>
           <t>Признак для товаров, которые содержат эротику, сцены секса, изображения с нецензурными выражениями, даже если они написаны частично или со спец.</t>
         </is>
       </c>
-      <c r="Q2" s="6" t="inlineStr">
+      <c r="Q2" s="7" t="inlineStr">
         <is>
           <t>Период, в течение которого производитель отвечает за качество товара.</t>
         </is>
       </c>
-      <c r="R2" s="6" t="inlineStr">
+      <c r="R2" s="7" t="inlineStr">
         <is>
           <t>Срок годности, установленный производителем.</t>
         </is>
@@ -38062,7 +38147,7 @@
           <t>ACRH1MS101RJ</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>9019109009 - Прочая аппаратура для механотерапии, аппараты массажные, аппаратура для  психологических тестов для определения способностей</t>
         </is>
@@ -38074,7 +38159,7 @@
           <t>ACRB1MS101RJ</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr"/>
+      <c r="B4" s="9" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -38082,7 +38167,7 @@
           <t>ACRB1MS101PN</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr"/>
+      <c r="B5" s="9" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -38090,7 +38175,7 @@
           <t>ACRB1MS101BL</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr"/>
+      <c r="B6" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="7">
@@ -38248,97 +38333,97 @@
       </c>
     </row>
     <row r="2" ht="46" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>Тот же артикул, что на листе «Товары».</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>Выберите одно значение из списка.</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>Количество единиц товара, которое будет продано клиенту за указанную цену.</t>
         </is>
       </c>
-      <c r="D2" s="6" t="inlineStr">
+      <c r="D2" s="7" t="inlineStr">
         <is>
           <t>Текстовое описание цвета - заполните, если товар имеет маркетинговое название цвета от поставщика, номер тона или оттенка, например: "№17 Нежная голубая лазурь"</t>
         </is>
       </c>
-      <c r="E2" s="6" t="inlineStr">
+      <c r="E2" s="7" t="inlineStr">
         <is>
           <t>Выберите из списка наиболее подходящий тип товара.</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" s="7" t="inlineStr">
         <is>
           <t>Выберите одно или несколько значений из выпадающего списка, но не более 4-х.</t>
         </is>
       </c>
-      <c r="G2" s="6" t="inlineStr">
+      <c r="G2" s="7" t="inlineStr">
         <is>
           <t>Вес товара без упаковки (нетто) в граммах в расчете на 1 SKU.</t>
         </is>
       </c>
-      <c r="H2" s="6" t="inlineStr">
+      <c r="H2" s="7" t="inlineStr">
         <is>
           <t>Выберите одно или несколько результатов из списка, но не более 3-х.</t>
         </is>
       </c>
-      <c r="I2" s="6" t="inlineStr">
+      <c r="I2" s="7" t="inlineStr">
         <is>
           <t>Выберите одно или несколько значений из списка, но не больше 2.</t>
         </is>
       </c>
-      <c r="J2" s="6" t="inlineStr">
+      <c r="J2" s="7" t="inlineStr">
         <is>
           <t>Выберите из списка или укажите вручную.</t>
         </is>
       </c>
-      <c r="K2" s="6" t="inlineStr">
+      <c r="K2" s="7" t="inlineStr">
         <is>
           <t>Выберите одно или несколько результатов из списка, но не более 3-х.</t>
         </is>
       </c>
-      <c r="L2" s="6" t="inlineStr">
+      <c r="L2" s="7" t="inlineStr">
         <is>
           <t>Размеры сторон товара в упаковке в сантиметрах.</t>
         </is>
       </c>
-      <c r="M2" s="6" t="inlineStr">
+      <c r="M2" s="7" t="inlineStr">
         <is>
           <t>Выберите одно или несколько значений из выпадающего списка, но не более 5-ти.</t>
         </is>
       </c>
-      <c r="N2" s="6" t="inlineStr">
+      <c r="N2" s="7" t="inlineStr">
         <is>
           <t>Размеры сторон товара без упаковки в миллиметрах.</t>
         </is>
       </c>
-      <c r="O2" s="6" t="inlineStr">
+      <c r="O2" s="7" t="inlineStr">
         <is>
           <t>Выберите одно или несколько значений из выпадающего списка, но не более 3-х.</t>
         </is>
       </c>
-      <c r="P2" s="6" t="inlineStr">
+      <c r="P2" s="7" t="inlineStr">
         <is>
           <t>Перечислите, что входит в комплект вместе с товаром: инструкция, чехол, комплект проводов и т.п.</t>
         </is>
       </c>
-      <c r="Q2" s="6" t="inlineStr">
+      <c r="Q2" s="7" t="inlineStr">
         <is>
           <t>Срок годности, установленный производителем.</t>
         </is>
       </c>
-      <c r="R2" s="6" t="inlineStr">
+      <c r="R2" s="7" t="inlineStr">
         <is>
           <t>Период, в течение которого производитель отвечает за качество товара.</t>
         </is>
       </c>
-      <c r="S2" s="6" t="inlineStr">
+      <c r="S2" s="7" t="inlineStr">
         <is>
           <t>Признак для товаров, которые содержат эротику, сцены секса, изображения с нецензурными выражениями, даже если они написаны частично или со спец.</t>
         </is>
@@ -38350,7 +38435,7 @@
           <t>AAND1BL101RD</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>4016999708 - Изделия из вулканизованной резины, кроме твердой резины, прочие: прочие, прочие</t>
         </is>
@@ -38362,7 +38447,7 @@
           <t>AAND1BL101BL</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>4016999708 - Изделия из вулканизованной резины, кроме твердой резины, прочие: прочие, прочие</t>
         </is>
@@ -38374,7 +38459,7 @@
           <t>AAND1BL102RD</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>4016999708 - Изделия из вулканизованной резины, кроме твердой резины, прочие: прочие, прочие</t>
         </is>
@@ -38386,7 +38471,7 @@
           <t>AAND1BL102BL</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>4016999708 - Изделия из вулканизованной резины, кроме твердой резины, прочие: прочие, прочие</t>
         </is>
@@ -38398,7 +38483,7 @@
           <t>AAND1RP301BG</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>5609000000 - Изделия из нитей или пряжи, плоских или аналогичных нитей товарной позиции 5404 или 5405, бечевка, веревки, канаты или тросы, в другом месте не поименованные</t>
         </is>
@@ -38410,7 +38495,7 @@
           <t>AAND1RP301YL</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>5609000000 - Изделия из нитей или пряжи, плоских или аналогичных нитей товарной позиции 5404 или 5405, бечевка, веревки, канаты или тросы, в другом месте не поименованные</t>
         </is>
@@ -38560,82 +38645,82 @@
       </c>
     </row>
     <row r="2" ht="46" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>Тот же артикул, что на листе «Товары».</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>Выберите одно значение из списка.</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>Максимальная длина режущей части, без учета ручки.</t>
         </is>
       </c>
-      <c r="D2" s="6" t="inlineStr">
+      <c r="D2" s="7" t="inlineStr">
         <is>
           <t>Текстовое описание цвета - заполните, если товар имеет маркетинговое название цвета от поставщика, номер тона или оттенка, например: "№17 Нежная голубая лазурь"</t>
         </is>
       </c>
-      <c r="E2" s="6" t="inlineStr">
+      <c r="E2" s="7" t="inlineStr">
         <is>
           <t>Выберите из списка наиболее подходящий тип товара.</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" s="7" t="inlineStr">
         <is>
           <t>Выберите из списка.</t>
         </is>
       </c>
-      <c r="G2" s="6" t="inlineStr">
+      <c r="G2" s="7" t="inlineStr">
         <is>
           <t>Выберите из списка или укажите вручную.</t>
         </is>
       </c>
-      <c r="H2" s="6" t="inlineStr">
+      <c r="H2" s="7" t="inlineStr">
         <is>
           <t>Выберите из списка или укажите вручную.</t>
         </is>
       </c>
-      <c r="I2" s="6" t="inlineStr">
+      <c r="I2" s="7" t="inlineStr">
         <is>
           <t>Выберите из списка или укажите вручную.</t>
         </is>
       </c>
-      <c r="J2" s="6" t="inlineStr">
+      <c r="J2" s="7" t="inlineStr">
         <is>
           <t>Выберите из списка.</t>
         </is>
       </c>
-      <c r="K2" s="6" t="inlineStr">
+      <c r="K2" s="7" t="inlineStr">
         <is>
           <t>Можно указать только целое число или десятичную дробь.</t>
         </is>
       </c>
-      <c r="L2" s="6" t="inlineStr">
+      <c r="L2" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Миниатюрное изображение, которое заменяет стандартный кружок цвета, например: крупный фрагмент товара, по которому понятен цвет, мазок краски или косметический </t>
         </is>
       </c>
-      <c r="M2" s="6" t="inlineStr">
+      <c r="M2" s="7" t="inlineStr">
         <is>
           <t>Период, в течение которого производитель отвечает за качество товара.</t>
         </is>
       </c>
-      <c r="N2" s="6" t="inlineStr">
+      <c r="N2" s="7" t="inlineStr">
         <is>
           <t>Вес товара без упаковки (нетто) в граммах в расчете на 1 SKU.</t>
         </is>
       </c>
-      <c r="O2" s="6" t="inlineStr">
+      <c r="O2" s="7" t="inlineStr">
         <is>
           <t>Автоматически укажем значение "Фабричное производство", если оставите это поле пустым.</t>
         </is>
       </c>
-      <c r="P2" s="6" t="inlineStr">
+      <c r="P2" s="7" t="inlineStr">
         <is>
           <t>Перечислите, что входит в комплект вместе с товаром: инструкция, чехол, комплект проводов и т.п.</t>
         </is>
@@ -38647,7 +38732,7 @@
           <t>AKTA2KN102YL</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>8211930000 - Прочие ножи с нефиксированными лезвиями</t>
         </is>
@@ -38659,7 +38744,7 @@
           <t>AKTA2KN102GN</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>8211930000 - Прочие ножи с нефиксированными лезвиями</t>
         </is>
@@ -38809,82 +38894,82 @@
       </c>
     </row>
     <row r="2" ht="46" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>Тот же артикул, что на листе «Товары».</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>Выберите одно значение из списка.</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>Выберите из списка наиболее подходящий тип товара.</t>
         </is>
       </c>
-      <c r="D2" s="6" t="inlineStr">
+      <c r="D2" s="7" t="inlineStr">
         <is>
           <t>Количество единиц товара, которое будет продано клиенту за указанную цену.</t>
         </is>
       </c>
-      <c r="E2" s="6" t="inlineStr">
+      <c r="E2" s="7" t="inlineStr">
         <is>
           <t>Вес товара без упаковки (нетто) в граммах в расчете на 1 SKU.</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" s="7" t="inlineStr">
         <is>
           <t>Укажите наименование организации, которая является производителем товара</t>
         </is>
       </c>
-      <c r="G2" s="6" t="inlineStr">
+      <c r="G2" s="7" t="inlineStr">
         <is>
           <t>Если информация о способе применения указана на упаковке или этикетке, то в данном поле информация должна либо дублировать, либо содержать больше данных.</t>
         </is>
       </c>
-      <c r="H2" s="6" t="inlineStr">
+      <c r="H2" s="7" t="inlineStr">
         <is>
           <t>Если состав средства имеет дополнительные особенности, выберите вариант из списка, укажите не более 6 значений.</t>
         </is>
       </c>
-      <c r="I2" s="6" t="inlineStr">
+      <c r="I2" s="7" t="inlineStr">
         <is>
           <t>Автоматически укажем значение "Взрослая", если оставите это поле пустым.</t>
         </is>
       </c>
-      <c r="J2" s="6" t="inlineStr">
+      <c r="J2" s="7" t="inlineStr">
         <is>
           <t>Автоматически укажем значение "Женский", если оставите это поле пустым.</t>
         </is>
       </c>
-      <c r="K2" s="6" t="inlineStr">
+      <c r="K2" s="7" t="inlineStr">
         <is>
           <t>Возрастная категория покупателя, для которого предназначен продукт.</t>
         </is>
       </c>
-      <c r="L2" s="6" t="inlineStr">
+      <c r="L2" s="7" t="inlineStr">
         <is>
           <t>Если на упаковке товара указан не "Объем", а "Вес", то заполните данную характеристику значением на упаковке.</t>
         </is>
       </c>
-      <c r="M2" s="6" t="inlineStr">
+      <c r="M2" s="7" t="inlineStr">
         <is>
           <t>Можно указать только целое число или десятичную дробь.</t>
         </is>
       </c>
-      <c r="N2" s="6" t="inlineStr">
+      <c r="N2" s="7" t="inlineStr">
         <is>
           <t>Выберите не больше 2 подходящих значений из списка.</t>
         </is>
       </c>
-      <c r="O2" s="6" t="inlineStr">
+      <c r="O2" s="7" t="inlineStr">
         <is>
           <t>Признак для товаров, которые содержат эротику, сцены секса, изображения с нецензурными выражениями, даже если они написаны частично или со спец.</t>
         </is>
       </c>
-      <c r="P2" s="6" t="inlineStr">
+      <c r="P2" s="7" t="inlineStr">
         <is>
           <t>Срок годности, установленный производителем.</t>
         </is>
@@ -39025,62 +39110,62 @@
       </c>
     </row>
     <row r="2" ht="46" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>Тот же артикул, что на листе «Товары».</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>Выберите одно значение из списка.</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>Можно указать только целое число или десятичную дробь.</t>
         </is>
       </c>
-      <c r="D2" s="6" t="inlineStr">
+      <c r="D2" s="7" t="inlineStr">
         <is>
           <t>Можно указать только целое число.</t>
         </is>
       </c>
-      <c r="E2" s="6" t="inlineStr">
+      <c r="E2" s="7" t="inlineStr">
         <is>
           <t>Выберите из списка наиболее подходящий тип товара.</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" s="7" t="inlineStr">
         <is>
           <t>Вес товара без упаковки (нетто) в граммах в расчете на 1 SKU.</t>
         </is>
       </c>
-      <c r="G2" s="6" t="inlineStr">
+      <c r="G2" s="7" t="inlineStr">
         <is>
           <t>Можно указать только целое число или десятичную дробь.</t>
         </is>
       </c>
-      <c r="H2" s="6" t="inlineStr">
+      <c r="H2" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Миниатюрное изображение, которое заменяет стандартный кружок цвета, например: крупный фрагмент товара, по которому понятен цвет, мазок краски или косметический </t>
         </is>
       </c>
-      <c r="I2" s="6" t="inlineStr">
+      <c r="I2" s="7" t="inlineStr">
         <is>
           <t>Основной материал изделия.</t>
         </is>
       </c>
-      <c r="J2" s="6" t="inlineStr">
+      <c r="J2" s="7" t="inlineStr">
         <is>
           <t>Период, в течение которого производитель отвечает за качество товара.</t>
         </is>
       </c>
-      <c r="K2" s="6" t="inlineStr">
+      <c r="K2" s="7" t="inlineStr">
         <is>
           <t>Автоматически укажем значение "Фабричное производство", если оставите это поле пустым.</t>
         </is>
       </c>
-      <c r="L2" s="6" t="inlineStr">
+      <c r="L2" s="7" t="inlineStr">
         <is>
           <t>Перечислите, что входит в комплект вместе с товаром: инструкция, чехол, комплект проводов и т.п.</t>
         </is>
@@ -39092,7 +39177,7 @@
           <t>AHMA7BW101BG</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>6307909800 - Прочие готовые изделия, включая выкройки одежды</t>
         </is>
@@ -39104,7 +39189,7 @@
           <t>AHMA1BW101BG</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>6307909800 - Прочие готовые изделия, включая выкройки одежды</t>
         </is>
@@ -39116,7 +39201,7 @@
           <t>AHMA3BW101BG</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>6307909800 - Прочие готовые изделия, включая выкройки одежды</t>
         </is>
@@ -39128,7 +39213,7 @@
           <t>AHMA3BW102BG</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>6307909800 - Прочие готовые изделия, включая выкройки одежды</t>
         </is>
@@ -39140,7 +39225,7 @@
           <t>AHMA3BW201WH</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>6307909800 - Прочие готовые изделия, включая выкройки одежды</t>
         </is>
@@ -39159,7 +39244,7 @@
           <t>AHMA2BW201WH</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>6307909800 - Прочие готовые изделия, включая выкройки одежды</t>
         </is>
@@ -39178,7 +39263,7 @@
           <t>AHMA1BW112WH</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>6307909800 - Прочие готовые изделия, включая выкройки одежды</t>
         </is>
@@ -39190,7 +39275,7 @@
           <t>AHMA1BW111WH</t>
         </is>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>6307909800 - Прочие готовые изделия, включая выкройки одежды</t>
         </is>
@@ -39202,7 +39287,7 @@
           <t>AHMA1BW302WH</t>
         </is>
       </c>
-      <c r="B13" s="9" t="inlineStr">
+      <c r="B13" s="10" t="inlineStr">
         <is>
           <t>6307909800 - Прочие готовые изделия, включая выкройки одежды</t>
         </is>
@@ -39331,77 +39416,77 @@
       </c>
     </row>
     <row r="2" ht="46" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>Тот же артикул, что на листе «Товары».</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>Выберите одно значение из списка.</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>Можно указать только целое число.</t>
         </is>
       </c>
-      <c r="D2" s="6" t="inlineStr">
+      <c r="D2" s="7" t="inlineStr">
         <is>
           <t>Текстовое описание цвета - заполните, если товар имеет маркетинговое название цвета от поставщика, номер тона или оттенка, например: "№17 Нежная голубая лазурь"</t>
         </is>
       </c>
-      <c r="E2" s="6" t="inlineStr">
+      <c r="E2" s="7" t="inlineStr">
         <is>
           <t>Выберите из списка наиболее подходящий тип товара.</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" s="7" t="inlineStr">
         <is>
           <t>Выберите из списка или укажите вручную.</t>
         </is>
       </c>
-      <c r="G2" s="6" t="inlineStr">
+      <c r="G2" s="7" t="inlineStr">
         <is>
           <t>Выберите одно или несколько значений из списка, но не больше 6.</t>
         </is>
       </c>
-      <c r="H2" s="6" t="inlineStr">
+      <c r="H2" s="7" t="inlineStr">
         <is>
           <t>Выберите из списка.</t>
         </is>
       </c>
-      <c r="I2" s="6" t="inlineStr">
+      <c r="I2" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Миниатюрное изображение, которое заменяет стандартный кружок цвета, например: крупный фрагмент товара, по которому понятен цвет, мазок краски или косметический </t>
         </is>
       </c>
-      <c r="J2" s="6" t="inlineStr">
+      <c r="J2" s="7" t="inlineStr">
         <is>
           <t>Основной материал изделия.</t>
         </is>
       </c>
-      <c r="K2" s="6" t="inlineStr">
+      <c r="K2" s="7" t="inlineStr">
         <is>
           <t>Признак для товаров, которые содержат эротику, сцены секса, изображения с нецензурными выражениями, даже если они написаны частично или со спец.</t>
         </is>
       </c>
-      <c r="L2" s="6" t="inlineStr">
+      <c r="L2" s="7" t="inlineStr">
         <is>
           <t>Период, в течение которого производитель отвечает за качество товара.</t>
         </is>
       </c>
-      <c r="M2" s="6" t="inlineStr">
+      <c r="M2" s="7" t="inlineStr">
         <is>
           <t>Вес товара без упаковки (нетто) в граммах в расчете на 1 SKU.</t>
         </is>
       </c>
-      <c r="N2" s="6" t="inlineStr">
+      <c r="N2" s="7" t="inlineStr">
         <is>
           <t>Автоматически укажем значение "Фабричное производство", если оставите это поле пустым.</t>
         </is>
       </c>
-      <c r="O2" s="6" t="inlineStr">
+      <c r="O2" s="7" t="inlineStr">
         <is>
           <t>Перечислите, что входит в комплект вместе с товаром: инструкция, чехол, комплект проводов и т.п.</t>
         </is>
@@ -39413,7 +39498,7 @@
           <t>AKTA4ST101CL</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>3923509000 - Прочие пробки, крышки, колпаки и другие укупорочные средства, из пластмасс</t>
         </is>
@@ -39425,7 +39510,7 @@
           <t>AKTA4ST103CL</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>3923509000 - Прочие пробки, крышки, колпаки и другие укупорочные средства, из пластмасс</t>
         </is>

--- a/docs/ozon/Озон_рабочая_книга.xlsx
+++ b/docs/ozon/Озон_рабочая_книга.xlsx
@@ -22,8 +22,11 @@
     <sheet name="Фитнес и йога" sheetId="13" state="visible" r:id="rId13"/>
     <sheet name="Шпатель-скребок кондитерский" sheetId="14" state="visible" r:id="rId14"/>
     <sheet name="Без категории" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Ядро (черновик с WB)" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'Ядро (черновик с WB)'!$A$1:$I$322</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -71,7 +74,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -113,6 +116,11 @@
         <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C55A11"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -131,7 +139,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -156,6 +164,15 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2410,6 +2427,5943 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I322"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t>Категория Ozon</t>
+        </is>
+      </c>
+      <c r="B1" s="12" t="inlineStr">
+        <is>
+          <t>Запрос</t>
+        </is>
+      </c>
+      <c r="C1" s="12" t="inlineStr">
+        <is>
+          <t>Приоритет (частота WB)</t>
+        </is>
+      </c>
+      <c r="D1" s="12" t="inlineStr">
+        <is>
+          <t>SKU на WB</t>
+        </is>
+      </c>
+      <c r="E1" s="13" t="inlineStr">
+        <is>
+          <t>Есть на Ozon?</t>
+        </is>
+      </c>
+      <c r="F1" s="13" t="inlineStr">
+        <is>
+          <t>Частота Ozon</t>
+        </is>
+      </c>
+      <c r="G1" s="13" t="inlineStr">
+        <is>
+          <t>В корзину, %</t>
+        </is>
+      </c>
+      <c r="H1" s="12" t="inlineStr">
+        <is>
+          <t>Риск</t>
+        </is>
+      </c>
+      <c r="I1" s="12" t="inlineStr">
+        <is>
+          <t>Куда кладём</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="54" customHeight="1">
+      <c r="A2" s="14" t="inlineStr"/>
+      <c r="B2" s="14" t="inlineStr"/>
+      <c r="C2" s="14" t="inlineStr">
+        <is>
+          <t>НЕ частота Ozon. WB считает показы за 30 дней, Ozon — уникальных людей за 7. Числа несопоставимы, это только порядок проверки.</t>
+        </is>
+      </c>
+      <c r="D2" s="14" t="inlineStr">
+        <is>
+          <t>Сколько наших карточек ранжировалось по запросу на WB.</t>
+        </is>
+      </c>
+      <c r="E2" s="14" t="inlineStr">
+        <is>
+          <t>ЗАПОЛНЯЕТЕ ВЫ. да / нет — по отчёту «Аналитика → Поисковые запросы».</t>
+        </is>
+      </c>
+      <c r="F2" s="14" t="inlineStr">
+        <is>
+          <t>ЗАПОЛНЯЕТЕ ВЫ. Число из отчёта Ozon.</t>
+        </is>
+      </c>
+      <c r="G2" s="14" t="inlineStr">
+        <is>
+          <t>ЗАПОЛНЯЕТЕ ВЫ. Доля добавлений в корзину из отчёта Ozon.</t>
+        </is>
+      </c>
+      <c r="H2" s="14" t="inlineStr">
+        <is>
+          <t>Запрос уводит товар в чужую категорию или под маркировку. Не вносить без разбора.</t>
+        </is>
+      </c>
+      <c r="I2" s="14" t="inlineStr">
+        <is>
+          <t>Название / характеристики / хештег. Заполняется после сверки.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Аксессуар для массажа</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>массажер для шеи</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>177872</v>
+      </c>
+      <c r="D3" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Аксессуар для массажа</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>массажер для тела</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>158637</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Аксессуар для массажа</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>массаж</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>28782</v>
+      </c>
+      <c r="D5" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Аксессуар для массажа</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>массажер для рук</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>15237</v>
+      </c>
+      <c r="D6" t="n">
+        <v>6</v>
+      </c>
+      <c r="H6" s="9" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Аксессуар для массажа</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>тренажер для спины</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>15233</v>
+      </c>
+      <c r="D7" t="n">
+        <v>3</v>
+      </c>
+      <c r="H7" s="9" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Аксессуар для массажа</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>массажер для тела ручной</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>12995</v>
+      </c>
+      <c r="D8" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Аксессуар для массажа</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>тренажер для шеи</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>11069</v>
+      </c>
+      <c r="D9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H9" s="9" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Аксессуар для массажа</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>су джок</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>11025</v>
+      </c>
+      <c r="D10" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Аксессуар для массажа</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>массажер для спины и шеи</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>9863</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Аксессуар для массажа</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>массажер для стоп</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>8732</v>
+      </c>
+      <c r="D12" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Аксессуар для массажа</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>роликовый массажер для тела</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>8480</v>
+      </c>
+      <c r="D13" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Аксессуар для массажа</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>от отеков тела</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>7653</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="9" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Аксессуар для массажа</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>массажер для шеи ручной</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>7479</v>
+      </c>
+      <c r="D15" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Аксессуар для массажа</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>пилатес</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>6590</v>
+      </c>
+      <c r="D16" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Аксессуар для массажа</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>массажер от целлюлита ручной</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>6530</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Аксессуар для массажа</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>для фитнеса инвентарь</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>6260</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Аксессуар для массажа</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>массажный ролик для тела</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>4962</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Аксессуар для массажа</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>массажер роликовый</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>4957</v>
+      </c>
+      <c r="D20" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Аксессуар для массажа</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>массажер для спины ручной</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>4525</v>
+      </c>
+      <c r="D21" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Аксессуар для массажа</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>тренажер для ног и рук</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>4008</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Аксессуар для массажа</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>массажер для пальцев рук</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>3684</v>
+      </c>
+      <c r="D23" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Аксессуар для массажа</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>тренажер для стоп</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>3579</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2</v>
+      </c>
+      <c r="H24" s="9" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Аксессуар для массажа</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>массажер для рук и пальцев</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>3285</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Аксессуар для массажа</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>ролик для массажа тела</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>2978</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Аксессуар для массажа</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>для массажа тела</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>2935</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Аксессуар для массажа</t>
+        </is>
+      </c>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>массажный аппарат</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>2793</v>
+      </c>
+      <c r="D28" t="n">
+        <v>3</v>
+      </c>
+      <c r="H28" s="9" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Аксессуар для массажа</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>для пилатеса</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>2700</v>
+      </c>
+      <c r="D29" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Аксессуар для массажа</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>массажер для пальцев</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>2581</v>
+      </c>
+      <c r="D30" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Аксессуар для массажа</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>тренажер для кисти</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>2423</v>
+      </c>
+      <c r="D31" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Аксессуар для массажа</t>
+        </is>
+      </c>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>массажер от отеков</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>2345</v>
+      </c>
+      <c r="D32" t="n">
+        <v>2</v>
+      </c>
+      <c r="H32" s="9" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Аксессуар для массажа</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>массажер для тела антицеллюлитный ручной</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>2188</v>
+      </c>
+      <c r="D33" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Аксессуар для массажа</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>ежики для массажа</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>2103</v>
+      </c>
+      <c r="D34" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Аксессуар для массажа</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>тренажер для пальцев</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>2076</v>
+      </c>
+      <c r="D35" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Аксессуар для массажа</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>мини массажер</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>1955</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Аксессуар для массажа</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>массажер для тела ручной роликовый</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>1909</v>
+      </c>
+      <c r="D37" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Аксессуар для массажа</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>массажер для ступней</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>1790</v>
+      </c>
+      <c r="D38" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Аксессуар для массажа</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>антицеллюлитный массажер роликовый</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>1711</v>
+      </c>
+      <c r="D39" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Аксессуар для массажа</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>массажер для спины роликовый</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>1705</v>
+      </c>
+      <c r="D40" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Аксессуар для массажа</t>
+        </is>
+      </c>
+      <c r="B41" s="9" t="inlineStr">
+        <is>
+          <t>массажер для коленей</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>1535</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1</v>
+      </c>
+      <c r="H41" s="9" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Аксессуар для массажа</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>массажер для шеи ручной роликовый</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>1510</v>
+      </c>
+      <c r="D42" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Аксессуар для массажа</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>су джок массажер</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>1410</v>
+      </c>
+      <c r="D43" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Аксессуар для массажа</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>тренажер для рук кистевой</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>1315</v>
+      </c>
+      <c r="D44" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Аксессуар для массажа</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>массажер для ног игольчатый</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>1300</v>
+      </c>
+      <c r="D45" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Аксессуар для массажа</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>массажер для ног антицеллюлитный</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>1271</v>
+      </c>
+      <c r="D46" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Аксессуар для массажа</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>массажер для стоп с шипами</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>1220</v>
+      </c>
+      <c r="D47" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Аксессуар для массажа</t>
+        </is>
+      </c>
+      <c r="B48" s="9" t="inlineStr">
+        <is>
+          <t>от плоскостопия массажер</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>1215</v>
+      </c>
+      <c r="D48" t="n">
+        <v>4</v>
+      </c>
+      <c r="H48" s="9" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Аксессуар для массажа</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>массажер ручной роликовый</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>1205</v>
+      </c>
+      <c r="D49" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Аксессуар для массажа</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>массажер для тела ручной с шипами</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>1130</v>
+      </c>
+      <c r="D50" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Аксессуар для массажа</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>лимфодренажный ролик</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>1110</v>
+      </c>
+      <c r="D51" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Аксессуар для массажа</t>
+        </is>
+      </c>
+      <c r="B52" s="9" t="inlineStr">
+        <is>
+          <t>механический массажер</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>1108</v>
+      </c>
+      <c r="D52" t="n">
+        <v>7</v>
+      </c>
+      <c r="H52" s="9" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Аксессуар для массажа</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>массажер шеи</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>1080</v>
+      </c>
+      <c r="D53" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Аксессуар для массажа</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>антицеллюлитный роликовый массажер для тела</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>950</v>
+      </c>
+      <c r="D54" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Аксессуар для массажа</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>массажер роликовый для шеи</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>895</v>
+      </c>
+      <c r="D55" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Аксессуар для массажа</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>массажер для шеи и плеч ручной</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>892</v>
+      </c>
+      <c r="D56" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Аксессуар для массажа</t>
+        </is>
+      </c>
+      <c r="B57" s="9" t="inlineStr">
+        <is>
+          <t>лимфодренажный тренажер</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>845</v>
+      </c>
+      <c r="D57" t="n">
+        <v>3</v>
+      </c>
+      <c r="H57" s="9" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Игрушка для животных</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>мячик для собак</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>25185</v>
+      </c>
+      <c r="D58" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Игрушка для животных</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>игрушки для собак крупных пород</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>21173</v>
+      </c>
+      <c r="D59" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Игрушка для животных</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>игрушки для собак средних пород</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>10210</v>
+      </c>
+      <c r="D60" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Игрушка для животных</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>ошейник для собак товары для животных</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>6258</v>
+      </c>
+      <c r="D61" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Игрушка для животных</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>канат для собак</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>5331</v>
+      </c>
+      <c r="D62" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Игрушка для животных</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>для крупных пород</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>4675</v>
+      </c>
+      <c r="D63" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Игрушка для животных</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>резиновые игрушки для собак</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>4127</v>
+      </c>
+      <c r="D64" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Игрушка для животных</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>игрушки для собак крупных пород прочные</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>3620</v>
+      </c>
+      <c r="D65" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Игрушка для животных</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>мячик для собак мелких пород</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>3285</v>
+      </c>
+      <c r="D66" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Игрушка для животных</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>прочная игрушка для собак</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>2343</v>
+      </c>
+      <c r="D67" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Игрушка для животных</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>игрушки для собак мячик</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>2142</v>
+      </c>
+      <c r="D68" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Игрушка для животных</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>мяч для собак прочный</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>2118</v>
+      </c>
+      <c r="D69" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Игрушка для животных</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>для мелких и средних пород</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>2005</v>
+      </c>
+      <c r="D70" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Игрушка для животных</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>мячик для собак крупных пород</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>1985</v>
+      </c>
+      <c r="D71" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Игрушка для животных</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>мячики для животных</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>1883</v>
+      </c>
+      <c r="D72" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Игрушка для животных</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>игрушки для собак средних пород прочные</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>1670</v>
+      </c>
+      <c r="D73" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Игрушка для животных</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>игрушка для зубов собаке</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>1608</v>
+      </c>
+      <c r="D74" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Игрушка для животных</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>неуловимое яйцо для собак</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1575</v>
+      </c>
+      <c r="D75" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Игрушка для животных</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>мяч для собак суперпрочный</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>1505</v>
+      </c>
+      <c r="D76" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Игрушка для животных</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>резиновый мячик для собак</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>1505</v>
+      </c>
+      <c r="D77" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Игрушка для животных</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>жевательная игрушка для собак</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>1353</v>
+      </c>
+      <c r="D78" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Игрушка для животных</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>антивандальная игрушка для собак</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>1330</v>
+      </c>
+      <c r="D79" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Игрушка для животных</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>игрушка для собак веревка</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>1327</v>
+      </c>
+      <c r="D80" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Игрушка для животных</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>мяч на веревке для собак</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>1150</v>
+      </c>
+      <c r="D81" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Игрушка для животных</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>канат для собак крупных пород</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>1105</v>
+      </c>
+      <c r="D82" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Игрушка для животных</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>игрушки для больших собак прочные</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>1077</v>
+      </c>
+      <c r="D83" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Игрушка для животных</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>для собак грызть</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>1022</v>
+      </c>
+      <c r="D84" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Игрушка для животных</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>игрушка для собак крупных пород крепкие</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>970</v>
+      </c>
+      <c r="D85" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Игрушка для животных</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>мячик для собак крупных пород прочный</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>855</v>
+      </c>
+      <c r="D86" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Игрушка для животных</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>канат для крупных собак</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>740</v>
+      </c>
+      <c r="D87" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Игрушка для животных</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>товары для собак крупных пород</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>698</v>
+      </c>
+      <c r="D88" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Кухонный нож</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>нож для пиццы</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>27065</v>
+      </c>
+      <c r="D89" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Кухонный нож</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>открывашка</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>26224</v>
+      </c>
+      <c r="D90" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Кухонный нож</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>нож для теста</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>13701</v>
+      </c>
+      <c r="D91" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Кухонный нож</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>консервный нож</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>11250</v>
+      </c>
+      <c r="D92" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Кухонный нож</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>открывашка для консервов и банок</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>6930</v>
+      </c>
+      <c r="D93" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Кухонный нож</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>нож для пиццы и теста</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>4074</v>
+      </c>
+      <c r="D94" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Кухонный нож</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>тесторезка</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>3758</v>
+      </c>
+      <c r="D95" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Кухонный нож</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>нож для теста пластиковый</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>3712</v>
+      </c>
+      <c r="D96" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Кухонный нож</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>для пиццы</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>3658</v>
+      </c>
+      <c r="D97" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Кухонный нож</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>нож для торта</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>3437</v>
+      </c>
+      <c r="D98" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Кухонный нож</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>открывашка для консервных банок</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>3380</v>
+      </c>
+      <c r="D99" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Кухонный нож</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>кондитерский нож</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>2406</v>
+      </c>
+      <c r="D100" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Кухонный нож</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>консервный нож открывашка</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>2345</v>
+      </c>
+      <c r="D101" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Кухонный нож</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>нож для резки теста</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>2333</v>
+      </c>
+      <c r="D102" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Кухонный нож</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>нож для теста пластиковый для резки</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>2128</v>
+      </c>
+      <c r="D103" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Кухонный нож</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>резак для теста</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>1911</v>
+      </c>
+      <c r="D104" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Кухонный нож</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>нож для торта кондитерский</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>1650</v>
+      </c>
+      <c r="D105" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Кухонный нож</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>нож для пиццы xiaomi</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>1380</v>
+      </c>
+      <c r="D106" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Кухонный нож</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>открывашка для консервов и банок универсальная</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>1315</v>
+      </c>
+      <c r="D107" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Кухонный нож</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>пиццерезка</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>1275</v>
+      </c>
+      <c r="D108" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Кухонный нож</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>открывашка для консервов универсальная</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>1230</v>
+      </c>
+      <c r="D109" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Кухонный нож</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>консервный нож для банок и консервов</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>1140</v>
+      </c>
+      <c r="D110" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Кухонный нож</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>тесторезка для теста</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>1085</v>
+      </c>
+      <c r="D111" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Кухонный нож</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>открывашка для банок консервных</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>1065</v>
+      </c>
+      <c r="D112" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Кухонный нож</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>нож для консервных банок</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>725</v>
+      </c>
+      <c r="D113" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Маска-бандаж</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>бандаж для лица</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>43190</v>
+      </c>
+      <c r="D114" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Маска-бандаж</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>бандаж</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>31450</v>
+      </c>
+      <c r="D115" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Маска-бандаж</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>подтяжка лица</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>10575</v>
+      </c>
+      <c r="D116" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Маска-бандаж</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>бандаж для лица и подбородка</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>7955</v>
+      </c>
+      <c r="D117" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Маска-бандаж</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>пластырь для подтяжки лица прозрачный</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>5050</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Маска-бандаж</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>для подбородка подтяжка</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>4775</v>
+      </c>
+      <c r="D119" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Маска-бандаж</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>маска для подбородка</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>4664</v>
+      </c>
+      <c r="D120" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Маска-бандаж</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>убрать второй подбородок</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>4180</v>
+      </c>
+      <c r="D121" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Маска-бандаж</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>силиконовая маска корсет для лица</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>3903</v>
+      </c>
+      <c r="D122" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Маска-бандаж</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>маска от второго подбородка</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>3850</v>
+      </c>
+      <c r="D123" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Маска-бандаж</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>маска бандаж для лица</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>3724</v>
+      </c>
+      <c r="D124" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Маска-бандаж</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>бандаж для подбородка</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>3546</v>
+      </c>
+      <c r="D125" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Маска-бандаж</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>от второго подбородка бандаж</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>2910</v>
+      </c>
+      <c r="D126" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Маска-бандаж</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>для подбородка</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>2796</v>
+      </c>
+      <c r="D127" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Маска-бандаж</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>силиконовая маска для лица многоразовая косметическая</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>2762</v>
+      </c>
+      <c r="D128" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Маска-бандаж</t>
+        </is>
+      </c>
+      <c r="B129" s="9" t="inlineStr">
+        <is>
+          <t>тренажер для лица</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>2620</v>
+      </c>
+      <c r="D129" t="n">
+        <v>3</v>
+      </c>
+      <c r="H129" s="9" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Маска-бандаж</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>бандаж для овала лица</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>2610</v>
+      </c>
+      <c r="D130" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Маска-бандаж</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>силиконовая маска для лица доктор хос</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>2470</v>
+      </c>
+      <c r="D131" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Маска-бандаж</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>повязка на лицо</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>2305</v>
+      </c>
+      <c r="D132" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Маска-бандаж</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>лифтинг для лица</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>2200</v>
+      </c>
+      <c r="D133" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Маска-бандаж</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>повязка на шею</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>2055</v>
+      </c>
+      <c r="D134" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Маска-бандаж</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>повязка для подбородка</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>2017</v>
+      </c>
+      <c r="D135" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Маска-бандаж</t>
+        </is>
+      </c>
+      <c r="B136" s="9" t="inlineStr">
+        <is>
+          <t>тренажер для челюсти</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>2007</v>
+      </c>
+      <c r="D136" t="n">
+        <v>1</v>
+      </c>
+      <c r="H136" s="9" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Маска-бандаж</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>подтяжка для подбородка и шеи</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>1910</v>
+      </c>
+      <c r="D137" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Маска-бандаж</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>подбородок убрать</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>1410</v>
+      </c>
+      <c r="D138" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Маска-бандаж</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>бандаж для лица и подбородка многоразовый</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>1385</v>
+      </c>
+      <c r="D139" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Маска-бандаж</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>лифтинг эффект для лица</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>1249</v>
+      </c>
+      <c r="D140" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Маска-бандаж</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>маска бандаж</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>1205</v>
+      </c>
+      <c r="D141" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Маска-бандаж</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>маска для шеи и декольте от морщин</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>1140</v>
+      </c>
+      <c r="D142" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Маска-бандаж</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>для подтяжки подбородка</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>1060</v>
+      </c>
+      <c r="D143" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Маска-бандаж</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>второй подбородок</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>1046</v>
+      </c>
+      <c r="D144" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Мешок для стирки</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>мешок для стирки</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>39267</v>
+      </c>
+      <c r="D145" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Мешок для стирки</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>для стирки</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
+        <v>31911</v>
+      </c>
+      <c r="D146" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Мешок для стирки</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>стирка</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
+        <v>14340</v>
+      </c>
+      <c r="D147" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Мешок для стирки</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>мешок для стирки бюстгальтера</t>
+        </is>
+      </c>
+      <c r="C148" t="n">
+        <v>11298</v>
+      </c>
+      <c r="D148" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Мешок для стирки</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>мешок для стирки белья</t>
+        </is>
+      </c>
+      <c r="C149" t="n">
+        <v>7230</v>
+      </c>
+      <c r="D149" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Мешок для стирки</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>сетка для стирки белья в машинке</t>
+        </is>
+      </c>
+      <c r="C150" t="n">
+        <v>4050</v>
+      </c>
+      <c r="D150" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Мешок для стирки</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>для стирки бюстгальтера</t>
+        </is>
+      </c>
+      <c r="C151" t="n">
+        <v>3252</v>
+      </c>
+      <c r="D151" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Мешок для стирки</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>мешки сетка</t>
+        </is>
+      </c>
+      <c r="C152" t="n">
+        <v>2925</v>
+      </c>
+      <c r="D152" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Мешок для стирки</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>набор для стирки</t>
+        </is>
+      </c>
+      <c r="C153" t="n">
+        <v>2870</v>
+      </c>
+      <c r="D153" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Мешок для стирки</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>мешки для стирки белья в стиральной машине</t>
+        </is>
+      </c>
+      <c r="C154" t="n">
+        <v>2680</v>
+      </c>
+      <c r="D154" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Мешок для стирки</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>мешок для белья</t>
+        </is>
+      </c>
+      <c r="C155" t="n">
+        <v>2406</v>
+      </c>
+      <c r="D155" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Мешок для стирки</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>мешок для стирки нижнего белья</t>
+        </is>
+      </c>
+      <c r="C156" t="n">
+        <v>2394</v>
+      </c>
+      <c r="D156" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Мешок для стирки</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>сетка для стирки</t>
+        </is>
+      </c>
+      <c r="C157" t="n">
+        <v>2220</v>
+      </c>
+      <c r="D157" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Мешок для стирки</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>чехол для стирки бюстгальтера</t>
+        </is>
+      </c>
+      <c r="C158" t="n">
+        <v>2080</v>
+      </c>
+      <c r="D158" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Мешок для стирки</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>мешок для стирки одежды</t>
+        </is>
+      </c>
+      <c r="C159" t="n">
+        <v>2055</v>
+      </c>
+      <c r="D159" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Мешок для стирки</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>мешок для стирки большой</t>
+        </is>
+      </c>
+      <c r="C160" t="n">
+        <v>1720</v>
+      </c>
+      <c r="D160" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Мешок для стирки</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>чехол для стирки нижнего белья</t>
+        </is>
+      </c>
+      <c r="C161" t="n">
+        <v>1428</v>
+      </c>
+      <c r="D161" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Мешок для стирки</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>мешок для стирки бюстгальтера в стиральной машине</t>
+        </is>
+      </c>
+      <c r="C162" t="n">
+        <v>1260</v>
+      </c>
+      <c r="D162" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Мешок для стирки</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>мешок для стирки носков</t>
+        </is>
+      </c>
+      <c r="C163" t="n">
+        <v>1172</v>
+      </c>
+      <c r="D163" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Мешок для стирки</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>мешочки для стирки в машинке</t>
+        </is>
+      </c>
+      <c r="C164" t="n">
+        <v>1135</v>
+      </c>
+      <c r="D164" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Мешок для стирки</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>для стирки носков</t>
+        </is>
+      </c>
+      <c r="C165" t="n">
+        <v>993</v>
+      </c>
+      <c r="D165" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Мешок для стирки</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>мешочек для стирки вещей</t>
+        </is>
+      </c>
+      <c r="C166" t="n">
+        <v>936</v>
+      </c>
+      <c r="D166" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Мешок для стирки</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>чехол для стирки</t>
+        </is>
+      </c>
+      <c r="C167" t="n">
+        <v>905</v>
+      </c>
+      <c r="D167" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Мешок для стирки</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>пакет для стирки</t>
+        </is>
+      </c>
+      <c r="C168" t="n">
+        <v>815</v>
+      </c>
+      <c r="D168" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Мешок для стирки</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>контейнер для стирки</t>
+        </is>
+      </c>
+      <c r="C169" t="n">
+        <v>785</v>
+      </c>
+      <c r="D169" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Пробка</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>пробка для бутылки</t>
+        </is>
+      </c>
+      <c r="C170" t="n">
+        <v>14788</v>
+      </c>
+      <c r="D170" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Пробка</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>пробка</t>
+        </is>
+      </c>
+      <c r="C171" t="n">
+        <v>11989</v>
+      </c>
+      <c r="D171" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Пробка</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>пробка для вина</t>
+        </is>
+      </c>
+      <c r="C172" t="n">
+        <v>11850</v>
+      </c>
+      <c r="D172" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Пробка</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>насадки для бутылки со вкусами</t>
+        </is>
+      </c>
+      <c r="C173" t="n">
+        <v>7310</v>
+      </c>
+      <c r="D173" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Пробка</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>пробка для шампанского</t>
+        </is>
+      </c>
+      <c r="C174" t="n">
+        <v>7305</v>
+      </c>
+      <c r="D174" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Пробка</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>вакуумная пробка для вина</t>
+        </is>
+      </c>
+      <c r="C175" t="n">
+        <v>3535</v>
+      </c>
+      <c r="D175" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Пробка</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>пробка для бутылки силиконовая</t>
+        </is>
+      </c>
+      <c r="C176" t="n">
+        <v>2115</v>
+      </c>
+      <c r="D176" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Пробка</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>пробка для бутылки вина</t>
+        </is>
+      </c>
+      <c r="C177" t="n">
+        <v>1815</v>
+      </c>
+      <c r="D177" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Пробка</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>пробка для бутылки масла</t>
+        </is>
+      </c>
+      <c r="C178" t="n">
+        <v>1815</v>
+      </c>
+      <c r="D178" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Пробка</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>для бутылок</t>
+        </is>
+      </c>
+      <c r="C179" t="n">
+        <v>1780</v>
+      </c>
+      <c r="D179" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Пробка</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>насадки для бутылки со вкусами набор</t>
+        </is>
+      </c>
+      <c r="C180" t="n">
+        <v>1765</v>
+      </c>
+      <c r="D180" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Пробка</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>пробка для вина многоразовая</t>
+        </is>
+      </c>
+      <c r="C181" t="n">
+        <v>1645</v>
+      </c>
+      <c r="D181" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Пробка</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>для домашнего вина</t>
+        </is>
+      </c>
+      <c r="C182" t="n">
+        <v>1375</v>
+      </c>
+      <c r="D182" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Пробка</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>пробка для шампанского многоразовая</t>
+        </is>
+      </c>
+      <c r="C183" t="n">
+        <v>1360</v>
+      </c>
+      <c r="D183" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Пробка</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>пробки для бутылок новогодние</t>
+        </is>
+      </c>
+      <c r="C184" t="n">
+        <v>1275</v>
+      </c>
+      <c r="D184" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Пробка</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>пробка резиновая для колбы</t>
+        </is>
+      </c>
+      <c r="C185" t="n">
+        <v>1043</v>
+      </c>
+      <c r="D185" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Пробка</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>пробки на бутыли</t>
+        </is>
+      </c>
+      <c r="C186" t="n">
+        <v>1015</v>
+      </c>
+      <c r="D186" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Пробка</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>насадка на бутылку для масла</t>
+        </is>
+      </c>
+      <c r="C187" t="n">
+        <v>980</v>
+      </c>
+      <c r="D187" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Пробка</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>крышка для бутылки вина</t>
+        </is>
+      </c>
+      <c r="C188" t="n">
+        <v>928</v>
+      </c>
+      <c r="D188" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Спортивный массажный мяч</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>мячик массажный</t>
+        </is>
+      </c>
+      <c r="C189" t="n">
+        <v>59435</v>
+      </c>
+      <c r="D189" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Спортивный массажный мяч</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>мяч для пилатеса</t>
+        </is>
+      </c>
+      <c r="C190" t="n">
+        <v>22715</v>
+      </c>
+      <c r="D190" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Спортивный массажный мяч</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>мяч массажный с шипами</t>
+        </is>
+      </c>
+      <c r="C191" t="n">
+        <v>12718</v>
+      </c>
+      <c r="D191" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Спортивный массажный мяч</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>шарик для массажа</t>
+        </is>
+      </c>
+      <c r="C192" t="n">
+        <v>11810</v>
+      </c>
+      <c r="D192" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Спортивный массажный мяч</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>мфр мяч</t>
+        </is>
+      </c>
+      <c r="C193" t="n">
+        <v>11026</v>
+      </c>
+      <c r="D193" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Спортивный массажный мяч</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>суджок-шарик</t>
+        </is>
+      </c>
+      <c r="C194" t="n">
+        <v>8302</v>
+      </c>
+      <c r="D194" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Спортивный массажный мяч</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>мячи для йоги</t>
+        </is>
+      </c>
+      <c r="C195" t="n">
+        <v>7573</v>
+      </c>
+      <c r="D195" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Спортивный массажный мяч</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>мяч для мфр</t>
+        </is>
+      </c>
+      <c r="C196" t="n">
+        <v>7121</v>
+      </c>
+      <c r="D196" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Спортивный массажный мяч</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>теннисный мяч для массажа</t>
+        </is>
+      </c>
+      <c r="C197" t="n">
+        <v>6460</v>
+      </c>
+      <c r="D197" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Спортивный массажный мяч</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>мфр</t>
+        </is>
+      </c>
+      <c r="C198" t="n">
+        <v>6161</v>
+      </c>
+      <c r="D198" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Спортивный массажный мяч</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>мячик массажный для стоп</t>
+        </is>
+      </c>
+      <c r="C199" t="n">
+        <v>5148</v>
+      </c>
+      <c r="D199" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Спортивный массажный мяч</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>мяч массажный для детей</t>
+        </is>
+      </c>
+      <c r="C200" t="n">
+        <v>4984</v>
+      </c>
+      <c r="D200" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Спортивный массажный мяч</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>тактильные мячики</t>
+        </is>
+      </c>
+      <c r="C201" t="n">
+        <v>4867</v>
+      </c>
+      <c r="D201" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Спортивный массажный мяч</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>мячик для стоп</t>
+        </is>
+      </c>
+      <c r="C202" t="n">
+        <v>4676</v>
+      </c>
+      <c r="D202" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Спортивный массажный мяч</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>мяч мфр массажный</t>
+        </is>
+      </c>
+      <c r="C203" t="n">
+        <v>4118</v>
+      </c>
+      <c r="D203" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Спортивный массажный мяч</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>шар для фитнеса</t>
+        </is>
+      </c>
+      <c r="C204" t="n">
+        <v>3699</v>
+      </c>
+      <c r="D204" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Спортивный массажный мяч</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>мячик массажер</t>
+        </is>
+      </c>
+      <c r="C205" t="n">
+        <v>1954</v>
+      </c>
+      <c r="D205" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Спортивный массажный мяч</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>массажные шарики для рук</t>
+        </is>
+      </c>
+      <c r="C206" t="n">
+        <v>1870</v>
+      </c>
+      <c r="D206" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Спортивный массажный мяч</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>мфр шар</t>
+        </is>
+      </c>
+      <c r="C207" t="n">
+        <v>1749</v>
+      </c>
+      <c r="D207" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Спортивный массажный мяч</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>мфр мяч для стоп</t>
+        </is>
+      </c>
+      <c r="C208" t="n">
+        <v>1658</v>
+      </c>
+      <c r="D208" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Спортивный массажный мяч</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>мячик с шипами</t>
+        </is>
+      </c>
+      <c r="C209" t="n">
+        <v>1635</v>
+      </c>
+      <c r="D209" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Спортивный массажный мяч</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>массажный шарик су-джок</t>
+        </is>
+      </c>
+      <c r="C210" t="n">
+        <v>1550</v>
+      </c>
+      <c r="D210" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Спортивный массажный мяч</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>суджок-шарик для массажа рук</t>
+        </is>
+      </c>
+      <c r="C211" t="n">
+        <v>1435</v>
+      </c>
+      <c r="D211" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Спортивный массажный мяч</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>шарик массажный с шипами</t>
+        </is>
+      </c>
+      <c r="C212" t="n">
+        <v>1400</v>
+      </c>
+      <c r="D212" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Спортивный массажный мяч</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>су джок мячик</t>
+        </is>
+      </c>
+      <c r="C213" t="n">
+        <v>1363</v>
+      </c>
+      <c r="D213" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Спортивный массажный мяч</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>шарик для ног массажный</t>
+        </is>
+      </c>
+      <c r="C214" t="n">
+        <v>1343</v>
+      </c>
+      <c r="D214" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Спортивный массажный мяч</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>колючий мячик</t>
+        </is>
+      </c>
+      <c r="C215" t="n">
+        <v>1338</v>
+      </c>
+      <c r="D215" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Спортивный массажный мяч</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>мячик массажный жесткий</t>
+        </is>
+      </c>
+      <c r="C216" t="n">
+        <v>1240</v>
+      </c>
+      <c r="D216" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Спортивный массажный мяч</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>мяч массажный для спины</t>
+        </is>
+      </c>
+      <c r="C217" t="n">
+        <v>1192</v>
+      </c>
+      <c r="D217" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Спортивный массажный мяч</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>суджок-шарик для детей</t>
+        </is>
+      </c>
+      <c r="C218" t="n">
+        <v>1180</v>
+      </c>
+      <c r="D218" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Спортивный массажный мяч</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>миофасциальный мяч</t>
+        </is>
+      </c>
+      <c r="C219" t="n">
+        <v>1157</v>
+      </c>
+      <c r="D219" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Спортивный массажный мяч</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>мяч ежик массажный</t>
+        </is>
+      </c>
+      <c r="C220" t="n">
+        <v>1097</v>
+      </c>
+      <c r="D220" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Спортивный массажный мяч</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>мяч мфр мягкий</t>
+        </is>
+      </c>
+      <c r="C221" t="n">
+        <v>1064</v>
+      </c>
+      <c r="D221" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Спортивный массажный мяч</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>мячик массажный с шипами для стоп</t>
+        </is>
+      </c>
+      <c r="C222" t="n">
+        <v>1055</v>
+      </c>
+      <c r="D222" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Спортивный массажный мяч</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>набор массажных мячей</t>
+        </is>
+      </c>
+      <c r="C223" t="n">
+        <v>1038</v>
+      </c>
+      <c r="D223" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Спортивный массажный мяч</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>массажер для рук шары</t>
+        </is>
+      </c>
+      <c r="C224" t="n">
+        <v>1031</v>
+      </c>
+      <c r="D224" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Таблетница</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>таблетница</t>
+        </is>
+      </c>
+      <c r="C225" t="n">
+        <v>209657</v>
+      </c>
+      <c r="D225" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Таблетница</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>таблетница на неделю</t>
+        </is>
+      </c>
+      <c r="C226" t="n">
+        <v>86685</v>
+      </c>
+      <c r="D226" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Таблетница</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>таблетница на день</t>
+        </is>
+      </c>
+      <c r="C227" t="n">
+        <v>36441</v>
+      </c>
+      <c r="D227" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Таблетница</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>органайзер для таблеток</t>
+        </is>
+      </c>
+      <c r="C228" t="n">
+        <v>14497</v>
+      </c>
+      <c r="D228" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Таблетница</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>контейнер для лекарств</t>
+        </is>
+      </c>
+      <c r="C229" t="n">
+        <v>12997</v>
+      </c>
+      <c r="D229" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Таблетница</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>контейнер для таблеток</t>
+        </is>
+      </c>
+      <c r="C230" t="n">
+        <v>12978</v>
+      </c>
+      <c r="D230" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Таблетница</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>таблетница на неделю 2 приема</t>
+        </is>
+      </c>
+      <c r="C231" t="n">
+        <v>11555</v>
+      </c>
+      <c r="D231" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Таблетница</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>таблетница маленькая</t>
+        </is>
+      </c>
+      <c r="C232" t="n">
+        <v>11185</v>
+      </c>
+      <c r="D232" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Таблетница</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>таблетница утро вечер</t>
+        </is>
+      </c>
+      <c r="C233" t="n">
+        <v>4758</v>
+      </c>
+      <c r="D233" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Таблетница</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>таблетница большая</t>
+        </is>
+      </c>
+      <c r="C234" t="n">
+        <v>3783</v>
+      </c>
+      <c r="D234" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Таблетница</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>для таблеток</t>
+        </is>
+      </c>
+      <c r="C235" t="n">
+        <v>3410</v>
+      </c>
+      <c r="D235" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Таблетница</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>коробка для таблеток</t>
+        </is>
+      </c>
+      <c r="C236" t="n">
+        <v>3338</v>
+      </c>
+      <c r="D236" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Таблетница</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>пилюля</t>
+        </is>
+      </c>
+      <c r="C237" t="n">
+        <v>3249</v>
+      </c>
+      <c r="D237" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Таблетница</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>контейнер для хранения лекарств</t>
+        </is>
+      </c>
+      <c r="C238" t="n">
+        <v>3185</v>
+      </c>
+      <c r="D238" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Таблетница</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>коробка для лекарств</t>
+        </is>
+      </c>
+      <c r="C239" t="n">
+        <v>2804</v>
+      </c>
+      <c r="D239" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Таблетница</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>мини таблетница</t>
+        </is>
+      </c>
+      <c r="C240" t="n">
+        <v>2486</v>
+      </c>
+      <c r="D240" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Таблетница</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>таблетница для таблеток</t>
+        </is>
+      </c>
+      <c r="C241" t="n">
+        <v>2448</v>
+      </c>
+      <c r="D241" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Таблетница</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>органайзер для таблеток на неделю</t>
+        </is>
+      </c>
+      <c r="C242" t="n">
+        <v>2365</v>
+      </c>
+      <c r="D242" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Таблетница</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>таблетница на неделю утро и вечер</t>
+        </is>
+      </c>
+      <c r="C243" t="n">
+        <v>2330</v>
+      </c>
+      <c r="D243" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Таблетница</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>таблетница на неделю 1 прием</t>
+        </is>
+      </c>
+      <c r="C244" t="n">
+        <v>2195</v>
+      </c>
+      <c r="D244" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Таблетница</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>контейнер для капсул</t>
+        </is>
+      </c>
+      <c r="C245" t="n">
+        <v>2140</v>
+      </c>
+      <c r="D245" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Таблетница</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>таблетница на неделю 4 приема</t>
+        </is>
+      </c>
+      <c r="C246" t="n">
+        <v>1970</v>
+      </c>
+      <c r="D246" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Таблетница</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>таблетница на 7 дней</t>
+        </is>
+      </c>
+      <c r="C247" t="n">
+        <v>1960</v>
+      </c>
+      <c r="D247" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Таблетница</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>бокс для таблеток</t>
+        </is>
+      </c>
+      <c r="C248" t="n">
+        <v>1880</v>
+      </c>
+      <c r="D248" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Таблетница</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>для лекарств</t>
+        </is>
+      </c>
+      <c r="C249" t="n">
+        <v>1827</v>
+      </c>
+      <c r="D249" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Таблетница</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>контейнер для таблеток на день</t>
+        </is>
+      </c>
+      <c r="C250" t="n">
+        <v>1690</v>
+      </c>
+      <c r="D250" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Таблетница</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>таблетница в сумку</t>
+        </is>
+      </c>
+      <c r="C251" t="n">
+        <v>1515</v>
+      </c>
+      <c r="D251" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Таблетница</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>таблетница на день маленькая</t>
+        </is>
+      </c>
+      <c r="C252" t="n">
+        <v>1490</v>
+      </c>
+      <c r="D252" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Таблетница</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>хранение лекарств</t>
+        </is>
+      </c>
+      <c r="C253" t="n">
+        <v>1395</v>
+      </c>
+      <c r="D253" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Таблетница</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>таблетница маленькая с собой</t>
+        </is>
+      </c>
+      <c r="C254" t="n">
+        <v>1365</v>
+      </c>
+      <c r="D254" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Таблетница</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>таблетница утро день вечер</t>
+        </is>
+      </c>
+      <c r="C255" t="n">
+        <v>1360</v>
+      </c>
+      <c r="D255" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Таблетница</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>таблетница на 7 дней утро день вечер</t>
+        </is>
+      </c>
+      <c r="C256" t="n">
+        <v>1354</v>
+      </c>
+      <c r="D256" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Таблетница</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>таблетница маленькая в сумку</t>
+        </is>
+      </c>
+      <c r="C257" t="n">
+        <v>1280</v>
+      </c>
+      <c r="D257" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Таблетница</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>для витаминов органайзер</t>
+        </is>
+      </c>
+      <c r="C258" t="n">
+        <v>1275</v>
+      </c>
+      <c r="D258" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Таблетница</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>таблетницы для женщин</t>
+        </is>
+      </c>
+      <c r="C259" t="n">
+        <v>1235</v>
+      </c>
+      <c r="D259" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Таблетница</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>кейс для таблеток</t>
+        </is>
+      </c>
+      <c r="C260" t="n">
+        <v>1222</v>
+      </c>
+      <c r="D260" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Таблетница</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>ящик для лекарств</t>
+        </is>
+      </c>
+      <c r="C261" t="n">
+        <v>1135</v>
+      </c>
+      <c r="D261" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>Таблетница</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>органайзер для таблеток большой</t>
+        </is>
+      </c>
+      <c r="C262" t="n">
+        <v>1120</v>
+      </c>
+      <c r="D262" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>Таблетница</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>футляр для таблеток</t>
+        </is>
+      </c>
+      <c r="C263" t="n">
+        <v>1105</v>
+      </c>
+      <c r="D263" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>Таблетница</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>контейнер для витаминов</t>
+        </is>
+      </c>
+      <c r="C264" t="n">
+        <v>1095</v>
+      </c>
+      <c r="D264" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>Таблетница</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>контейнер под таблетки</t>
+        </is>
+      </c>
+      <c r="C265" t="n">
+        <v>1035</v>
+      </c>
+      <c r="D265" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>Таблетница</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>таблетница на день 4 секции</t>
+        </is>
+      </c>
+      <c r="C266" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D266" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>Таблетница</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>таблетница на неделю органайзер</t>
+        </is>
+      </c>
+      <c r="C267" t="n">
+        <v>953</v>
+      </c>
+      <c r="D267" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Таблетница</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>контейнер под лекарства</t>
+        </is>
+      </c>
+      <c r="C268" t="n">
+        <v>910</v>
+      </c>
+      <c r="D268" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>Таблетница</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>компактная таблетница</t>
+        </is>
+      </c>
+      <c r="C269" t="n">
+        <v>865</v>
+      </c>
+      <c r="D269" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>Таблетница</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>таблетница на день большая</t>
+        </is>
+      </c>
+      <c r="C270" t="n">
+        <v>855</v>
+      </c>
+      <c r="D270" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>Таблетница</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>таблетница на неделю большая</t>
+        </is>
+      </c>
+      <c r="C271" t="n">
+        <v>840</v>
+      </c>
+      <c r="D271" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>Таблетница</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>таблетница мужская</t>
+        </is>
+      </c>
+      <c r="C272" t="n">
+        <v>808</v>
+      </c>
+      <c r="D272" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>Таблетница</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>таблетница круглая</t>
+        </is>
+      </c>
+      <c r="C273" t="n">
+        <v>805</v>
+      </c>
+      <c r="D273" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>Фитнес и йога</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>скакалка</t>
+        </is>
+      </c>
+      <c r="C274" t="n">
+        <v>98963</v>
+      </c>
+      <c r="D274" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>Фитнес и йога</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>скакалка спортивная взрослая</t>
+        </is>
+      </c>
+      <c r="C275" t="n">
+        <v>10370</v>
+      </c>
+      <c r="D275" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>Фитнес и йога</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>скакалка гимнастическая</t>
+        </is>
+      </c>
+      <c r="C276" t="n">
+        <v>10132</v>
+      </c>
+      <c r="D276" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>Фитнес и йога</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>спорт товары</t>
+        </is>
+      </c>
+      <c r="C277" t="n">
+        <v>6220</v>
+      </c>
+      <c r="D277" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>Фитнес и йога</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>спортивный инвентарь для детей</t>
+        </is>
+      </c>
+      <c r="C278" t="n">
+        <v>3633</v>
+      </c>
+      <c r="D278" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>Фитнес и йога</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>прыгалка детская</t>
+        </is>
+      </c>
+      <c r="C279" t="n">
+        <v>3411</v>
+      </c>
+      <c r="D279" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>Фитнес и йога</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>скакалка скоростная</t>
+        </is>
+      </c>
+      <c r="C280" t="n">
+        <v>3369</v>
+      </c>
+      <c r="D280" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>Фитнес и йога</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>спорт инвентарь для женщин</t>
+        </is>
+      </c>
+      <c r="C281" t="n">
+        <v>3170</v>
+      </c>
+      <c r="D281" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>Фитнес и йога</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>кардиотренажер</t>
+        </is>
+      </c>
+      <c r="C282" t="n">
+        <v>2935</v>
+      </c>
+      <c r="D282" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>Фитнес и йога</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>для спорта мужчинам инвентарь</t>
+        </is>
+      </c>
+      <c r="C283" t="n">
+        <v>2775</v>
+      </c>
+      <c r="D283" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>Фитнес и йога</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>прыгалка для спорта</t>
+        </is>
+      </c>
+      <c r="C284" t="n">
+        <v>2645</v>
+      </c>
+      <c r="D284" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>Фитнес и йога</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>скакалка спортивная детская</t>
+        </is>
+      </c>
+      <c r="C285" t="n">
+        <v>2540</v>
+      </c>
+      <c r="D285" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>Фитнес и йога</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>скакалка без шнура</t>
+        </is>
+      </c>
+      <c r="C286" t="n">
+        <v>2445</v>
+      </c>
+      <c r="D286" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>Фитнес и йога</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>скакалка с утяжелителем</t>
+        </is>
+      </c>
+      <c r="C287" t="n">
+        <v>1790</v>
+      </c>
+      <c r="D287" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>Фитнес и йога</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>спорт инвентарь для спорта мужской</t>
+        </is>
+      </c>
+      <c r="C288" t="n">
+        <v>1775</v>
+      </c>
+      <c r="D288" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>Фитнес и йога</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>спортивный инвентарь для тренировок дома</t>
+        </is>
+      </c>
+      <c r="C289" t="n">
+        <v>1705</v>
+      </c>
+      <c r="D289" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>Фитнес и йога</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>кардиотренажер для рук и ног</t>
+        </is>
+      </c>
+      <c r="C290" t="n">
+        <v>1607</v>
+      </c>
+      <c r="D290" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>Фитнес и йога</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>скакалки для фитнеса</t>
+        </is>
+      </c>
+      <c r="C291" t="n">
+        <v>1583</v>
+      </c>
+      <c r="D291" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>Фитнес и йога</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>скакалка спортивная взрослая женская</t>
+        </is>
+      </c>
+      <c r="C292" t="n">
+        <v>1385</v>
+      </c>
+      <c r="D292" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>Фитнес и йога</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>прыгалка скакалка</t>
+        </is>
+      </c>
+      <c r="C293" t="n">
+        <v>1367</v>
+      </c>
+      <c r="D293" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>Фитнес и йога</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>фитнес резинки 30 кг</t>
+        </is>
+      </c>
+      <c r="C294" t="n">
+        <v>1162</v>
+      </c>
+      <c r="D294" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>Фитнес и йога</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>спорт товары для фитнеса</t>
+        </is>
+      </c>
+      <c r="C295" t="n">
+        <v>1148</v>
+      </c>
+      <c r="D295" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>Фитнес и йога</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>резинка для спорта для ягодиц</t>
+        </is>
+      </c>
+      <c r="C296" t="n">
+        <v>984</v>
+      </c>
+      <c r="D296" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>Фитнес и йога</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>скакалка для дома</t>
+        </is>
+      </c>
+      <c r="C297" t="n">
+        <v>940</v>
+      </c>
+      <c r="D297" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>Фитнес и йога</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>набор для тренировок</t>
+        </is>
+      </c>
+      <c r="C298" t="n">
+        <v>927</v>
+      </c>
+      <c r="D298" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>Фитнес и йога</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>прыгалки взрослые</t>
+        </is>
+      </c>
+      <c r="C299" t="n">
+        <v>901</v>
+      </c>
+      <c r="D299" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>Фитнес и йога</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>пилатес лента</t>
+        </is>
+      </c>
+      <c r="C300" t="n">
+        <v>900</v>
+      </c>
+      <c r="D300" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>Фитнес и йога</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>скакалка взрослая</t>
+        </is>
+      </c>
+      <c r="C301" t="n">
+        <v>899</v>
+      </c>
+      <c r="D301" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>Фитнес и йога</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>фитнес кольцо</t>
+        </is>
+      </c>
+      <c r="C302" t="n">
+        <v>880</v>
+      </c>
+      <c r="D302" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>Фитнес и йога</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>резинка для йоги</t>
+        </is>
+      </c>
+      <c r="C303" t="n">
+        <v>840</v>
+      </c>
+      <c r="D303" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>Фитнес и йога</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>резинка для спорта тканевая</t>
+        </is>
+      </c>
+      <c r="C304" t="n">
+        <v>797</v>
+      </c>
+      <c r="D304" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>Фитнес и йога</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>резинки для фитнеса комплект</t>
+        </is>
+      </c>
+      <c r="C305" t="n">
+        <v>790</v>
+      </c>
+      <c r="D305" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>Фитнес и йога</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>набор резинок для спорта</t>
+        </is>
+      </c>
+      <c r="C306" t="n">
+        <v>695</v>
+      </c>
+      <c r="D306" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>Фитнес и йога</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>тканевые фитнес ленты</t>
+        </is>
+      </c>
+      <c r="C307" t="n">
+        <v>663</v>
+      </c>
+      <c r="D307" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>Шпатель-скребок кондитерский</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>шпатель кондитерский</t>
+        </is>
+      </c>
+      <c r="C308" t="n">
+        <v>29285</v>
+      </c>
+      <c r="D308" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>Шпатель-скребок кондитерский</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>кондитерский набор</t>
+        </is>
+      </c>
+      <c r="C309" t="n">
+        <v>24228</v>
+      </c>
+      <c r="D309" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>Шпатель-скребок кондитерский</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>для кондитера</t>
+        </is>
+      </c>
+      <c r="C310" t="n">
+        <v>14998</v>
+      </c>
+      <c r="D310" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>Шпатель-скребок кондитерский</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>для теста</t>
+        </is>
+      </c>
+      <c r="C311" t="n">
+        <v>4767</v>
+      </c>
+      <c r="D311" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>Шпатель-скребок кондитерский</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>нож для теста пластиковый</t>
+        </is>
+      </c>
+      <c r="C312" t="n">
+        <v>3712</v>
+      </c>
+      <c r="D312" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>Шпатель-скребок кондитерский</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>лопатка кондитерская</t>
+        </is>
+      </c>
+      <c r="C313" t="n">
+        <v>3411</v>
+      </c>
+      <c r="D313" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>Шпатель-скребок кондитерский</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>шпатель для теста</t>
+        </is>
+      </c>
+      <c r="C314" t="n">
+        <v>3296</v>
+      </c>
+      <c r="D314" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>Шпатель-скребок кондитерский</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>шпатель кондитерский металлический</t>
+        </is>
+      </c>
+      <c r="C315" t="n">
+        <v>3291</v>
+      </c>
+      <c r="D315" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>Шпатель-скребок кондитерский</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>выпечка инструменты</t>
+        </is>
+      </c>
+      <c r="C316" t="n">
+        <v>2712</v>
+      </c>
+      <c r="D316" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>Шпатель-скребок кондитерский</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>шпатель кухонный</t>
+        </is>
+      </c>
+      <c r="C317" t="n">
+        <v>1730</v>
+      </c>
+      <c r="D317" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>Шпатель-скребок кондитерский</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>скребок для теста</t>
+        </is>
+      </c>
+      <c r="C318" t="n">
+        <v>1584</v>
+      </c>
+      <c r="D318" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>Шпатель-скребок кондитерский</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>набор шпателей кондитерских</t>
+        </is>
+      </c>
+      <c r="C319" t="n">
+        <v>1388</v>
+      </c>
+      <c r="D319" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>Шпатель-скребок кондитерский</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>шпатель кондитерский пластиковый</t>
+        </is>
+      </c>
+      <c r="C320" t="n">
+        <v>1015</v>
+      </c>
+      <c r="D320" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>Шпатель-скребок кондитерский</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>нож для теста скребок</t>
+        </is>
+      </c>
+      <c r="C321" t="n">
+        <v>992</v>
+      </c>
+      <c r="D321" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>Шпатель-скребок кондитерский</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>нож для теста шпатель</t>
+        </is>
+      </c>
+      <c r="C322" t="n">
+        <v>930</v>
+      </c>
+      <c r="D322" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:I322"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/docs/ozon/Озон_рабочая_книга.xlsx
+++ b/docs/ozon/Озон_рабочая_книга.xlsx
@@ -8786,9 +8786,9 @@
           <t>Маска-бандаж</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Бандаж для лица розовый</t>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>Бандаж для лица и подбородка из лайкры, маска для подтяжки, розовый</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -8810,6 +8810,11 @@
           <t>АРОЛС</t>
         </is>
       </c>
+      <c r="X3" s="10" t="inlineStr">
+        <is>
+          <t>#подтяжка_лица #овал_лица #уход_за_лицом #второй_подбородок #лифтинг #домашний_уход</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -8822,9 +8827,9 @@
           <t>Маска-бандаж</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Бандаж для лица черный</t>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>Бандаж для лица и подбородка, маска для подтяжки овала, черный</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -8854,6 +8859,11 @@
           <t>АРОЛС</t>
         </is>
       </c>
+      <c r="X4" s="10" t="inlineStr">
+        <is>
+          <t>#подтяжка_лица #овал_лица #уход_за_лицом #второй_подбородок #лифтинг #домашний_уход</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -8866,9 +8876,9 @@
           <t>Маска-бандаж</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Бандаж для лица серый</t>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>Бандаж для лица и подбородка силиконовый, маска для подтяжки овала</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -8898,6 +8908,11 @@
           <t>АРОЛС</t>
         </is>
       </c>
+      <c r="X5" s="10" t="inlineStr">
+        <is>
+          <t>#подтяжка_лица #овал_лица #уход_за_лицом #второй_подбородок #лифтинг #домашний_уход</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8910,9 +8925,9 @@
           <t>Мешок для стирки</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Мешки 7 шт.</t>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>Мешки для стирки белья, набор 7 шт с контейнером, бежевые</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -8942,6 +8957,11 @@
           <t>АРОЛС</t>
         </is>
       </c>
+      <c r="X6" s="10" t="inlineStr">
+        <is>
+          <t>#сетка_для_стирки #деликатная_стирка #стирка_белья #уход_за_одеждой #для_бюстгальтера #защита_белья #стиральная_машина</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8954,9 +8974,9 @@
           <t>Мешок для стирки</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Мешок для бюстгалтеров</t>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>Чехол мешок для стирки бюстгальтера с каркасом 15х17 см, бежевый</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -8986,6 +9006,11 @@
           <t>АРОЛС</t>
         </is>
       </c>
+      <c r="X7" s="10" t="inlineStr">
+        <is>
+          <t>#сетка_для_стирки #деликатная_стирка #стирка_белья #уход_за_одеждой #для_бюстгальтера #защита_белья #стиральная_машина</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -8998,9 +9023,9 @@
           <t>Мешок для стирки</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Мешки 3 шт.</t>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>Мешки для стирки одежды и носков, набор 3 шт, бежевые</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -9027,6 +9052,11 @@
           <t>АРОЛС</t>
         </is>
       </c>
+      <c r="X8" s="10" t="inlineStr">
+        <is>
+          <t>#сетка_для_стирки #деликатная_стирка #стирка_белья #уход_за_одеждой #для_бюстгальтера #защита_белья #стиральная_машина</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -9039,9 +9069,9 @@
           <t>Мешок для стирки</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Мешки/деликат 3 шт.</t>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>Мешочки для стирки белья и шелка в машинке, набор 3 шт</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -9071,6 +9101,11 @@
           <t>АРОЛС</t>
         </is>
       </c>
+      <c r="X9" s="10" t="inlineStr">
+        <is>
+          <t>#сетка_для_стирки #деликатная_стирка #стирка_белья #уход_за_одеждой #для_бюстгальтера #защита_белья #стиральная_машина</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -9083,9 +9118,9 @@
           <t>Мешок для стирки</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Мешки/шнурок мелк 3 шт.</t>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>Сетка для стирки белья мелкая ячейка, набор мешков 3 шт</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -9115,6 +9150,11 @@
           <t>АРОЛС</t>
         </is>
       </c>
+      <c r="X10" s="10" t="inlineStr">
+        <is>
+          <t>#сетка_для_стирки #деликатная_стирка #стирка_белья #уход_за_одеждой #для_бюстгальтера #защита_белья #стиральная_машина</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -9127,9 +9167,9 @@
           <t>Мешок для стирки</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Мешки/шнурок крупн 3 шт.</t>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>Сетка для стирки белья в машинке крупная ячейка, набор 3 шт</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -9159,6 +9199,11 @@
           <t>АРОЛС</t>
         </is>
       </c>
+      <c r="X11" s="10" t="inlineStr">
+        <is>
+          <t>#сетка_для_стирки #деликатная_стирка #стирка_белья #уход_за_одеждой #для_бюстгальтера #защита_белья #стиральная_машина</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -9171,9 +9216,9 @@
           <t>Мешок для стирки</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Мешки 2 шт. серый</t>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>Мешок для стирки бюстгальтера с каркасом и нижнего белья, 2 шт</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -9203,6 +9248,11 @@
           <t>АРОЛС</t>
         </is>
       </c>
+      <c r="X12" s="10" t="inlineStr">
+        <is>
+          <t>#сетка_для_стирки #деликатная_стирка #стирка_белья #уход_за_одеждой #для_бюстгальтера #защита_белья #стиральная_машина</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -9215,9 +9265,9 @@
           <t>Мешок для стирки</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Мешки 2 шт. розовый</t>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>Мешки для стирки бюстгальтера и нижнего белья, набор 2 шт</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -9239,6 +9289,11 @@
           <t>АРОЛС</t>
         </is>
       </c>
+      <c r="X13" s="10" t="inlineStr">
+        <is>
+          <t>#сетка_для_стирки #деликатная_стирка #стирка_белья #уход_за_одеждой #для_бюстгальтера #защита_белья #стиральная_машина</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -9251,9 +9306,9 @@
           <t>Мешок для стирки</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Мешок 60*80 крупн</t>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>Мешок для стирки пуховика и одеяла большой 60х80 см, крупная сетка</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -9283,6 +9338,11 @@
           <t>АРОЛС</t>
         </is>
       </c>
+      <c r="X14" s="10" t="inlineStr">
+        <is>
+          <t>#сетка_для_стирки #деликатная_стирка #стирка_белья #уход_за_одеждой #для_бюстгальтера #защита_белья #стиральная_машина</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -9295,9 +9355,9 @@
           <t>Мешок для стирки</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Мешок 60*80 мелк</t>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>Мешок для стирки подушек и пуховика большой 60х80 см, мелкая сетка</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -9327,6 +9387,11 @@
           <t>АРОЛС</t>
         </is>
       </c>
+      <c r="X15" s="10" t="inlineStr">
+        <is>
+          <t>#сетка_для_стирки #деликатная_стирка #стирка_белья #уход_за_одеждой #для_бюстгальтера #защита_белья #стиральная_машина</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -9339,9 +9404,9 @@
           <t>Мешок для стирки</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Мешок для обуви XL - 35 см</t>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>Мешок для стирки обуви каркасный 35 см, до 47 размера</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -9363,6 +9428,11 @@
           <t>АРОЛС</t>
         </is>
       </c>
+      <c r="X16" s="10" t="inlineStr">
+        <is>
+          <t>#сетка_для_стирки #деликатная_стирка #стирка_белья #уход_за_одеждой #для_бюстгальтера #защита_белья #стиральная_машина</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -9375,9 +9445,9 @@
           <t>Аксессуар для массажа</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Массажер для пальцев</t>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>Массажер для пальцев рук роликовый, для кистей, оранжевый</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -9407,6 +9477,11 @@
           <t>АРОЛС</t>
         </is>
       </c>
+      <c r="X17" s="10" t="inlineStr">
+        <is>
+          <t>#массаж_шеи #роликовый_массажер #самомассаж #расслабление #после_работы #уход_за_телом</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -9419,9 +9494,9 @@
           <t>Аксессуар для массажа</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Массажер для тела оранжевый</t>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>Массажер для шеи и спины ручной роликовый ленточный, оранжевый</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -9451,6 +9526,11 @@
           <t>АРОЛС</t>
         </is>
       </c>
+      <c r="X18" s="10" t="inlineStr">
+        <is>
+          <t>#массаж_шеи #роликовый_массажер #самомассаж #расслабление #после_работы #уход_за_телом</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -9463,9 +9543,9 @@
           <t>Аксессуар для массажа</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Массажер для тела розовый</t>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>Массажер для шеи и плеч ручной роликовый ленточный, розовый</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -9495,6 +9575,11 @@
           <t>АРОЛС</t>
         </is>
       </c>
+      <c r="X19" s="10" t="inlineStr">
+        <is>
+          <t>#массаж_шеи #роликовый_массажер #самомассаж #расслабление #после_работы #уход_за_телом</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -9507,9 +9592,9 @@
           <t>Аксессуар для массажа</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Массажер для тела голубой</t>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>Массажер для шеи и спины ручной роликовый ленточный, голубой</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -9539,6 +9624,11 @@
           <t>АРОЛС</t>
         </is>
       </c>
+      <c r="X20" s="10" t="inlineStr">
+        <is>
+          <t>#массаж_шеи #роликовый_массажер #самомассаж #расслабление #после_работы #уход_за_телом</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -9551,9 +9641,9 @@
           <t>Спортивный массажный мяч</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Мяч с шипами белый 6 см</t>
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>Мячик массажный с шипами 6 см жесткий, шарик для стоп, белый</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -9583,6 +9673,11 @@
           <t>АРОЛС</t>
         </is>
       </c>
+      <c r="X21" s="10" t="inlineStr">
+        <is>
+          <t>#мфр #миофасциальный_релиз #массаж_стоп #йога #пилатес #самомассаж #восстановление</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -9595,9 +9690,9 @@
           <t>Спортивный массажный мяч</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Мяч с шипами розовый 6 см</t>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>Мячик массажный с шипами 6 см жесткий, шарик для стоп, розовый</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -9627,6 +9722,11 @@
           <t>АРОЛС</t>
         </is>
       </c>
+      <c r="X22" s="10" t="inlineStr">
+        <is>
+          <t>#мфр #миофасциальный_релиз #массаж_стоп #йога #пилатес #самомассаж #восстановление</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -9639,9 +9739,9 @@
           <t>Спортивный массажный мяч</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Мяч с шипами голубой 6 см</t>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>Мячик массажный с шипами 6 см жесткий, шарик для стоп, голубой</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -9671,6 +9771,11 @@
           <t>АРОЛС</t>
         </is>
       </c>
+      <c r="X23" s="10" t="inlineStr">
+        <is>
+          <t>#мфр #миофасциальный_релиз #массаж_стоп #йога #пилатес #самомассаж #восстановление</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -9683,9 +9788,9 @@
           <t>Спортивный массажный мяч</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Мяч с шипами оранжевый 6 см</t>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>Мячик массажный с шипами 6 см жесткий, шарик для стоп, оранжевый</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -9715,6 +9820,11 @@
           <t>АРОЛС</t>
         </is>
       </c>
+      <c r="X24" s="10" t="inlineStr">
+        <is>
+          <t>#мфр #миофасциальный_релиз #массаж_стоп #йога #пилатес #самомассаж #восстановление</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -9727,9 +9837,9 @@
           <t>Спортивный массажный мяч</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Мяч с шипами черный 6 см</t>
+      <c r="C25" s="10" t="inlineStr">
+        <is>
+          <t>Мячик массажный с шипами 6 см жесткий, шарик для стоп, черный</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -9759,6 +9869,11 @@
           <t>АРОЛС</t>
         </is>
       </c>
+      <c r="X25" s="10" t="inlineStr">
+        <is>
+          <t>#мфр #миофасциальный_релиз #массаж_стоп #йога #пилатес #самомассаж #восстановление</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -9771,9 +9886,9 @@
           <t>Спортивный массажный мяч</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Мяч с шипами белый 7 см</t>
+      <c r="C26" s="10" t="inlineStr">
+        <is>
+          <t>Мяч массажный с шипами 7 см жесткий, мячик для стоп, белый</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -9803,6 +9918,11 @@
           <t>АРОЛС</t>
         </is>
       </c>
+      <c r="X26" s="10" t="inlineStr">
+        <is>
+          <t>#мфр #миофасциальный_релиз #массаж_стоп #йога #пилатес #самомассаж #восстановление</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -9815,9 +9935,9 @@
           <t>Спортивный массажный мяч</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Мяч с шипами розовый 7 см</t>
+      <c r="C27" s="10" t="inlineStr">
+        <is>
+          <t>Мяч массажный с шипами 7 см жесткий, мячик для стоп, розовый</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -9847,6 +9967,11 @@
           <t>АРОЛС</t>
         </is>
       </c>
+      <c r="X27" s="10" t="inlineStr">
+        <is>
+          <t>#мфр #миофасциальный_релиз #массаж_стоп #йога #пилатес #самомассаж #восстановление</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -9859,9 +9984,9 @@
           <t>Спортивный массажный мяч</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Мяч с шипами голубой 7 см</t>
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>Мяч массажный с шипами 7 см жесткий, мячик для стоп, голубой</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -9891,6 +10016,11 @@
           <t>АРОЛС</t>
         </is>
       </c>
+      <c r="X28" s="10" t="inlineStr">
+        <is>
+          <t>#мфр #миофасциальный_релиз #массаж_стоп #йога #пилатес #самомассаж #восстановление</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -9903,9 +10033,9 @@
           <t>Спортивный массажный мяч</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Мяч с шипами оранжевый 7 см</t>
+      <c r="C29" s="10" t="inlineStr">
+        <is>
+          <t>Мяч массажный с шипами 7 см жесткий, мячик для стоп, оранжевый</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -9935,6 +10065,11 @@
           <t>АРОЛС</t>
         </is>
       </c>
+      <c r="X29" s="10" t="inlineStr">
+        <is>
+          <t>#мфр #миофасциальный_релиз #массаж_стоп #йога #пилатес #самомассаж #восстановление</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -9947,9 +10082,9 @@
           <t>Спортивный массажный мяч</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Мяч с шипами черный 7 см</t>
+      <c r="C30" s="10" t="inlineStr">
+        <is>
+          <t>Мяч массажный с шипами 7 см жесткий, мячик для стоп, черный</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -9979,6 +10114,11 @@
           <t>АРОЛС</t>
         </is>
       </c>
+      <c r="X30" s="10" t="inlineStr">
+        <is>
+          <t>#мфр #миофасциальный_релиз #массаж_стоп #йога #пилатес #самомассаж #восстановление</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -9991,9 +10131,9 @@
           <t>Спортивный массажный мяч</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Мяч с шипами розовый 9 см</t>
+      <c r="C31" s="10" t="inlineStr">
+        <is>
+          <t>Мяч массажный с шипами 9 см жесткий, шарик для спины, розовый</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -10023,6 +10163,11 @@
           <t>АРОЛС</t>
         </is>
       </c>
+      <c r="X31" s="10" t="inlineStr">
+        <is>
+          <t>#мфр #миофасциальный_релиз #массаж_стоп #йога #пилатес #самомассаж #восстановление</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -10035,9 +10180,9 @@
           <t>Спортивный массажный мяч</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Мяч с шипами голубой 9 см</t>
+      <c r="C32" s="10" t="inlineStr">
+        <is>
+          <t>Мяч массажный с шипами 9 см жесткий, шарик для спины, голубой</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -10067,6 +10212,11 @@
           <t>АРОЛС</t>
         </is>
       </c>
+      <c r="X32" s="10" t="inlineStr">
+        <is>
+          <t>#мфр #миофасциальный_релиз #массаж_стоп #йога #пилатес #самомассаж #восстановление</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -10079,9 +10229,9 @@
           <t>Спортивный массажный мяч</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Мяч с шипами оранжевый 9 см</t>
+      <c r="C33" s="10" t="inlineStr">
+        <is>
+          <t>Мяч массажный с шипами 9 см жесткий, шарик для спины, оранжевый</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -10111,6 +10261,11 @@
           <t>АРОЛС</t>
         </is>
       </c>
+      <c r="X33" s="10" t="inlineStr">
+        <is>
+          <t>#мфр #миофасциальный_релиз #массаж_стоп #йога #пилатес #самомассаж #восстановление</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -10123,9 +10278,9 @@
           <t>Спортивный массажный мяч</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Мяч с шипами черный 9 см</t>
+      <c r="C34" s="10" t="inlineStr">
+        <is>
+          <t>Мяч массажный с шипами 9 см жесткий, шарик для спины, черный</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -10155,6 +10310,11 @@
           <t>АРОЛС</t>
         </is>
       </c>
+      <c r="X34" s="10" t="inlineStr">
+        <is>
+          <t>#мфр #миофасциальный_релиз #массаж_стоп #йога #пилатес #самомассаж #восстановление</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -10167,9 +10327,9 @@
           <t>Спортивный массажный мяч</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Мяч с шипами фиолетовый 9 см</t>
+      <c r="C35" s="10" t="inlineStr">
+        <is>
+          <t>Мяч массажный с шипами 9 см жесткий, шарик для спины, фиолетовый</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -10199,6 +10359,11 @@
           <t>АРОЛС</t>
         </is>
       </c>
+      <c r="X35" s="10" t="inlineStr">
+        <is>
+          <t>#мфр #миофасциальный_релиз #массаж_стоп #йога #пилатес #самомассаж #восстановление</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -10211,9 +10376,9 @@
           <t>Спортивный массажный мяч</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Мяч гладкий голубой</t>
+      <c r="C36" s="10" t="inlineStr">
+        <is>
+          <t>Мяч массажный мфр для йоги и пилатеса, шарик для массажа, голубой</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -10240,6 +10405,11 @@
           <t>АРОЛС</t>
         </is>
       </c>
+      <c r="X36" s="10" t="inlineStr">
+        <is>
+          <t>#мфр #миофасциальный_релиз #массаж_стоп #йога #пилатес #самомассаж #восстановление</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -10252,9 +10422,9 @@
           <t>Спортивный массажный мяч</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Мяч гладкий сиреневый</t>
+      <c r="C37" s="10" t="inlineStr">
+        <is>
+          <t>Мяч массажный мфр для йоги и пилатеса, шарик для массажа, сиреневый</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -10281,6 +10451,11 @@
           <t>АРОЛС</t>
         </is>
       </c>
+      <c r="X37" s="10" t="inlineStr">
+        <is>
+          <t>#мфр #миофасциальный_релиз #массаж_стоп #йога #пилатес #самомассаж #восстановление</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -10293,9 +10468,9 @@
           <t>Спортивный массажный мяч</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Мяч гладкий оранжевый</t>
+      <c r="C38" s="10" t="inlineStr">
+        <is>
+          <t>Мяч массажный мфр для йоги и пилатеса, шарик для массажа, оранжевый</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -10322,6 +10497,11 @@
           <t>АРОЛС</t>
         </is>
       </c>
+      <c r="X38" s="10" t="inlineStr">
+        <is>
+          <t>#мфр #миофасциальный_релиз #массаж_стоп #йога #пилатес #самомассаж #восстановление</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -10334,9 +10514,9 @@
           <t>Фитнес и йога</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Набор эластичных лент 3 шт. в мешке</t>
+      <c r="C39" s="10" t="inlineStr">
+        <is>
+          <t>Фитнес резинки тканевые для ягодиц и ног, набор 3 шт, 27-68 кг</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -10366,6 +10546,11 @@
           <t>АРОЛС</t>
         </is>
       </c>
+      <c r="X39" s="10" t="inlineStr">
+        <is>
+          <t>#скакалка #фитнес_резинки #домашние_тренировки #кардио #для_ягодиц #спортинвентарь #растяжка</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -10378,9 +10563,9 @@
           <t>Фитнес и йога</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Набор эластичных лент 5 шт. в мешке</t>
+      <c r="C40" s="10" t="inlineStr">
+        <is>
+          <t>Фитнес резинки тканевые для ног и ягодиц, эспандер, набор 5 шт</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -10410,6 +10595,11 @@
           <t>АРОЛС</t>
         </is>
       </c>
+      <c r="X40" s="10" t="inlineStr">
+        <is>
+          <t>#скакалка #фитнес_резинки #домашние_тренировки #кардио #для_ягодиц #спортинвентарь #растяжка</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -10422,9 +10612,9 @@
           <t>Фитнес и йога</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Набор эластичных лент 4 шт.</t>
+      <c r="C41" s="10" t="inlineStr">
+        <is>
+          <t>Фитнес резинки латексные для йоги, эспандер лента, набор 4 шт</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -10451,6 +10641,11 @@
           <t>АРОЛС</t>
         </is>
       </c>
+      <c r="X41" s="10" t="inlineStr">
+        <is>
+          <t>#скакалка #фитнес_резинки #домашние_тренировки #кардио #для_ягодиц #спортинвентарь #растяжка</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -10463,9 +10658,9 @@
           <t>Фитнес и йога</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Набор эластичных лент 5 шт.</t>
+      <c r="C42" s="10" t="inlineStr">
+        <is>
+          <t>Фитнес резинки эластичные ленты для спорта, набор 5 шт</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -10487,6 +10682,11 @@
           <t>АРОЛС</t>
         </is>
       </c>
+      <c r="X42" s="10" t="inlineStr">
+        <is>
+          <t>#скакалка #фитнес_резинки #домашние_тренировки #кардио #для_ягодиц #спортинвентарь #растяжка</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -10499,9 +10699,9 @@
           <t>Фитнес и йога</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Скакалка черная</t>
+      <c r="C43" s="10" t="inlineStr">
+        <is>
+          <t>Скакалка скоростная спортивная взрослая, стальной трос 3 м, черная</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -10528,6 +10728,11 @@
           <t>АРОЛС</t>
         </is>
       </c>
+      <c r="X43" s="10" t="inlineStr">
+        <is>
+          <t>#скакалка #фитнес_резинки #домашние_тренировки #кардио #для_ягодиц #спортинвентарь #растяжка</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -10540,9 +10745,9 @@
           <t>Фитнес и йога</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Скакалка красная</t>
+      <c r="C44" s="10" t="inlineStr">
+        <is>
+          <t>Скакалка скоростная спортивная 3 м на подшипниках, красная</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -10569,6 +10774,11 @@
           <t>АРОЛС</t>
         </is>
       </c>
+      <c r="X44" s="10" t="inlineStr">
+        <is>
+          <t>#скакалка #фитнес_резинки #домашние_тренировки #кардио #для_ягодиц #спортинвентарь #растяжка</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -10581,9 +10791,9 @@
           <t>Фитнес и йога</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Скакалка синяя</t>
+      <c r="C45" s="10" t="inlineStr">
+        <is>
+          <t>Скакалка спортивная взрослая женская скоростная 3 м, голубая</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -10610,6 +10820,11 @@
           <t>АРОЛС</t>
         </is>
       </c>
+      <c r="X45" s="10" t="inlineStr">
+        <is>
+          <t>#скакалка #фитнес_резинки #домашние_тренировки #кардио #для_ягодиц #спортинвентарь #растяжка</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -10878,9 +11093,9 @@
           <t>Таблетница</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Таблетница прям 7*2 черн</t>
+      <c r="C54" s="10" t="inlineStr">
+        <is>
+          <t>Таблетница на неделю 2 приема большая, контейнер для лекарств, черная</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -10910,6 +11125,11 @@
           <t>АРОЛС</t>
         </is>
       </c>
+      <c r="X54" s="10" t="inlineStr">
+        <is>
+          <t>#органайзер_для_таблеток #контейнер_для_лекарств #на_неделю #утро_вечер #для_витаминов #хранение_лекарств #в_дорогу #аптечка</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -10922,9 +11142,9 @@
           <t>Таблетница</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Таблетница прям 7*2 черн/цветн</t>
+      <c r="C55" s="10" t="inlineStr">
+        <is>
+          <t>Таблетница на неделю утро вечер, органайзер для таблеток, цветная</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -10954,6 +11174,11 @@
           <t>АРОЛС</t>
         </is>
       </c>
+      <c r="X55" s="10" t="inlineStr">
+        <is>
+          <t>#органайзер_для_таблеток #контейнер_для_лекарств #на_неделю #утро_вечер #для_витаминов #хранение_лекарств #в_дорогу #аптечка</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -10966,9 +11191,9 @@
           <t>Таблетница</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Таблетница прям 7*2 бел/цветн</t>
+      <c r="C56" s="10" t="inlineStr">
+        <is>
+          <t>Таблетница на неделю 2 приема, контейнер для таблеток, прозрачная</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -10998,6 +11223,11 @@
           <t>АРОЛС</t>
         </is>
       </c>
+      <c r="X56" s="10" t="inlineStr">
+        <is>
+          <t>#органайзер_для_таблеток #контейнер_для_лекарств #на_неделю #утро_вечер #для_витаминов #хранение_лекарств #в_дорогу #аптечка</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -11010,9 +11240,9 @@
           <t>Таблетница</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Таблетница прям 7*2 сирен/цветн</t>
+      <c r="C57" s="10" t="inlineStr">
+        <is>
+          <t>Таблетница на неделю 2 приема или на 14 дней, органайзер, сиреневая</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -11042,6 +11272,11 @@
           <t>АРОЛС</t>
         </is>
       </c>
+      <c r="X57" s="10" t="inlineStr">
+        <is>
+          <t>#органайзер_для_таблеток #контейнер_для_лекарств #на_неделю #утро_вечер #для_витаминов #хранение_лекарств #в_дорогу #аптечка</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -11054,9 +11289,9 @@
           <t>Таблетница</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Таблетница круглая 7*2 черн Д</t>
+      <c r="C58" s="10" t="inlineStr">
+        <is>
+          <t>Таблетница на неделю 2 приема круглая, органайзер для таблеток, черная</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -11083,6 +11318,11 @@
           <t>АРОЛС</t>
         </is>
       </c>
+      <c r="X58" s="10" t="inlineStr">
+        <is>
+          <t>#органайзер_для_таблеток #контейнер_для_лекарств #на_неделю #утро_вечер #для_витаминов #хранение_лекарств #в_дорогу #аптечка</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -11095,9 +11335,9 @@
           <t>Таблетница</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Таблетница круглая 7*2 черн/цвет Д</t>
+      <c r="C59" s="10" t="inlineStr">
+        <is>
+          <t>Таблетница на неделю 2 приема круглая, органайзер для таблеток, цветная</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -11124,6 +11364,11 @@
           <t>АРОЛС</t>
         </is>
       </c>
+      <c r="X59" s="10" t="inlineStr">
+        <is>
+          <t>#органайзер_для_таблеток #контейнер_для_лекарств #на_неделю #утро_вечер #для_витаминов #хранение_лекарств #в_дорогу #аптечка</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -11154,9 +11399,9 @@
           <t>Таблетница</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Таблетница круглая 7*2 сер</t>
+      <c r="C61" s="10" t="inlineStr">
+        <is>
+          <t>Таблетница на неделю 2 приема круглая компактная, органайзер, серая</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -11186,6 +11431,11 @@
           <t>АРОЛС</t>
         </is>
       </c>
+      <c r="X61" s="10" t="inlineStr">
+        <is>
+          <t>#органайзер_для_таблеток #контейнер_для_лекарств #на_неделю #утро_вечер #для_витаминов #хранение_лекарств #в_дорогу #аптечка</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -11198,9 +11448,9 @@
           <t>Таблетница</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Таблетница круглая 7*2 сер /цвет</t>
+      <c r="C62" s="10" t="inlineStr">
+        <is>
+          <t>Таблетница на неделю утро вечер круглая, контейнер для лекарств, цветная</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -11230,6 +11480,11 @@
           <t>АРОЛС</t>
         </is>
       </c>
+      <c r="X62" s="10" t="inlineStr">
+        <is>
+          <t>#органайзер_для_таблеток #контейнер_для_лекарств #на_неделю #утро_вечер #для_витаминов #хранение_лекарств #в_дорогу #аптечка</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -11242,9 +11497,9 @@
           <t>Таблетница</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Таблетница круглая 7*2 бел</t>
+      <c r="C63" s="10" t="inlineStr">
+        <is>
+          <t>Таблетница круглая на неделю 2 приема, контейнер для лекарств, прозрачная</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -11274,6 +11529,11 @@
           <t>АРОЛС</t>
         </is>
       </c>
+      <c r="X63" s="10" t="inlineStr">
+        <is>
+          <t>#органайзер_для_таблеток #контейнер_для_лекарств #на_неделю #утро_вечер #для_витаминов #хранение_лекарств #в_дорогу #аптечка</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -11286,9 +11546,9 @@
           <t>Игрушка для животных</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Мяч регби красный</t>
+      <c r="C64" s="10" t="inlineStr">
+        <is>
+          <t>Мячик для собак мелких пород на резинке, игрушка регби 7 см</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -11315,6 +11575,11 @@
           <t>АРОЛС</t>
         </is>
       </c>
+      <c r="X64" s="10" t="inlineStr">
+        <is>
+          <t>#игрушки_для_собак #прочная_игрушка #для_крупных_пород #для_мелких_пород #канат_для_собак #активные_игры #для_питомца</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -11327,9 +11592,9 @@
           <t>Игрушка для животных</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Мяч регби синий</t>
+      <c r="C65" s="10" t="inlineStr">
+        <is>
+          <t>Мячик для собак мелких пород на веревке, прочная игрушка, синий</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -11356,6 +11621,11 @@
           <t>АРОЛС</t>
         </is>
       </c>
+      <c r="X65" s="10" t="inlineStr">
+        <is>
+          <t>#игрушки_для_собак #прочная_игрушка #для_крупных_пород #для_мелких_пород #канат_для_собак #активные_игры #для_питомца</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -11368,9 +11638,9 @@
           <t>Игрушка для животных</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Мяч шина красный</t>
+      <c r="C66" s="10" t="inlineStr">
+        <is>
+          <t>Мяч для собак крупных пород на резинке, прочная игрушка, красный</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -11397,6 +11667,11 @@
           <t>АРОЛС</t>
         </is>
       </c>
+      <c r="X66" s="10" t="inlineStr">
+        <is>
+          <t>#игрушки_для_собак #прочная_игрушка #для_крупных_пород #для_мелких_пород #канат_для_собак #активные_игры #для_питомца</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -11409,9 +11684,9 @@
           <t>Игрушка для животных</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Мяч шина синий</t>
+      <c r="C67" s="10" t="inlineStr">
+        <is>
+          <t>Мяч для собак крупных пород на веревке, прочная игрушка, синий</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -11438,6 +11713,11 @@
           <t>АРОЛС</t>
         </is>
       </c>
+      <c r="X67" s="10" t="inlineStr">
+        <is>
+          <t>#игрушки_для_собак #прочная_игрушка #для_крупных_пород #для_мелких_пород #канат_для_собак #активные_игры #для_питомца</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -11450,9 +11730,9 @@
           <t>Игрушка для животных</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Канат бол бежевый 55см/520гр</t>
+      <c r="C68" s="10" t="inlineStr">
+        <is>
+          <t>Канат для собак крупных пород, игрушка петля 55 см, хлопок</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -11474,6 +11754,11 @@
           <t>АРОЛС</t>
         </is>
       </c>
+      <c r="X68" s="10" t="inlineStr">
+        <is>
+          <t>#игрушки_для_собак #прочная_игрушка #для_крупных_пород #для_мелких_пород #канат_для_собак #активные_игры #для_питомца</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -11486,9 +11771,9 @@
           <t>Игрушка для животных</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Канат мал желтый 55см/330гр</t>
+      <c r="C69" s="10" t="inlineStr">
+        <is>
+          <t>Канат для собак средних пород, игрушка жгут 55 см, хлопок</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -11510,6 +11795,11 @@
           <t>АРОЛС</t>
         </is>
       </c>
+      <c r="X69" s="10" t="inlineStr">
+        <is>
+          <t>#игрушки_для_собак #прочная_игрушка #для_крупных_пород #для_мелких_пород #канат_для_собак #активные_игры #для_питомца</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -11522,9 +11812,9 @@
           <t>Пробка</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Набор пробок 4 шт. в коробке нежн</t>
+      <c r="C70" s="10" t="inlineStr">
+        <is>
+          <t>Пробка для бутылки и вина силиконовая многоразовая, набор 4 шт</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -11554,6 +11844,11 @@
           <t>АРОЛС</t>
         </is>
       </c>
+      <c r="X70" s="10" t="inlineStr">
+        <is>
+          <t>#пробка_для_вина #для_шампанского #винные_аксессуары #сервировка #многоразовая #барные_аксессуары</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -11566,9 +11861,9 @@
           <t>Пробка</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Набор пробок 4 шт. в коробке ярк</t>
+      <c r="C71" s="10" t="inlineStr">
+        <is>
+          <t>Пробка для бутылки вина многоразовая, крышка закрывашка, 4 шт</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -11598,6 +11893,11 @@
           <t>АРОЛС</t>
         </is>
       </c>
+      <c r="X71" s="10" t="inlineStr">
+        <is>
+          <t>#пробка_для_вина #для_шампанского #винные_аксессуары #сервировка #многоразовая #барные_аксессуары</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -11610,9 +11910,9 @@
           <t>Пробка</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Набор пробок 4 шт.</t>
+      <c r="C72" s="10" t="inlineStr">
+        <is>
+          <t>Пробка для вина и шампанского силиконовая, стоппер бутылки 4 шт</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -11639,6 +11939,11 @@
           <t>АРОЛС</t>
         </is>
       </c>
+      <c r="X72" s="10" t="inlineStr">
+        <is>
+          <t>#пробка_для_вина #для_шампанского #винные_аксессуары #сервировка #многоразовая #барные_аксессуары</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -11651,9 +11956,9 @@
           <t>Шпатель-скребок кондитерский</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Шпатель желтый</t>
+      <c r="C73" s="10" t="inlineStr">
+        <is>
+          <t>Шпатель скребок кондитерский для теста стальной, лопатка, желтый</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -11683,6 +11988,11 @@
           <t>АРОЛС</t>
         </is>
       </c>
+      <c r="X73" s="10" t="inlineStr">
+        <is>
+          <t>#кондитерский_инвентарь #для_теста #выпечка #для_кондитера #скребок_для_теста #лопатка</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -11695,9 +12005,9 @@
           <t>Кухонный нож</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Нож для пиццы желтый</t>
+      <c r="C74" s="10" t="inlineStr">
+        <is>
+          <t>Нож для пиццы и теста качающийся с чехлом 15 см, тесторезка, желтый</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -11724,6 +12034,11 @@
           <t>АРОЛС</t>
         </is>
       </c>
+      <c r="X74" s="10" t="inlineStr">
+        <is>
+          <t>#нож_для_пиццы #для_теста #тесторезка #кухонные_принадлежности #выпечка #для_кондитера</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -11736,9 +12051,9 @@
           <t>Кухонный нож</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Нож для пиццы зеленый</t>
+      <c r="C75" s="10" t="inlineStr">
+        <is>
+          <t>Нож для пиццы и теста качающийся с чехлом 15 см, резак, зеленый</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -11763,6 +12078,11 @@
       <c r="R75" t="inlineStr">
         <is>
           <t>АРОЛС</t>
+        </is>
+      </c>
+      <c r="X75" s="10" t="inlineStr">
+        <is>
+          <t>#нож_для_пиццы #для_теста #тесторезка #кухонные_принадлежности #выпечка #для_кондитера</t>
         </is>
       </c>
     </row>

--- a/docs/ozon/Озон_рабочая_книга.xlsx
+++ b/docs/ozon/Озон_рабочая_книга.xlsx
@@ -139,7 +139,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -171,6 +171,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -11130,6 +11133,25 @@
           <t>#органайзер_для_таблеток #контейнер_для_лекарств #на_неделю #утро_вечер #для_витаминов #хранение_лекарств #в_дорогу #аптечка</t>
         </is>
       </c>
+      <c r="Y54" s="15" t="inlineStr">
+        <is>
+          <t>Таблетница на неделю 2 приема: большой органайзер для таблеток на 14 ячеек, футляр 15 × 9 × 4 см. Семь съёмных контейнеров по дням, в каждом два отсека - утро и вечер.
+Кому подходит
+Тем, кто принимает несколько препаратов сразу и раскладывает их на неделю вперёд: пожилым родителям, людям на постоянной терапии, тем, кто пьёт витамины курсом. Строгий чёрный корпус - вариант для рабочего стола и мужской сумки.
+Семь контейнеров, а не одна коробка
+Контейнеры вынимаются из футляра поодиночке. Запас на неделю раскладывается дома, с собой берётся один, тот что нужен сегодня. Контейнер 7,8 × 3,5 × 1,8 см, помещается в карман и в небольшую сумку. Остальные шесть остаются в футляре.
+Утро и вечер разделены
+В каждом контейнере две откидные половины с отдельными крышками: на одной солнце, на другой луна. Открывается только та половина, которая нужна. Вечерняя доза не смешивается с утренней, а по пустому отсеку видно, принята утренняя или нет.
+Чёрный корпус и чёрные контейнеры
+Дни различаются надписью - SUN, MON, TUE и далее. Цветных вставок нет, коробка не выглядит игрушечной.
+Что в неё складывают
+Таблетки, капсулы, витамины и добавки. Обычная раскладка: назначенные препараты в утренние отсеки, витамины и добавки в вечерние, чтобы не путать обязательное с необязательным.
+Размер и вес
+Футляр 15 × 9 × 4 см, 170 граммов пустым, материал пластик. Плоский: лежит в ящике тумбы, в сумке и в бардачке, не выпирает.
+Уход
+Моется тёплой водой, перед раскладкой просушивается - от влаги таблетки крошатся. Заполненный контейнер держат в недоступном для детей месте.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -11179,6 +11201,25 @@
           <t>#органайзер_для_таблеток #контейнер_для_лекарств #на_неделю #утро_вечер #для_витаминов #хранение_лекарств #в_дорогу #аптечка</t>
         </is>
       </c>
+      <c r="Y55" s="15" t="inlineStr">
+        <is>
+          <t>Таблетница на неделю утро вечер: органайзер для таблеток на 14 ячеек, футляр 15 × 9 × 4 см. Семь съёмных контейнеров, каждый своего цвета - день опознаётся по цвету, а не по мелкой надписи.
+Кому подходит
+Тем, кто принимает лекарства утром спросонья и вечером перед сном, и тем, кто раскладывает таблетки не себе, а родителям: по цвету видно, тот контейнер взят или соседний.
+Цвет вместо чтения
+Красный, оранжевый, жёлтый, зелёный, голубой, синий, фиолетовый - семь контейнеров идут по порядку дней. Чтобы найти сегодняшний, не нужно вглядываться в буквы: достаточно запомнить, что вторник жёлтый. Разница между «взял и пошёл» и «сначала нашёл очки».
+Утро и вечер разделены
+В каждом контейнере две откидные половины с отдельными крышками, на одной солнце, на другой луна. Открывается только нужная. По пустой половине видно, принята доза или нет.
+Один контейнер берётся с собой
+Контейнеры вынимаются поодиночке. Контейнер 7,8 × 3,5 × 1,8 см помещается в карман, в косметичку, в небольшую сумку. Футляр с остальными шестью остаётся дома.
+Что в неё складывают
+Таблетки, капсулы, витамины и добавки. Обычная раскладка: назначенные препараты в утренние отсеки, витамины и добавки в вечерние.
+Размер и вес
+Футляр 15 × 9 × 4 см, 170 граммов пустым, материал пластик. Дымчатый пластик полупрозрачный: видно, какие контейнеры ещё полные, не открывая крышку.
+Уход
+Моется тёплой водой, перед раскладкой просушивается. Заполненный контейнер держат в недоступном для детей месте.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -11228,6 +11269,25 @@
           <t>#органайзер_для_таблеток #контейнер_для_лекарств #на_неделю #утро_вечер #для_витаминов #хранение_лекарств #в_дорогу #аптечка</t>
         </is>
       </c>
+      <c r="Y56" s="15" t="inlineStr">
+        <is>
+          <t>Таблетница на неделю 2 приема: контейнер для таблеток на 14 ячеек в прозрачном корпусе, футляр 15 × 9 × 4 см. Семь съёмных контейнеров по дням, утро и вечер в каждом.
+Кому подходит
+Тем, кто хочет видеть остаток не открывая коробку: сколько дней уже пройдено и когда пора раскладывать следующую неделю. Удобно, когда таблетки раскладывает один человек, а принимает другой.
+Прозрачный корпус
+Крышка и стенки прозрачные, контейнеры цветные. Взгляд на закрытый футляр сразу отвечает, дошли вы до четверга или нет, и какой контейнер вынули и не поставили обратно.
+Утро и вечер разделены
+В каждом контейнере две откидные половины с отдельными крышками, на одной солнце, на другой луна. Открывается только нужная половина, соседняя доза остаётся закрытой.
+Один контейнер берётся с собой
+Контейнеры вынимаются поодиночке, каждый своего цвета. Контейнер 7,8 × 3,5 × 1,8 см помещается в карман и в небольшую сумку, футляр с остальными шестью остаётся дома.
+Что в неё складывают
+Таблетки, капсулы, витамины и добавки. Обычная раскладка: назначенные препараты в утренние отсеки, витамины и добавки в вечерние, чтобы не путать обязательное с необязательным.
+Размер и вес
+Футляр 15 × 9 × 4 см, 170 граммов пустым, материал пластик. Плоский: лежит в ящике тумбы, в сумке, в бардачке.
+Уход
+Моется тёплой водой, перед раскладкой просушивается - от влаги таблетки крошатся. Заполненный контейнер держат в недоступном для детей месте.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -11277,6 +11337,25 @@
           <t>#органайзер_для_таблеток #контейнер_для_лекарств #на_неделю #утро_вечер #для_витаминов #хранение_лекарств #в_дорогу #аптечка</t>
         </is>
       </c>
+      <c r="Y57" s="15" t="inlineStr">
+        <is>
+          <t>Таблетница на неделю 2 приема или на 14 дней: семь съёмных контейнеров, в каждом две откидные половины, всего 14 отсеков. Футляр 15 × 9 × 4 см. При одном приёме в день раскладки хватает на две недели.
+Кому подходит
+Тем, у кого приём один раз в день и раскладывать каждую неделю не хочется, и тем, кто уезжает на две недели: запас помещается в одну коробку.
+Две недели вместо одной
+При одном приёме отсеки заполняются подряд: четырнадцать отсеков - четырнадцать дней. Раскладывать приходится вдвое реже. При двух приёмах работает обычная схема, утро и вечер, семь дней.
+Утро и вечер разделены
+В каждом контейнере две откидные половины с отдельными крышками, на одной солнце, на другой луна. Открывается только нужная, соседняя доза не высыпается.
+Один контейнер берётся с собой
+Контейнеры вынимаются поодиночке, каждый своего цвета. Контейнер 7,8 × 3,5 × 1,8 см помещается в карман и в небольшую сумку.
+Что в неё складывают
+Таблетки, капсулы, витамины и добавки. Обычная раскладка: назначенные препараты в утренние отсеки, витамины и добавки в вечерние.
+Размер и вес
+Футляр 15 × 9 × 4 см, 170 граммов пустым, материал пластик. Корпус сиреневый, контейнеры цветные.
+Уход
+Моется тёплой водой, перед раскладкой просушивается. Заполненный контейнер держат в недоступном для детей месте.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -11323,6 +11402,27 @@
           <t>#органайзер_для_таблеток #контейнер_для_лекарств #на_неделю #утро_вечер #для_витаминов #хранение_лекарств #в_дорогу #аптечка</t>
         </is>
       </c>
+      <c r="Y58" s="15" t="inlineStr">
+        <is>
+          <t>Таблетница на неделю 2 приема, круглая: семь круглых контейнеров в футляре 15 × 7 × 7 см, 14 отсеков. Крышка фиксируется креплениями и не раскрывается сама.
+Кому подходит
+Тем, кто возит таблетницу в сумке, рюкзаке и чемодане: содержимое не рассыпается в дороге. Строгий чёрный корпус без цветных вставок.
+Крепления на корпусе
+Отличие этой сборки от простой круглой - крепления по краю крышки. Футляр держится закрытым сам, контейнеры остаются на местах.
+Круглый контейнер удобнее в руке
+Контейнер 6 см в поперечнике и 1,8 см толщиной. Плоский и без углов: не цепляется в кармане, вынимается одной рукой. Таблетки лежат в один слой, нужную видно сразу.
+Утро и вечер разделены
+Контейнер поделён надвое, у каждой половины своя откидная крышка: на одной солнце, на другой луна. Открывается только нужная. По пустой половине видно, принята доза или нет.
+Чёрный корпус, чёрные контейнеры
+Дни различаются надписью - Sun, Mon, Tue и далее. Вид строгий, коробка не выглядит игрушечной ни на рабочем столе, ни в мужской сумке.
+Что в неё складывают
+Таблетки, капсулы, витамины и добавки. Обычная раскладка: назначенные препараты в утренние отсеки, витамины и добавки в вечерние.
+Размер и вес
+Футляр 15 × 7 × 7 см, 165 граммов пустым, материал пластик. Помещается в ящик тумбы и в дорожную сумку.
+Уход
+Моется тёплой водой, перед раскладкой просушивается. Заполненный контейнер держат в недоступном для детей месте.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -11369,6 +11469,27 @@
           <t>#органайзер_для_таблеток #контейнер_для_лекарств #на_неделю #утро_вечер #для_витаминов #хранение_лекарств #в_дорогу #аптечка</t>
         </is>
       </c>
+      <c r="Y59" s="15" t="inlineStr">
+        <is>
+          <t>Таблетница на неделю 2 приема, круглая цветная: семь круглых контейнеров разных цветов, 14 отсеков, футляр 15 × 7 × 7 см. Крышка фиксируется креплениями и не раскрывается сама.
+Кому подходит
+Тем, кто возит таблетницу с собой и хочет находить нужный день по цвету, а не по надписи: в дороге это быстрее, а крепления держат содержимое на местах.
+Крепления на корпусе
+Отличие этой сборки от простой круглой - крепления по краю крышки. Футляр держится закрытым в сумке, рюкзаке и чемодане, контейнеры остаются на местах.
+Цвет вместо чтения
+Семь контейнеров идут цветами по порядку дней. Найти сегодняшний можно не вглядываясь в мелкие буквы на торце: достаточно запомнить, что среда зелёная.
+Круглый контейнер удобнее в руке
+Контейнер 6 см в поперечнике и 1,8 см толщиной. Без углов: не цепляется в кармане, вынимается из сумки одной рукой. Таблетки лежат в один слой.
+Утро и вечер разделены
+Контейнер поделён надвое, у каждой половины своя откидная крышка: на одной солнце, на другой луна. Открывается только нужная половина.
+Что в неё складывают
+Таблетки, капсулы, витамины и добавки. Обычная раскладка: назначенные препараты в утренние отсеки, витамины и добавки в вечерние.
+Размер и вес
+Футляр 15 × 7 × 7 см, 165 граммов пустым, материал пластик. Корпус чёрный дымчатый, контейнеры цветные.
+Уход
+Моется тёплой водой, перед раскладкой просушивается. Заполненный контейнер держат в недоступном для детей месте.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -11436,6 +11557,25 @@
           <t>#органайзер_для_таблеток #контейнер_для_лекарств #на_неделю #утро_вечер #для_витаминов #хранение_лекарств #в_дорогу #аптечка</t>
         </is>
       </c>
+      <c r="Y61" s="15" t="inlineStr">
+        <is>
+          <t>Таблетница на неделю 2 приема, круглая и компактная: семь круглых контейнеров в футляре 15 × 7 × 7 см, 14 отсеков. Один контейнер - один день, 6 см в поперечнике, помещается в ладонь.
+Кому подходит
+Тем, кто носит таблетки с собой каждый день: круглая шайба ложится в карман ровнее плоского кейса. Серый корпус без цветных вставок - спокойный вариант для сумки и стола.
+Круглый контейнер удобнее в руке
+Контейнер 6 см в поперечнике и 1,8 см толщиной. Плоский и без углов: не цепляется в кармане, не давит через ткань, вынимается из сумки одной рукой. Форма шайбы держит таблетки в один слой, нужную видно сразу.
+Утро и вечер разделены
+Контейнер поделён надвое, у каждой половины своя откидная крышка: на одной солнце, на другой луна. Открывается только нужная. По пустой половине видно, принята доза или нет.
+Серый корпус, серые контейнеры
+Дни различаются надписью - Sun, Mon, Tue и далее. Дымчатый пластик полупрозрачный: содержимое просматривается сквозь стенку, видно, какие контейнеры ещё полные.
+Что в неё складывают
+Таблетки, капсулы, витамины и добавки. Обычная раскладка: назначенные препараты в утренние отсеки, витамины и добавки в вечерние.
+Размер и вес
+Футляр 15 × 7 × 7 см, 150 граммов пустым, материал пластик. По площади компактнее плоской модели, помещается в ящик тумбы и в дорожную сумку.
+Уход
+Моется тёплой водой, перед раскладкой просушивается. Заполненный контейнер держат в недоступном для детей месте.</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -11485,6 +11625,25 @@
           <t>#органайзер_для_таблеток #контейнер_для_лекарств #на_неделю #утро_вечер #для_витаминов #хранение_лекарств #в_дорогу #аптечка</t>
         </is>
       </c>
+      <c r="Y62" s="15" t="inlineStr">
+        <is>
+          <t>Таблетница на неделю утро вечер, круглая: семь круглых контейнеров, каждый своего цвета, 14 отсеков. Футляр 15 × 7 × 7 см, один контейнер 6 см в поперечнике помещается в ладонь.
+Кому подходит
+Тем, кто принимает лекарства дважды в день и не хочет каждый раз искать нужный день: цвет читается быстрее надписи. И тем, кто берёт один день с собой, а остальные оставляет дома.
+Цвет вместо чтения
+Семь контейнеров идут цветами по порядку дней. Чтобы найти сегодняшний, не нужно вглядываться в мелкие буквы на торце - достаточно запомнить, что среда зелёная. Утром спросонья это заметная разница.
+Круглый контейнер удобнее в руке
+Контейнер 6 см в поперечнике и 1,8 см толщиной. Без углов: не цепляется в кармане, вынимается из сумки одной рукой. Таблетки лежат в один слой, нужную видно сразу.
+Утро и вечер разделены
+Контейнер поделён надвое, у каждой половины своя откидная крышка: на одной солнце, на другой луна. Открывается только нужная половина.
+Что в неё складывают
+Таблетки, капсулы, витамины и добавки. Обычная раскладка: назначенные препараты в утренние отсеки, витамины и добавки в вечерние.
+Размер и вес
+Футляр 15 × 7 × 7 см, 150 граммов пустым, материал пластик. Корпус дымчато-серый, полупрозрачный: видно, какие контейнеры ещё полные.
+Уход
+Моется тёплой водой, перед раскладкой просушивается. Заполненный контейнер держат в недоступном для детей месте.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -11532,6 +11691,25 @@
       <c r="X63" s="10" t="inlineStr">
         <is>
           <t>#органайзер_для_таблеток #контейнер_для_лекарств #на_неделю #утро_вечер #для_витаминов #хранение_лекарств #в_дорогу #аптечка</t>
+        </is>
+      </c>
+      <c r="Y63" s="15" t="inlineStr">
+        <is>
+          <t>Таблетница круглая на неделю 2 приема, маленькая: контейнер одного дня 6 см в поперечнике и 1,8 см толщиной, помещается в ладонь и в карман. Семь контейнеров, 14 отсеков, футляр 15 × 7 × 7 см.
+Кому подходит
+Тем, кто носит таблетки с собой: на работу, в поездку, в спортивную сумку. Расчёт этой модели - карман, а не тумба.
+Размер под сумку
+Из футляра вынимается один контейнер толщиной 1,8 см. Он ложится в карман брюк, в карман куртки, в косметичку и в маленькую сумку, не выпирая. Остальные шесть остаются дома в футляре.
+Прозрачный корпус
+Футляр прозрачный, контейнеры цветные: видно, какие дни ещё заполнены, не открывая крышку. Понятно, дошли вы до четверга или пора раскладывать следующую неделю.
+Утро и вечер разделены
+Контейнер поделён надвое, у каждой половины своя откидная крышка: на одной солнце, на другой луна. Открывается только нужная, вторая доза остаётся закрытой.
+Что в неё складывают
+Таблетки, капсулы, витамины и добавки. Обычная раскладка: назначенные препараты в утренние отсеки, витамины и добавки в вечерние.
+Размер и вес
+Футляр 15 × 7 × 7 см, 150 граммов пустым, материал пластик.
+Уход
+Моется тёплой водой, перед раскладкой просушивается - от влаги таблетки крошатся. Заполненный контейнер держат в недоступном для детей месте.</t>
         </is>
       </c>
     </row>

--- a/docs/ozon/Озон_рабочая_книга.xlsx
+++ b/docs/ozon/Озон_рабочая_книга.xlsx
@@ -8965,6 +8965,26 @@
           <t>#сетка_для_стирки #деликатная_стирка #стирка_белья #уход_за_одеждой #для_бюстгальтера #защита_белья #стиральная_машина</t>
         </is>
       </c>
+      <c r="Y6" s="15" t="inlineStr">
+        <is>
+          <t>Мешки для стирки белья, набор из семи с жёстким контейнером под бюстгальтер: от 40 × 50 см под рубашки до 18 × 22 под носки. Семь размеров закрывают всю закладку.
+Кому подходит
+Тем, кто стирает на семью и каждый раз делит бельё на заходы: деликатное отдельно, носки отдельно, бюстгальтер руками.
+Что в наборе
+Рубашки и объёмные вещи - 40 × 50 см. Платья и блузки - 30 × 40. Деликатные ткани - 20 × 30. Нижнее бельё - 20 × 20. Носки - 18 × 22. Бюстгальтеры - два мешка: мягкий 15 × 18 и жёсткий каркасный контейнер 15 × 17.
+Каркасный контейнер - то, чего нет в обычных наборах
+Бюстгальтер в мягкой сетке складывается вдвое, поролон заминается, косточка выгибается. Седьмой предмет набора - жёсткий цилиндр: чашки лежат в нём как в коробке и не сминаются под весом белья.
+Стирка перестаёт делиться на заходы
+Семь мешков позволяют разложить всё сразу и запустить одну стирку: вещи разного типа не соприкасаются, но едут вместе.
+Молния с фиксатором
+У каждого мешка молния и пластиковый фиксатор на бегунке: прижимает замок, чтобы тот не разошёлся на отжиме.
+Петля и швы
+У каждого вшита петелька - повесить сушиться прямо с содержимым или убрать на крючок. Края обмётаны, сетка плотная: держит форму, высокую температуру и многократные стирки. Полиэстер не линяет и не красит бельё.
+Как стирать
+Каждый мешок заполнять на две трети, молнию закрывать до конца, бегунок заводить под фиксатор. Режим по ярлыку вещей внутри. Бюстгальтер застегнуть на крючки и уложить чашка в чашку.
+Шесть мешков складываются в ладонь, седьмой держит форму для бюстгальтера. Цвет бежевый. В комплекте семь мешков.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -9014,6 +9034,26 @@
           <t>#сетка_для_стирки #деликатная_стирка #стирка_белья #уход_за_одеждой #для_бюстгальтера #защита_белья #стиральная_машина</t>
         </is>
       </c>
+      <c r="Y7" s="15" t="inlineStr">
+        <is>
+          <t>Чехол мешок для стирки бюстгальтера с каркасом: жёсткий цилиндр 17 × 15 см. Чашки лежат внутри как в коробке и не сминаются под весом остального белья.
+Кому подходит
+Тем, у кого бюстгальтеры с косточками, поролоном и пуш-апом, и кто стирает их в машине, а не руками. Один мешок рассчитан на один бюстгальтер, уложенный чашка в чашку.
+Почему нужен именно каркас
+В обычной плоской сетке чашка складывается вдвое, поролон заминается, косточка выгибается и со временем выходит из шва. Здесь дно и крышка усилены пластиковыми каркасами: мешок держит объём и пустым, и с бельём внутри.
+Молния с фиксатором
+Молния идёт по кругу крышки, на бегунке пластиковый фиксатор - он прижимает замок, чтобы тот не разошёлся при отжиме. Мешок остаётся закрытым весь цикл.
+Объёмная сетка
+Ткань в два слоя, между ними воздух. Вода и порошок проходят свободно, полоскание не остаётся внутри. Ячейка внешнего слоя около 2 мм, внутреннего около 0,5 мм - сквозных отверстий нет.
+Размер
+Цилиндр 17 см в ширину и 15 в высоту. Чашки до 75J входят. Заполнять на две трети объёма: так вещь лежит свободно и полощется целиком.
+Петля
+Текстильная петля сбоку - повесить сушиться прямо с бельём внутри или убрать на крючок в ванной.
+Как стирать
+Бюстгальтер застегнуть на крючки, чтобы они не цеплялись за кружево, уложить чашка в чашку. Деликатный режим, 30 °C. Отжим по бирке белья, для деликатных тканей это 400-800 оборотов; корпус проверен на 1000. Сушить в расправленном виде.
+Цвет бежевый, однотонный. В комплекте один мешок.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -9060,6 +9100,27 @@
           <t>#сетка_для_стирки #деликатная_стирка #стирка_белья #уход_за_одеждой #для_бюстгальтера #защита_белья #стиральная_машина</t>
         </is>
       </c>
+      <c r="Y8" s="15" t="inlineStr">
+        <is>
+          <t>Мешки для стирки одежды и носков, набор из трёх: 40 × 50 см под рубашки и объёмные вещи, 30 × 40 под платья и блузки, 18 × 22 под носки и мелочь. Все три на молнии.
+Кому подходит
+Тем, кто устал доставать носки из фильтра, и тем, кто хочет стирать рубашки и платья в машине, не разбирая закладку на несколько заходов.
+Три размера - три задачи
+Мешок работает, когда вещь лежит в нём свободно. Один универсальный либо мал для рубашки, либо велик для носков. Здесь под каждую закладку свой объём: большой берёт свитер или рубашку, средний платье и блузку, маленький собирает носки.
+Носки остаются парой
+Носок уходит под манжету люка и остаётся в фильтре - это конструкция машины, а не примета. Мешок 18 × 22 держит их вместе: закинули парой, достали парой.
+Молния с фиксатором
+У каждого мешка молния и пластиковый фиксатор на бегунке - он прижимает замок, чтобы тот не разошёлся на отжиме.
+Петля
+У каждого вшита петелька: повесить сушиться прямо с содержимым или убрать на крючок в ванной.
+Сетка
+Трёхслойная ячеистая ткань, её называют 3D-сеткой: держит форму, высокую температуру и многократные стирки, хорошо выполаскивается. Шерстяные вещи в ней стирать можно - мешок снимает трение и не даёт волокну скатываться.
+Как стирать
+Заполнять на две трети, молнию закрывать до конца, бегунок заводить под фиксатор. Режим по ярлыку самих вещей.
+Между стирками мешки складываются плоско и работают как сортировка: грязное сразу попадает в нужный, и закладку не приходится собирать по квартире.
+Цвет бежевый. В комплекте три мешка.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -9109,6 +9170,27 @@
           <t>#сетка_для_стирки #деликатная_стирка #стирка_белья #уход_за_одеждой #для_бюстгальтера #защита_белья #стиральная_машина</t>
         </is>
       </c>
+      <c r="Y9" s="15" t="inlineStr">
+        <is>
+          <t>Мешочки для стирки белья и шелка в машинке, набор из трёх: ракушка под бюстгальтер, цилиндр 20 × 30 см под шёлк и деликатные ткани, мешок 20 × 20 см под нижнее бельё.
+Кому подходит
+Тем, у кого в стирку идут шёлк, кружево и тонкий трикотаж, и кто хочет стирать их машиной, а не в тазу.
+Ракушка под бюстгальтер
+Форма повторяет чашку: бюстгальтер лежит в ней как на полке, не складывается вдвое и не мнётся под весом остального белья. В плоском мешке чашка складывается, поролон заминается, косточка со временем выходит из шва.
+Цилиндр под деликатные ткани
+Шёлк, кружево, тонкий трикотаж, колготки - всё, что цепляется за чужие молнии и пуговицы. Объём 20 × 30 см позволяет вещам лежать свободно: только так они прополаскиваются.
+Мешок под нижнее бельё
+Трусики и носки в общей стирке уходят под манжету люка и оседают в фильтре. Мешок 20 × 20 держит их вместе: закинули горстью, достали горстью.
+Молния с фиксатором
+У каждого мешочка молния и пластиковый фиксатор на бегунке: прижимает замок, чтобы тот не разошёлся на отжиме.
+Петля и швы
+У каждого вшита петелька - повесить сушиться прямо с бельём или убрать на крючок. Сетка плотная, швы обмётаны, вода и порошок проходят свободно.
+Как стирать
+Бюстгальтер застегнуть на крючки и уложить чашка в чашку. Остальные мешочки заполнять свободно, не набивая. Деликатный режим, 30 °C, отжим минимальный.
+Ракушка держит форму кроем, без жёсткого пластика: чашки защищены, а сам чехол складывается плоско. Жёсткий каркасный контейнер есть отдельной карточкой и в наборе из семи.
+Цвет бежевый. В комплекте три мешочка.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -9158,6 +9240,26 @@
           <t>#сетка_для_стирки #деликатная_стирка #стирка_белья #уход_за_одеждой #для_бюстгальтера #защита_белья #стиральная_машина</t>
         </is>
       </c>
+      <c r="Y10" s="15" t="inlineStr">
+        <is>
+          <t>Сетка для стирки белья, мелкая ячейка, набор из трёх мешков: 30 × 40, 40 × 50 и 50 × 60 см. Три размера под разные вещи, до 1,5, 2,5 и 4 кг сухого белья.
+Кому подходит
+Тем, кто стирает всё одной загрузкой и хочет разложить её по типам вещей, и тем, у кого в стирку идут кружево, тонкий трикотаж и вещи с ворсом.
+Три размера и три задачи
+Маленький 30 × 40 до 1,5 кг: носки, нижнее бельё, детские вещи. Средний 40 × 50 до 2,5 кг: футболки, рубашки, трикотаж. Большой 50 × 60 до 4 кг: постельное, свитеры, полотенца.
+Мелкая сетка
+Ячейка мелкая, ткань почти сплошная на просвет. Крючки, молнии и пуговицы не цепляют соседние вещи, кружево не вытягивается, а вода и порошок проходят свободно. От набора с крупной ячейкой отличается только на ощупь: эта мягче. Пошив, швы, фурнитура и размеры у обоих одинаковые.
+Пух и шерсть остаются внутри
+Мелкая ячейка держит то, что сыплется: пуховые вещи, шерстяные свитеры, пледы с ворсом. Наполнитель и ворс остаются в мешке, а не в барабане и фильтре.
+Затяжка со стопором
+У каждого мешка горловина на шнурке с пластиковым стопором. Затянули, сдвинули фиксатор - узел не нужен, и в барабане мешок не раскрывается. Мокрый шнурок развязывать не придётся.
+Как стирать
+Каждый мешок заполнять на две трети - вещам нужно место, чтобы прополоскаться. Режим по ярлыку вещей: сами мешки держат высокую температуру и многократные стирки.
+Разложить один раз
+Три мешка стоят открытыми, вещи попадают сразу в нужный, и к стирке закладка уже разобрана. Пустые складываются в ладонь и не занимают полку.
+В комплекте три мешка.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -9207,6 +9309,24 @@
           <t>#сетка_для_стирки #деликатная_стирка #стирка_белья #уход_за_одеждой #для_бюстгальтера #защита_белья #стиральная_машина</t>
         </is>
       </c>
+      <c r="Y11" s="15" t="inlineStr">
+        <is>
+          <t>Сетка для стирки белья в машинке, крупная ячейка, набор из трёх: 50 × 60, 40 × 50 и 30 × 40 см. До 4, 2,5 и 1,5 кг сухого белья. Плотные вещи полощутся свободнее.
+Кому подходит
+Тем, кто стирает джинсы, худи, полотенца и постельное: плотная вещь держит внутри много воды, и крупная ячейка выпускает её без задержки.
+Три размера, до 4 кг
+Большой 50 × 60 до 4 кг: свитеры, худи, полотенца, постельное. Средний 40 × 50 до 2,5 кг: джинсы, рубашки, спортивная форма. Маленький 30 × 40 до 1,5 кг: носки, футболки, детские вещи.
+Крупная сетка
+Вода проходит свободно, порошок вымывается, вещь не остаётся мыльной в середине. От набора с мелкой ячейкой отличается только на ощупь: эта жёстче. Пошив, швы, фурнитура и размеры у обоих одинаковые. Для кружева и тонкого трикотажа есть тот же набор с мелкой ячейкой.
+Зачем это машине
+Джинсы и худи без мешка наматываются на вал и сбивают балансировку на отжиме, мелочь уходит в фильтр. Три размера позволяют разложить всю закладку и постирать её за раз.
+Затяжка со стопором
+Горловина каждого мешка стягивается шнурком с пластиковым стопором. Затянули, сдвинули - узел не нужен, и в барабане мешок не раскрывается.
+Как стирать
+Заполнять на две трети, затягивать шнурок и сдвигать стопор. Режим по ярлыку вещей; мешки выдерживают высокую температуру и многократные стирки. Сушить расправленными. Килограммы указаны для сухого белья в свободной укладке - при ней вещи простирываются равномерно.
+В комплекте три мешка.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -9256,6 +9376,26 @@
           <t>#сетка_для_стирки #деликатная_стирка #стирка_белья #уход_за_одеждой #для_бюстгальтера #защита_белья #стиральная_машина</t>
         </is>
       </c>
+      <c r="Y12" s="15" t="inlineStr">
+        <is>
+          <t>Мешок для стирки бюстгальтера с каркасом и нижнего белья, набор из двух: жёсткий цилиндр 17 × 15 см под чашки и мягкая ракушка 18 × 16 см под колготки и мелочь.
+Кому подходит
+Тем, кто стирает бельё одной загрузкой и не хочет делить её на заходы: бюстгальтер едет в жёстком мешке, колготки и трусики в мягком, обе вещи в одной машине.
+Жёсткий - для бюстгальтера
+В обычной сетке чашка складывается вдвое, поролон заминается, косточка выгибается. Дно и крышка цилиндра усилены пластиковыми каркасами: чашка пуш-ап держит форму и на высоких оборотах.
+Мягкий - для колготок
+Капроновые колготки в общей стирке цепляются за молнии и крючки соседних вещей и выходят со стрелками. В отдельной ракушке они ни с чем не соприкасаются и не перекручиваются вокруг других вещей.
+Молния с фиксатором
+У обоих мешков молния идёт по кругу, на бегунках пластиковые фиксаторы: прижимают замок, чтобы он не разошёлся на отжиме. Мешки остаются закрытыми весь цикл.
+Объёмная сетка
+Два слоя ткани с воздухом между ними. Вода проходит свободно, порошок вымывается, высокую температуру и многократные стирки ткань держит.
+Петли
+У каждого мешка текстильная петля - повесить сушиться прямо с содержимым или убрать на крючок.
+Как стирать
+Бюстгальтер застегнуть на крючки и уложить чашка в чашку. Мелочь в мягкий мешок класть свободно: вещам нужно место, чтобы прополоскаться. Деликатный режим, 30 °C, отжим минимальный. Наполнять на две трети.
+Цвет белый, молнии серые. В комплекте два мешка.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -9297,6 +9437,26 @@
           <t>#сетка_для_стирки #деликатная_стирка #стирка_белья #уход_за_одеждой #для_бюстгальтера #защита_белья #стиральная_машина</t>
         </is>
       </c>
+      <c r="Y13" s="15" t="inlineStr">
+        <is>
+          <t>Мешки для стирки бюстгальтера и нижнего белья, набор из двух: мягкая ракушка 18 × 16 см под колготки, трусики и носки и жёсткий цилиндр 17 × 15 см под чашки.
+Кому подходит
+Тем, у кого мелочь теряется в каждой стирке: носки уходят под манжету люка, колготки выходят со стрелками, а бюстгальтер после машины теряет форму.
+Мелочь собрана в одном месте
+Капроновые колготки в общей стирке цепляются за чужие молнии и крючки. Носки и трусики перекручиваются и оседают в фильтре. Мягкая ракушка 18 × 16 см держит всё это вместе: закинули горстью, достали горстью.
+Бюстгальтеру - отдельный, с каркасом
+Второй мешок в наборе жёсткий, цилиндр 17 × 15 см. В обычной сетке чашка складывается вдвое, поролон заминается, косточка выгибается. Здесь внутри пластиковые рёбра, и чашка лежит как в коробке.
+Молния с фиксатором
+У обоих молния по кругу, на бегунке пластиковый фиксатор: прижимает замок, чтобы тот не разошёлся при отжиме.
+Объёмная сетка
+Два слоя ткани с воздухом между ними: вода и порошок проходят свободно, ничего не остаётся внутри. Ткань выдерживает высокую температуру и многократные стирки.
+Петли
+Текстильная петля у каждого мешка - повесить сушиться с содержимым или убрать на крючок.
+Как стирать
+Мягкий мешок не набивать: половина объёма остаётся свободной, иначе вещи не прополощутся. Бюстгальтер застегнуть на крючки, уложить чашка в чашку. Деликатный режим, 30 °C, отжим минимальный.
+Цвет белый, молнии розовые. Мягкий мешок складывается плоско и занимает в шкафу место одной сложенной футболки. В комплекте два мешка.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -9346,6 +9506,25 @@
           <t>#сетка_для_стирки #деликатная_стирка #стирка_белья #уход_за_одеждой #для_бюстгальтера #защита_белья #стиральная_машина</t>
         </is>
       </c>
+      <c r="Y14" s="15" t="inlineStr">
+        <is>
+          <t>Мешок для стирки пуховика и одеяла, большой, 60 × 80 см, крупная сетка. Объёмная вещь стирается целиком: ячейка пропускает воду свободно и вещь не остаётся мыльной внутри.
+Кому подходит
+Тем, кто стирает дома пуховик, зимнюю куртку, шторы и тюль. Всё это держит внутри много воды, и через плотную сетку такой объём полощется плохо.
+Что сюда помещается
+Пуховик или зимняя куртка целиком. Комплект штор, тюль. Плед, полутороспальное одеяло. Подушка вместе с наполнителем: от размера 50 × 70 входит свободно.
+Размер
+Высота 60 см, ширина 80. Заполнять на две трети: объёмной вещи нужно место, чтобы двигаться в барабане, иначе она сбивается в ком с одной стороны и машина уходит в дисбаланс на отжиме.
+Затяжка со стопором
+Горловина стягивается шнурком с пластиковым стопором. Затянули, сдвинули фиксатор - узел не нужен, и в барабане мешок не раскрывается.
+Как стирать
+Режим по ярлыку самой вещи: пуховику обычно нужен деликатный и низкая температура, шторам щадящий. Мешок выдерживает высокую температуру и многократные стирки, ограничение задаёт содержимое. Сушить расправленным.
+Между стирками
+Пустой мешок складывается в ладонь. В нём удобно хранить сезонные вещи - тот же пуховик до холодов или шторы до окна.
+Для перьевой подушки, шерсти и длинного ворса есть тот же размер с мелкой сеткой: она держит внутри всё, что сыплется.
+В комплекте один мешок.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -9395,6 +9574,25 @@
           <t>#сетка_для_стирки #деликатная_стирка #стирка_белья #уход_за_одеждой #для_бюстгальтера #защита_белья #стиральная_машина</t>
         </is>
       </c>
+      <c r="Y15" s="15" t="inlineStr">
+        <is>
+          <t>Мешок для стирки подушек и пуховика, большой, 60 × 80 см, мелкая сетка. Ячейка держит внутри перо и пух: они не оседают на барабане и не переходят на следующую загрузку.
+Кому подходит
+Тем, кто стирает дома перьевые подушки, шерстяные свитеры, пледы с длинным ворсом и мягкие игрушки с набивкой - всё, что сыплется или линяет на остальное бельё.
+Зачем здесь мелкая ячейка
+Перьевая подушка отдаёт наполнитель через любой шов и любую крупную сетку. Пух оседает на барабане, забивает фильтр и потом переходит на чистое бельё. Мелкая ячейка его не пропускает.
+Что сюда помещается
+Подушка 50 × 70 целиком, вместе с наполнителем. Одеяло 180 × 200 средней плотности. Вещи из ангоры и мохера, детские игрушки. Изделия с пухом и пером стирать можно; для чистого пуха и пера нужен плотный чехол из тика.
+Размер
+Высота 60 см, ширина 80. Заполнять на две трети: подушке нужно место, чтобы перевернуться в барабане и прополоскаться.
+Затяжка со стопором
+Горловина стягивается шнурком, на нём пластиковый стопор. Затянули, сдвинули фиксатор - узел не нужен, и в барабане мешок не раскрывается. Развязывать мокрый шнурок тоже не придётся.
+Как стирать
+Подушку и шерсть - по ярлыку самой вещи, обычно деликатный режим и низкая температура. Сам мешок выдерживает высокую температуру и многократные стирки, ограничение задаёт содержимое. Сушить расправленным.
+Для объёмных вещей в оболочке - пуховика, куртки, штор - есть тот же размер с крупной сеткой, там полоскание свободнее.
+В комплекте один мешок.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -9436,6 +9634,27 @@
           <t>#сетка_для_стирки #деликатная_стирка #стирка_белья #уход_за_одеждой #для_бюстгальтера #защита_белья #стиральная_машина</t>
         </is>
       </c>
+      <c r="Y16" s="15" t="inlineStr">
+        <is>
+          <t>Мешок для стирки обуви каркасный, размер XL, высота 35 см. Берёт пару до 47 размера - то, во что обычный мешок для обуви уже не помещается.
+Кому подходит
+Тем, у кого большой размер ноги и высокие кроссовки: в стандартный мешок на 40-42 размер такая пара входит только сложенной и упирается в сетку.
+Каркас
+Внутри жёсткие рёбра, мешок не сминается под весом обуви и держит форму весь цикл. Удары принимают каркас и объёмная сетка, а не стекло люка: барабан и уплотнитель остаются целыми.
+Молния с фиксатором
+Молния по кругу крышки, на бегунке пластиковый фиксатор. Он прижимает замок, чтобы тот не разошёлся на отжиме, и пара остаётся внутри до конца стирки.
+Объёмная сетка
+Два слоя ткани с воздухом между ними. Вода проходит свободно, порошок вымывается, высокую температуру и многократные стирки ткань держит.
+Что ещё в него кладут
+Мягкие игрушки, объёмные шапки, домашние тапочки, детские сапожки - всё, что нужно отделить от белья и сохранить в форме.
+Петля
+Сбоку текстильная петля: повесить сушиться прямо с содержимым или убрать на крючок.
+Как стирать
+Стельки и шнурки вынуть и стирать отдельно. Пару уложить подошвой к подошве, молнию застегнуть до конца, бегунок завести под фиксатор. Деликатный режим, 30 °C, без отжима. Сушить при комнатной температуре, набив бумагой. Машинную стирку хорошо переносят текстильные кроссовки, кеды и слипоны - под них мешок и сделан.
+Каркас держит форму постоянно, поэтому мешок и работает как коробка для пары.
+В комплекте один мешок.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -9681,6 +9900,26 @@
           <t>#мфр #миофасциальный_релиз #массаж_стоп #йога #пилатес #самомассаж #восстановление</t>
         </is>
       </c>
+      <c r="Y21" s="15" t="inlineStr">
+        <is>
+          <t>Мячик массажный с шипами 6 см, жёсткий пластик. Помещается в ладони: одним мячом прорабатываются стопы, кисти и участок под лопаткой.
+Кому подходит
+Тем, кто занимается дома или в зале и хочет разогреть стопы до занятия и снять напряжение в кистях после упоров.
+Жёсткость высокая
+Мяч не проминается под весом тела. Воздействие точечное и глубокое.
+Диаметр 6 см - точечная проработка
+Шар такого размера помещается в ладони и заходит в свод стопы, между костями кисти, под лопатку. Мячи большего диаметра дают широкое давление и в эти участки не попадают.
+Как пользоваться
+Стопа: мяч кладётся на пол, прокатывается от пятки к пальцам, по минуте на каждую ногу. Кисть: мяч зажимается между ладонями, движения круговые. Спина: мяч прижимается к стене и прокатывается вдоль лопатки.
+Шипы
+Шипы с округлыми концами, из того же материала, что и мяч. Нажим распределяется по площади, кожа не царапается.
+Материал и уход
+ПВХ. Моется водой с мылом, влагу не впитывает, сохнет сразу.
+Габариты
+Диаметр 6 см, вес 40 граммов. Помещается в карман сумки, рюкзак, ящик стола.
+В комплекте один мяч. Бытовой инструмент для самомассажа.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -9730,6 +9969,28 @@
           <t>#мфр #миофасциальный_релиз #массаж_стоп #йога #пилатес #самомассаж #восстановление</t>
         </is>
       </c>
+      <c r="Y22" s="15" t="inlineStr">
+        <is>
+          <t>Мячик массажный с шипами, диаметр 6 см, жёсткий пластик. Полностью ложится в ладонь: кисти и пальцы прорабатываются одной рукой, без опоры.
+Кому подходит
+Тем, кто целый день за клавиатурой: к вечеру напряжение скапливается в ладонях и предплечьях.
+Жёсткость высокая
+Мяч не проминается при нажиме ладонью. Воздействие точечное.
+Кисти после клавиатуры
+Мяч зажимается между ладонями или прижимается ладонью к столу, движения круговые, по минуте на каждую руку.
+Пальцы
+Мяч прокатывается подушечками пальцев по очереди: шипы дают точечный нажим на каждую фалангу. Тот же приём применяют к тыльной стороне ладони.
+Диаметр 6 см
+Шар такого размера полностью ложится в ладонь, его можно удерживать одной рукой и работать без опоры. Мячи большего диаметра из ладони выходят.
+Шипы
+Шипы с округлыми концами, из того же материала, что и мяч. Нажим распределяется по площади, кожа не царапается.
+Материал и уход
+ПВХ. Моется водой с мылом, влагу не впитывает, сохнет сразу.
+Габариты
+Диаметр 6 см, вес 40 граммов. Помещается в карман сумки, рюкзак, ящик рабочего стола.
+В комплекте один мяч. Бытовой инструмент для самомассажа.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -9779,6 +10040,26 @@
           <t>#мфр #миофасциальный_релиз #массаж_стоп #йога #пилатес #самомассаж #восстановление</t>
         </is>
       </c>
+      <c r="Y23" s="15" t="inlineStr">
+        <is>
+          <t>Мячик массажный с шипами, диаметр 6 см, жёсткий пластик. Работает у стены: спину можно проработать самому, без второго человека.
+Кому подходит
+Тем, у кого затекает спина за компьютером и ноет между лопаткой и позвоночником - там, куда рукой не дотянуться.
+Жёсткость высокая
+Мяч не проминается под весом тела. Воздействие точечное и глубокое.
+Спина у стены
+Мяч прижимается к стене спиной и прокатывается вдоль лопатки и вдоль позвоночника, по мышцам справа и слева, не по самим позвонкам. Вес тела задаёт нажим: сильнее прислонились - глубже.
+Шея и надплечья
+Мяч прижимается к стене на уровне трапеции и прокатывается от основания шеи к плечу. Диаметр 6 см позволяет попасть в точку под лопаткой.
+Шипы
+Шипы с округлыми концами, из того же материала, что и мяч. Нажим распределяется по площади, кожа не царапается.
+Материал и уход
+ПВХ. Моется водой с мылом, влагу не впитывает, сохнет сразу.
+Габариты
+Диаметр 6 см, вес 40 граммов. Помещается в сумку, рюкзак, ящик стола.
+В комплекте один мяч. Бытовой инструмент для самомассажа.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -9828,6 +10109,26 @@
           <t>#мфр #миофасциальный_релиз #массаж_стоп #йога #пилатес #самомассаж #восстановление</t>
         </is>
       </c>
+      <c r="Y24" s="15" t="inlineStr">
+        <is>
+          <t>Мячик массажный с шипами, жёсткий, диаметр 6 см. Для кистей и стоп: шар ложится в ладонь и заходит в свод стопы. Оранжевый видно на полу и в сумке.
+Кому подходит
+Тем, кто хочет один мяч и на руки, и на ноги, и тем, кто носит его с собой: яркий цвет не теряется среди инвентаря.
+Жёсткость высокая
+Мяч не проминается при нажиме. Воздействие точечное.
+Кисти и стопы
+Мяч прокатывается между ладонями, по подушечкам пальцев, по своду стопы. По минуте на каждую руку и ногу, сеанс от одной до трёх минут на зону.
+Точечный нажим
+Шипы с округлыми концами создают множество точек контакта. Нажим распределяется по площади и не приходится в одну точку, кожа не царапается.
+Диаметр 6 см
+Шар полностью ложится в ладонь и заходит в свод стопы. Им можно работать одной рукой, без опоры и без второго человека.
+Материал и уход
+ПВХ. Моется водой с мылом, влагу не впитывает, сохнет сразу.
+Габариты
+Диаметр 6 см, вес 40 граммов. Помещается в карман, сумку, ящик стола.
+В комплекте один мяч. Бытовой инструмент для самомассажа.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -9877,6 +10178,26 @@
           <t>#мфр #миофасциальный_релиз #массаж_стоп #йога #пилатес #самомассаж #восстановление</t>
         </is>
       </c>
+      <c r="Y25" s="15" t="inlineStr">
+        <is>
+          <t>Мячик массажный с шипами, диаметр 6 см, жёсткий пластик. Заходит в свод стопы и прокатывает участок между пяткой и подушечкой.
+Кому подходит
+Тем, кто проводит день на ногах: продавцам, поварам, парикмахерам. И тем, у кого к вечеру ноет свод стопы и пятка.
+Жёсткость высокая
+Мяч не проминается под весом тела. Воздействие точечное и глубокое.
+Стопы после дня на ногах
+Мяч кладётся на пол и прокатывается стопой от пятки к пальцам, по минуте на каждую ногу. Нажим задаётся весом: стоя сильнее, сидя мягче.
+Свод стопы
+Диаметр 6 см заходит в свод и достаёт до участка между пяткой и подушечкой. Мячи большего диаметра под сводом не помещаются и катятся по подошве поверхностно.
+Шипы
+Шипы с округлыми концами, из того же материала, что и мяч. Нажим распределяется по площади, кожа не царапается.
+Материал и уход
+ПВХ. Моется водой с мылом, влагу не впитывает, сохнет сразу. Не боится влажного пола и ванной.
+Габариты
+Диаметр 6 см, вес 40 граммов. Помещается в спортивную сумку, рюкзак, ящик стола.
+В комплекте один мяч. Бытовой инструмент для самомассажа.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -9926,6 +10247,26 @@
           <t>#мфр #миофасциальный_релиз #массаж_стоп #йога #пилатес #самомассаж #восстановление</t>
         </is>
       </c>
+      <c r="Y26" s="15" t="inlineStr">
+        <is>
+          <t>Мяч массажный с шипами, 7 см, жёсткий пластик - средний размер линейки. Работает и по спине у стены, и по стопе на полу.
+Кому подходит
+Тем, кто берёт один мяч на всё: семёрка захватывает участок шире шестёрки и при этом ещё заходит под свод стопы, куда девятка не помещается.
+Жёсткость высокая
+Мяч не проминается под весом тела. Воздействие глубокое.
+Спина, плечи, стопы
+У стены мяч прокатывается вдоль лопатки и по трапеции, вес тела задаёт нажим. На полу - стопой от пятки к пальцам. По минуте на зону, движения медленные.
+Средний размер линейки
+Семь сантиметров крупнее шестёрки и мельче девятки. По спине такой мяч берёт полосу мышцы шире, а под сводом стопы всё ещё помещается.
+Шипы
+Шипы с округлыми концами, из того же материала, что и мяч. Нажим распределяется по площади, кожа не царапается.
+Материал и уход
+ПВХ. Моется водой с мылом, влагу не впитывает, сохнет сразу.
+Габариты
+Диаметр 7 см, вес 60 граммов. Помещается в спортивную сумку, рюкзак, ящик стола.
+В комплекте один мяч. Бытовой инструмент для самомассажа.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -9975,6 +10316,28 @@
           <t>#мфр #миофасциальный_релиз #массаж_стоп #йога #пилатес #самомассаж #восстановление</t>
         </is>
       </c>
+      <c r="Y27" s="15" t="inlineStr">
+        <is>
+          <t>Мяч массажный с шипами, диаметр 7 см, жёсткий пластик. Для миофасциального релиза: прокатки мышцы после нагрузки.
+Кому подходит
+Тем, кто тренируется и восстанавливается сам: после бега, зала, длинной прогулки или дня на ногах.
+Жёсткость высокая
+Мяч не проминается под весом тела. Воздействие глубокое.
+После занятия
+Миофасциальный релиз делают после нагрузки, а не до неё: мяч прокатывают по мышце медленно, задерживаясь на участках, где напряжение ощутимее. По минуте на зону, пять-десять минут на подход.
+Где применяют
+Стопа перед упражнениями на равновесие, предплечья после упоров, спина у стены, задняя поверхность бедра сидя на полу. Работают по мышце, обходя кость и сустав.
+Диаметр 7 см
+Средний размер линейки: захватывает участок шире, чем 6 см, и при этом заходит под свод стопы, куда 9 см не помещается.
+Шипы
+Шипы с округлыми концами, из того же материала, что и мяч. Нажим распределяется по площади, кожа не царапается.
+Материал и уход
+ПВХ. Моется водой с мылом, влагу не впитывает, сохнет сразу.
+Габариты
+Диаметр 7 см, вес 60 граммов. Помещается в спортивную сумку, рюкзак, ящик стола.
+В комплекте один мяч. Бытовой инструмент для самомассажа.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -10024,6 +10387,26 @@
           <t>#мфр #миофасциальный_релиз #массаж_стоп #йога #пилатес #самомассаж #восстановление</t>
         </is>
       </c>
+      <c r="Y28" s="15" t="inlineStr">
+        <is>
+          <t>Мяч массажный с шипами, жёсткий, диаметр 7 см. Работает у стены: спина и трапеция прорабатываются самостоятельно, без второго человека.
+Кому подходит
+Тем, у кого к вечеру каменеет трапеция и тянет между лопатками: за рулём, за столом, за прилавком.
+Жёсткость высокая
+Мяч не проминается под весом тела. Воздействие глубокое.
+Спина у стены
+Мяч прижимается к стене спиной и прокатывается вдоль лопатки и вдоль позвоночника, по мышцам справа и слева, не по самим позвонкам. Сильнее прислонились - глубже проработка.
+Плечи и трапеция
+На уровне надплечья мяч прокатывается от основания шеи к плечу. Диаметр 7 см захватывает полосу мышцы шире, чем шестёрка, поэтому проход по трапеции получается за одно движение.
+Шипы
+Шипы с округлыми концами, из того же материала, что и мяч. Нажим распределяется по площади, кожа не царапается.
+Материал и уход
+ПВХ. Моется водой с мылом, влагу не впитывает, сохнет сразу.
+Габариты
+Диаметр 7 см, вес 60 граммов. Помещается в спортивную сумку, рюкзак, ящик стола.
+В комплекте один мяч. Бытовой инструмент для самомассажа.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -10073,6 +10456,28 @@
           <t>#мфр #миофасциальный_релиз #массаж_стоп #йога #пилатес #самомассаж #восстановление</t>
         </is>
       </c>
+      <c r="Y29" s="15" t="inlineStr">
+        <is>
+          <t>Мяч массажный с шипами, диаметр 7 см, жёсткий пластик. Прокатывает свод стопы, пятку и икру. Оранжевый видно на полу и в сумке.
+Кому подходит
+Тем, кто много ходит и бегает: к вечеру устают стопы, а икры забиваются после нагрузки.
+Жёсткость высокая
+Мяч не проминается под весом тела. Воздействие глубокое.
+Стопы после дня на ногах
+Мяч кладётся на пол и прокатывается стопой от пятки к пальцам, по минуте на каждую ногу. Сидя нажим мягче, стоя сильнее.
+Икры и голени
+Сидя на полу мяч подкладывается под икру, нога прокатывается от щиколотки к колену. Вторая нога сверху добавляет нажим, если его не хватает.
+Диаметр 7 см
+Средний размер линейки: под сводом стопы помещается, а по икре идёт шире, чем шестёрка.
+Шипы
+Шипы с округлыми концами, из того же материала, что и мяч. Нажим распределяется по площади, кожа не царапается.
+Материал и уход
+ПВХ. Моется водой с мылом, влагу не впитывает, сохнет сразу.
+Габариты
+Диаметр 7 см, вес 60 граммов. Помещается в спортивную сумку, рюкзак, ящик стола.
+В комплекте один мяч. Бытовой инструмент для самомассажа.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -10122,6 +10527,28 @@
           <t>#мфр #миофасциальный_релиз #массаж_стоп #йога #пилатес #самомассаж #восстановление</t>
         </is>
       </c>
+      <c r="Y30" s="15" t="inlineStr">
+        <is>
+          <t>Мяч массажный с шипами, диаметр 7 см, жёсткий пластик. Точечное воздействие вместо равномерного нажима: шипы продавливают мышцу глубже гладкой поверхности.
+Кому подходит
+Тем, кто уже пробовал гладкий мяч или ролик и хочет проработку жёстче и точнее.
+Жёсткость высокая
+Мяч не проминается под весом тела. Воздействие глубокое.
+Чем отличается от гладкого
+Шипы цепляют мышцу на небольших участках и продавливают её глубже, чем гладкая поверхность при том же нажиме. Гладкий мяч работает площадью, этот точками.
+Куда применяют
+Спина у стены, трапеция, свод стопы, икра сидя на полу. По минуте на зону, движения медленные, по мышце, обходя кость и сустав.
+Диаметр 7 см
+Средний размер линейки: шире шестёрки по захвату и при этом заходит под свод стопы, куда 9 см не помещается.
+Шипы
+Шипы с округлыми концами, из того же материала, что и мяч. Нажим распределяется по площади, кожа не царапается.
+Материал и уход
+ПВХ. Моется водой с мылом, влагу не впитывает, сохнет сразу.
+Габариты
+Диаметр 7 см, вес 60 граммов. Помещается в спортивную сумку, рюкзак, ящик стола.
+В комплекте один мяч. Бытовой инструмент для самомассажа.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -10171,6 +10598,26 @@
           <t>#мфр #миофасциальный_релиз #массаж_стоп #йога #пилатес #самомассаж #восстановление</t>
         </is>
       </c>
+      <c r="Y31" s="15" t="inlineStr">
+        <is>
+          <t>Мяч массажный с шипами 9 см, жёсткий пластик - крупный размер линейки. Для бёдер, ягодичных и спины: за один проход захватывается полоса мышцы, а не точка.
+Кому подходит
+Тем, кто работает с крупными мышцами: после приседаний, бега, велосипеда. Мелкий мяч на бедре уходит вглубь и работает слишком резко.
+Жёсткость высокая
+Мяч не проминается под весом тела. Воздействие глубокое.
+Крупные мышцы
+Девять сантиметров дают широкое давление: бедро, ягодичные и широчайшие прорабатываются полосой. Для мелких участков вроде свода стопы берут 6 или 7 см.
+Как пользоваться
+Мяч подкладывается под мышцу сидя или лёжа, тело прокатывается по нему медленно. По минуте на зону, пять-десять минут на подход, после нагрузки, а не до неё.
+Шипы
+Шипы с округлыми концами, из того же материала, что и мяч. Нажим распределяется по площади, кожа не царапается.
+Материал и уход
+ПВХ. Моется водой с мылом, влагу не впитывает, сохнет сразу.
+Габариты
+Диаметр 9 см, вес 100 граммов. Помещается в спортивную сумку и рюкзак.
+В комплекте один мяч. Бытовой инструмент для самомассажа.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -10220,6 +10667,26 @@
           <t>#мфр #миофасциальный_релиз #массаж_стоп #йога #пилатес #самомассаж #восстановление</t>
         </is>
       </c>
+      <c r="Y32" s="15" t="inlineStr">
+        <is>
+          <t>Мяч массажный с шипами 9 см, жёсткий пластик. Работает у стены: спина проходится полосой, без второго человека и без ролика.
+Кому подходит
+Тем, кто хочет пройти всю спину за несколько минут: широкий шар берёт полосу мышцы за проход.
+Жёсткость высокая
+Мяч не проминается под весом тела. Воздействие глубокое.
+Спина у стены
+Мяч прижимается к стене спиной и прокатывается вдоль позвоночника, по мышцам справа и слева, не по самим позвонкам. Вес тела задаёт нажим: сильнее прислонились - глубже.
+Широкая проработка
+Диаметр 9 см захватывает полосу мышцы за один проход, поэтому спина проходится быстрее, чем мелким мячом. Для точки под лопаткой берут 6 см.
+Шипы
+Шипы с округлыми концами, из того же материала, что и мяч. Нажим распределяется по площади, кожа не царапается.
+Материал и уход
+ПВХ. Моется водой с мылом, влагу не впитывает, сохнет сразу.
+Габариты
+Диаметр 9 см, вес 100 граммов. Помещается в спортивную сумку и рюкзак.
+В комплекте один мяч. Бытовой инструмент для самомассажа.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -10269,6 +10736,28 @@
           <t>#мфр #миофасциальный_релиз #массаж_стоп #йога #пилатес #самомассаж #восстановление</t>
         </is>
       </c>
+      <c r="Y33" s="15" t="inlineStr">
+        <is>
+          <t>Мяч массажный с шипами, диаметр 9 см, жёсткий пластик. Для икр, бёдер и ягодичных мышц. Оранжевый видно на полу и в сумке.
+Кому подходит
+Тем, у кого забиваются ноги: после бега, велосипеда, долгой ходьбы или смены на ногах.
+Жёсткость высокая
+Мяч не проминается под весом тела. Воздействие глубокое.
+Бёдра и ягодичные
+Мяч подкладывается под мышцу сидя на полу, вес тела задаёт нажим. Прокатывание идёт медленно, с задержкой на участках, где напряжение ощутимее.
+Икры после нагрузки
+Сидя мяч подкладывается под икру, нога прокатывается от щиколотки к колену. Вторая нога сверху добавляет нажим, если его не хватает.
+Диаметр 9 см
+Крупный размер линейки: за один проход захватывается полоса мышцы, а не точка. Для мелких участков вроде свода стопы берут 6 или 7 см.
+Шипы
+Шипы с округлыми концами, из того же материала, что и мяч. Нажим распределяется по площади, кожа не царапается.
+Материал и уход
+ПВХ. Моется водой с мылом, влагу не впитывает, сохнет сразу.
+Габариты
+Диаметр 9 см, вес 100 граммов. Помещается в спортивную сумку и рюкзак.
+В комплекте один мяч. Бытовой инструмент для самомассажа.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -10318,6 +10807,26 @@
           <t>#мфр #миофасциальный_релиз #массаж_стоп #йога #пилатес #самомассаж #восстановление</t>
         </is>
       </c>
+      <c r="Y34" s="15" t="inlineStr">
+        <is>
+          <t>Мяч массажный с шипами, 9 см, жёсткий пластик. Крупный шар распределяет вес тела по большей площади: давление глубокое, но не сосредоточено в одной точке.
+Кому подходит
+Тем, кому точечный нажим мелкого мяча кажется слишком резким, а проработка нужна глубокая.
+Жёсткость высокая
+Мяч не проминается под весом тела. Воздействие глубокое.
+Почему 9 см
+Широкий захват за один проход: бедро, ягодичная мышца и спина проходятся быстрее. В свод стопы такой мяч уже не помещается - там работают шестёркой или семёркой.
+Куда применяют
+Бедро и ягодичная мышца сидя на полу, спина у стены, задняя поверхность голени. По минуте на зону, движения медленные.
+Шипы
+Шипы с округлыми концами, из того же материала, что и мяч. Нажим распределяется по площади, кожа не царапается.
+Материал и уход
+ПВХ. Моется водой с мылом, влагу не впитывает, сохнет сразу.
+Габариты
+Диаметр 9 см, вес 100 граммов. Помещается в спортивную сумку и рюкзак.
+В комплекте один мяч. Бытовой инструмент для самомассажа.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -10367,6 +10876,26 @@
           <t>#мфр #миофасциальный_релиз #массаж_стоп #йога #пилатес #самомассаж #восстановление</t>
         </is>
       </c>
+      <c r="Y35" s="15" t="inlineStr">
+        <is>
+          <t>Мяч массажный с шипами, жёсткий, 9 см - крупный размер линейки. Прокатывает подошву целиком: пятка, свод и подушечка за один проход.
+Кому подходит
+Тем, кто хочет пройти всю стопу разом, а не искать точку под сводом: широкий шар берёт подошву площадью.
+Жёсткость высокая
+Мяч не проминается под весом тела. Воздействие глубокое.
+Подошва целиком
+Диаметр 9 см идёт по подошве широко, захватывая пятку, свод и подушечку за одно движение. Точечная работа под сводом - задача мяча 6 см, этот берёт площадью.
+Как пользоваться
+Мяч кладётся на пол, стопа прокатывает его от пятки к пальцам. Сидя нажим мягче, стоя сильнее. По минуте на каждую ногу.
+Шипы
+Шипы с округлыми концами, из того же материала, что и мяч. Нажим распределяется по площади, кожа не царапается.
+Материал и уход
+ПВХ. Моется водой с мылом, влагу не впитывает, сохнет сразу. Не боится влажного пола и ванной.
+Габариты
+Диаметр 9 см, вес 100 граммов. Помещается в спортивную сумку и рюкзак.
+В комплекте один мяч. Бытовой инструмент для самомассажа.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -10413,6 +10942,24 @@
           <t>#мфр #миофасциальный_релиз #массаж_стоп #йога #пилатес #самомассаж #восстановление</t>
         </is>
       </c>
+      <c r="Y36" s="15" t="inlineStr">
+        <is>
+          <t>Мяч массажный для мфр: гладкий шар 6 см из плотного ТПЭ. Ставят на пол, наступают и катают - свод стопы прорабатывается весом тела за пять минут.
+Кому подходит
+Тем, кто занимается йогой и пилатесом и восстанавливается сам, и тем, у кого к вечеру ноют стопы после дня на ногах.
+Стопа после дня на ногах
+Мяч кладут под стопу сидя или стоя и прокатывают от пятки к пальцам. Плотный шар не сминается под весом, поэтому давление доходит до подошвенной фасции, а не расплывается по поверхности.
+Гладкий, а не шипастый
+Гладкая поверхность скользит по коже: прокатка идёт непрерывно, без зацепов и покалывания. Шипы работают точечно, гладкий шар - глубокой прокаткой.
+Диаметр 6 см
+Ровно под свод стопы и под ладонь. Тот же мяч проходит по икрам, между лопаткой и позвоночником, по ягодичной мышце и предплечью.
+Как работают
+После нагрузки, медленно, по десять-пятнадцать секунд на точке. Вес добавляют постепенно: сначала сидя, потом стоя с опорой.
+Уход
+Мыть тёплой водой с мылом, вытирать насухо, хранить при комнатной температуре.
+В комплекте один мяч. Бытовой инструмент для самомассажа.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -10459,6 +11006,26 @@
           <t>#мфр #миофасциальный_релиз #массаж_стоп #йога #пилатес #самомассаж #восстановление</t>
         </is>
       </c>
+      <c r="Y37" s="15" t="inlineStr">
+        <is>
+          <t>Мяч массажный для мфр: гладкий шар 6 см из плотного ТПЭ. Жёсткость здесь рабочая - мяч не проминается и передаёт нажим в мышцу целиком.
+Кому подходит
+Тем, кому мягкий мяч кажется бесполезным: он сминается под весом и гасит давление на себя.
+Жёсткий - значит рабочий
+Плотный ТПЭ держит форму: вы наваливаетесь корпусом, и вся нагрузка уходит в мышцу, а не в стенку мяча.
+Гладкая поверхность
+Мяч скользит по коже и одежде - прокатка идёт вдоль мышечного волокна одним движением. Не цепляется за ткань и не оставляет следов на коже, в отличие от шипастых моделей.
+Диаметр 6 см
+Ложится в ладонь и под свод стопы, проходит между лопаткой и позвоночником, работает по ягодичной мышце и по предплечью. Помещается в карман спортивной сумки.
+Куда прикладывают
+Стопы, икры, бёдра, ягодичные мышцы, спина вдоль позвоночника, предплечья и кисти.
+Как работают
+Мяч подкладывают под мышцу и переносят на него вес - у стены, на полу, сидя. Держат по десять-пятнадцать секунд на точке, прокатывают медленно, дышат ровно.
+Уход
+Мыть тёплой водой с мылом, вытирать насухо, хранить при комнатной температуре.
+В комплекте один мяч. Бытовой инструмент для самомассажа.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -10503,6 +11070,26 @@
       <c r="X38" s="10" t="inlineStr">
         <is>
           <t>#мфр #миофасциальный_релиз #массаж_стоп #йога #пилатес #самомассаж #восстановление</t>
+        </is>
+      </c>
+      <c r="Y38" s="15" t="inlineStr">
+        <is>
+          <t>Мяч массажный для мфр: гладкий шар 6 см из плотного ТПЭ. Оранжевый - видно на полу и в сумке, не теряется среди инвентаря.
+Кому подходит
+Тем, кто носит мяч с собой на занятие и обратно, и тем, кто прорабатывает глубокие слои мышц, до которых руками не достать.
+Жёсткость передаёт нажим целиком
+Плотный ТПЭ не проминается под весом тела. Вы наваливаетесь на мяч корпусом, и давление уходит в мышцу, а не гасится стенкой.
+Гладкая поверхность
+Мяч скользит вдоль мышцы одним движением, не цепляясь за кожу и одежду. Прокатка получается непрерывной, в отличие от шипастых моделей с точечным воздействием.
+Диаметр 6 см
+Под ладонь и под свод стопы. Проходит между лопаткой и позвоночником, работает по ягодичной мышце, икре и предплечью. Помещается в карман сумки.
+Куда прикладывают
+Стопы после дня на ногах, икры и бёдра после бега, ягодичные мышцы, спина вдоль позвоночника, кисти после клавиатуры.
+Как работают
+После нагрузки. Медленно, по десять-пятнадцать секунд на точке, с ровным дыханием. Нажим наращивают постепенно.
+Уход
+Мыть тёплой водой с мылом, вытирать насухо.
+В комплекте один мяч. Бытовой инструмент для самомассажа.</t>
         </is>
       </c>
     </row>

--- a/docs/ozon/Озон_рабочая_книга.xlsx
+++ b/docs/ozon/Озон_рабочая_книга.xlsx
@@ -8818,6 +8818,28 @@
           <t>#подтяжка_лица #овал_лица #уход_за_лицом #второй_подбородок #лифтинг #домашний_уход</t>
         </is>
       </c>
+      <c r="Y3" s="15" t="inlineStr">
+        <is>
+          <t>Бандаж для лица и подбородка из лайкры: тканевая повязка для поддержки овала лица, лента 45-67 см с липучкой. Мягкий розовый цвет, ткань без жёстких швов.
+Кому подходит
+Тем, кто носит повязку подолгу и дома: мягкая лайкра не натирает и не оставляет следов на коже.
+Один размер на всех
+Лента растягивается от 45 до 67 см и застёгивается липучкой в любом положении. Обхват подбирается под голову - подойдёт и подростку, и взрослому.
+Не давит на уши
+Вырезы под ушные раковины: ухо не заминается и не потеет под лентой. В бандаже можно лежать на боку и заниматься домашними делами.
+Поддержка подбородка
+Нижняя часть усилена и держит линию подбородка всё время ношения. Натяжение регулируется отдельно от обхвата, его легко ослабить.
+Ширина 8,5 см
+Широкая лента распределяет нагрузку по щеке, а не режет узкой полосой. Над ухом сужается до 7,5 см, чтобы не мешать.
+Ткань дышит
+Лайкра тянется в двух направлениях и возвращает форму после стирки. Не скользит по коже и не сползает во время ношения.
+Когда носят
+После вечернего ухода, во время домашних дел, во сне. Рекомендуемое время - от 30 минут.
+Уход
+Стирать вручную в тёплой воде до 30 градусов, сушить на горизонтальной поверхности вдали от батареи и прямого солнца.
+В комплекте один бандаж.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -8867,6 +8889,26 @@
           <t>#подтяжка_лица #овал_лица #уход_за_лицом #второй_подбородок #лифтинг #домашний_уход</t>
         </is>
       </c>
+      <c r="Y4" s="15" t="inlineStr">
+        <is>
+          <t>Бандаж для лица и подбородка: тканевая повязка из лайкры, поддерживает контур подбородка и щёк. Лента 45-67 см с липучкой. Чёрный не просвечивает и не желтеет от кремов.
+Кому подходит
+Тем, кто делает домашний уход вечером и хочет зафиксировать результат на время процедуры, и тем, кому важно, чтобы повязка не бросалась в глаза.
+Один размер на всех
+Лента растягивается от 45 до 67 см и фиксируется липучкой в любом положении. Обхват регулируется под голову, а не подбирается по размерной сетке - подойдёт и женщине, и мужчине.
+Не давит на уши
+В ленте вырезы под ушные раковины: ухо остаётся снаружи и не заминается. В повязке можно лежать на боку, читать и смотреть телевизор.
+Поддержка подбородка
+Нижняя часть ленты усилена: она принимает вес и держит линию подбородка всё время ношения. Натяжение регулируется отдельно от обхвата - можно ослабить, если давит.
+Ширина 8,5 см
+Лента широкая, нагрузка распределяется по всей щеке, а не режет узкой полосой. Над ухом лента сужается до 7,5 см.
+Когда носят
+Вечером после ухода за кожей, во время домашних дел, во сне. Рекомендуемое время - от 30 минут.
+Уход
+Стирать вручную в тёплой воде до 30 градусов, сушить на горизонтальной поверхности вдали от батареи и солнца, не отжимать скручиванием.
+В комплекте один бандаж.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -8914,6 +8956,26 @@
       <c r="X5" s="10" t="inlineStr">
         <is>
           <t>#подтяжка_лица #овал_лица #уход_за_лицом #второй_подбородок #лифтинг #домашний_уход</t>
+        </is>
+      </c>
+      <c r="Y5" s="15" t="inlineStr">
+        <is>
+          <t>Бандаж для лица и подбородка силиконовый: формованная маска длиной 65 см с десятью массажными точками на внутренней стороне. Держит линию челюсти плотнее тканевой повязки.
+Кому подходит
+Тем, кто уже носил тканевую повязку и хочет фиксацию жёстче, и тем, кто пользуется кремами и сыворотками: силикон их не впитывает.
+Десять массажных точек
+На внутренней стороне выпуклости шиацу - они приходятся на точки вдоль челюсти и под подбородком. При надетом бандаже точки прижимаются к коже, при снятии их можно промассировать пальцами через силикон.
+Силикон, а не ткань
+Формованный корпус держит форму сам и не растягивается со временем, как трикотаж. Не впитывает крем и сыворотку, моется под краном за секунду.
+Плотная фиксация
+Застёжка на липучке по всей длине 65 см - натяжение выставляется точно. На корпусе помечена сторона, чтобы не надеть наизнанку.
+Не давит на уши
+Анатомические вырезы под ушные раковины: ухо остаётся свободным, лента проходит над ним.
+Когда носят
+После вечернего ухода, во время домашних дел, во сне. Рекомендуемое время - от 30 минут.
+Уход
+Мыть тёплой водой с мылом, вытирать насухо. Хранить в расправленном виде, не складывать под грузом.
+В комплекте один бандаж.</t>
         </is>
       </c>
     </row>
@@ -9704,6 +9766,24 @@
           <t>#массаж_шеи #роликовый_массажер #самомассаж #расслабление #после_работы #уход_за_телом</t>
         </is>
       </c>
+      <c r="Y17" s="15" t="inlineStr">
+        <is>
+          <t>Массажер для пальцев рук роликовый: палец вставляется внутрь, резиновые ролики прокатываются по подушечке и боковым поверхностям. Длина 14 см - помещается в карман и в ящик стола.
+Кому подходит
+Тем, кто работает руками: печатает, пишет от руки, шьёт, играет на инструменте. К вечеру кисть немеет и пальцы плохо разгибаются.
+Резиновые ролики, а не пластик
+Резина мягче пластика и не скользит по сухой коже: ролик идёт по пальцу плавно, с нажимом, но без щипка. Корпус акриловый - лёгкий и прочный, 40 граммов в руке.
+Как пользоваться
+Вставить палец, прокатить от основания к кончику пять-десять раз, перейти к следующему. На всю кисть уходит две-три минуты. Две короткие сессии в течение дня работают лучше одной длинной вечером.
+Не только пальцы
+Зажав массажёр в другой руке, прокатывают ладонь по основанию большого пальца и мышцы предплечья - те же зоны, что нагружаются мышкой и клавиатурой.
+Размер и комплект
+Длина 14 см, диаметр 3 см, вес 40 граммов. В коробке массажёр и вкладыш, коробку удобно оставить для хранения.
+Уход
+Протирать влажной тканью, хранить в коробке из комплекта.
+Бытовой инструмент для самомассажа.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -9753,6 +9833,26 @@
           <t>#массаж_шеи #роликовый_массажер #самомассаж #расслабление #после_работы #уход_за_телом</t>
         </is>
       </c>
+      <c r="Y18" s="15" t="inlineStr">
+        <is>
+          <t>Массажер для шеи и спины ручной роликовый ленточный: гибкая лента 110 см, ролики идут по шее, плечам и спине. Давление жёсткое.
+Кому подходит
+Тем, у кого к вечеру каменеет шея и спина после дня за компьютером или смены на ногах, и тем, кому некого попросить размять спину.
+Жёсткость высокая
+Нажим доходит до мышцы под слоем ткани. Это инструмент для глубокой проработки, а не для лёгкого поглаживания.
+Достаёт туда, куда рука не дотягивается
+Длины 110 см хватает, чтобы обхватить спину крест-накрест и пройти от шеи до поясницы. Ручки по краям работают рычагом: усилие прикладывается руками, нагрузка приходится на мышцы. Тем же движением, за одну ручку, лента проходит по бёдрам, икрам и предплечьям.
+Широкий захват за один проход
+Роликовые узлы расставлены по всей длине ленты, каждый собран из нескольких рельефных роликов. За одно движение прорабатывается полоса мышц, а не узкая дорожка.
+Пластик вместо дерева
+Деревянная лента после бани сохнет долго. Эта ополаскивается под душем и убирается сухой, моется водой с мылом. Подходит для бани и хранения в ванной.
+Складывается вдвое
+В сложенном виде 55 см, вес 160 граммов. Помещается в спортивную сумку, рюкзак, чемодан, ящик рабочего стола.
+Интенсивность регулируется натяжением
+Сильнее натянута лента - проработка глубже, слабее - мягче. Ролики вращаются свободно и скользят по коже гладко.
+В комплекте один массажёр. Бытовой инструмент для самомассажа.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -9802,6 +9902,26 @@
           <t>#массаж_шеи #роликовый_массажер #самомассаж #расслабление #после_работы #уход_за_телом</t>
         </is>
       </c>
+      <c r="Y19" s="15" t="inlineStr">
+        <is>
+          <t>Массажер для шеи и плеч ручной роликовый ленточный, розовый: гибкая лента 110 см, заводится за спину крест-накрест. Давление жёсткое.
+Кому подходит
+Тем, кто сидит весь день: к вечеру напряжение скапливается в шее, между лопатками и в пояснице - до этих участков рука дотягивается плохо.
+Работает рычагом
+Ручки по краям: при попеременном натяжении роликовые узлы идут вдоль позвоночника снизу вверх и обратно. Этим лента отличается от мяча и валика - не нужно ложиться на пол или искать стену.
+Жёсткость высокая
+Нажим доходит до глубоких слоёв, проработка основательная.
+Шея, плечи, спина, ноги
+Той же лентой, за одну ручку, прорабатываются бёдра, икры и предплечья. Роликовые узлы расставлены по всей длине и собраны из нескольких рельефных роликов: за одно движение захватывается широкая полоса мышц.
+Пластик вместо дерева
+Деревянная лента после бани сохнет долго. Эта ополаскивается под душем и убирается сухой, моется водой с мылом.
+Складывается вдвое
+В сложенном виде 55 см, вес 160 граммов. Помещается в сумку, рюкзак, ящик рабочего стола.
+Интенсивность регулируется натяжением
+Сильнее натянута лента - проработка глубже, слабее - мягче.
+В комплекте один массажёр. Бытовой инструмент для самомассажа.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -9849,6 +9969,26 @@
       <c r="X20" s="10" t="inlineStr">
         <is>
           <t>#массаж_шеи #роликовый_массажер #самомассаж #расслабление #после_работы #уход_за_телом</t>
+        </is>
+      </c>
+      <c r="Y20" s="15" t="inlineStr">
+        <is>
+          <t>Массажер для шеи и спины ручной роликовый ленточный, голубой: гибкая лента 110 см. Одной лентой прорабатываются шея, спина, ноги и руки. Давление жёсткое.
+Кому подходит
+Тем, у кого устают ноги: икры и бёдра после смены на ногах или долгой дороги остаются напряжёнными.
+Для ног после нагрузки
+Лента ведётся снизу вверх, от щиколотки к колену и выше. Ролики усиливают кровообращение, ощущение тяжести уменьшается.
+Жёсткость высокая
+Нажим доходит до глубоких слоёв - такой массажёр выбирают, когда нужна серьёзная проработка мышц.
+Одной лентой - всё тело
+За две ручки лента идёт по спине крест-накрест, от шеи до поясницы. За одну ручку работает точечно: по бедру, икре, предплечью. Роликовые узлы расставлены по всей длине и собраны из нескольких рельефных роликов, поэтому за движение захватывается широкая полоса мышц.
+Пластик вместо дерева
+Деревянная лента после бани сохнет долго. Эта ополаскивается под душем и убирается сухой, моется водой с мылом.
+Складывается вдвое
+В сложенном виде 55 см, вес 160 граммов. Помещается в спортивную сумку, рюкзак, чемодан.
+Интенсивность регулируется натяжением
+Сильнее натянута лента - проработка глубже, слабее - мягче. Ролики вращаются свободно и скользят по коже гладко.
+В комплекте один массажёр. Бытовой инструмент для самомассажа.</t>
         </is>
       </c>
     </row>
@@ -11141,6 +11281,28 @@
           <t>#скакалка #фитнес_резинки #домашние_тренировки #кардио #для_ягодиц #спортинвентарь #растяжка</t>
         </is>
       </c>
+      <c r="Y39" s="15" t="inlineStr">
+        <is>
+          <t>Фитнес резинки тканевые, набор из трёх с калиброванной нагрузкой 27, 40 и 68 кг. Ширина 80 мм, толщина 3 мм, кольцо 75 см по окружности. В комплекте мешочек.
+Кому подходит
+Тем, кто работает на ягодицы и бёдра всерьёз, и тем, кому узкие кольца режут кожу: широкая лента распределяет нагрузку по бедру.
+Три калиброванных уровня
+Light 27 кг - разминка и активация мышц. Medium 40 кг - базовая нагрузка регулярных занятий. Heavy 68 кг - силовая работа. Нагрузка указана в килограммах, между уровнями честный шаг.
+Размер 75 см по окружности
+В сложенном виде лента 38 см, в кольце 75 см по окружности. Такой размер садится на бёдра выше колена без перетяжки и не сползает вниз в приседе. Замерьте бедро в самом широком месте: при окружности больше 70 см подходит именно эта модель.
+Почему 80 мм ширины
+Восемь сантиметров шире стандартных тканевых резинок. Широкая лента не режет кожу под 68 кг сопротивления, и тяжёлый уровень остаётся рабочим до того, как устанет мышца.
+Не скатываются и не съезжают
+Край обработан по усиленной технологии, лента не скручивается в жгут. Многослойное плетение с двойным противоскользящим слоем держит её и на голой коже, и на одежде.
+Что с ними делать
+Приседания, ягодичный мостик, шаги в сторону, ракушка, махи назад стоя, разведение бёдер сидя. Йога и пилатес - на лёгком уровне.
+Как подобрать
+Рабочая резинка - та, на которой 15 повторов даются с трудом на последних трёх. Начинать стоит с Light даже опытным: тканевая лента ощущается жёстче латексной той же нагрузки.
+Уход
+Ополоснуть тёплой водой, сушить при комнатной температуре, хранить в мешочке нерастянутыми.
+В комплекте три резинки и мешочек.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -11190,6 +11352,26 @@
           <t>#скакалка #фитнес_резинки #домашние_тренировки #кардио #для_ягодиц #спортинвентарь #растяжка</t>
         </is>
       </c>
+      <c r="Y40" s="15" t="inlineStr">
+        <is>
+          <t>Фитнес резинки тканевые, набор из пяти с нагрузкой от 9 до 45 кг: для ног, ягодиц, рук и плеч. Ширина 6 см, плотное плетение хлопка с латексом. В комплекте мешочек для хранения.
+Кому подходит
+Тем, кто занимается дома и в поездках, и тем, кто начинает с нуля: набор закрывает и разминку, и силовую работу, поэтому его не приходится менять через месяц.
+Пять уровней с честным шагом
+X-LIGHT 9 кг, LIGHT 18 кг, MEDIUM 27 кг, HEAVY 36 кг, X-HEAVY 45 кг. Шаг ровно девять килограммов - это рабочая прогрессия, а не пять оттенков одного сопротивления. Лёгкие идут на разминку и руки, средние на регулярные тренировки, тяжёлые на приседания и отведения.
+Не скатываются и не съезжают
+Край обработан по усиленной технологии, лента не скручивается в жгут под нагрузкой. Многослойное плетение с двойным противоскользящим слоем держит её на месте и на голой коже, и на одежде.
+Почему тканевые, а не силиконовые
+Внутри плетения латексная нить, снаружи хлопок с полиэстером. Лента шириной 6 см лежит плоско и держится на месте, тогда как силиконовая скользит по коже и скручивается на бедре.
+Что с ними делать
+Приседания, ягодичный мостик, шаги в сторону, ракушка, махи назад стоя, разведение рук, тяга к поясу. Резинка нужна там, где вес тела уже мало, а гантели ещё некуда положить.
+Как подобрать нагрузку
+Рабочая резинка - та, на которой вы делаете 15 повторов и последние три даются тяжело. Если 20 повторов идут легко, берите следующую по жёсткости.
+Уход
+Ополоснуть тёплой водой, сушить при комнатной температуре вдали от батареи, хранить в мешочке нерастянутыми - так плетение дольше держит упругость.
+В комплекте пять резинок и мешочек.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -11236,6 +11418,28 @@
           <t>#скакалка #фитнес_резинки #домашние_тренировки #кардио #для_ягодиц #спортинвентарь #растяжка</t>
         </is>
       </c>
+      <c r="Y41" s="15" t="inlineStr">
+        <is>
+          <t>Фитнес резинки латексные, набор из четырёх замкнутым кольцом: четыре уровня нагрузки от лёгкой до усиленной. Толщина 2 мм, покрытие Soft Touch. Для йоги, пилатеса, фитнеса и растяжки.
+Кому подходит
+Тем, кто занимается йогой и пилатесом: здесь лента нужна не для силы, а для контроля - она задаёт сопротивление в асане и подсказывает телу, какая мышца работает.
+Четыре уровня - четыре цвета
+Light - разминка и руки, розовая. Medium - тонус мышц, голубая. Heavy - ноги и ягодицы, зелёная. X-Heavy - силовой тренинг, сиреневая. Нагрузка напечатана прямо на ленте, гадать не приходится.
+Многослойный латекс с памятью формы
+Ленты из 100 % натурального многослойного латекса: он возвращается в исходное состояние даже после долгого растяжения, поэтому резинка не остаётся вытянутой после подхода и держит сопротивление дольше однослойной.
+Soft Touch - что это на ощупь
+Поверхность бархатистая, а не глянцевая. Глянцевый латекс скользит по коже и по одежде, и на отведении ноги лента уезжает вниз. Бархатистая текстура цепляется мягко.
+Состав без отдушек
+Латекс без добавок и наполнителей, запаха нет. Резкий химический запах у дешёвых лент дают именно добавки.
+Что с ними делать
+Приседания, ягодичный мостик, шаги в сторону, ракушка, махи назад стоя, разведение рук, растяжка с лентой как с ремнём. Рабочие уровни в йоге и пилатесе - нижние два, верхние идут в силовую часть.
+Ровное сопротивление
+Натуральный латекс тянется плавно и возвращает силу по всей амплитуде, без рывка в начале и провала в конце.
+Уход
+Протирать сухой тканью, хранить в тени нерастянутыми, не стирать в машине. Заниматься до нанесения крема - так лента дольше держит упругость.
+В комплекте четыре резинки.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -11323,6 +11527,24 @@
           <t>#скакалка #фитнес_резинки #домашние_тренировки #кардио #для_ягодиц #спортинвентарь #растяжка</t>
         </is>
       </c>
+      <c r="Y43" s="15" t="inlineStr">
+        <is>
+          <t>Скакалка скоростная спортивная взрослая: стальной трос 3 метра с регулировкой длины, ручки 17 см на подшипниках из нержавеющей стали. Трос не закручивается и держит темп весь подход.
+Кому подходит
+Тем, кто прыгает на счёт: бокс, кроссфит, интервальное кардио. И тем, у кого обычная скакалка перекручивается через десяток оборотов.
+Трос: 49 стальных нитей в резиновой оболочке
+Это не ПВХ-шнур, а стальной трос - 49 сплетённых нитей из нержавеющей стали под резиновым покрытием. Тонкий и тяжёлый одновременно: снижает сопротивление воздуха, идёт быстрее пластикового, не спутывается и не заламывается при хранении.
+Ручка: пять слоёв вокруг алюминия
+Силиконовый слой снаружи, под ним алюминиевый сплав, антикоррозийный слой, прозрачная основа и матовое покрытие. Алюминий даёт жёсткость без веса, силикон не проскальзывает во влажной ладони. Полная длина ручки 17 см, до подшипника 13,5 см - хват, при котором кисть не устаёт на длинных подходах.
+Что даёт подшипник
+Трос вращается на подшипнике из нержавеющей стали внутри ручки: намотки нет, вращение плавное. В обычной скакалке шнур закреплён жёстко и перекручивается.
+Как настроить длину
+Длина регулируется нажимным замком: нажали, вытянули или убрали трос, отпустили. Встаньте на середину троса одной ногой - ручки в вытянутых вдоль тела руках должны доходить до подмышек. Для скоростных прыжков трос укорачивают ещё на 10-15 см.
+Трос защищён оболочкой
+Резиновая оболочка гасит удар о покрытие и принимает на себя трение вместо стали - для улицы это главный запас прочности. Регулировочный замок затягивают без усилия, до щелчка.
+Длина настраивается под рост до 195 см. Уход: протирать трос после уличных тренировок, хранить смотанным свободно, без тугих петель.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -11369,6 +11591,22 @@
           <t>#скакалка #фитнес_резинки #домашние_тренировки #кардио #для_ягодиц #спортинвентарь #растяжка</t>
         </is>
       </c>
+      <c r="Y44" s="15" t="inlineStr">
+        <is>
+          <t>Скакалка скоростная на подшипниках: стальной трос 3 метра с регулировкой длины, ручки 17 см. Свободное вращение держит ритм - трос не закручивается на длинном подходе.
+Кому подходит
+Тем, кто считает повторы: кроссфит, двойные прыжки, интервальные раунды. Подшипник в каждой ручке - то, что отличает скоростную скакалку от обычной.
+Трос: 49 стальных нитей в резиновой оболочке
+Не ПВХ-шнур, а стальной трос - 49 сплетённых нитей из нержавеющей стали под резиновым покрытием. Тонкий и тяжёлый одновременно: снижает сопротивление воздуха и идёт быстрее пластикового. Именно на таком тросе получаются двойные прыжки, лёгкий шнур на нужной скорости складывается.
+Ручка: пять слоёв вокруг алюминия
+Силиконовый слой снаружи, под ним алюминиевый сплав, антикоррозийный слой, прозрачная основа и матовое покрытие. Алюминий даёт жёсткость без веса, силикон не проскальзывает во влажной ладони. Полная длина ручки 17 см, до подшипника 13,5 см - такой хват позволяет вести скакалку кистью, а не всей рукой.
+Как настроить под себя
+Длина регулируется нажимным замком: нажали, вытянули или убрали трос, отпустили. Встаньте на середину троса одной ногой - ручки в вытянутых вдоль тела руках должны доходить до подмышек. Для двойных прыжков укоротите ещё на 10-15 см.
+Трос защищён оболочкой
+Резиновая оболочка гасит удар о покрытие и принимает на себя трение вместо стали - для улицы это главный запас прочности. Регулировочный замок затягивают без усилия, до щелчка.
+Уход: протирать трос после уличных тренировок, хранить смотанным свободно, без тугих петель.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -11413,6 +11651,24 @@
       <c r="X45" s="10" t="inlineStr">
         <is>
           <t>#скакалка #фитнес_резинки #домашние_тренировки #кардио #для_ягодиц #спортинвентарь #растяжка</t>
+        </is>
+      </c>
+      <c r="Y45" s="15" t="inlineStr">
+        <is>
+          <t>Скакалка спортивная взрослая скоростная, бирюзово-голубая: стальной трос 3 метра с регулировкой длины, ручки 17 см на подшипниках. Свободное вращение держит темп ровным весь подход.
+Кому подходит
+Тем, кто прыгает дома и в зале, и подросткам: три метра троса хватает при росте до 195 см, а точная настройка длины делает скакалку пригодной для любого роста в семье. В фигурном катании прыжки на скакалке идут базовой разминкой перед льдом.
+Трос: 49 стальных нитей в резиновой оболочке
+Не ПВХ-шнур, а стальной трос - 49 сплетённых нитей из нержавеющей стали под резиновым покрытием. Тонкий и тяжёлый одновременно: снижает сопротивление воздуха, идёт быстрее пластикового, не спутывается и не заламывается при хранении.
+Ручка: пять слоёв вокруг алюминия
+Силиконовый слой снаружи, под ним алюминиевый сплав, антикоррозийный слой, прозрачная основа и матовое покрытие. Алюминий даёт жёсткость без веса, силикон не проскальзывает во влажной ладони. Полная длина ручки 17 см, до подшипника 13,5 см.
+Что даёт подшипник
+Трос вращается на подшипнике из нержавеющей стали внутри ручки: намотки нет, вращение плавное, темп не сбивается.
+Как настроить длину
+Длина регулируется нажимным замком: нажали, вытянули или убрали трос, отпустили. Встаньте на середину троса одной ногой - ручки в вытянутых вдоль тела руках должны доходить до подмышек. Для скоростных прыжков укоротите ещё на 10-15 см.
+Трос защищён оболочкой
+Резиновая оболочка гасит удар о покрытие и принимает на себя трение вместо стали. Регулировочный замок затягивают без усилия, до щелчка.
+Уход: протирать трос после уличных тренировок, хранить смотанным свободно, без тугих петель.</t>
         </is>
       </c>
     </row>
@@ -12345,6 +12601,24 @@
           <t>#игрушки_для_собак #прочная_игрушка #для_крупных_пород #для_мелких_пород #канат_для_собак #активные_игры #для_питомца</t>
         </is>
       </c>
+      <c r="Y64" s="15" t="inlineStr">
+        <is>
+          <t>Мячик для собак мелких пород на резинке: мяч в форме регби 7 см из ТПР, эластичный ремешок 28 см с петлёй. Поверхность в шипах, бросок уходит дальше, чем рукой.
+Кому подходит
+Мелким и средним породам - от той-терьера до бордер-колли. Овальная форма регби удобнее круглой для небольшой пасти: мяч захватывается поперёк и не проваливается глубже.
+Поверхность
+Мяч покрыт мягкими шипами. Они массируют дёсны и снимают мягкий налёт, пока собака держит игрушку в пасти. Механика, а не состав: никаких паст и пропиток.
+Лёгкий на бросок
+Мяч заметно легче монолитного того же диаметра: летит дальше и выше отскакивает от асфальта. Собака видит траекторию, ловит на подскоке и приносит быстрее. Упругая стенка держит форму и возвращает мяч в исходный вид после хватки.
+Ремешок вместо верёвки
+Подвес эластичный. В перетягивании это удобнее верёвки: зубы собаки не встречаются с вашей рукой. Отпущенный мяч возвращается по резинке, поэтому руку держат в стороне. Игрушка рассчитана на игру с хозяином.
+Как играть
+Апортировка: бросок за ремешок, собака приносит, обмен на лакомство. Перетягивание: тянуть горизонтально и от корпуса, без рывков вверх - рывок вверх нагружает шейные позвонки.
+Уход
+Мыть тёплой водой, сушить перед хранением. Ремешок после прогулки в грязи стирают вручную. Игрушку убирают при первых отгрызенных кусках.
+В комплекте один мяч на ремешке.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -12359,7 +12633,7 @@
       </c>
       <c r="C65" s="10" t="inlineStr">
         <is>
-          <t>Мячик для собак мелких пород на веревке, прочная игрушка, синий</t>
+          <t>Мячик для собак мелких пород на резинке, прочная игрушка, синий</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -12391,6 +12665,26 @@
           <t>#игрушки_для_собак #прочная_игрушка #для_крупных_пород #для_мелких_пород #канат_для_собак #активные_игры #для_питомца</t>
         </is>
       </c>
+      <c r="Y65" s="15" t="inlineStr">
+        <is>
+          <t>Мячик для собак мелких пород, тёмно-синий: мяч в форме регби 7 см из ТПР на эластичном ремешке 28 см. Поверхность в шипах, бросок уходит дальше, чем рукой.
+Кому подходит
+Мелким и средним породам - от той-терьера до бордер-колли. Овальная форма регби удобнее круглой для небольшой пасти: мяч захватывается поперёк и не проваливается глубже.
+Поверхность
+Мяч покрыт мягкими шипами. Они массируют дёсны и снимают мягкий налёт, пока собака держит игрушку в пасти. Механика, а не состав.
+Лёгкий на бросок
+Мяч заметно легче монолитного того же диаметра: летит дальше и выше отскакивает от асфальта. Собака видит траекторию, ловит на подскоке и приносит быстрее. Упругая стенка держит форму и возвращает мяч в исходный вид после хватки.
+Ремешок вместо верёвки
+Подвес эластичный, а не верёвочный. Отпущенный мяч возвращается по резинке, поэтому руку держат в стороне, а ремешок под натяжением рядом с собакой не отпускают.
+Чем отличается от круглой версии
+У модели на 29 см мяч круглый и с рельефом-протектором - она для крупных и средних пород. Здесь мяч регби с шипами и легче на 55 граммов: расчёт под небольшую пасть.
+Как играть
+Апортировка через обмен на лакомство, перетягивание горизонтально и от корпуса, без рывков вверх. Игра заканчивается раньше, чем собака устанет.
+Уход
+Мыть тёплой водой, сушить перед хранением. Ремешок после грязной прогулки стирают вручную.
+В комплекте один мяч на ремешке.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -12437,6 +12731,24 @@
           <t>#игрушки_для_собак #прочная_игрушка #для_крупных_пород #для_мелких_пород #канат_для_собак #активные_игры #для_питомца</t>
         </is>
       </c>
+      <c r="Y66" s="15" t="inlineStr">
+        <is>
+          <t>Мяч для собак крупных пород на резинке: шар 7 см из ТПР, эластичный ремешок 29 см с петлёй. Бросок уходит в полтора-два раза дальше, чем рукой.
+Кому подходит
+Средним и крупным породам - овчаркам, лабрадорам, метисам. Диаметр 7 см рассчитан на крупную пасть: мяч не проваливается за корень языка. Для собаки от 25 кг мяч 6 см уже мал.
+Поверхность
+По мячу идёт рельеф-протектор, как на шине. Он массирует дёсны и снимает мягкий налёт, пока собака держит мяч в пасти. Эффект механический, без пропиток и добавок.
+Лёгкий на бросок
+Мяч заметно легче монолитного того же диаметра: летит дальше и выше отскакивает от асфальта. Собака видит траекторию, ловит на подскоке и приносит быстрее. Упругая стенка держит форму и возвращает мяч в исходный вид после хватки.
+Ремешок вместо верёвки
+Подвес эластичный. Он удобнее верёвки и в броске, и в перетягивании: зубы собаки не встречаются с вашей рукой. Отпущенный мяч возвращается по резинке, поэтому руку держат в стороне, а ремешок под натяжением рядом с собакой не отпускают.
+Как играть
+Бросок за ремешок, обмен на лакомство, команда «дай». Перетягивать горизонтально и от корпуса, без рывков вверх: рывок вверх нагружает шейные позвонки. Игра заканчивается раньше, чем собака устанет - так она сохраняет интерес к игрушке.
+Уход
+Мыть тёплой водой с мылом, сушить перед хранением. Мяч осматривают после каждой активной игры и убирают при первых надкусах.
+В комплекте один мяч на ремешке.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -12451,7 +12763,7 @@
       </c>
       <c r="C67" s="10" t="inlineStr">
         <is>
-          <t>Мяч для собак крупных пород на веревке, прочная игрушка, синий</t>
+          <t>Мяч для собак крупных пород на резинке, прочная игрушка, синий</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -12483,6 +12795,24 @@
           <t>#игрушки_для_собак #прочная_игрушка #для_крупных_пород #для_мелких_пород #канат_для_собак #активные_игры #для_питомца</t>
         </is>
       </c>
+      <c r="Y67" s="15" t="inlineStr">
+        <is>
+          <t>Мяч для собак крупных пород, тёмно-синий: шар 7 см из ТПР на эластичном ремешке 29 см с петлёй. Бросок уходит в полтора-два раза дальше, чем рукой.
+Кому подходит
+Средним и крупным породам - овчаркам, лабрадорам, метисам. Диаметр 7 см рассчитан на крупную пасть: мяч не проваливается за корень языка. Для собаки от 25 кг мяч 6 см уже мал.
+Поверхность
+По мячу идёт рельеф-протектор, как на шине. Он массирует дёсны и снимает мягкий налёт, пока собака держит мяч в пасти. Эффект механический, без пропиток и добавок.
+Лёгкий на бросок
+Мяч заметно легче монолитного того же диаметра: летит дальше и выше отскакивает от асфальта. Собака видит траекторию, ловит на подскоке и приносит быстрее. Упругая стенка держит форму и возвращает мяч в исходный вид после хватки.
+Ремешок вместо верёвки
+Подвес эластичный, а не верёвочный. Для апорта и перетягивания это удобнее: зубы собаки не встречаются с вашей рукой. Отпущенный мяч возвращается по резинке, поэтому руку держат в стороне.
+Чем отличается от версии с шипами
+У модели на 28 см мяч в форме регби и поверхность в шипах - она для мелких и средних пород. Здесь мяч круглый, тяжелее и с протектором: расчёт под крупную пасть и сильный захват.
+Уход
+Мыть тёплой водой с мылом, сушить перед хранением. Мяч осматривают после каждой активной игры и убирают при первых надкусах.
+В комплекте один мяч на ремешке.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -12524,6 +12854,24 @@
           <t>#игрушки_для_собак #прочная_игрушка #для_крупных_пород #для_мелких_пород #канат_для_собак #активные_игры #для_питомца</t>
         </is>
       </c>
+      <c r="Y68" s="15" t="inlineStr">
+        <is>
+          <t>Канат для собак крупных пород: хлопковая нить, 55 × 5 см, 580 граммов. Плетение сомкнуто в замкнутую петлю - её перехватывают двумя руками и тянут в полную силу.
+Кому подходит
+Средним и крупным породам. Полкило веса означают плотное плетение: канат держит нагрузку, под которой лёгкий вариант распустился бы за неделю.
+Петля вместо жгута
+Замкнутое кольцо удобно брать двумя руками, а собака берёт канат в любом месте по кругу. Для крупной собаки канат часто удобнее мяча: его проще перехватить, и он не улетает под мебель.
+Чистит зубы во время игры
+Хлопковые волокна работают как зубная нить: пока собака тянет и грызёт канат, снимается мягкий налёт, а дёсны получают массаж. Эффект механический, без пропиток и добавок.
+Как играть
+Перетягивание в полную силу, апортировка, жевание под присмотром. Тянуть горизонтально и от корпуса, без рывков вверх - рывок вверх бьёт по шейным позвонкам собаки, а вашей спине достаётся не меньше.
+Плотное плетение
+Натуральный хлопок держит форму в перетягивании и не красится. Канат меняют, когда он распустился больше чем на треть длины или собака начала отрывать длинные нити.
+Уход
+Стирать вручную в тёплой воде без кондиционера, сушить полностью: влажный канат внутри плесневеет.
+В комплекте один канат.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -12565,6 +12913,24 @@
           <t>#игрушки_для_собак #прочная_игрушка #для_крупных_пород #для_мелких_пород #канат_для_собак #активные_игры #для_питомца</t>
         </is>
       </c>
+      <c r="Y69" s="15" t="inlineStr">
+        <is>
+          <t>Канат для собак средних пород: хлопковая нить, 55 × 5 см, 380 граммов. Прямой жгут с распущенными кистями на концах - кисти собака треплет и жуёт, а вы держите канат за середину.
+Кому подходит
+Мелким и средним породам. Вес 380 граммов и толщина 5 см рассчитаны на пасть небольшой собаки: канат удобно захватывается и не волочится по земле. Для крупной породы есть версия на 580 граммов.
+Кисти на концах
+Собака берёт канат за кисти первыми - они мягче середины и треплются охотнее. За них же её удобно учить приносить игрушку.
+Чистит зубы во время игры
+Хлопковые волокна работают как зубная нить: снимают мягкий налёт с зубов и массируют дёсны, пока собака тянет канат. Механика, а не состав: никаких пропиток.
+Как играть
+Перетягивание, апортировка, самостоятельное жевание под присмотром. Тянуть горизонтально, от корпуса, без рывков вверх. Канат хорошо работает якорем для команды «дай»: собака отпускает, получает лакомство, игра продолжается.
+Когда менять
+Когда жгут распустился больше чем на треть длины или собака начала отрывать длинные нити.
+Уход
+Стирать вручную в тёплой воде без кондиционера, сушить полностью перед тем, как убрать.
+В комплекте один канат.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -12611,7 +12977,28 @@
       </c>
       <c r="X70" s="10" t="inlineStr">
         <is>
-          <t>#пробка_для_вина #для_шампанского #винные_аксессуары #сервировка #многоразовая #барные_аксессуары</t>
+          <t>#пробка_для_вина #винные_аксессуары #сервировка #многоразовая #барные_аксессуары #для_бутылки</t>
+        </is>
+      </c>
+      <c r="Y70" s="15" t="inlineStr">
+        <is>
+          <t>Пробка для бутылки и вина силиконовая многоразовая: набор из четырёх штук в коробке, высота 6 см. Открытая бутылка закрывается за секунду и не протекает даже лёжа.
+Кому подходит
+Тем, кто не допивает бутылку за вечер, и тем, кто хранит в холодильнике масло, сироп и соусы в бутылках без родных крышек.
+Не протекает при перевороте
+По телу пробки идут кольцевые уплотнения: они прижимаются к горлышку изнутри, и бутылку можно положить в холодильник на бок или везти в сумке.
+Силикон снаружи, сталь внутри
+Корпус из пищевого силикона, внутри стальная вставка - она держит форму и не даёт пробке смяться при нажатии. Силикон не впитывает запах вина и не окрашивается.
+Одно движение ладонью
+Закрыть - нажать сверху, открыть - потянуть за рифлёный верх. Штопор и усилия не нужны, справится одна рука даже с полной бутылкой.
+Подходит к разным бутылкам
+Конус диаметром 2,4 см у основания садится в стандартное винное горлышко, в бутылку из-под пива, крепкого алкоголя, сиропа и масла.
+Четыре цвета в наборе
+Серый, жёлтый, розовый и голубой: открытые бутылки не путаются, каждой своя пробка.
+Размер и упаковка
+Высота 6 см, диаметр 2,4 см. Четыре штуки в картонной коробке - набор подходит для подарка.
+Уход
+Мыть тёплой водой, просушивать перед хранением.</t>
         </is>
       </c>
     </row>
@@ -12660,7 +13047,28 @@
       </c>
       <c r="X71" s="10" t="inlineStr">
         <is>
-          <t>#пробка_для_вина #для_шампанского #винные_аксессуары #сервировка #многоразовая #барные_аксессуары</t>
+          <t>#пробка_для_вина #винные_аксессуары #сервировка #многоразовая #барные_аксессуары #для_бутылки</t>
+        </is>
+      </c>
+      <c r="Y71" s="15" t="inlineStr">
+        <is>
+          <t>Пробка для бутылки вина многоразовая: набор из четырёх силиконовых закрывашек, высота 6,5 см. Закрывается нажатием ладони, открывается потягиванием за верх.
+Кому подходит
+Тем, кто держит на кухне несколько открытых бутылок разом: яркие цвета видно издалека, и понятно, какая уже открыта.
+Быстро закрыть, легко открыть
+Нажать сверху - закрыто, потянуть за рифлёный верх - открыто. Штопор и зажимы не нужны, хватает одной руки.
+Не протекает при перевороте
+Кольцевые уплотнения прижимаются к горлышку изнутри. Бутылку можно положить в холодильник на бок или взять с собой - не подтекает.
+Силикон снаружи, сталь внутри
+Корпус из пищевого силикона, внутри стальная вставка держит форму. Силикон не впитывает запах и не окрашивается от красного вина.
+Подходит к разным бутылкам
+Конус диаметром 2,5 см садится в горлышко вина, пива, крепкого алкоголя, сиропа и масла - одна закрывашка на весь бар и кухню.
+Четыре ярких цвета
+Синий, зелёный, красный и салатовый.
+Размер и упаковка
+Высота 6,5 см, диаметр 2,5 см - помещаются в кухонный ящик. Четыре штуки в картонной коробке.
+Уход
+Можно мыть в посудомоечной машине или тёплой водой вручную, просушивать перед хранением.</t>
         </is>
       </c>
     </row>
@@ -12677,7 +13085,7 @@
       </c>
       <c r="C72" s="10" t="inlineStr">
         <is>
-          <t>Пробка для вина и шампанского силиконовая, стоппер бутылки 4 шт</t>
+          <t>Пробка для вина силиконовая многоразовая, стоппер для бутылки, 4 шт</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -12706,7 +13114,7 @@
       </c>
       <c r="X72" s="10" t="inlineStr">
         <is>
-          <t>#пробка_для_вина #для_шампанского #винные_аксессуары #сервировка #многоразовая #барные_аксессуары</t>
+          <t>#пробка_для_вина #винные_аксессуары #сервировка #многоразовая #барные_аксессуары #для_бутылки</t>
         </is>
       </c>
     </row>
@@ -12758,6 +13166,24 @@
           <t>#кондитерский_инвентарь #для_теста #выпечка #для_кондитера #скребок_для_теста #лопатка</t>
         </is>
       </c>
+      <c r="Y73" s="15" t="inlineStr">
+        <is>
+          <t>Шпатель скребок кондитерский для теста: два инструмента в наборе - гибкий пластиковый скребок 15 × 10,5 см и металлический нож-шпатель 15 × 11,3 см с таблицей мер.
+Кому подходит
+Тем, кто печёт дома регулярно: замес и разделка теста, работа с бисквитом и кремом, чистка стола от муки и налипшего теста.
+Гибкий скребок для теста
+Пластиковая пластина с изогнутым краем адаптируется к кривизне посуды: собирает тесто со стенок миски, снимает остатки с доски, выравнивает крем на боку торта. Ручка-валик по верхней кромке - нажимать удобно всей ладонью.
+Нож-шпатель со шкалой
+Лезвие из нержавеющей стали с антимикробным покрытием разрезает тесто на порции одним движением. На полотно нанесена таблица перевода мер: чашки, ложки, миллилитры. Не нужно искать в телефоне, сколько миллилитров в половине чашки - шкала перед глазами.
+Складываются вместе
+Два предмета вкладываются друг в друга и занимают место одного. Помещаются в ящик стола и в отделение кухонного органайзера.
+Размеры
+Скребок 15 × 10,5 см, нож-шпатель 15 × 11,3 см, толщина ручки 2,6 см.
+Уход
+Мыть тёплой водой с моющим средством, вытирать насухо. Пластиковый скребок допускает мытьё в посудомоечной машине.
+Набор в картонной коробке.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -12804,6 +13230,28 @@
           <t>#нож_для_пиццы #для_теста #тесторезка #кухонные_принадлежности #выпечка #для_кондитера</t>
         </is>
       </c>
+      <c r="Y74" s="15" t="inlineStr">
+        <is>
+          <t>Нож для пиццы и теста качающийся: лезвие-полумесяц 15,5 см с ручкой под всю ладонь, в комплекте чехол. Разрезает пиццу одним нажимом, не сдвигая начинку.
+Кому подходит
+Тем, кого раздражает круглый ролик: колесо тянет сыр и колбасу за собой к краю куска.
+Режет нажимом, а не прокатыванием
+Дугообразное лезвие опускается сверху и качается на месте - начинка остаётся там, где лежала. Целую пиццу проходит за три-четыре движения.
+Ручка на всю ладонь
+Пластиковая скоба с проёмом: рука ложится сверху, усилие идёт от плеча, а не от пальцев. Кисть не устаёт даже на плотном тесте и холодной пицце из коробки.
+Лезвие из нержавеющей стали
+Не тупится о керамику противня, не ржавеет после мойки. Заточка идёт по всей дуге - работает и середина, и края.
+Чехол с вентиляцией
+Надевается на лезвие: нож можно положить в ящик к остальным приборам, не порезав руку при поиске. В чехле прорези - лезвие сохнет и не отсыревает при хранении.
+Не только пицца
+Тесто на полосы, зелень, овощи для рагу, орехи, лаваш и тортилья. Ширина 15,5 см закрывает доску за один проход.
+Размеры
+Лезвие 15,5 см, высота 11,5 см, глубина 7 см.
+Уход
+Мыть тёплой водой или в посудомоечной машине, вытирать насухо. Хранить в чехле.
+В комплекте нож и защитный чехол.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -12848,6 +13296,25 @@
       <c r="X75" s="10" t="inlineStr">
         <is>
           <t>#нож_для_пиццы #для_теста #тесторезка #кухонные_принадлежности #выпечка #для_кондитера</t>
+        </is>
+      </c>
+      <c r="Y75" s="15" t="inlineStr">
+        <is>
+          <t>Нож для пиццы и теста качающийся: лезвие-полумесяц 15 см в пластиковой ручке, в комплекте чехол. Режет нажимом сверху, а не прокатыванием, поэтому начинка остаётся на месте.
+Кому подходит
+Тем, кто раскатывает тесто дома: полосы для лапши и штруделя, порции пиццы, зелень, овощи для рагу, орехи, лаваш.
+Начинка не съезжает
+Круглый ролик тянет сыр и колбасу за собой к краю куска. Дуга опускается сверху и качается на месте: разрез идёт сквозь, а не волочит. Полоса теста получается ровной по всей длине, без тянущегося края.
+Ручка на всю ладонь
+Пластиковая скоба с проёмом под кисть. Усилие идёт от плеча, пальцы не работают на излом - удобно и при плотном тесте, и при холодной пицце.
+Лезвие из нержавеющей стали
+Не ржавеет после мойки, не тупится о противень. Заточка по всей дуге.
+Чехол с вентиляцией
+Надевается на лезвие: нож лежит в общем ящике безопасно. Прорези в чехле не дают скапливаться влаге после мытья.
+Размеры и комплект
+Лезвие 15 см, высота 11,5 см. В коробке нож и защитный чехол.
+Уход
+Мыть тёплой водой или в посудомоечной машине, вытирать насухо. Хранить в чехле.</t>
         </is>
       </c>
     </row>

--- a/docs/ozon/Озон_рабочая_книга.xlsx
+++ b/docs/ozon/Озон_рабочая_книга.xlsx
@@ -948,6 +948,27 @@
           <t>9506919000 - Прочий инвентарь и оборудование для занятий общей физкультурой, гимнастикой или атлетикой</t>
         </is>
       </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>белый</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="inlineStr">
+        <is>
+          <t>Мяч массажный</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="H3" s="10" t="inlineStr">
+        <is>
+          <t>ПВХ (поливинилхлорид)</t>
+        </is>
+      </c>
+      <c r="I3" s="10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -960,6 +981,27 @@
           <t>9506919000 - Прочий инвентарь и оборудование для занятий общей физкультурой, гимнастикой или атлетикой</t>
         </is>
       </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>розовый</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>Мяч массажный</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="H4" s="10" t="inlineStr">
+        <is>
+          <t>ПВХ (поливинилхлорид)</t>
+        </is>
+      </c>
+      <c r="I4" s="10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -972,6 +1014,27 @@
           <t>9506919000 - Прочий инвентарь и оборудование для занятий общей физкультурой, гимнастикой или атлетикой</t>
         </is>
       </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>голубой</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>Мяч массажный</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="H5" s="10" t="inlineStr">
+        <is>
+          <t>ПВХ (поливинилхлорид)</t>
+        </is>
+      </c>
+      <c r="I5" s="10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -984,6 +1047,27 @@
           <t>9506919000 - Прочий инвентарь и оборудование для занятий общей физкультурой, гимнастикой или атлетикой</t>
         </is>
       </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>оранжевый</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>Мяч массажный</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="H6" s="10" t="inlineStr">
+        <is>
+          <t>ПВХ (поливинилхлорид)</t>
+        </is>
+      </c>
+      <c r="I6" s="10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -996,6 +1080,27 @@
           <t>9506919000 - Прочий инвентарь и оборудование для занятий общей физкультурой, гимнастикой или атлетикой</t>
         </is>
       </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>черный</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>Мяч массажный</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="H7" s="10" t="inlineStr">
+        <is>
+          <t>ПВХ (поливинилхлорид)</t>
+        </is>
+      </c>
+      <c r="I7" s="10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1008,6 +1113,27 @@
           <t>9506919000 - Прочий инвентарь и оборудование для занятий общей физкультурой, гимнастикой или атлетикой</t>
         </is>
       </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>белый</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>Мяч массажный</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>ПВХ (поливинилхлорид)</t>
+        </is>
+      </c>
+      <c r="I8" s="10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1020,6 +1146,27 @@
           <t>9506919000 - Прочий инвентарь и оборудование для занятий общей физкультурой, гимнастикой или атлетикой</t>
         </is>
       </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>розовый</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>Мяч массажный</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="H9" s="10" t="inlineStr">
+        <is>
+          <t>ПВХ (поливинилхлорид)</t>
+        </is>
+      </c>
+      <c r="I9" s="10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1032,6 +1179,27 @@
           <t>9506919000 - Прочий инвентарь и оборудование для занятий общей физкультурой, гимнастикой или атлетикой</t>
         </is>
       </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>голубой</t>
+        </is>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>Мяч массажный</t>
+        </is>
+      </c>
+      <c r="G10" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="H10" s="10" t="inlineStr">
+        <is>
+          <t>ПВХ (поливинилхлорид)</t>
+        </is>
+      </c>
+      <c r="I10" s="10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1044,6 +1212,27 @@
           <t>9506919000 - Прочий инвентарь и оборудование для занятий общей физкультурой, гимнастикой или атлетикой</t>
         </is>
       </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>оранжевый</t>
+        </is>
+      </c>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>Мяч массажный</t>
+        </is>
+      </c>
+      <c r="G11" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="H11" s="10" t="inlineStr">
+        <is>
+          <t>ПВХ (поливинилхлорид)</t>
+        </is>
+      </c>
+      <c r="I11" s="10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1056,6 +1245,27 @@
           <t>9506919000 - Прочий инвентарь и оборудование для занятий общей физкультурой, гимнастикой или атлетикой</t>
         </is>
       </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>черный</t>
+        </is>
+      </c>
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>Мяч массажный</t>
+        </is>
+      </c>
+      <c r="G12" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="H12" s="10" t="inlineStr">
+        <is>
+          <t>ПВХ (поливинилхлорид)</t>
+        </is>
+      </c>
+      <c r="I12" s="10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1068,6 +1278,27 @@
           <t>9506919000 - Прочий инвентарь и оборудование для занятий общей физкультурой, гимнастикой или атлетикой</t>
         </is>
       </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>розовый</t>
+        </is>
+      </c>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>Мяч массажный</t>
+        </is>
+      </c>
+      <c r="G13" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="H13" s="10" t="inlineStr">
+        <is>
+          <t>ПВХ (поливинилхлорид)</t>
+        </is>
+      </c>
+      <c r="I13" s="10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1080,6 +1311,27 @@
           <t>9506919000 - Прочий инвентарь и оборудование для занятий общей физкультурой, гимнастикой или атлетикой</t>
         </is>
       </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>голубой</t>
+        </is>
+      </c>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>Мяч массажный</t>
+        </is>
+      </c>
+      <c r="G14" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="H14" s="10" t="inlineStr">
+        <is>
+          <t>ПВХ (поливинилхлорид)</t>
+        </is>
+      </c>
+      <c r="I14" s="10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1092,6 +1344,27 @@
           <t>9506919000 - Прочий инвентарь и оборудование для занятий общей физкультурой, гимнастикой или атлетикой</t>
         </is>
       </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>оранжевый</t>
+        </is>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>Мяч массажный</t>
+        </is>
+      </c>
+      <c r="G15" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="H15" s="10" t="inlineStr">
+        <is>
+          <t>ПВХ (поливинилхлорид)</t>
+        </is>
+      </c>
+      <c r="I15" s="10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1104,6 +1377,27 @@
           <t>9506919000 - Прочий инвентарь и оборудование для занятий общей физкультурой, гимнастикой или атлетикой</t>
         </is>
       </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>черный</t>
+        </is>
+      </c>
+      <c r="E16" s="10" t="inlineStr">
+        <is>
+          <t>Мяч массажный</t>
+        </is>
+      </c>
+      <c r="G16" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="H16" s="10" t="inlineStr">
+        <is>
+          <t>ПВХ (поливинилхлорид)</t>
+        </is>
+      </c>
+      <c r="I16" s="10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1116,6 +1410,27 @@
           <t>9506919000 - Прочий инвентарь и оборудование для занятий общей физкультурой, гимнастикой или атлетикой</t>
         </is>
       </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>фиолетовый</t>
+        </is>
+      </c>
+      <c r="E17" s="10" t="inlineStr">
+        <is>
+          <t>Мяч массажный</t>
+        </is>
+      </c>
+      <c r="G17" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="H17" s="10" t="inlineStr">
+        <is>
+          <t>ПВХ (поливинилхлорид)</t>
+        </is>
+      </c>
+      <c r="I17" s="10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1123,6 +1438,27 @@
           <t>ACRB1MS103BL</t>
         </is>
       </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>голубой</t>
+        </is>
+      </c>
+      <c r="E18" s="10" t="inlineStr">
+        <is>
+          <t>Мяч массажный</t>
+        </is>
+      </c>
+      <c r="G18" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="H18" s="10" t="inlineStr">
+        <is>
+          <t>Термопластический эластомер (TPE)</t>
+        </is>
+      </c>
+      <c r="I18" s="10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1130,12 +1466,54 @@
           <t>ACRB1MS103LI</t>
         </is>
       </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>сиреневый</t>
+        </is>
+      </c>
+      <c r="E19" s="10" t="inlineStr">
+        <is>
+          <t>Мяч массажный</t>
+        </is>
+      </c>
+      <c r="G19" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="H19" s="10" t="inlineStr">
+        <is>
+          <t>Термопластический эластомер (TPE)</t>
+        </is>
+      </c>
+      <c r="I19" s="10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
           <t>ACRB1MS103RJ</t>
         </is>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>оранжевый</t>
+        </is>
+      </c>
+      <c r="E20" s="10" t="inlineStr">
+        <is>
+          <t>Мяч массажный</t>
+        </is>
+      </c>
+      <c r="G20" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="H20" s="10" t="inlineStr">
+        <is>
+          <t>Термопластический эластомер (TPE)</t>
+        </is>
+      </c>
+      <c r="I20" s="10" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1384,6 +1762,57 @@
           <t>3926909709 - Изделия прочие из пластмасс и изделия из прочих материалов товарных позиций 3901 - 3914, прочие, прочие, прочие, прочие</t>
         </is>
       </c>
+      <c r="C3" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>Таблетница</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="n">
+        <v>14</v>
+      </c>
+      <c r="H3" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" s="10" t="inlineStr">
+        <is>
+          <t>Пластик</t>
+        </is>
+      </c>
+      <c r="J3" s="10" t="inlineStr">
+        <is>
+          <t>16 x 12 x 5</t>
+        </is>
+      </c>
+      <c r="K3" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="L3" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="M3" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="N3" s="10" t="inlineStr">
+        <is>
+          <t>150x90x40</t>
+        </is>
+      </c>
+      <c r="O3" s="10" t="n">
+        <v>170</v>
+      </c>
+      <c r="P3" s="10" t="inlineStr">
+        <is>
+          <t>Пакет с клапаном</t>
+        </is>
+      </c>
+      <c r="R3" s="10" t="inlineStr">
+        <is>
+          <t>Контейнер для таблеток на день - 7 шт.; Футляр-органайзер - 1 шт.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1396,6 +1825,57 @@
           <t>3926909709 - Изделия прочие из пластмасс и изделия из прочих материалов товарных позиций 3901 - 3914, прочие, прочие, прочие, прочие</t>
         </is>
       </c>
+      <c r="C4" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>Таблетница</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="n">
+        <v>14</v>
+      </c>
+      <c r="H4" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" s="10" t="inlineStr">
+        <is>
+          <t>Пластик</t>
+        </is>
+      </c>
+      <c r="J4" s="10" t="inlineStr">
+        <is>
+          <t>16 x 12 x 5</t>
+        </is>
+      </c>
+      <c r="K4" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="L4" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="M4" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="N4" s="10" t="inlineStr">
+        <is>
+          <t>150x90x40</t>
+        </is>
+      </c>
+      <c r="O4" s="10" t="n">
+        <v>170</v>
+      </c>
+      <c r="P4" s="10" t="inlineStr">
+        <is>
+          <t>Пакет с клапаном</t>
+        </is>
+      </c>
+      <c r="R4" s="10" t="inlineStr">
+        <is>
+          <t>Контейнер для таблеток на день - 7 шт.; Футляр-органайзер - 1 шт.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1408,6 +1888,57 @@
           <t>3926909709 - Изделия прочие из пластмасс и изделия из прочих материалов товарных позиций 3901 - 3914, прочие, прочие, прочие, прочие</t>
         </is>
       </c>
+      <c r="C5" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>Таблетница</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="n">
+        <v>14</v>
+      </c>
+      <c r="H5" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="10" t="inlineStr">
+        <is>
+          <t>Пластик</t>
+        </is>
+      </c>
+      <c r="J5" s="10" t="inlineStr">
+        <is>
+          <t>16 x 12 x 5</t>
+        </is>
+      </c>
+      <c r="K5" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="L5" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="M5" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="N5" s="10" t="inlineStr">
+        <is>
+          <t>150x90x40</t>
+        </is>
+      </c>
+      <c r="O5" s="10" t="n">
+        <v>170</v>
+      </c>
+      <c r="P5" s="10" t="inlineStr">
+        <is>
+          <t>Пакет с клапаном</t>
+        </is>
+      </c>
+      <c r="R5" s="10" t="inlineStr">
+        <is>
+          <t>Контейнер для таблеток на день - 7 шт.; Футляр-органайзер - 1 шт.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1420,6 +1951,57 @@
           <t>3926909709 - Изделия прочие из пластмасс и изделия из прочих материалов товарных позиций 3901 - 3914, прочие, прочие, прочие, прочие</t>
         </is>
       </c>
+      <c r="C6" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>Таблетница</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="n">
+        <v>14</v>
+      </c>
+      <c r="H6" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>Пластик</t>
+        </is>
+      </c>
+      <c r="J6" s="10" t="inlineStr">
+        <is>
+          <t>16 x 12 x 5</t>
+        </is>
+      </c>
+      <c r="K6" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="L6" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="M6" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="N6" s="10" t="inlineStr">
+        <is>
+          <t>150x90x40</t>
+        </is>
+      </c>
+      <c r="O6" s="10" t="n">
+        <v>170</v>
+      </c>
+      <c r="P6" s="10" t="inlineStr">
+        <is>
+          <t>Пакет с клапаном</t>
+        </is>
+      </c>
+      <c r="R6" s="10" t="inlineStr">
+        <is>
+          <t>Контейнер для таблеток на день - 7 шт.; Футляр-органайзер - 1 шт.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1432,6 +2014,57 @@
           <t>3926909709 - Изделия прочие из пластмасс и изделия из прочих материалов товарных позиций 3901 - 3914, прочие, прочие, прочие, прочие</t>
         </is>
       </c>
+      <c r="C7" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>Таблетница</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="n">
+        <v>14</v>
+      </c>
+      <c r="H7" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>Пластик</t>
+        </is>
+      </c>
+      <c r="J7" s="10" t="inlineStr">
+        <is>
+          <t>17 x 12 x 7</t>
+        </is>
+      </c>
+      <c r="K7" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="L7" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="M7" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="N7" s="10" t="inlineStr">
+        <is>
+          <t>150x70x70</t>
+        </is>
+      </c>
+      <c r="O7" s="10" t="n">
+        <v>165</v>
+      </c>
+      <c r="P7" s="10" t="inlineStr">
+        <is>
+          <t>Пакет с клапаном</t>
+        </is>
+      </c>
+      <c r="R7" s="10" t="inlineStr">
+        <is>
+          <t>Круглый контейнер для таблеток на день - 7 шт.; Футляр-органайзер - 1 шт.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1444,6 +2077,57 @@
           <t>3926909709 - Изделия прочие из пластмасс и изделия из прочих материалов товарных позиций 3901 - 3914, прочие, прочие, прочие, прочие</t>
         </is>
       </c>
+      <c r="C8" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>Таблетница</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="n">
+        <v>14</v>
+      </c>
+      <c r="H8" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>Пластик</t>
+        </is>
+      </c>
+      <c r="J8" s="10" t="inlineStr">
+        <is>
+          <t>17 x 12 x 7</t>
+        </is>
+      </c>
+      <c r="K8" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="L8" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="M8" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="N8" s="10" t="inlineStr">
+        <is>
+          <t>150x70x70</t>
+        </is>
+      </c>
+      <c r="O8" s="10" t="n">
+        <v>165</v>
+      </c>
+      <c r="P8" s="10" t="inlineStr">
+        <is>
+          <t>Пакет с клапаном</t>
+        </is>
+      </c>
+      <c r="R8" s="10" t="inlineStr">
+        <is>
+          <t>Круглый контейнер для таблеток на день - 7 шт.; Футляр-органайзер - 1 шт.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1456,6 +2140,57 @@
           <t>3926909709 - Изделия прочие из пластмасс и изделия из прочих материалов товарных позиций 3901 - 3914, прочие, прочие, прочие, прочие</t>
         </is>
       </c>
+      <c r="C9" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>Таблетница</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>14</v>
+      </c>
+      <c r="H9" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="10" t="inlineStr">
+        <is>
+          <t>Пластик</t>
+        </is>
+      </c>
+      <c r="J9" s="10" t="inlineStr">
+        <is>
+          <t>17 x 12 x 7</t>
+        </is>
+      </c>
+      <c r="K9" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="L9" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="M9" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="N9" s="10" t="inlineStr">
+        <is>
+          <t>150x70x70</t>
+        </is>
+      </c>
+      <c r="O9" s="10" t="n">
+        <v>150</v>
+      </c>
+      <c r="P9" s="10" t="inlineStr">
+        <is>
+          <t>Пакет с клапаном</t>
+        </is>
+      </c>
+      <c r="R9" s="10" t="inlineStr">
+        <is>
+          <t>Круглый контейнер для таблеток на день - 7 шт.; Футляр-органайзер - 1 шт.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1468,6 +2203,57 @@
           <t>3926909709 - Изделия прочие из пластмасс и изделия из прочих материалов товарных позиций 3901 - 3914, прочие, прочие, прочие, прочие</t>
         </is>
       </c>
+      <c r="C10" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>Таблетница</t>
+        </is>
+      </c>
+      <c r="E10" s="10" t="n">
+        <v>14</v>
+      </c>
+      <c r="H10" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="10" t="inlineStr">
+        <is>
+          <t>Пластик</t>
+        </is>
+      </c>
+      <c r="J10" s="10" t="inlineStr">
+        <is>
+          <t>17 x 12 x 7</t>
+        </is>
+      </c>
+      <c r="K10" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="L10" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="M10" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="N10" s="10" t="inlineStr">
+        <is>
+          <t>150x70x70</t>
+        </is>
+      </c>
+      <c r="O10" s="10" t="n">
+        <v>150</v>
+      </c>
+      <c r="P10" s="10" t="inlineStr">
+        <is>
+          <t>Пакет с клапаном</t>
+        </is>
+      </c>
+      <c r="R10" s="10" t="inlineStr">
+        <is>
+          <t>Круглый контейнер для таблеток на день - 7 шт.; Футляр-органайзер - 1 шт.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1478,6 +2264,57 @@
       <c r="B11" s="10" t="inlineStr">
         <is>
           <t>3926909709 - Изделия прочие из пластмасс и изделия из прочих материалов товарных позиций 3901 - 3914, прочие, прочие, прочие, прочие</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>Таблетница</t>
+        </is>
+      </c>
+      <c r="E11" s="10" t="n">
+        <v>14</v>
+      </c>
+      <c r="H11" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" s="10" t="inlineStr">
+        <is>
+          <t>Пластик</t>
+        </is>
+      </c>
+      <c r="J11" s="10" t="inlineStr">
+        <is>
+          <t>17 x 12 x 7</t>
+        </is>
+      </c>
+      <c r="K11" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="L11" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="M11" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="N11" s="10" t="inlineStr">
+        <is>
+          <t>150x70x70</t>
+        </is>
+      </c>
+      <c r="O11" s="10" t="n">
+        <v>150</v>
+      </c>
+      <c r="P11" s="10" t="inlineStr">
+        <is>
+          <t>Пакет с клапаном</t>
+        </is>
+      </c>
+      <c r="R11" s="10" t="inlineStr">
+        <is>
+          <t>Круглый контейнер для таблеток на день - 7 шт.; Футляр-органайзер - 1 шт.</t>
         </is>
       </c>
     </row>
@@ -1822,6 +2659,40 @@
           <t>9506919000 - Прочий инвентарь и оборудование для занятий общей физкультурой, гимнастикой или атлетикой</t>
         </is>
       </c>
+      <c r="C3" s="10" t="n">
+        <v>38</v>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>Фитнес-резинка</t>
+        </is>
+      </c>
+      <c r="F3" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="G3" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="I3" s="10" t="inlineStr">
+        <is>
+          <t>Ягодицы</t>
+        </is>
+      </c>
+      <c r="J3" s="10" t="inlineStr">
+        <is>
+          <t>Взрослая</t>
+        </is>
+      </c>
+      <c r="K3" s="10" t="inlineStr">
+        <is>
+          <t>Набор</t>
+        </is>
+      </c>
+      <c r="L3" s="10" t="inlineStr">
+        <is>
+          <t>Фитнес-резинка - 3 шт.; Мешочек для хранения - 1 шт.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1834,6 +2705,37 @@
           <t>9506919000 - Прочий инвентарь и оборудование для занятий общей физкультурой, гимнастикой или атлетикой</t>
         </is>
       </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>Фитнес-резинка</t>
+        </is>
+      </c>
+      <c r="F4" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="G4" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="I4" s="10" t="inlineStr">
+        <is>
+          <t>Ягодицы</t>
+        </is>
+      </c>
+      <c r="J4" s="10" t="inlineStr">
+        <is>
+          <t>Взрослая</t>
+        </is>
+      </c>
+      <c r="K4" s="10" t="inlineStr">
+        <is>
+          <t>Набор</t>
+        </is>
+      </c>
+      <c r="L4" s="10" t="inlineStr">
+        <is>
+          <t>Фитнес-резинка - 5 шт.; Мешочек для хранения - 1 шт.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1846,6 +2748,34 @@
           <t>9506919000 - Прочий инвентарь и оборудование для занятий общей физкультурой, гимнастикой или атлетикой</t>
         </is>
       </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>Фитнес-резинка</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="I5" s="10" t="inlineStr">
+        <is>
+          <t>Ягодицы</t>
+        </is>
+      </c>
+      <c r="J5" s="10" t="inlineStr">
+        <is>
+          <t>Взрослая</t>
+        </is>
+      </c>
+      <c r="K5" s="10" t="inlineStr">
+        <is>
+          <t>Набор</t>
+        </is>
+      </c>
+      <c r="L5" s="10" t="inlineStr">
+        <is>
+          <t>Фитнес-резинка - 4 шт.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1853,6 +2783,24 @@
           <t>ACRB5FR400CL</t>
         </is>
       </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>Фитнес-резинка</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="J6" s="10" t="inlineStr">
+        <is>
+          <t>Взрослая</t>
+        </is>
+      </c>
+      <c r="K6" s="10" t="inlineStr">
+        <is>
+          <t>Набор</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1860,6 +2808,37 @@
           <t>ACRB1SK101BC</t>
         </is>
       </c>
+      <c r="C7" s="10" t="n">
+        <v>300</v>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>Скакалка</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>Ноги</t>
+        </is>
+      </c>
+      <c r="J7" s="10" t="inlineStr">
+        <is>
+          <t>Взрослая</t>
+        </is>
+      </c>
+      <c r="K7" s="10" t="inlineStr">
+        <is>
+          <t>Подшипники в рукоятках (ручках)</t>
+        </is>
+      </c>
+      <c r="L7" s="10" t="inlineStr">
+        <is>
+          <t>Скакалка - 1 шт.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1867,11 +2846,73 @@
           <t>ACRB1SK101RD</t>
         </is>
       </c>
+      <c r="C8" s="10" t="n">
+        <v>300</v>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>Скакалка</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>Ноги</t>
+        </is>
+      </c>
+      <c r="J8" s="10" t="inlineStr">
+        <is>
+          <t>Взрослая</t>
+        </is>
+      </c>
+      <c r="K8" s="10" t="inlineStr">
+        <is>
+          <t>Подшипники в рукоятках (ручках)</t>
+        </is>
+      </c>
+      <c r="L8" s="10" t="inlineStr">
+        <is>
+          <t>Скакалка - 1 шт.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
           <t>ACRB1SK101BL</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="n">
+        <v>300</v>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>Скакалка</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="10" t="inlineStr">
+        <is>
+          <t>Ноги</t>
+        </is>
+      </c>
+      <c r="J9" s="10" t="inlineStr">
+        <is>
+          <t>Взрослая</t>
+        </is>
+      </c>
+      <c r="K9" s="10" t="inlineStr">
+        <is>
+          <t>Подшипники в рукоятках (ручках)</t>
+        </is>
+      </c>
+      <c r="L9" s="10" t="inlineStr">
+        <is>
+          <t>Скакалка - 1 шт.</t>
         </is>
       </c>
     </row>
@@ -2084,6 +3125,50 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>AKTA2KN101YL</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>желтый</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="E3" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" s="10" t="inlineStr">
+        <is>
+          <t>Шпатель-скребок кондитерский</t>
+        </is>
+      </c>
+      <c r="H3" s="10" t="inlineStr">
+        <is>
+          <t>Скребок для теста</t>
+        </is>
+      </c>
+      <c r="J3" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="K3" s="10" t="inlineStr">
+        <is>
+          <t>Нержавеющая сталь</t>
+        </is>
+      </c>
+      <c r="L3" s="10" t="inlineStr">
+        <is>
+          <t>Пластик</t>
+        </is>
+      </c>
+      <c r="N3" s="10" t="inlineStr">
+        <is>
+          <t>Фабричное производство</t>
+        </is>
+      </c>
+      <c r="O3" s="10" t="inlineStr">
+        <is>
+          <t>Скребок пластиковый - 1 шт.; Нож-шпатель металлический - 1 шт.</t>
         </is>
       </c>
     </row>
@@ -45658,6 +46743,49 @@
           <t>9019109009 - Прочая аппаратура для механотерапии, аппараты массажные, аппаратура для  психологических тестов для определения способностей</t>
         </is>
       </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>Аксессуар для массажа</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>оранжевый</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="G3" s="10" t="inlineStr">
+        <is>
+          <t>Вставить палец внутрь и прокатить ролики от основания к кончику пять-десять раз. На кисть уходит две-три минуты.</t>
+        </is>
+      </c>
+      <c r="H3" s="10" t="inlineStr">
+        <is>
+          <t>Роликовый</t>
+        </is>
+      </c>
+      <c r="I3" s="10" t="inlineStr">
+        <is>
+          <t>Руки</t>
+        </is>
+      </c>
+      <c r="K3" s="10" t="inlineStr">
+        <is>
+          <t>Акрил</t>
+        </is>
+      </c>
+      <c r="N3" s="10" t="inlineStr">
+        <is>
+          <t>Картонная коробка</t>
+        </is>
+      </c>
+      <c r="O3" s="10" t="inlineStr">
+        <is>
+          <t>Массажер - 1 шт.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -45666,6 +46794,44 @@
         </is>
       </c>
       <c r="B4" s="9" t="inlineStr"/>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>Аксессуар для массажа</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>оранжевый</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="n">
+        <v>160</v>
+      </c>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>Взять за ручки, завести ленту за спину и прокатывать ролики по мышцам. Интенсивность задаётся натяжением ленты.</t>
+        </is>
+      </c>
+      <c r="H4" s="10" t="inlineStr">
+        <is>
+          <t>Роликовый</t>
+        </is>
+      </c>
+      <c r="I4" s="10" t="inlineStr">
+        <is>
+          <t>Шея</t>
+        </is>
+      </c>
+      <c r="K4" s="10" t="inlineStr">
+        <is>
+          <t>Пластик</t>
+        </is>
+      </c>
+      <c r="O4" s="10" t="inlineStr">
+        <is>
+          <t>Массажер - 1 шт.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -45674,6 +46840,44 @@
         </is>
       </c>
       <c r="B5" s="9" t="inlineStr"/>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>Аксессуар для массажа</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>розовый</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="n">
+        <v>160</v>
+      </c>
+      <c r="G5" s="10" t="inlineStr">
+        <is>
+          <t>Взять за ручки, завести ленту за спину и прокатывать ролики по мышцам. Интенсивность задаётся натяжением ленты.</t>
+        </is>
+      </c>
+      <c r="H5" s="10" t="inlineStr">
+        <is>
+          <t>Роликовый</t>
+        </is>
+      </c>
+      <c r="I5" s="10" t="inlineStr">
+        <is>
+          <t>Шея</t>
+        </is>
+      </c>
+      <c r="K5" s="10" t="inlineStr">
+        <is>
+          <t>Пластик</t>
+        </is>
+      </c>
+      <c r="O5" s="10" t="inlineStr">
+        <is>
+          <t>Массажер - 1 шт.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -45682,6 +46886,44 @@
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr"/>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>Аксессуар для массажа</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>голубой</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="n">
+        <v>160</v>
+      </c>
+      <c r="G6" s="10" t="inlineStr">
+        <is>
+          <t>Взять за ручки, завести ленту за спину и прокатывать ролики по мышцам. Интенсивность задаётся натяжением ленты.</t>
+        </is>
+      </c>
+      <c r="H6" s="10" t="inlineStr">
+        <is>
+          <t>Роликовый</t>
+        </is>
+      </c>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>Шея</t>
+        </is>
+      </c>
+      <c r="K6" s="10" t="inlineStr">
+        <is>
+          <t>Пластик</t>
+        </is>
+      </c>
+      <c r="O6" s="10" t="inlineStr">
+        <is>
+          <t>Массажер - 1 шт.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="7">
@@ -45946,6 +47188,59 @@
           <t>4016999708 - Изделия из вулканизованной резины, кроме твердой резины, прочие: прочие, прочие</t>
         </is>
       </c>
+      <c r="C3" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>красный</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="inlineStr">
+        <is>
+          <t>Мяч</t>
+        </is>
+      </c>
+      <c r="F3" s="10" t="inlineStr">
+        <is>
+          <t>Для собак</t>
+        </is>
+      </c>
+      <c r="H3" s="10" t="inlineStr">
+        <is>
+          <t>Мяч</t>
+        </is>
+      </c>
+      <c r="I3" s="10" t="inlineStr">
+        <is>
+          <t>для апортировки и дрессировки</t>
+        </is>
+      </c>
+      <c r="J3" s="10" t="inlineStr">
+        <is>
+          <t>Улица</t>
+        </is>
+      </c>
+      <c r="K3" s="10" t="inlineStr">
+        <is>
+          <t>С шипами</t>
+        </is>
+      </c>
+      <c r="L3" s="10" t="inlineStr">
+        <is>
+          <t>11 x 8 x 6</t>
+        </is>
+      </c>
+      <c r="M3" s="10" t="inlineStr">
+        <is>
+          <t>Термопластичная резина (ТПР)</t>
+        </is>
+      </c>
+      <c r="P3" s="10" t="inlineStr">
+        <is>
+          <t>Мяч на ремешке - 1 шт.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -45958,6 +47253,59 @@
           <t>4016999708 - Изделия из вулканизованной резины, кроме твердой резины, прочие: прочие, прочие</t>
         </is>
       </c>
+      <c r="C4" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>темно-синий</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>Мяч</t>
+        </is>
+      </c>
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>Для собак</t>
+        </is>
+      </c>
+      <c r="H4" s="10" t="inlineStr">
+        <is>
+          <t>Мяч</t>
+        </is>
+      </c>
+      <c r="I4" s="10" t="inlineStr">
+        <is>
+          <t>для апортировки и дрессировки</t>
+        </is>
+      </c>
+      <c r="J4" s="10" t="inlineStr">
+        <is>
+          <t>Улица</t>
+        </is>
+      </c>
+      <c r="K4" s="10" t="inlineStr">
+        <is>
+          <t>С шипами</t>
+        </is>
+      </c>
+      <c r="L4" s="10" t="inlineStr">
+        <is>
+          <t>11 x 8 x 6</t>
+        </is>
+      </c>
+      <c r="M4" s="10" t="inlineStr">
+        <is>
+          <t>Термопластичная резина (ТПР)</t>
+        </is>
+      </c>
+      <c r="P4" s="10" t="inlineStr">
+        <is>
+          <t>Мяч на ремешке - 1 шт.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -45970,6 +47318,59 @@
           <t>4016999708 - Изделия из вулканизованной резины, кроме твердой резины, прочие: прочие, прочие</t>
         </is>
       </c>
+      <c r="C5" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>красный</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>Мяч</t>
+        </is>
+      </c>
+      <c r="F5" s="10" t="inlineStr">
+        <is>
+          <t>Для собак</t>
+        </is>
+      </c>
+      <c r="H5" s="10" t="inlineStr">
+        <is>
+          <t>Мяч</t>
+        </is>
+      </c>
+      <c r="I5" s="10" t="inlineStr">
+        <is>
+          <t>для апортировки и дрессировки</t>
+        </is>
+      </c>
+      <c r="J5" s="10" t="inlineStr">
+        <is>
+          <t>Улица</t>
+        </is>
+      </c>
+      <c r="L5" s="10" t="inlineStr">
+        <is>
+          <t>12 x 9 x 7</t>
+        </is>
+      </c>
+      <c r="M5" s="10" t="inlineStr">
+        <is>
+          <t>Термопластичная резина (ТПР)</t>
+        </is>
+      </c>
+      <c r="N5" s="10" t="inlineStr">
+        <is>
+          <t>70x70x70</t>
+        </is>
+      </c>
+      <c r="P5" s="10" t="inlineStr">
+        <is>
+          <t>Мяч на ремешке - 1 шт.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -45982,6 +47383,59 @@
           <t>4016999708 - Изделия из вулканизованной резины, кроме твердой резины, прочие: прочие, прочие</t>
         </is>
       </c>
+      <c r="C6" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>темно-синий</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>Мяч</t>
+        </is>
+      </c>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>Для собак</t>
+        </is>
+      </c>
+      <c r="H6" s="10" t="inlineStr">
+        <is>
+          <t>Мяч</t>
+        </is>
+      </c>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>для апортировки и дрессировки</t>
+        </is>
+      </c>
+      <c r="J6" s="10" t="inlineStr">
+        <is>
+          <t>Улица</t>
+        </is>
+      </c>
+      <c r="L6" s="10" t="inlineStr">
+        <is>
+          <t>12 x 9 x 7</t>
+        </is>
+      </c>
+      <c r="M6" s="10" t="inlineStr">
+        <is>
+          <t>Термопластичная резина (ТПР)</t>
+        </is>
+      </c>
+      <c r="N6" s="10" t="inlineStr">
+        <is>
+          <t>70x70x70</t>
+        </is>
+      </c>
+      <c r="P6" s="10" t="inlineStr">
+        <is>
+          <t>Мяч на ремешке - 1 шт.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -45994,6 +47448,67 @@
           <t>5609000000 - Изделия из нитей или пряжи, плоских или аналогичных нитей товарной позиции 5404 или 5405, бечевка, веревки, канаты или тросы, в другом месте не поименованные</t>
         </is>
       </c>
+      <c r="C7" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>бежевый</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>Канат</t>
+        </is>
+      </c>
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>Для собак</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="n">
+        <v>580</v>
+      </c>
+      <c r="H7" s="10" t="inlineStr">
+        <is>
+          <t>Канат, веревка</t>
+        </is>
+      </c>
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>для здоровья зубов и десен</t>
+        </is>
+      </c>
+      <c r="J7" s="10" t="inlineStr">
+        <is>
+          <t>Улица</t>
+        </is>
+      </c>
+      <c r="K7" s="10" t="inlineStr">
+        <is>
+          <t>Из натуральных материалов</t>
+        </is>
+      </c>
+      <c r="L7" s="10" t="inlineStr">
+        <is>
+          <t>19 x 19 x 8</t>
+        </is>
+      </c>
+      <c r="M7" s="10" t="inlineStr">
+        <is>
+          <t>Хлопок</t>
+        </is>
+      </c>
+      <c r="N7" s="10" t="inlineStr">
+        <is>
+          <t>550x50</t>
+        </is>
+      </c>
+      <c r="P7" s="10" t="inlineStr">
+        <is>
+          <t>Канат - 1 шт.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -46004,6 +47519,67 @@
       <c r="B8" s="10" t="inlineStr">
         <is>
           <t>5609000000 - Изделия из нитей или пряжи, плоских или аналогичных нитей товарной позиции 5404 или 5405, бечевка, веревки, канаты или тросы, в другом месте не поименованные</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>желтый</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>Канат</t>
+        </is>
+      </c>
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>Для собак</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="n">
+        <v>380</v>
+      </c>
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>Канат, веревка</t>
+        </is>
+      </c>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>для здоровья зубов и десен</t>
+        </is>
+      </c>
+      <c r="J8" s="10" t="inlineStr">
+        <is>
+          <t>Улица</t>
+        </is>
+      </c>
+      <c r="K8" s="10" t="inlineStr">
+        <is>
+          <t>Из натуральных материалов</t>
+        </is>
+      </c>
+      <c r="L8" s="10" t="inlineStr">
+        <is>
+          <t>21 x 15 x 6</t>
+        </is>
+      </c>
+      <c r="M8" s="10" t="inlineStr">
+        <is>
+          <t>Хлопок</t>
+        </is>
+      </c>
+      <c r="N8" s="10" t="inlineStr">
+        <is>
+          <t>550x50</t>
+        </is>
+      </c>
+      <c r="P8" s="10" t="inlineStr">
+        <is>
+          <t>Канат - 1 шт.</t>
         </is>
       </c>
     </row>
@@ -46243,6 +47819,57 @@
           <t>8211930000 - Прочие ножи с нефиксированными лезвиями</t>
         </is>
       </c>
+      <c r="C3" s="10" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>желтый</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="inlineStr">
+        <is>
+          <t>Кухонный нож</t>
+        </is>
+      </c>
+      <c r="F3" s="10" t="inlineStr">
+        <is>
+          <t>Гладкая</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="inlineStr">
+        <is>
+          <t>для пиццы</t>
+        </is>
+      </c>
+      <c r="H3" s="10" t="inlineStr">
+        <is>
+          <t>Пластик</t>
+        </is>
+      </c>
+      <c r="I3" s="10" t="inlineStr">
+        <is>
+          <t>Нержавеющая сталь</t>
+        </is>
+      </c>
+      <c r="J3" s="10" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="K3" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O3" s="10" t="inlineStr">
+        <is>
+          <t>Фабричное производство</t>
+        </is>
+      </c>
+      <c r="P3" s="10" t="inlineStr">
+        <is>
+          <t>Нож - 1 шт.; Защитный чехол - 1 шт.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -46253,6 +47880,57 @@
       <c r="B4" s="10" t="inlineStr">
         <is>
           <t>8211930000 - Прочие ножи с нефиксированными лезвиями</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>зеленый</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>Кухонный нож</t>
+        </is>
+      </c>
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>Гладкая</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>для пиццы</t>
+        </is>
+      </c>
+      <c r="H4" s="10" t="inlineStr">
+        <is>
+          <t>Пластик</t>
+        </is>
+      </c>
+      <c r="I4" s="10" t="inlineStr">
+        <is>
+          <t>Нержавеющая сталь</t>
+        </is>
+      </c>
+      <c r="J4" s="10" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="K4" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" s="10" t="inlineStr">
+        <is>
+          <t>Фабричное производство</t>
+        </is>
+      </c>
+      <c r="P4" s="10" t="inlineStr">
+        <is>
+          <t>Нож - 1 шт.; Защитный чехол - 1 шт.</t>
         </is>
       </c>
     </row>
@@ -46487,6 +48165,27 @@
           <t>ACRF1BN101PN</t>
         </is>
       </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>Маска-бандаж</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" s="10" t="inlineStr">
+        <is>
+          <t>Надеть на подбородок, свести ленту на макушке и отрегулировать натяжение липучкой. Носить от 30 минут.</t>
+        </is>
+      </c>
+      <c r="I3" s="10" t="inlineStr">
+        <is>
+          <t>Взрослая</t>
+        </is>
+      </c>
+      <c r="M3" s="10" t="n">
+        <v>8.5</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -46494,11 +48193,50 @@
           <t>ACRF1BN101BC</t>
         </is>
       </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>Маска-бандаж</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>Надеть на подбородок, свести ленту на макушке и отрегулировать натяжение липучкой. Носить от 30 минут.</t>
+        </is>
+      </c>
+      <c r="I4" s="10" t="inlineStr">
+        <is>
+          <t>Взрослая</t>
+        </is>
+      </c>
+      <c r="M4" s="10" t="n">
+        <v>8.5</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
           <t>ACRF1BN201GR</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>Маска-бандаж</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="10" t="inlineStr">
+        <is>
+          <t>Надеть на подбородок, свести ленту на макушке и отрегулировать натяжение липучкой. Носить от 30 минут.</t>
+        </is>
+      </c>
+      <c r="I5" s="10" t="inlineStr">
+        <is>
+          <t>Взрослая</t>
         </is>
       </c>
     </row>
@@ -46688,6 +48426,29 @@
           <t>6307909800 - Прочие готовые изделия, включая выкройки одежды</t>
         </is>
       </c>
+      <c r="D3" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="E3" s="10" t="inlineStr">
+        <is>
+          <t>Мешок для стирки</t>
+        </is>
+      </c>
+      <c r="I3" s="10" t="inlineStr">
+        <is>
+          <t>Полиэстер</t>
+        </is>
+      </c>
+      <c r="K3" s="10" t="inlineStr">
+        <is>
+          <t>Фабричное производство</t>
+        </is>
+      </c>
+      <c r="L3" s="10" t="inlineStr">
+        <is>
+          <t>Мешок для стирки рубашек 40 × 50 см - 1 шт.; Мешок для стирки платьев 30 × 40 см - 1 шт.; Мешок для стирки деликатных тканей 20 × 30 см - 1 шт.; Мешок для стирки нижнего белья 20 × 20 см - 1 шт.; Мешок для стирки носков 18 × 22 см - 1 шт.; Мешок для стирки бюстгальтера 15 × 18 см - 1 шт.; Мешок-контейнер для стирки бюстгальтера с каркасом 15 × 17 см - 1 шт.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -46700,6 +48461,35 @@
           <t>6307909800 - Прочие готовые изделия, включая выкройки одежды</t>
         </is>
       </c>
+      <c r="C4" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="D4" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>Мешок для стирки</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="n">
+        <v>17</v>
+      </c>
+      <c r="I4" s="10" t="inlineStr">
+        <is>
+          <t>Полиэстер</t>
+        </is>
+      </c>
+      <c r="K4" s="10" t="inlineStr">
+        <is>
+          <t>Фабричное производство</t>
+        </is>
+      </c>
+      <c r="L4" s="10" t="inlineStr">
+        <is>
+          <t>Мешок-контейнер для стирки бюстгальтера с каркасом 17 × 15 см - 1 шт.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -46712,6 +48502,29 @@
           <t>6307909800 - Прочие готовые изделия, включая выкройки одежды</t>
         </is>
       </c>
+      <c r="D5" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>Мешок для стирки</t>
+        </is>
+      </c>
+      <c r="I5" s="10" t="inlineStr">
+        <is>
+          <t>Полиэстер</t>
+        </is>
+      </c>
+      <c r="K5" s="10" t="inlineStr">
+        <is>
+          <t>Фабричное производство</t>
+        </is>
+      </c>
+      <c r="L5" s="10" t="inlineStr">
+        <is>
+          <t>Мешок для стирки рубашек 40 × 50 см - 1 шт.; Мешок для стирки платьев 30 × 40 см - 1 шт.; Мешок для стирки носков 18 × 22 см - 1 шт.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -46724,6 +48537,29 @@
           <t>6307909800 - Прочие готовые изделия, включая выкройки одежды</t>
         </is>
       </c>
+      <c r="D6" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>Мешок для стирки</t>
+        </is>
+      </c>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>Полиэстер</t>
+        </is>
+      </c>
+      <c r="K6" s="10" t="inlineStr">
+        <is>
+          <t>Фабричное производство</t>
+        </is>
+      </c>
+      <c r="L6" s="10" t="inlineStr">
+        <is>
+          <t>Мешок для стирки бюстгальтера 15 × 18 см - 1 шт.; Мешок для стирки деликатных тканей 20 × 30 см - 1 шт.; Мешок для стирки нижнего белья 20 × 20 см - 1 шт.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -46736,6 +48572,29 @@
           <t>6307909800 - Прочие готовые изделия, включая выкройки одежды</t>
         </is>
       </c>
+      <c r="D7" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>Мешок для стирки</t>
+        </is>
+      </c>
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>Полиэстер</t>
+        </is>
+      </c>
+      <c r="K7" s="10" t="inlineStr">
+        <is>
+          <t>Фабричное производство</t>
+        </is>
+      </c>
+      <c r="L7" s="10" t="inlineStr">
+        <is>
+          <t>Мешок для стирки 30 × 40 см - 1 шт.; Мешок для стирки 40 × 50 см - 1 шт.; Мешок для стирки 50 × 60 см - 1 шт.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -46743,6 +48602,29 @@
           <t>AHMA3BW202WH</t>
         </is>
       </c>
+      <c r="D8" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>Мешок для стирки</t>
+        </is>
+      </c>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>Полиэстер</t>
+        </is>
+      </c>
+      <c r="K8" s="10" t="inlineStr">
+        <is>
+          <t>Фабричное производство</t>
+        </is>
+      </c>
+      <c r="L8" s="10" t="inlineStr">
+        <is>
+          <t>Мешок для стирки 30 × 40 см - 1 шт.; Мешок для стирки 40 × 50 см - 1 шт.; Мешок для стирки 50 × 60 см - 1 шт.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -46755,6 +48637,29 @@
           <t>6307909800 - Прочие готовые изделия, включая выкройки одежды</t>
         </is>
       </c>
+      <c r="D9" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>Мешок для стирки</t>
+        </is>
+      </c>
+      <c r="I9" s="10" t="inlineStr">
+        <is>
+          <t>Полиэстер</t>
+        </is>
+      </c>
+      <c r="K9" s="10" t="inlineStr">
+        <is>
+          <t>Фабричное производство</t>
+        </is>
+      </c>
+      <c r="L9" s="10" t="inlineStr">
+        <is>
+          <t>Мешок-контейнер для стирки бюстгальтера с каркасом 17 × 15 см - 1 шт.; Мешок для стирки нижнего белья 18 × 16 см - 1 шт.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -46762,6 +48667,29 @@
           <t>AHMA2BW202WH</t>
         </is>
       </c>
+      <c r="D10" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>Мешок для стирки</t>
+        </is>
+      </c>
+      <c r="I10" s="10" t="inlineStr">
+        <is>
+          <t>Полиэстер</t>
+        </is>
+      </c>
+      <c r="K10" s="10" t="inlineStr">
+        <is>
+          <t>Фабричное производство</t>
+        </is>
+      </c>
+      <c r="L10" s="10" t="inlineStr">
+        <is>
+          <t>Мешок-контейнер для стирки бюстгальтера с каркасом 17 × 15 см - 1 шт.; Мешок для стирки нижнего белья 18 × 16 см - 1 шт.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -46774,6 +48702,35 @@
           <t>6307909800 - Прочие готовые изделия, включая выкройки одежды</t>
         </is>
       </c>
+      <c r="C11" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="D11" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>Мешок для стирки</t>
+        </is>
+      </c>
+      <c r="G11" s="10" t="n">
+        <v>80</v>
+      </c>
+      <c r="I11" s="10" t="inlineStr">
+        <is>
+          <t>Полиэстер</t>
+        </is>
+      </c>
+      <c r="K11" s="10" t="inlineStr">
+        <is>
+          <t>Фабричное производство</t>
+        </is>
+      </c>
+      <c r="L11" s="10" t="inlineStr">
+        <is>
+          <t>Мешок для стирки 60 × 80 см крупная сетка - 1 шт.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -46786,6 +48743,35 @@
           <t>6307909800 - Прочие готовые изделия, включая выкройки одежды</t>
         </is>
       </c>
+      <c r="C12" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="D12" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>Мешок для стирки</t>
+        </is>
+      </c>
+      <c r="G12" s="10" t="n">
+        <v>80</v>
+      </c>
+      <c r="I12" s="10" t="inlineStr">
+        <is>
+          <t>Полиэстер</t>
+        </is>
+      </c>
+      <c r="K12" s="10" t="inlineStr">
+        <is>
+          <t>Фабричное производство</t>
+        </is>
+      </c>
+      <c r="L12" s="10" t="inlineStr">
+        <is>
+          <t>Мешок для стирки 60 × 80 см мелкая сетка - 1 шт.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -46796,6 +48782,32 @@
       <c r="B13" s="10" t="inlineStr">
         <is>
           <t>6307909800 - Прочие готовые изделия, включая выкройки одежды</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="n">
+        <v>35</v>
+      </c>
+      <c r="D13" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>Мешок для стирки</t>
+        </is>
+      </c>
+      <c r="I13" s="10" t="inlineStr">
+        <is>
+          <t>Полиэстер</t>
+        </is>
+      </c>
+      <c r="K13" s="10" t="inlineStr">
+        <is>
+          <t>Фабричное производство</t>
+        </is>
+      </c>
+      <c r="L13" s="10" t="inlineStr">
+        <is>
+          <t>Мешок для стирки обуви каркасный 35 см - 1 шт.</t>
         </is>
       </c>
     </row>
@@ -47009,6 +49021,39 @@
           <t>3923509000 - Прочие пробки, крышки, колпаки и другие укупорочные средства, из пластмасс</t>
         </is>
       </c>
+      <c r="C3" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>серый, желтый, розовый, голубой</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="inlineStr">
+        <is>
+          <t>Пробка для бутылки</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="inlineStr">
+        <is>
+          <t>универсальный</t>
+        </is>
+      </c>
+      <c r="J3" s="10" t="inlineStr">
+        <is>
+          <t>Силикон</t>
+        </is>
+      </c>
+      <c r="N3" s="10" t="inlineStr">
+        <is>
+          <t>Фабричное производство</t>
+        </is>
+      </c>
+      <c r="O3" s="10" t="inlineStr">
+        <is>
+          <t>Пробка - 4 шт.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -47021,11 +49066,82 @@
           <t>3923509000 - Прочие пробки, крышки, колпаки и другие укупорочные средства, из пластмасс</t>
         </is>
       </c>
+      <c r="C4" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>синий, зеленый, красный, салатовый</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>Пробка для бутылки</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>универсальный</t>
+        </is>
+      </c>
+      <c r="H4" s="10" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="J4" s="10" t="inlineStr">
+        <is>
+          <t>Силикон</t>
+        </is>
+      </c>
+      <c r="N4" s="10" t="inlineStr">
+        <is>
+          <t>Фабричное производство</t>
+        </is>
+      </c>
+      <c r="O4" s="10" t="inlineStr">
+        <is>
+          <t>Пробка - 4 шт.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
           <t>AKTA4ST102CL</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>серый, желтый, розовый, голубой</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>Пробка для бутылки</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="inlineStr">
+        <is>
+          <t>универсальный</t>
+        </is>
+      </c>
+      <c r="J5" s="10" t="inlineStr">
+        <is>
+          <t>Силикон</t>
+        </is>
+      </c>
+      <c r="N5" s="10" t="inlineStr">
+        <is>
+          <t>Фабричное производство</t>
+        </is>
+      </c>
+      <c r="O5" s="10" t="inlineStr">
+        <is>
+          <t>Пробка - 4 шт.</t>
         </is>
       </c>
     </row>

--- a/docs/ozon/Озон_рабочая_книга.xlsx
+++ b/docs/ozon/Озон_рабочая_книга.xlsx
@@ -2660,7 +2660,7 @@
         </is>
       </c>
       <c r="C3" s="10" t="n">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="D3" s="10" t="inlineStr">
         <is>
@@ -47206,6 +47206,9 @@
           <t>Для собак</t>
         </is>
       </c>
+      <c r="G3" s="10" t="n">
+        <v>80</v>
+      </c>
       <c r="H3" s="10" t="inlineStr">
         <is>
           <t>Мяч</t>
@@ -47234,6 +47237,11 @@
       <c r="M3" s="10" t="inlineStr">
         <is>
           <t>Термопластичная резина (ТПР)</t>
+        </is>
+      </c>
+      <c r="N3" s="10" t="inlineStr">
+        <is>
+          <t>280x80x60</t>
         </is>
       </c>
       <c r="P3" s="10" t="inlineStr">
@@ -47271,6 +47279,9 @@
           <t>Для собак</t>
         </is>
       </c>
+      <c r="G4" s="10" t="n">
+        <v>80</v>
+      </c>
       <c r="H4" s="10" t="inlineStr">
         <is>
           <t>Мяч</t>
@@ -47299,6 +47310,11 @@
       <c r="M4" s="10" t="inlineStr">
         <is>
           <t>Термопластичная резина (ТПР)</t>
+        </is>
+      </c>
+      <c r="N4" s="10" t="inlineStr">
+        <is>
+          <t>280x80x60</t>
         </is>
       </c>
       <c r="P4" s="10" t="inlineStr">
@@ -47336,6 +47352,9 @@
           <t>Для собак</t>
         </is>
       </c>
+      <c r="G5" s="10" t="n">
+        <v>140</v>
+      </c>
       <c r="H5" s="10" t="inlineStr">
         <is>
           <t>Мяч</t>
@@ -47363,7 +47382,7 @@
       </c>
       <c r="N5" s="10" t="inlineStr">
         <is>
-          <t>70x70x70</t>
+          <t>290x80x60</t>
         </is>
       </c>
       <c r="P5" s="10" t="inlineStr">
@@ -47401,6 +47420,9 @@
           <t>Для собак</t>
         </is>
       </c>
+      <c r="G6" s="10" t="n">
+        <v>140</v>
+      </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
           <t>Мяч</t>
@@ -47428,7 +47450,7 @@
       </c>
       <c r="N6" s="10" t="inlineStr">
         <is>
-          <t>70x70x70</t>
+          <t>290x80x60</t>
         </is>
       </c>
       <c r="P6" s="10" t="inlineStr">

--- a/docs/ozon/Озон_рабочая_книга.xlsx
+++ b/docs/ozon/Озон_рабочая_книга.xlsx
@@ -948,6 +948,27 @@
           <t>9506919000 - Прочий инвентарь и оборудование для занятий общей физкультурой, гимнастикой или атлетикой</t>
         </is>
       </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>белый</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="inlineStr">
+        <is>
+          <t>Мяч массажный</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="H3" s="10" t="inlineStr">
+        <is>
+          <t>ПВХ (поливинилхлорид)</t>
+        </is>
+      </c>
+      <c r="I3" s="10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -960,6 +981,27 @@
           <t>9506919000 - Прочий инвентарь и оборудование для занятий общей физкультурой, гимнастикой или атлетикой</t>
         </is>
       </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>розовый</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>Мяч массажный</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="H4" s="10" t="inlineStr">
+        <is>
+          <t>ПВХ (поливинилхлорид)</t>
+        </is>
+      </c>
+      <c r="I4" s="10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -972,6 +1014,27 @@
           <t>9506919000 - Прочий инвентарь и оборудование для занятий общей физкультурой, гимнастикой или атлетикой</t>
         </is>
       </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>голубой</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>Мяч массажный</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="H5" s="10" t="inlineStr">
+        <is>
+          <t>ПВХ (поливинилхлорид)</t>
+        </is>
+      </c>
+      <c r="I5" s="10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -984,6 +1047,27 @@
           <t>9506919000 - Прочий инвентарь и оборудование для занятий общей физкультурой, гимнастикой или атлетикой</t>
         </is>
       </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>оранжевый</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>Мяч массажный</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="H6" s="10" t="inlineStr">
+        <is>
+          <t>ПВХ (поливинилхлорид)</t>
+        </is>
+      </c>
+      <c r="I6" s="10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -996,6 +1080,27 @@
           <t>9506919000 - Прочий инвентарь и оборудование для занятий общей физкультурой, гимнастикой или атлетикой</t>
         </is>
       </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>черный</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>Мяч массажный</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="H7" s="10" t="inlineStr">
+        <is>
+          <t>ПВХ (поливинилхлорид)</t>
+        </is>
+      </c>
+      <c r="I7" s="10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1008,6 +1113,27 @@
           <t>9506919000 - Прочий инвентарь и оборудование для занятий общей физкультурой, гимнастикой или атлетикой</t>
         </is>
       </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>белый</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>Мяч массажный</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>ПВХ (поливинилхлорид)</t>
+        </is>
+      </c>
+      <c r="I8" s="10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1020,6 +1146,27 @@
           <t>9506919000 - Прочий инвентарь и оборудование для занятий общей физкультурой, гимнастикой или атлетикой</t>
         </is>
       </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>розовый</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>Мяч массажный</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="H9" s="10" t="inlineStr">
+        <is>
+          <t>ПВХ (поливинилхлорид)</t>
+        </is>
+      </c>
+      <c r="I9" s="10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1032,6 +1179,27 @@
           <t>9506919000 - Прочий инвентарь и оборудование для занятий общей физкультурой, гимнастикой или атлетикой</t>
         </is>
       </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>голубой</t>
+        </is>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>Мяч массажный</t>
+        </is>
+      </c>
+      <c r="G10" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="H10" s="10" t="inlineStr">
+        <is>
+          <t>ПВХ (поливинилхлорид)</t>
+        </is>
+      </c>
+      <c r="I10" s="10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1044,6 +1212,27 @@
           <t>9506919000 - Прочий инвентарь и оборудование для занятий общей физкультурой, гимнастикой или атлетикой</t>
         </is>
       </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>оранжевый</t>
+        </is>
+      </c>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>Мяч массажный</t>
+        </is>
+      </c>
+      <c r="G11" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="H11" s="10" t="inlineStr">
+        <is>
+          <t>ПВХ (поливинилхлорид)</t>
+        </is>
+      </c>
+      <c r="I11" s="10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1056,6 +1245,27 @@
           <t>9506919000 - Прочий инвентарь и оборудование для занятий общей физкультурой, гимнастикой или атлетикой</t>
         </is>
       </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>черный</t>
+        </is>
+      </c>
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>Мяч массажный</t>
+        </is>
+      </c>
+      <c r="G12" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="H12" s="10" t="inlineStr">
+        <is>
+          <t>ПВХ (поливинилхлорид)</t>
+        </is>
+      </c>
+      <c r="I12" s="10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1068,6 +1278,27 @@
           <t>9506919000 - Прочий инвентарь и оборудование для занятий общей физкультурой, гимнастикой или атлетикой</t>
         </is>
       </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>розовый</t>
+        </is>
+      </c>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>Мяч массажный</t>
+        </is>
+      </c>
+      <c r="G13" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="H13" s="10" t="inlineStr">
+        <is>
+          <t>ПВХ (поливинилхлорид)</t>
+        </is>
+      </c>
+      <c r="I13" s="10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1080,6 +1311,27 @@
           <t>9506919000 - Прочий инвентарь и оборудование для занятий общей физкультурой, гимнастикой или атлетикой</t>
         </is>
       </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>голубой</t>
+        </is>
+      </c>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>Мяч массажный</t>
+        </is>
+      </c>
+      <c r="G14" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="H14" s="10" t="inlineStr">
+        <is>
+          <t>ПВХ (поливинилхлорид)</t>
+        </is>
+      </c>
+      <c r="I14" s="10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1092,6 +1344,27 @@
           <t>9506919000 - Прочий инвентарь и оборудование для занятий общей физкультурой, гимнастикой или атлетикой</t>
         </is>
       </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>оранжевый</t>
+        </is>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>Мяч массажный</t>
+        </is>
+      </c>
+      <c r="G15" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="H15" s="10" t="inlineStr">
+        <is>
+          <t>ПВХ (поливинилхлорид)</t>
+        </is>
+      </c>
+      <c r="I15" s="10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1104,6 +1377,27 @@
           <t>9506919000 - Прочий инвентарь и оборудование для занятий общей физкультурой, гимнастикой или атлетикой</t>
         </is>
       </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>черный</t>
+        </is>
+      </c>
+      <c r="E16" s="10" t="inlineStr">
+        <is>
+          <t>Мяч массажный</t>
+        </is>
+      </c>
+      <c r="G16" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="H16" s="10" t="inlineStr">
+        <is>
+          <t>ПВХ (поливинилхлорид)</t>
+        </is>
+      </c>
+      <c r="I16" s="10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1116,6 +1410,27 @@
           <t>9506919000 - Прочий инвентарь и оборудование для занятий общей физкультурой, гимнастикой или атлетикой</t>
         </is>
       </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>фиолетовый</t>
+        </is>
+      </c>
+      <c r="E17" s="10" t="inlineStr">
+        <is>
+          <t>Мяч массажный</t>
+        </is>
+      </c>
+      <c r="G17" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="H17" s="10" t="inlineStr">
+        <is>
+          <t>ПВХ (поливинилхлорид)</t>
+        </is>
+      </c>
+      <c r="I17" s="10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1123,6 +1438,27 @@
           <t>ACRB1MS103BL</t>
         </is>
       </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>голубой</t>
+        </is>
+      </c>
+      <c r="E18" s="10" t="inlineStr">
+        <is>
+          <t>Мяч массажный</t>
+        </is>
+      </c>
+      <c r="G18" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="H18" s="10" t="inlineStr">
+        <is>
+          <t>Термопластический эластомер (TPE)</t>
+        </is>
+      </c>
+      <c r="I18" s="10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1130,12 +1466,54 @@
           <t>ACRB1MS103LI</t>
         </is>
       </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>сиреневый</t>
+        </is>
+      </c>
+      <c r="E19" s="10" t="inlineStr">
+        <is>
+          <t>Мяч массажный</t>
+        </is>
+      </c>
+      <c r="G19" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="H19" s="10" t="inlineStr">
+        <is>
+          <t>Термопластический эластомер (TPE)</t>
+        </is>
+      </c>
+      <c r="I19" s="10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
           <t>ACRB1MS103RJ</t>
         </is>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>оранжевый</t>
+        </is>
+      </c>
+      <c r="E20" s="10" t="inlineStr">
+        <is>
+          <t>Мяч массажный</t>
+        </is>
+      </c>
+      <c r="G20" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="H20" s="10" t="inlineStr">
+        <is>
+          <t>Термопластический эластомер (TPE)</t>
+        </is>
+      </c>
+      <c r="I20" s="10" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1384,6 +1762,57 @@
           <t>3926909709 - Изделия прочие из пластмасс и изделия из прочих материалов товарных позиций 3901 - 3914, прочие, прочие, прочие, прочие</t>
         </is>
       </c>
+      <c r="C3" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>Таблетница</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="n">
+        <v>14</v>
+      </c>
+      <c r="H3" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" s="10" t="inlineStr">
+        <is>
+          <t>Пластик</t>
+        </is>
+      </c>
+      <c r="J3" s="10" t="inlineStr">
+        <is>
+          <t>16 x 12 x 5</t>
+        </is>
+      </c>
+      <c r="K3" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="L3" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="M3" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="N3" s="10" t="inlineStr">
+        <is>
+          <t>150x90x40</t>
+        </is>
+      </c>
+      <c r="O3" s="10" t="n">
+        <v>170</v>
+      </c>
+      <c r="P3" s="10" t="inlineStr">
+        <is>
+          <t>Пакет с клапаном</t>
+        </is>
+      </c>
+      <c r="R3" s="10" t="inlineStr">
+        <is>
+          <t>Контейнер для таблеток на день - 7 шт.; Футляр-органайзер - 1 шт.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1396,6 +1825,57 @@
           <t>3926909709 - Изделия прочие из пластмасс и изделия из прочих материалов товарных позиций 3901 - 3914, прочие, прочие, прочие, прочие</t>
         </is>
       </c>
+      <c r="C4" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>Таблетница</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="n">
+        <v>14</v>
+      </c>
+      <c r="H4" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" s="10" t="inlineStr">
+        <is>
+          <t>Пластик</t>
+        </is>
+      </c>
+      <c r="J4" s="10" t="inlineStr">
+        <is>
+          <t>16 x 12 x 5</t>
+        </is>
+      </c>
+      <c r="K4" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="L4" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="M4" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="N4" s="10" t="inlineStr">
+        <is>
+          <t>150x90x40</t>
+        </is>
+      </c>
+      <c r="O4" s="10" t="n">
+        <v>170</v>
+      </c>
+      <c r="P4" s="10" t="inlineStr">
+        <is>
+          <t>Пакет с клапаном</t>
+        </is>
+      </c>
+      <c r="R4" s="10" t="inlineStr">
+        <is>
+          <t>Контейнер для таблеток на день - 7 шт.; Футляр-органайзер - 1 шт.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1408,6 +1888,57 @@
           <t>3926909709 - Изделия прочие из пластмасс и изделия из прочих материалов товарных позиций 3901 - 3914, прочие, прочие, прочие, прочие</t>
         </is>
       </c>
+      <c r="C5" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>Таблетница</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="n">
+        <v>14</v>
+      </c>
+      <c r="H5" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="10" t="inlineStr">
+        <is>
+          <t>Пластик</t>
+        </is>
+      </c>
+      <c r="J5" s="10" t="inlineStr">
+        <is>
+          <t>16 x 12 x 5</t>
+        </is>
+      </c>
+      <c r="K5" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="L5" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="M5" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="N5" s="10" t="inlineStr">
+        <is>
+          <t>150x90x40</t>
+        </is>
+      </c>
+      <c r="O5" s="10" t="n">
+        <v>170</v>
+      </c>
+      <c r="P5" s="10" t="inlineStr">
+        <is>
+          <t>Пакет с клапаном</t>
+        </is>
+      </c>
+      <c r="R5" s="10" t="inlineStr">
+        <is>
+          <t>Контейнер для таблеток на день - 7 шт.; Футляр-органайзер - 1 шт.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1420,6 +1951,57 @@
           <t>3926909709 - Изделия прочие из пластмасс и изделия из прочих материалов товарных позиций 3901 - 3914, прочие, прочие, прочие, прочие</t>
         </is>
       </c>
+      <c r="C6" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>Таблетница</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="n">
+        <v>14</v>
+      </c>
+      <c r="H6" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>Пластик</t>
+        </is>
+      </c>
+      <c r="J6" s="10" t="inlineStr">
+        <is>
+          <t>16 x 12 x 5</t>
+        </is>
+      </c>
+      <c r="K6" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="L6" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="M6" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="N6" s="10" t="inlineStr">
+        <is>
+          <t>150x90x40</t>
+        </is>
+      </c>
+      <c r="O6" s="10" t="n">
+        <v>170</v>
+      </c>
+      <c r="P6" s="10" t="inlineStr">
+        <is>
+          <t>Пакет с клапаном</t>
+        </is>
+      </c>
+      <c r="R6" s="10" t="inlineStr">
+        <is>
+          <t>Контейнер для таблеток на день - 7 шт.; Футляр-органайзер - 1 шт.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1432,6 +2014,57 @@
           <t>3926909709 - Изделия прочие из пластмасс и изделия из прочих материалов товарных позиций 3901 - 3914, прочие, прочие, прочие, прочие</t>
         </is>
       </c>
+      <c r="C7" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>Таблетница</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="n">
+        <v>14</v>
+      </c>
+      <c r="H7" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>Пластик</t>
+        </is>
+      </c>
+      <c r="J7" s="10" t="inlineStr">
+        <is>
+          <t>17 x 12 x 7</t>
+        </is>
+      </c>
+      <c r="K7" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="L7" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="M7" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="N7" s="10" t="inlineStr">
+        <is>
+          <t>150x70x70</t>
+        </is>
+      </c>
+      <c r="O7" s="10" t="n">
+        <v>165</v>
+      </c>
+      <c r="P7" s="10" t="inlineStr">
+        <is>
+          <t>Пакет с клапаном</t>
+        </is>
+      </c>
+      <c r="R7" s="10" t="inlineStr">
+        <is>
+          <t>Круглый контейнер для таблеток на день - 7 шт.; Футляр-органайзер - 1 шт.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1444,6 +2077,57 @@
           <t>3926909709 - Изделия прочие из пластмасс и изделия из прочих материалов товарных позиций 3901 - 3914, прочие, прочие, прочие, прочие</t>
         </is>
       </c>
+      <c r="C8" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>Таблетница</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="n">
+        <v>14</v>
+      </c>
+      <c r="H8" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>Пластик</t>
+        </is>
+      </c>
+      <c r="J8" s="10" t="inlineStr">
+        <is>
+          <t>17 x 12 x 7</t>
+        </is>
+      </c>
+      <c r="K8" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="L8" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="M8" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="N8" s="10" t="inlineStr">
+        <is>
+          <t>150x70x70</t>
+        </is>
+      </c>
+      <c r="O8" s="10" t="n">
+        <v>165</v>
+      </c>
+      <c r="P8" s="10" t="inlineStr">
+        <is>
+          <t>Пакет с клапаном</t>
+        </is>
+      </c>
+      <c r="R8" s="10" t="inlineStr">
+        <is>
+          <t>Круглый контейнер для таблеток на день - 7 шт.; Футляр-органайзер - 1 шт.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1456,6 +2140,57 @@
           <t>3926909709 - Изделия прочие из пластмасс и изделия из прочих материалов товарных позиций 3901 - 3914, прочие, прочие, прочие, прочие</t>
         </is>
       </c>
+      <c r="C9" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>Таблетница</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>14</v>
+      </c>
+      <c r="H9" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="10" t="inlineStr">
+        <is>
+          <t>Пластик</t>
+        </is>
+      </c>
+      <c r="J9" s="10" t="inlineStr">
+        <is>
+          <t>17 x 12 x 7</t>
+        </is>
+      </c>
+      <c r="K9" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="L9" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="M9" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="N9" s="10" t="inlineStr">
+        <is>
+          <t>150x70x70</t>
+        </is>
+      </c>
+      <c r="O9" s="10" t="n">
+        <v>150</v>
+      </c>
+      <c r="P9" s="10" t="inlineStr">
+        <is>
+          <t>Пакет с клапаном</t>
+        </is>
+      </c>
+      <c r="R9" s="10" t="inlineStr">
+        <is>
+          <t>Круглый контейнер для таблеток на день - 7 шт.; Футляр-органайзер - 1 шт.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1468,6 +2203,57 @@
           <t>3926909709 - Изделия прочие из пластмасс и изделия из прочих материалов товарных позиций 3901 - 3914, прочие, прочие, прочие, прочие</t>
         </is>
       </c>
+      <c r="C10" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>Таблетница</t>
+        </is>
+      </c>
+      <c r="E10" s="10" t="n">
+        <v>14</v>
+      </c>
+      <c r="H10" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="10" t="inlineStr">
+        <is>
+          <t>Пластик</t>
+        </is>
+      </c>
+      <c r="J10" s="10" t="inlineStr">
+        <is>
+          <t>17 x 12 x 7</t>
+        </is>
+      </c>
+      <c r="K10" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="L10" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="M10" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="N10" s="10" t="inlineStr">
+        <is>
+          <t>150x70x70</t>
+        </is>
+      </c>
+      <c r="O10" s="10" t="n">
+        <v>150</v>
+      </c>
+      <c r="P10" s="10" t="inlineStr">
+        <is>
+          <t>Пакет с клапаном</t>
+        </is>
+      </c>
+      <c r="R10" s="10" t="inlineStr">
+        <is>
+          <t>Круглый контейнер для таблеток на день - 7 шт.; Футляр-органайзер - 1 шт.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1478,6 +2264,57 @@
       <c r="B11" s="10" t="inlineStr">
         <is>
           <t>3926909709 - Изделия прочие из пластмасс и изделия из прочих материалов товарных позиций 3901 - 3914, прочие, прочие, прочие, прочие</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>Таблетница</t>
+        </is>
+      </c>
+      <c r="E11" s="10" t="n">
+        <v>14</v>
+      </c>
+      <c r="H11" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" s="10" t="inlineStr">
+        <is>
+          <t>Пластик</t>
+        </is>
+      </c>
+      <c r="J11" s="10" t="inlineStr">
+        <is>
+          <t>17 x 12 x 7</t>
+        </is>
+      </c>
+      <c r="K11" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="L11" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="M11" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="N11" s="10" t="inlineStr">
+        <is>
+          <t>150x70x70</t>
+        </is>
+      </c>
+      <c r="O11" s="10" t="n">
+        <v>150</v>
+      </c>
+      <c r="P11" s="10" t="inlineStr">
+        <is>
+          <t>Пакет с клапаном</t>
+        </is>
+      </c>
+      <c r="R11" s="10" t="inlineStr">
+        <is>
+          <t>Круглый контейнер для таблеток на день - 7 шт.; Футляр-органайзер - 1 шт.</t>
         </is>
       </c>
     </row>
@@ -1822,6 +2659,40 @@
           <t>9506919000 - Прочий инвентарь и оборудование для занятий общей физкультурой, гимнастикой или атлетикой</t>
         </is>
       </c>
+      <c r="C3" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>Фитнес-резинка</t>
+        </is>
+      </c>
+      <c r="F3" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="G3" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="I3" s="10" t="inlineStr">
+        <is>
+          <t>Ягодицы</t>
+        </is>
+      </c>
+      <c r="J3" s="10" t="inlineStr">
+        <is>
+          <t>Взрослая</t>
+        </is>
+      </c>
+      <c r="K3" s="10" t="inlineStr">
+        <is>
+          <t>Набор</t>
+        </is>
+      </c>
+      <c r="L3" s="10" t="inlineStr">
+        <is>
+          <t>Фитнес-резинка - 3 шт.; Мешочек для хранения - 1 шт.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1834,6 +2705,37 @@
           <t>9506919000 - Прочий инвентарь и оборудование для занятий общей физкультурой, гимнастикой или атлетикой</t>
         </is>
       </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>Фитнес-резинка</t>
+        </is>
+      </c>
+      <c r="F4" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="G4" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="I4" s="10" t="inlineStr">
+        <is>
+          <t>Ягодицы</t>
+        </is>
+      </c>
+      <c r="J4" s="10" t="inlineStr">
+        <is>
+          <t>Взрослая</t>
+        </is>
+      </c>
+      <c r="K4" s="10" t="inlineStr">
+        <is>
+          <t>Набор</t>
+        </is>
+      </c>
+      <c r="L4" s="10" t="inlineStr">
+        <is>
+          <t>Фитнес-резинка - 5 шт.; Мешочек для хранения - 1 шт.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1846,6 +2748,34 @@
           <t>9506919000 - Прочий инвентарь и оборудование для занятий общей физкультурой, гимнастикой или атлетикой</t>
         </is>
       </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>Фитнес-резинка</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="I5" s="10" t="inlineStr">
+        <is>
+          <t>Ягодицы</t>
+        </is>
+      </c>
+      <c r="J5" s="10" t="inlineStr">
+        <is>
+          <t>Взрослая</t>
+        </is>
+      </c>
+      <c r="K5" s="10" t="inlineStr">
+        <is>
+          <t>Набор</t>
+        </is>
+      </c>
+      <c r="L5" s="10" t="inlineStr">
+        <is>
+          <t>Фитнес-резинка - 4 шт.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1853,6 +2783,24 @@
           <t>ACRB5FR400CL</t>
         </is>
       </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>Фитнес-резинка</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="J6" s="10" t="inlineStr">
+        <is>
+          <t>Взрослая</t>
+        </is>
+      </c>
+      <c r="K6" s="10" t="inlineStr">
+        <is>
+          <t>Набор</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1860,6 +2808,37 @@
           <t>ACRB1SK101BC</t>
         </is>
       </c>
+      <c r="C7" s="10" t="n">
+        <v>300</v>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>Скакалка</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>Ноги</t>
+        </is>
+      </c>
+      <c r="J7" s="10" t="inlineStr">
+        <is>
+          <t>Взрослая</t>
+        </is>
+      </c>
+      <c r="K7" s="10" t="inlineStr">
+        <is>
+          <t>Подшипники в рукоятках (ручках)</t>
+        </is>
+      </c>
+      <c r="L7" s="10" t="inlineStr">
+        <is>
+          <t>Скакалка - 1 шт.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1867,11 +2846,73 @@
           <t>ACRB1SK101RD</t>
         </is>
       </c>
+      <c r="C8" s="10" t="n">
+        <v>300</v>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>Скакалка</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>Ноги</t>
+        </is>
+      </c>
+      <c r="J8" s="10" t="inlineStr">
+        <is>
+          <t>Взрослая</t>
+        </is>
+      </c>
+      <c r="K8" s="10" t="inlineStr">
+        <is>
+          <t>Подшипники в рукоятках (ручках)</t>
+        </is>
+      </c>
+      <c r="L8" s="10" t="inlineStr">
+        <is>
+          <t>Скакалка - 1 шт.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
           <t>ACRB1SK101BL</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="n">
+        <v>300</v>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>Скакалка</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="10" t="inlineStr">
+        <is>
+          <t>Ноги</t>
+        </is>
+      </c>
+      <c r="J9" s="10" t="inlineStr">
+        <is>
+          <t>Взрослая</t>
+        </is>
+      </c>
+      <c r="K9" s="10" t="inlineStr">
+        <is>
+          <t>Подшипники в рукоятках (ручках)</t>
+        </is>
+      </c>
+      <c r="L9" s="10" t="inlineStr">
+        <is>
+          <t>Скакалка - 1 шт.</t>
         </is>
       </c>
     </row>
@@ -2084,6 +3125,50 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>AKTA2KN101YL</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>желтый</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="E3" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" s="10" t="inlineStr">
+        <is>
+          <t>Шпатель-скребок кондитерский</t>
+        </is>
+      </c>
+      <c r="H3" s="10" t="inlineStr">
+        <is>
+          <t>Скребок для теста</t>
+        </is>
+      </c>
+      <c r="J3" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="K3" s="10" t="inlineStr">
+        <is>
+          <t>Нержавеющая сталь</t>
+        </is>
+      </c>
+      <c r="L3" s="10" t="inlineStr">
+        <is>
+          <t>Пластик</t>
+        </is>
+      </c>
+      <c r="N3" s="10" t="inlineStr">
+        <is>
+          <t>Фабричное производство</t>
+        </is>
+      </c>
+      <c r="O3" s="10" t="inlineStr">
+        <is>
+          <t>Скребок пластиковый - 1 шт.; Нож-шпатель металлический - 1 шт.</t>
         </is>
       </c>
     </row>
@@ -45658,6 +46743,49 @@
           <t>9019109009 - Прочая аппаратура для механотерапии, аппараты массажные, аппаратура для  психологических тестов для определения способностей</t>
         </is>
       </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>Аксессуар для массажа</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>оранжевый</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="G3" s="10" t="inlineStr">
+        <is>
+          <t>Вставить палец внутрь и прокатить ролики от основания к кончику пять-десять раз. На кисть уходит две-три минуты.</t>
+        </is>
+      </c>
+      <c r="H3" s="10" t="inlineStr">
+        <is>
+          <t>Роликовый</t>
+        </is>
+      </c>
+      <c r="I3" s="10" t="inlineStr">
+        <is>
+          <t>Руки</t>
+        </is>
+      </c>
+      <c r="K3" s="10" t="inlineStr">
+        <is>
+          <t>Акрил</t>
+        </is>
+      </c>
+      <c r="N3" s="10" t="inlineStr">
+        <is>
+          <t>Картонная коробка</t>
+        </is>
+      </c>
+      <c r="O3" s="10" t="inlineStr">
+        <is>
+          <t>Массажер - 1 шт.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -45666,6 +46794,44 @@
         </is>
       </c>
       <c r="B4" s="9" t="inlineStr"/>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>Аксессуар для массажа</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>оранжевый</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="n">
+        <v>160</v>
+      </c>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>Взять за ручки, завести ленту за спину и прокатывать ролики по мышцам. Интенсивность задаётся натяжением ленты.</t>
+        </is>
+      </c>
+      <c r="H4" s="10" t="inlineStr">
+        <is>
+          <t>Роликовый</t>
+        </is>
+      </c>
+      <c r="I4" s="10" t="inlineStr">
+        <is>
+          <t>Шея</t>
+        </is>
+      </c>
+      <c r="K4" s="10" t="inlineStr">
+        <is>
+          <t>Пластик</t>
+        </is>
+      </c>
+      <c r="O4" s="10" t="inlineStr">
+        <is>
+          <t>Массажер - 1 шт.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -45674,6 +46840,44 @@
         </is>
       </c>
       <c r="B5" s="9" t="inlineStr"/>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>Аксессуар для массажа</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>розовый</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="n">
+        <v>160</v>
+      </c>
+      <c r="G5" s="10" t="inlineStr">
+        <is>
+          <t>Взять за ручки, завести ленту за спину и прокатывать ролики по мышцам. Интенсивность задаётся натяжением ленты.</t>
+        </is>
+      </c>
+      <c r="H5" s="10" t="inlineStr">
+        <is>
+          <t>Роликовый</t>
+        </is>
+      </c>
+      <c r="I5" s="10" t="inlineStr">
+        <is>
+          <t>Шея</t>
+        </is>
+      </c>
+      <c r="K5" s="10" t="inlineStr">
+        <is>
+          <t>Пластик</t>
+        </is>
+      </c>
+      <c r="O5" s="10" t="inlineStr">
+        <is>
+          <t>Массажер - 1 шт.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -45682,6 +46886,44 @@
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr"/>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>Аксессуар для массажа</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>голубой</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="n">
+        <v>160</v>
+      </c>
+      <c r="G6" s="10" t="inlineStr">
+        <is>
+          <t>Взять за ручки, завести ленту за спину и прокатывать ролики по мышцам. Интенсивность задаётся натяжением ленты.</t>
+        </is>
+      </c>
+      <c r="H6" s="10" t="inlineStr">
+        <is>
+          <t>Роликовый</t>
+        </is>
+      </c>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>Шея</t>
+        </is>
+      </c>
+      <c r="K6" s="10" t="inlineStr">
+        <is>
+          <t>Пластик</t>
+        </is>
+      </c>
+      <c r="O6" s="10" t="inlineStr">
+        <is>
+          <t>Массажер - 1 шт.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="7">
@@ -45946,6 +47188,67 @@
           <t>4016999708 - Изделия из вулканизованной резины, кроме твердой резины, прочие: прочие, прочие</t>
         </is>
       </c>
+      <c r="C3" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>красный</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="inlineStr">
+        <is>
+          <t>Мяч</t>
+        </is>
+      </c>
+      <c r="F3" s="10" t="inlineStr">
+        <is>
+          <t>Для собак</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="n">
+        <v>80</v>
+      </c>
+      <c r="H3" s="10" t="inlineStr">
+        <is>
+          <t>Мяч</t>
+        </is>
+      </c>
+      <c r="I3" s="10" t="inlineStr">
+        <is>
+          <t>для апортировки и дрессировки</t>
+        </is>
+      </c>
+      <c r="J3" s="10" t="inlineStr">
+        <is>
+          <t>Улица</t>
+        </is>
+      </c>
+      <c r="K3" s="10" t="inlineStr">
+        <is>
+          <t>С шипами</t>
+        </is>
+      </c>
+      <c r="L3" s="10" t="inlineStr">
+        <is>
+          <t>11 x 8 x 6</t>
+        </is>
+      </c>
+      <c r="M3" s="10" t="inlineStr">
+        <is>
+          <t>Термопластичная резина (ТПР)</t>
+        </is>
+      </c>
+      <c r="N3" s="10" t="inlineStr">
+        <is>
+          <t>280x80x60</t>
+        </is>
+      </c>
+      <c r="P3" s="10" t="inlineStr">
+        <is>
+          <t>Мяч на ремешке - 1 шт.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -45958,6 +47261,67 @@
           <t>4016999708 - Изделия из вулканизованной резины, кроме твердой резины, прочие: прочие, прочие</t>
         </is>
       </c>
+      <c r="C4" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>темно-синий</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>Мяч</t>
+        </is>
+      </c>
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>Для собак</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="n">
+        <v>80</v>
+      </c>
+      <c r="H4" s="10" t="inlineStr">
+        <is>
+          <t>Мяч</t>
+        </is>
+      </c>
+      <c r="I4" s="10" t="inlineStr">
+        <is>
+          <t>для апортировки и дрессировки</t>
+        </is>
+      </c>
+      <c r="J4" s="10" t="inlineStr">
+        <is>
+          <t>Улица</t>
+        </is>
+      </c>
+      <c r="K4" s="10" t="inlineStr">
+        <is>
+          <t>С шипами</t>
+        </is>
+      </c>
+      <c r="L4" s="10" t="inlineStr">
+        <is>
+          <t>11 x 8 x 6</t>
+        </is>
+      </c>
+      <c r="M4" s="10" t="inlineStr">
+        <is>
+          <t>Термопластичная резина (ТПР)</t>
+        </is>
+      </c>
+      <c r="N4" s="10" t="inlineStr">
+        <is>
+          <t>280x80x60</t>
+        </is>
+      </c>
+      <c r="P4" s="10" t="inlineStr">
+        <is>
+          <t>Мяч на ремешке - 1 шт.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -45970,6 +47334,62 @@
           <t>4016999708 - Изделия из вулканизованной резины, кроме твердой резины, прочие: прочие, прочие</t>
         </is>
       </c>
+      <c r="C5" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>красный</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>Мяч</t>
+        </is>
+      </c>
+      <c r="F5" s="10" t="inlineStr">
+        <is>
+          <t>Для собак</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="n">
+        <v>140</v>
+      </c>
+      <c r="H5" s="10" t="inlineStr">
+        <is>
+          <t>Мяч</t>
+        </is>
+      </c>
+      <c r="I5" s="10" t="inlineStr">
+        <is>
+          <t>для апортировки и дрессировки</t>
+        </is>
+      </c>
+      <c r="J5" s="10" t="inlineStr">
+        <is>
+          <t>Улица</t>
+        </is>
+      </c>
+      <c r="L5" s="10" t="inlineStr">
+        <is>
+          <t>12 x 9 x 7</t>
+        </is>
+      </c>
+      <c r="M5" s="10" t="inlineStr">
+        <is>
+          <t>Термопластичная резина (ТПР)</t>
+        </is>
+      </c>
+      <c r="N5" s="10" t="inlineStr">
+        <is>
+          <t>290x80x60</t>
+        </is>
+      </c>
+      <c r="P5" s="10" t="inlineStr">
+        <is>
+          <t>Мяч на ремешке - 1 шт.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -45982,6 +47402,62 @@
           <t>4016999708 - Изделия из вулканизованной резины, кроме твердой резины, прочие: прочие, прочие</t>
         </is>
       </c>
+      <c r="C6" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>темно-синий</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>Мяч</t>
+        </is>
+      </c>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>Для собак</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="n">
+        <v>140</v>
+      </c>
+      <c r="H6" s="10" t="inlineStr">
+        <is>
+          <t>Мяч</t>
+        </is>
+      </c>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>для апортировки и дрессировки</t>
+        </is>
+      </c>
+      <c r="J6" s="10" t="inlineStr">
+        <is>
+          <t>Улица</t>
+        </is>
+      </c>
+      <c r="L6" s="10" t="inlineStr">
+        <is>
+          <t>12 x 9 x 7</t>
+        </is>
+      </c>
+      <c r="M6" s="10" t="inlineStr">
+        <is>
+          <t>Термопластичная резина (ТПР)</t>
+        </is>
+      </c>
+      <c r="N6" s="10" t="inlineStr">
+        <is>
+          <t>290x80x60</t>
+        </is>
+      </c>
+      <c r="P6" s="10" t="inlineStr">
+        <is>
+          <t>Мяч на ремешке - 1 шт.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -45994,6 +47470,67 @@
           <t>5609000000 - Изделия из нитей или пряжи, плоских или аналогичных нитей товарной позиции 5404 или 5405, бечевка, веревки, канаты или тросы, в другом месте не поименованные</t>
         </is>
       </c>
+      <c r="C7" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>бежевый</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>Канат</t>
+        </is>
+      </c>
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>Для собак</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="n">
+        <v>580</v>
+      </c>
+      <c r="H7" s="10" t="inlineStr">
+        <is>
+          <t>Канат, веревка</t>
+        </is>
+      </c>
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>для здоровья зубов и десен</t>
+        </is>
+      </c>
+      <c r="J7" s="10" t="inlineStr">
+        <is>
+          <t>Улица</t>
+        </is>
+      </c>
+      <c r="K7" s="10" t="inlineStr">
+        <is>
+          <t>Из натуральных материалов</t>
+        </is>
+      </c>
+      <c r="L7" s="10" t="inlineStr">
+        <is>
+          <t>19 x 19 x 8</t>
+        </is>
+      </c>
+      <c r="M7" s="10" t="inlineStr">
+        <is>
+          <t>Хлопок</t>
+        </is>
+      </c>
+      <c r="N7" s="10" t="inlineStr">
+        <is>
+          <t>550x50</t>
+        </is>
+      </c>
+      <c r="P7" s="10" t="inlineStr">
+        <is>
+          <t>Канат - 1 шт.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -46004,6 +47541,67 @@
       <c r="B8" s="10" t="inlineStr">
         <is>
           <t>5609000000 - Изделия из нитей или пряжи, плоских или аналогичных нитей товарной позиции 5404 или 5405, бечевка, веревки, канаты или тросы, в другом месте не поименованные</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>желтый</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>Канат</t>
+        </is>
+      </c>
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>Для собак</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="n">
+        <v>380</v>
+      </c>
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>Канат, веревка</t>
+        </is>
+      </c>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>для здоровья зубов и десен</t>
+        </is>
+      </c>
+      <c r="J8" s="10" t="inlineStr">
+        <is>
+          <t>Улица</t>
+        </is>
+      </c>
+      <c r="K8" s="10" t="inlineStr">
+        <is>
+          <t>Из натуральных материалов</t>
+        </is>
+      </c>
+      <c r="L8" s="10" t="inlineStr">
+        <is>
+          <t>21 x 15 x 6</t>
+        </is>
+      </c>
+      <c r="M8" s="10" t="inlineStr">
+        <is>
+          <t>Хлопок</t>
+        </is>
+      </c>
+      <c r="N8" s="10" t="inlineStr">
+        <is>
+          <t>550x50</t>
+        </is>
+      </c>
+      <c r="P8" s="10" t="inlineStr">
+        <is>
+          <t>Канат - 1 шт.</t>
         </is>
       </c>
     </row>
@@ -46243,6 +47841,57 @@
           <t>8211930000 - Прочие ножи с нефиксированными лезвиями</t>
         </is>
       </c>
+      <c r="C3" s="10" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>желтый</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="inlineStr">
+        <is>
+          <t>Кухонный нож</t>
+        </is>
+      </c>
+      <c r="F3" s="10" t="inlineStr">
+        <is>
+          <t>Гладкая</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="inlineStr">
+        <is>
+          <t>для пиццы</t>
+        </is>
+      </c>
+      <c r="H3" s="10" t="inlineStr">
+        <is>
+          <t>Пластик</t>
+        </is>
+      </c>
+      <c r="I3" s="10" t="inlineStr">
+        <is>
+          <t>Нержавеющая сталь</t>
+        </is>
+      </c>
+      <c r="J3" s="10" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="K3" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O3" s="10" t="inlineStr">
+        <is>
+          <t>Фабричное производство</t>
+        </is>
+      </c>
+      <c r="P3" s="10" t="inlineStr">
+        <is>
+          <t>Нож - 1 шт.; Защитный чехол - 1 шт.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -46253,6 +47902,57 @@
       <c r="B4" s="10" t="inlineStr">
         <is>
           <t>8211930000 - Прочие ножи с нефиксированными лезвиями</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>зеленый</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>Кухонный нож</t>
+        </is>
+      </c>
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>Гладкая</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>для пиццы</t>
+        </is>
+      </c>
+      <c r="H4" s="10" t="inlineStr">
+        <is>
+          <t>Пластик</t>
+        </is>
+      </c>
+      <c r="I4" s="10" t="inlineStr">
+        <is>
+          <t>Нержавеющая сталь</t>
+        </is>
+      </c>
+      <c r="J4" s="10" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="K4" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" s="10" t="inlineStr">
+        <is>
+          <t>Фабричное производство</t>
+        </is>
+      </c>
+      <c r="P4" s="10" t="inlineStr">
+        <is>
+          <t>Нож - 1 шт.; Защитный чехол - 1 шт.</t>
         </is>
       </c>
     </row>
@@ -46487,6 +48187,27 @@
           <t>ACRF1BN101PN</t>
         </is>
       </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>Маска-бандаж</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" s="10" t="inlineStr">
+        <is>
+          <t>Надеть на подбородок, свести ленту на макушке и отрегулировать натяжение липучкой. Носить от 30 минут.</t>
+        </is>
+      </c>
+      <c r="I3" s="10" t="inlineStr">
+        <is>
+          <t>Взрослая</t>
+        </is>
+      </c>
+      <c r="M3" s="10" t="n">
+        <v>8.5</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -46494,11 +48215,50 @@
           <t>ACRF1BN101BC</t>
         </is>
       </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>Маска-бандаж</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>Надеть на подбородок, свести ленту на макушке и отрегулировать натяжение липучкой. Носить от 30 минут.</t>
+        </is>
+      </c>
+      <c r="I4" s="10" t="inlineStr">
+        <is>
+          <t>Взрослая</t>
+        </is>
+      </c>
+      <c r="M4" s="10" t="n">
+        <v>8.5</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
           <t>ACRF1BN201GR</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>Маска-бандаж</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="10" t="inlineStr">
+        <is>
+          <t>Надеть на подбородок, свести ленту на макушке и отрегулировать натяжение липучкой. Носить от 30 минут.</t>
+        </is>
+      </c>
+      <c r="I5" s="10" t="inlineStr">
+        <is>
+          <t>Взрослая</t>
         </is>
       </c>
     </row>
@@ -46688,6 +48448,29 @@
           <t>6307909800 - Прочие готовые изделия, включая выкройки одежды</t>
         </is>
       </c>
+      <c r="D3" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="E3" s="10" t="inlineStr">
+        <is>
+          <t>Мешок для стирки</t>
+        </is>
+      </c>
+      <c r="I3" s="10" t="inlineStr">
+        <is>
+          <t>Полиэстер</t>
+        </is>
+      </c>
+      <c r="K3" s="10" t="inlineStr">
+        <is>
+          <t>Фабричное производство</t>
+        </is>
+      </c>
+      <c r="L3" s="10" t="inlineStr">
+        <is>
+          <t>Мешок для стирки рубашек 40 × 50 см - 1 шт.; Мешок для стирки платьев 30 × 40 см - 1 шт.; Мешок для стирки деликатных тканей 20 × 30 см - 1 шт.; Мешок для стирки нижнего белья 20 × 20 см - 1 шт.; Мешок для стирки носков 18 × 22 см - 1 шт.; Мешок для стирки бюстгальтера 15 × 18 см - 1 шт.; Мешок-контейнер для стирки бюстгальтера с каркасом 15 × 17 см - 1 шт.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -46700,6 +48483,35 @@
           <t>6307909800 - Прочие готовые изделия, включая выкройки одежды</t>
         </is>
       </c>
+      <c r="C4" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="D4" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>Мешок для стирки</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="n">
+        <v>17</v>
+      </c>
+      <c r="I4" s="10" t="inlineStr">
+        <is>
+          <t>Полиэстер</t>
+        </is>
+      </c>
+      <c r="K4" s="10" t="inlineStr">
+        <is>
+          <t>Фабричное производство</t>
+        </is>
+      </c>
+      <c r="L4" s="10" t="inlineStr">
+        <is>
+          <t>Мешок-контейнер для стирки бюстгальтера с каркасом 17 × 15 см - 1 шт.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -46712,6 +48524,29 @@
           <t>6307909800 - Прочие готовые изделия, включая выкройки одежды</t>
         </is>
       </c>
+      <c r="D5" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>Мешок для стирки</t>
+        </is>
+      </c>
+      <c r="I5" s="10" t="inlineStr">
+        <is>
+          <t>Полиэстер</t>
+        </is>
+      </c>
+      <c r="K5" s="10" t="inlineStr">
+        <is>
+          <t>Фабричное производство</t>
+        </is>
+      </c>
+      <c r="L5" s="10" t="inlineStr">
+        <is>
+          <t>Мешок для стирки рубашек 40 × 50 см - 1 шт.; Мешок для стирки платьев 30 × 40 см - 1 шт.; Мешок для стирки носков 18 × 22 см - 1 шт.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -46724,6 +48559,29 @@
           <t>6307909800 - Прочие готовые изделия, включая выкройки одежды</t>
         </is>
       </c>
+      <c r="D6" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>Мешок для стирки</t>
+        </is>
+      </c>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>Полиэстер</t>
+        </is>
+      </c>
+      <c r="K6" s="10" t="inlineStr">
+        <is>
+          <t>Фабричное производство</t>
+        </is>
+      </c>
+      <c r="L6" s="10" t="inlineStr">
+        <is>
+          <t>Мешок для стирки бюстгальтера 15 × 18 см - 1 шт.; Мешок для стирки деликатных тканей 20 × 30 см - 1 шт.; Мешок для стирки нижнего белья 20 × 20 см - 1 шт.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -46736,6 +48594,29 @@
           <t>6307909800 - Прочие готовые изделия, включая выкройки одежды</t>
         </is>
       </c>
+      <c r="D7" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>Мешок для стирки</t>
+        </is>
+      </c>
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>Полиэстер</t>
+        </is>
+      </c>
+      <c r="K7" s="10" t="inlineStr">
+        <is>
+          <t>Фабричное производство</t>
+        </is>
+      </c>
+      <c r="L7" s="10" t="inlineStr">
+        <is>
+          <t>Мешок для стирки 30 × 40 см - 1 шт.; Мешок для стирки 40 × 50 см - 1 шт.; Мешок для стирки 50 × 60 см - 1 шт.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -46743,6 +48624,29 @@
           <t>AHMA3BW202WH</t>
         </is>
       </c>
+      <c r="D8" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>Мешок для стирки</t>
+        </is>
+      </c>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>Полиэстер</t>
+        </is>
+      </c>
+      <c r="K8" s="10" t="inlineStr">
+        <is>
+          <t>Фабричное производство</t>
+        </is>
+      </c>
+      <c r="L8" s="10" t="inlineStr">
+        <is>
+          <t>Мешок для стирки 30 × 40 см - 1 шт.; Мешок для стирки 40 × 50 см - 1 шт.; Мешок для стирки 50 × 60 см - 1 шт.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -46755,6 +48659,29 @@
           <t>6307909800 - Прочие готовые изделия, включая выкройки одежды</t>
         </is>
       </c>
+      <c r="D9" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>Мешок для стирки</t>
+        </is>
+      </c>
+      <c r="I9" s="10" t="inlineStr">
+        <is>
+          <t>Полиэстер</t>
+        </is>
+      </c>
+      <c r="K9" s="10" t="inlineStr">
+        <is>
+          <t>Фабричное производство</t>
+        </is>
+      </c>
+      <c r="L9" s="10" t="inlineStr">
+        <is>
+          <t>Мешок-контейнер для стирки бюстгальтера с каркасом 17 × 15 см - 1 шт.; Мешок для стирки нижнего белья 18 × 16 см - 1 шт.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -46762,6 +48689,29 @@
           <t>AHMA2BW202WH</t>
         </is>
       </c>
+      <c r="D10" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>Мешок для стирки</t>
+        </is>
+      </c>
+      <c r="I10" s="10" t="inlineStr">
+        <is>
+          <t>Полиэстер</t>
+        </is>
+      </c>
+      <c r="K10" s="10" t="inlineStr">
+        <is>
+          <t>Фабричное производство</t>
+        </is>
+      </c>
+      <c r="L10" s="10" t="inlineStr">
+        <is>
+          <t>Мешок-контейнер для стирки бюстгальтера с каркасом 17 × 15 см - 1 шт.; Мешок для стирки нижнего белья 18 × 16 см - 1 шт.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -46774,6 +48724,35 @@
           <t>6307909800 - Прочие готовые изделия, включая выкройки одежды</t>
         </is>
       </c>
+      <c r="C11" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="D11" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>Мешок для стирки</t>
+        </is>
+      </c>
+      <c r="G11" s="10" t="n">
+        <v>80</v>
+      </c>
+      <c r="I11" s="10" t="inlineStr">
+        <is>
+          <t>Полиэстер</t>
+        </is>
+      </c>
+      <c r="K11" s="10" t="inlineStr">
+        <is>
+          <t>Фабричное производство</t>
+        </is>
+      </c>
+      <c r="L11" s="10" t="inlineStr">
+        <is>
+          <t>Мешок для стирки 60 × 80 см крупная сетка - 1 шт.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -46786,6 +48765,35 @@
           <t>6307909800 - Прочие готовые изделия, включая выкройки одежды</t>
         </is>
       </c>
+      <c r="C12" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="D12" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>Мешок для стирки</t>
+        </is>
+      </c>
+      <c r="G12" s="10" t="n">
+        <v>80</v>
+      </c>
+      <c r="I12" s="10" t="inlineStr">
+        <is>
+          <t>Полиэстер</t>
+        </is>
+      </c>
+      <c r="K12" s="10" t="inlineStr">
+        <is>
+          <t>Фабричное производство</t>
+        </is>
+      </c>
+      <c r="L12" s="10" t="inlineStr">
+        <is>
+          <t>Мешок для стирки 60 × 80 см мелкая сетка - 1 шт.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -46796,6 +48804,32 @@
       <c r="B13" s="10" t="inlineStr">
         <is>
           <t>6307909800 - Прочие готовые изделия, включая выкройки одежды</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="n">
+        <v>35</v>
+      </c>
+      <c r="D13" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>Мешок для стирки</t>
+        </is>
+      </c>
+      <c r="I13" s="10" t="inlineStr">
+        <is>
+          <t>Полиэстер</t>
+        </is>
+      </c>
+      <c r="K13" s="10" t="inlineStr">
+        <is>
+          <t>Фабричное производство</t>
+        </is>
+      </c>
+      <c r="L13" s="10" t="inlineStr">
+        <is>
+          <t>Мешок для стирки обуви каркасный 35 см - 1 шт.</t>
         </is>
       </c>
     </row>
@@ -47009,6 +49043,39 @@
           <t>3923509000 - Прочие пробки, крышки, колпаки и другие укупорочные средства, из пластмасс</t>
         </is>
       </c>
+      <c r="C3" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>серый, желтый, розовый, голубой</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="inlineStr">
+        <is>
+          <t>Пробка для бутылки</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="inlineStr">
+        <is>
+          <t>универсальный</t>
+        </is>
+      </c>
+      <c r="J3" s="10" t="inlineStr">
+        <is>
+          <t>Силикон</t>
+        </is>
+      </c>
+      <c r="N3" s="10" t="inlineStr">
+        <is>
+          <t>Фабричное производство</t>
+        </is>
+      </c>
+      <c r="O3" s="10" t="inlineStr">
+        <is>
+          <t>Пробка - 4 шт.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -47021,11 +49088,82 @@
           <t>3923509000 - Прочие пробки, крышки, колпаки и другие укупорочные средства, из пластмасс</t>
         </is>
       </c>
+      <c r="C4" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>синий, зеленый, красный, салатовый</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>Пробка для бутылки</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>универсальный</t>
+        </is>
+      </c>
+      <c r="H4" s="10" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="J4" s="10" t="inlineStr">
+        <is>
+          <t>Силикон</t>
+        </is>
+      </c>
+      <c r="N4" s="10" t="inlineStr">
+        <is>
+          <t>Фабричное производство</t>
+        </is>
+      </c>
+      <c r="O4" s="10" t="inlineStr">
+        <is>
+          <t>Пробка - 4 шт.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
           <t>AKTA4ST102CL</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>серый, желтый, розовый, голубой</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>Пробка для бутылки</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="inlineStr">
+        <is>
+          <t>универсальный</t>
+        </is>
+      </c>
+      <c r="J5" s="10" t="inlineStr">
+        <is>
+          <t>Силикон</t>
+        </is>
+      </c>
+      <c r="N5" s="10" t="inlineStr">
+        <is>
+          <t>Фабричное производство</t>
+        </is>
+      </c>
+      <c r="O5" s="10" t="inlineStr">
+        <is>
+          <t>Пробка - 4 шт.</t>
         </is>
       </c>
     </row>
